--- a/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
+++ b/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
@@ -1,9 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30431"/>
-  <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BDBFEAB0-8FA0-4B87-9855-2B5C2BC42DDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xoi\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{98105D56-1CB3-4410-A731-5F58A06E101B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,6 +24,7 @@
     <definedName name="AGUA">#REF!</definedName>
     <definedName name="ANTICIPO" localSheetId="0">#REF!</definedName>
     <definedName name="ANTICIPO">#REF!</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'C-9-12'!$B$2:$R$124</definedName>
     <definedName name="AZULEJO">#REF!</definedName>
     <definedName name="BASE">#REF!</definedName>
     <definedName name="BASE1">#REF!</definedName>
@@ -69,7 +75,6 @@
     <definedName name="PMETAL">#REF!</definedName>
     <definedName name="PorcentajeCompletado">PercentCompleteBeyond*PeriodInPlan</definedName>
     <definedName name="precio">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'C-9-12'!$B$2:$R$124</definedName>
     <definedName name="Real">(PeriodInActual*(#REF!&gt;0))*PeriodInPlan</definedName>
     <definedName name="REGADERA">#REF!</definedName>
     <definedName name="RRRR">#REF!</definedName>
@@ -104,7 +109,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="131">
   <si>
     <t>PUNTO DE ACTA DE CONTRATO</t>
   </si>
@@ -506,7 +511,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-&quot;Q&quot;* #,##0.00_-;\-&quot;Q&quot;* #,##0.00_-;_-&quot;Q&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -669,15 +674,16 @@
     </font>
     <font>
       <b/>
-      <sz val="9"/>
-      <name val="Open Sans"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="10">
@@ -1280,7 +1286,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="258">
+  <cellXfs count="259">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -1677,11 +1683,11 @@
     <xf numFmtId="0" fontId="19" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -1727,385 +1733,388 @@
     <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="26" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="25" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="2" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="14" fontId="23" fillId="7" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="19" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="5" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="14" fontId="23" fillId="7" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Currency" xfId="1" builtinId="4"/>
+    <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -2218,6 +2227,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2521,31 +2534,31 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="B2:W125"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="17.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="3.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="2.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="4.85546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" style="49" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.42578125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="16.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13.28515625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="10.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="3.109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="2.33203125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="4.88671875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" style="49" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.33203125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.44140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="16.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="13.33203125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10.44140625" style="1" customWidth="1"/>
     <col min="12" max="12" width="19" style="1" customWidth="1"/>
-    <col min="13" max="13" width="16.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="6.85546875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="16.28515625" style="1" customWidth="1"/>
-    <col min="16" max="16" width="24.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.85546875" style="3" customWidth="1"/>
-    <col min="18" max="18" width="2.140625" style="3" customWidth="1"/>
-    <col min="19" max="19" width="2.28515625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="11.42578125" style="1" customWidth="1"/>
-    <col min="21" max="16384" width="11.42578125" style="1"/>
+    <col min="13" max="13" width="16.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="6.88671875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="16.33203125" style="1" customWidth="1"/>
+    <col min="16" max="16" width="24.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.88671875" style="3" customWidth="1"/>
+    <col min="18" max="18" width="2.109375" style="3" customWidth="1"/>
+    <col min="19" max="19" width="2.33203125" style="1" customWidth="1"/>
+    <col min="20" max="20" width="11.44140625" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="11.44140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:21">
+    <row r="2" spans="2:21" x14ac:dyDescent="0.3">
       <c r="B2" s="52"/>
       <c r="C2" s="52"/>
       <c r="D2" s="53"/>
@@ -2564,30 +2577,30 @@
       <c r="Q2" s="52"/>
       <c r="R2" s="52"/>
     </row>
-    <row r="3" spans="2:21" ht="27" customHeight="1">
+    <row r="3" spans="2:21" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="52"/>
       <c r="C3" s="52"/>
       <c r="D3" s="53"/>
       <c r="E3" s="52"/>
-      <c r="F3" s="202" t="s">
+      <c r="F3" s="151" t="s">
         <v>0</v>
       </c>
-      <c r="G3" s="144"/>
-      <c r="H3" s="144"/>
-      <c r="I3" s="144"/>
-      <c r="J3" s="144"/>
+      <c r="G3" s="152"/>
+      <c r="H3" s="152"/>
+      <c r="I3" s="152"/>
+      <c r="J3" s="152"/>
       <c r="K3" s="56"/>
-      <c r="L3" s="202" t="s">
+      <c r="L3" s="151" t="s">
         <v>1</v>
       </c>
-      <c r="M3" s="144"/>
-      <c r="N3" s="144"/>
+      <c r="M3" s="152"/>
+      <c r="N3" s="152"/>
       <c r="O3" s="57"/>
       <c r="P3" s="56"/>
       <c r="Q3" s="52"/>
       <c r="R3" s="52"/>
     </row>
-    <row r="4" spans="2:21" ht="12.95" customHeight="1">
+    <row r="4" spans="2:21" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="52"/>
       <c r="C4" s="52"/>
       <c r="D4" s="53"/>
@@ -2598,68 +2611,68 @@
       <c r="I4" s="55"/>
       <c r="J4" s="56"/>
       <c r="K4" s="56"/>
-      <c r="L4" s="145" t="s">
+      <c r="L4" s="242" t="s">
         <v>2</v>
       </c>
-      <c r="M4" s="214"/>
-      <c r="N4" s="214"/>
+      <c r="M4" s="134"/>
+      <c r="N4" s="134"/>
       <c r="O4" s="57"/>
       <c r="P4" s="56"/>
       <c r="Q4" s="52"/>
       <c r="R4" s="52"/>
     </row>
-    <row r="5" spans="2:21" ht="24" customHeight="1">
+    <row r="5" spans="2:21" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="52"/>
       <c r="C5" s="52"/>
       <c r="D5" s="53"/>
       <c r="E5" s="52"/>
-      <c r="F5" s="206" t="s">
+      <c r="F5" s="182" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="215"/>
-      <c r="H5" s="205" t="s">
+      <c r="G5" s="183"/>
+      <c r="H5" s="178" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="216"/>
-      <c r="J5" s="216"/>
+      <c r="I5" s="179"/>
+      <c r="J5" s="179"/>
       <c r="K5" s="56"/>
-      <c r="L5" s="214"/>
-      <c r="M5" s="214"/>
-      <c r="N5" s="214"/>
+      <c r="L5" s="134"/>
+      <c r="M5" s="134"/>
+      <c r="N5" s="134"/>
       <c r="O5" s="57"/>
       <c r="P5" s="56"/>
       <c r="Q5" s="52"/>
       <c r="R5" s="52"/>
       <c r="U5" s="2"/>
     </row>
-    <row r="6" spans="2:21" ht="24" customHeight="1">
+    <row r="6" spans="2:21" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="52"/>
       <c r="C6" s="52"/>
       <c r="D6" s="53"/>
       <c r="E6" s="52"/>
-      <c r="F6" s="155" t="s">
+      <c r="F6" s="246" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="144"/>
-      <c r="H6" s="205" t="s">
+      <c r="G6" s="152"/>
+      <c r="H6" s="178" t="s">
         <v>6</v>
       </c>
-      <c r="I6" s="216"/>
-      <c r="J6" s="216"/>
+      <c r="I6" s="179"/>
+      <c r="J6" s="179"/>
       <c r="K6" s="56"/>
-      <c r="L6" s="212" t="s">
+      <c r="L6" s="159" t="s">
         <v>7</v>
       </c>
-      <c r="M6" s="213" t="s">
+      <c r="M6" s="164" t="s">
         <v>8</v>
       </c>
-      <c r="N6" s="217"/>
+      <c r="N6" s="165"/>
       <c r="O6" s="57"/>
       <c r="P6" s="56"/>
       <c r="Q6" s="52"/>
       <c r="R6" s="52"/>
     </row>
-    <row r="7" spans="2:21" ht="6.95" customHeight="1">
+    <row r="7" spans="2:21" ht="6.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="52"/>
       <c r="C7" s="52"/>
       <c r="D7" s="53"/>
@@ -2670,39 +2683,39 @@
       <c r="I7" s="61"/>
       <c r="J7" s="62"/>
       <c r="K7" s="56"/>
-      <c r="L7" s="144"/>
-      <c r="M7" s="214"/>
-      <c r="N7" s="214"/>
+      <c r="L7" s="152"/>
+      <c r="M7" s="166"/>
+      <c r="N7" s="166"/>
       <c r="O7" s="57"/>
       <c r="P7" s="56"/>
       <c r="Q7" s="52"/>
       <c r="R7" s="52"/>
     </row>
-    <row r="8" spans="2:21" ht="24" customHeight="1">
+    <row r="8" spans="2:21" ht="24" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="52"/>
       <c r="C8" s="52"/>
       <c r="D8" s="53"/>
       <c r="E8" s="52"/>
-      <c r="F8" s="203" t="s">
+      <c r="F8" s="175" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="144"/>
-      <c r="H8" s="204" t="s">
+      <c r="G8" s="152"/>
+      <c r="H8" s="176" t="s">
         <v>10</v>
       </c>
-      <c r="I8" s="218"/>
-      <c r="J8" s="218"/>
+      <c r="I8" s="177"/>
+      <c r="J8" s="177"/>
       <c r="K8" s="56"/>
-      <c r="L8" s="144"/>
-      <c r="M8" s="219"/>
-      <c r="N8" s="219"/>
+      <c r="L8" s="152"/>
+      <c r="M8" s="167"/>
+      <c r="N8" s="167"/>
       <c r="O8" s="56"/>
       <c r="P8" s="56"/>
       <c r="Q8" s="52"/>
       <c r="R8" s="52"/>
       <c r="U8" s="2"/>
     </row>
-    <row r="9" spans="2:21" ht="12.95" customHeight="1">
+    <row r="9" spans="2:21" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B9" s="52"/>
       <c r="C9" s="52"/>
       <c r="D9" s="53"/>
@@ -2721,7 +2734,7 @@
       <c r="Q9" s="52"/>
       <c r="R9" s="52"/>
     </row>
-    <row r="10" spans="2:21" ht="7.7" customHeight="1">
+    <row r="10" spans="2:21" ht="7.65" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="59"/>
       <c r="C10" s="59"/>
       <c r="D10" s="60"/>
@@ -2740,7 +2753,7 @@
       <c r="Q10" s="59"/>
       <c r="R10" s="59"/>
     </row>
-    <row r="11" spans="2:21" ht="9.9499999999999993" customHeight="1">
+    <row r="11" spans="2:21" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="59"/>
       <c r="C11" s="59"/>
       <c r="D11" s="60"/>
@@ -2759,150 +2772,150 @@
       <c r="Q11" s="59"/>
       <c r="R11" s="59"/>
     </row>
-    <row r="12" spans="2:21" ht="21.95" customHeight="1">
+    <row r="12" spans="2:21" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="63"/>
       <c r="C12" s="63"/>
-      <c r="D12" s="193" t="s">
+      <c r="D12" s="202" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="220"/>
-      <c r="F12" s="187" t="s">
+      <c r="E12" s="203"/>
+      <c r="F12" s="186" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="221"/>
-      <c r="H12" s="221"/>
-      <c r="I12" s="221"/>
-      <c r="J12" s="221"/>
+      <c r="G12" s="187"/>
+      <c r="H12" s="187"/>
+      <c r="I12" s="187"/>
+      <c r="J12" s="187"/>
       <c r="K12" s="69"/>
-      <c r="L12" s="207" t="s">
+      <c r="L12" s="184" t="s">
         <v>13</v>
       </c>
-      <c r="M12" s="144"/>
-      <c r="N12" s="144"/>
-      <c r="O12" s="222"/>
+      <c r="M12" s="152"/>
+      <c r="N12" s="152"/>
+      <c r="O12" s="185"/>
       <c r="P12" s="106" t="s">
         <v>14</v>
       </c>
       <c r="Q12" s="59"/>
       <c r="R12" s="59"/>
     </row>
-    <row r="13" spans="2:21" ht="21.95" customHeight="1">
+    <row r="13" spans="2:21" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="63"/>
       <c r="C13" s="63"/>
-      <c r="D13" s="156" t="s">
+      <c r="D13" s="180" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="223"/>
-      <c r="F13" s="201" t="s">
+      <c r="E13" s="181"/>
+      <c r="F13" s="174" t="s">
         <v>16</v>
       </c>
-      <c r="G13" s="224"/>
-      <c r="H13" s="224"/>
-      <c r="I13" s="224"/>
-      <c r="J13" s="224"/>
+      <c r="G13" s="158"/>
+      <c r="H13" s="158"/>
+      <c r="I13" s="158"/>
+      <c r="J13" s="158"/>
       <c r="K13" s="70"/>
-      <c r="L13" s="196" t="s">
+      <c r="L13" s="211" t="s">
         <v>17</v>
       </c>
-      <c r="M13" s="225"/>
-      <c r="N13" s="225"/>
-      <c r="O13" s="225"/>
+      <c r="M13" s="212"/>
+      <c r="N13" s="212"/>
+      <c r="O13" s="212"/>
       <c r="P13" s="7" t="s">
         <v>18</v>
       </c>
       <c r="Q13" s="59"/>
       <c r="R13" s="59"/>
     </row>
-    <row r="14" spans="2:21" ht="21.95" customHeight="1">
+    <row r="14" spans="2:21" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="63"/>
       <c r="C14" s="63"/>
-      <c r="D14" s="156" t="s">
+      <c r="D14" s="180" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="223"/>
-      <c r="F14" s="201" t="s">
+      <c r="E14" s="181"/>
+      <c r="F14" s="174" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="224"/>
-      <c r="H14" s="224"/>
-      <c r="I14" s="224"/>
-      <c r="J14" s="224"/>
+      <c r="G14" s="158"/>
+      <c r="H14" s="158"/>
+      <c r="I14" s="158"/>
+      <c r="J14" s="158"/>
       <c r="K14" s="71"/>
-      <c r="L14" s="146" t="s">
+      <c r="L14" s="172" t="s">
         <v>21</v>
       </c>
-      <c r="M14" s="226"/>
-      <c r="N14" s="226"/>
-      <c r="O14" s="226"/>
+      <c r="M14" s="173"/>
+      <c r="N14" s="173"/>
+      <c r="O14" s="173"/>
       <c r="P14" s="7" t="s">
         <v>22</v>
       </c>
       <c r="Q14" s="59"/>
       <c r="R14" s="59"/>
     </row>
-    <row r="15" spans="2:21" ht="21.95" customHeight="1">
+    <row r="15" spans="2:21" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="63"/>
       <c r="C15" s="63"/>
-      <c r="D15" s="156" t="s">
+      <c r="D15" s="180" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="223"/>
-      <c r="F15" s="201" t="s">
+      <c r="E15" s="181"/>
+      <c r="F15" s="174" t="s">
         <v>24</v>
       </c>
-      <c r="G15" s="224"/>
-      <c r="H15" s="224"/>
-      <c r="I15" s="224"/>
-      <c r="J15" s="224"/>
+      <c r="G15" s="158"/>
+      <c r="H15" s="158"/>
+      <c r="I15" s="158"/>
+      <c r="J15" s="158"/>
       <c r="K15" s="59"/>
-      <c r="L15" s="146" t="s">
+      <c r="L15" s="172" t="s">
         <v>25</v>
       </c>
-      <c r="M15" s="226"/>
-      <c r="N15" s="226"/>
-      <c r="O15" s="226"/>
+      <c r="M15" s="173"/>
+      <c r="N15" s="173"/>
+      <c r="O15" s="173"/>
       <c r="P15" s="7" t="s">
         <v>26</v>
       </c>
       <c r="Q15" s="59"/>
       <c r="R15" s="59"/>
     </row>
-    <row r="16" spans="2:21" ht="21.95" customHeight="1" thickBot="1">
+    <row r="16" spans="2:21" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="63"/>
       <c r="C16" s="63"/>
-      <c r="D16" s="195" t="s">
+      <c r="D16" s="209" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="227"/>
-      <c r="F16" s="211" t="s">
+      <c r="E16" s="210"/>
+      <c r="F16" s="157" t="s">
         <v>28</v>
       </c>
-      <c r="G16" s="224"/>
-      <c r="H16" s="224"/>
-      <c r="I16" s="224"/>
-      <c r="J16" s="224"/>
+      <c r="G16" s="158"/>
+      <c r="H16" s="158"/>
+      <c r="I16" s="158"/>
+      <c r="J16" s="158"/>
       <c r="K16" s="69"/>
-      <c r="L16" s="146" t="s">
+      <c r="L16" s="172" t="s">
         <v>29</v>
       </c>
-      <c r="M16" s="226"/>
-      <c r="N16" s="226"/>
-      <c r="O16" s="226"/>
+      <c r="M16" s="173"/>
+      <c r="N16" s="173"/>
+      <c r="O16" s="173"/>
       <c r="P16" s="7" t="s">
         <v>30</v>
       </c>
       <c r="Q16" s="59"/>
       <c r="R16" s="59"/>
     </row>
-    <row r="17" spans="2:19" s="3" customFormat="1" ht="18" customHeight="1" thickBot="1">
+    <row r="17" spans="2:19" s="3" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B17" s="64"/>
       <c r="C17" s="64"/>
       <c r="D17" s="65"/>
       <c r="E17" s="66"/>
       <c r="F17" s="67"/>
       <c r="G17" s="67"/>
-      <c r="H17" s="172"/>
-      <c r="I17" s="139"/>
+      <c r="H17" s="237"/>
+      <c r="I17" s="145"/>
       <c r="J17" s="68"/>
       <c r="K17" s="70"/>
       <c r="L17" s="59"/>
@@ -2912,152 +2925,152 @@
       <c r="Q17" s="59"/>
       <c r="R17" s="59"/>
     </row>
-    <row r="18" spans="2:19" s="8" customFormat="1" ht="21.95" customHeight="1" thickBot="1">
+    <row r="18" spans="2:19" s="8" customFormat="1" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="79"/>
       <c r="C18" s="79"/>
-      <c r="D18" s="210" t="s">
+      <c r="D18" s="156" t="s">
         <v>31</v>
       </c>
-      <c r="E18" s="228"/>
-      <c r="F18" s="228"/>
-      <c r="G18" s="228"/>
-      <c r="H18" s="228"/>
-      <c r="I18" s="228"/>
-      <c r="J18" s="229"/>
+      <c r="E18" s="154"/>
+      <c r="F18" s="154"/>
+      <c r="G18" s="154"/>
+      <c r="H18" s="154"/>
+      <c r="I18" s="154"/>
+      <c r="J18" s="155"/>
       <c r="K18" s="77"/>
-      <c r="L18" s="170" t="s">
+      <c r="L18" s="219" t="s">
         <v>32</v>
       </c>
-      <c r="M18" s="228"/>
-      <c r="N18" s="228"/>
-      <c r="O18" s="228"/>
-      <c r="P18" s="229"/>
+      <c r="M18" s="154"/>
+      <c r="N18" s="154"/>
+      <c r="O18" s="154"/>
+      <c r="P18" s="155"/>
       <c r="Q18" s="59"/>
       <c r="R18" s="59"/>
       <c r="S18" s="1"/>
     </row>
-    <row r="19" spans="2:19" ht="21.95" customHeight="1" thickBot="1">
+    <row r="19" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="78"/>
       <c r="C19" s="78"/>
-      <c r="D19" s="150" t="s">
+      <c r="D19" s="217" t="s">
         <v>33</v>
       </c>
-      <c r="E19" s="230"/>
-      <c r="F19" s="230"/>
-      <c r="G19" s="230"/>
-      <c r="H19" s="231"/>
-      <c r="I19" s="157" t="s">
+      <c r="E19" s="139"/>
+      <c r="F19" s="139"/>
+      <c r="G19" s="139"/>
+      <c r="H19" s="140"/>
+      <c r="I19" s="193" t="s">
         <v>34</v>
       </c>
-      <c r="J19" s="230"/>
+      <c r="J19" s="139"/>
       <c r="K19" s="59"/>
-      <c r="L19" s="134" t="s">
+      <c r="L19" s="153" t="s">
         <v>17</v>
       </c>
-      <c r="M19" s="228"/>
-      <c r="N19" s="228"/>
-      <c r="O19" s="229"/>
+      <c r="M19" s="154"/>
+      <c r="N19" s="154"/>
+      <c r="O19" s="155"/>
       <c r="P19" s="88" t="s">
         <v>35</v>
       </c>
       <c r="Q19" s="59"/>
       <c r="R19" s="59"/>
     </row>
-    <row r="20" spans="2:19" ht="21.95" customHeight="1" thickBot="1">
+    <row r="20" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="78"/>
       <c r="C20" s="78"/>
-      <c r="D20" s="179" t="s">
+      <c r="D20" s="138" t="s">
         <v>36</v>
       </c>
-      <c r="E20" s="230"/>
-      <c r="F20" s="230"/>
-      <c r="G20" s="230"/>
-      <c r="H20" s="231"/>
-      <c r="I20" s="147" t="s">
+      <c r="E20" s="139"/>
+      <c r="F20" s="139"/>
+      <c r="G20" s="139"/>
+      <c r="H20" s="140"/>
+      <c r="I20" s="161" t="s">
         <v>34</v>
       </c>
-      <c r="J20" s="230"/>
+      <c r="J20" s="139"/>
       <c r="K20" s="59"/>
-      <c r="L20" s="182" t="s">
+      <c r="L20" s="218" t="s">
         <v>21</v>
       </c>
-      <c r="M20" s="228"/>
-      <c r="N20" s="228"/>
-      <c r="O20" s="229"/>
+      <c r="M20" s="154"/>
+      <c r="N20" s="154"/>
+      <c r="O20" s="155"/>
       <c r="P20" s="89" t="s">
         <v>37</v>
       </c>
       <c r="Q20" s="59"/>
       <c r="R20" s="59"/>
     </row>
-    <row r="21" spans="2:19" ht="21.95" customHeight="1" thickBot="1">
+    <row r="21" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="78"/>
       <c r="C21" s="78"/>
-      <c r="D21" s="150" t="s">
+      <c r="D21" s="217" t="s">
         <v>38</v>
       </c>
-      <c r="E21" s="230"/>
-      <c r="F21" s="230"/>
-      <c r="G21" s="230"/>
-      <c r="H21" s="231"/>
-      <c r="I21" s="157" t="s">
+      <c r="E21" s="139"/>
+      <c r="F21" s="139"/>
+      <c r="G21" s="139"/>
+      <c r="H21" s="140"/>
+      <c r="I21" s="193" t="s">
         <v>39</v>
       </c>
-      <c r="J21" s="230"/>
+      <c r="J21" s="139"/>
       <c r="K21" s="59"/>
-      <c r="L21" s="134" t="s">
+      <c r="L21" s="153" t="s">
         <v>25</v>
       </c>
-      <c r="M21" s="228"/>
-      <c r="N21" s="228"/>
-      <c r="O21" s="229"/>
+      <c r="M21" s="154"/>
+      <c r="N21" s="154"/>
+      <c r="O21" s="155"/>
       <c r="P21" s="88" t="s">
         <v>37</v>
       </c>
       <c r="Q21" s="59"/>
       <c r="R21" s="59"/>
     </row>
-    <row r="22" spans="2:19" ht="21.95" customHeight="1" thickBot="1">
+    <row r="22" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="78"/>
       <c r="C22" s="78"/>
-      <c r="D22" s="179" t="s">
+      <c r="D22" s="138" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="230"/>
-      <c r="F22" s="230"/>
-      <c r="G22" s="230"/>
-      <c r="H22" s="231"/>
-      <c r="I22" s="147" t="s">
+      <c r="E22" s="139"/>
+      <c r="F22" s="139"/>
+      <c r="G22" s="139"/>
+      <c r="H22" s="140"/>
+      <c r="I22" s="161" t="s">
         <v>34</v>
       </c>
-      <c r="J22" s="230"/>
+      <c r="J22" s="139"/>
       <c r="K22" s="59"/>
-      <c r="L22" s="194" t="s">
+      <c r="L22" s="204" t="s">
         <v>29</v>
       </c>
-      <c r="M22" s="232"/>
-      <c r="N22" s="232"/>
-      <c r="O22" s="233"/>
+      <c r="M22" s="205"/>
+      <c r="N22" s="205"/>
+      <c r="O22" s="206"/>
       <c r="P22" s="90" t="s">
         <v>41</v>
       </c>
       <c r="Q22" s="59"/>
       <c r="R22" s="59"/>
     </row>
-    <row r="23" spans="2:19" ht="21.95" customHeight="1" thickBot="1">
+    <row r="23" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="78"/>
       <c r="C23" s="78"/>
-      <c r="D23" s="150" t="s">
+      <c r="D23" s="217" t="s">
         <v>42</v>
       </c>
-      <c r="E23" s="230"/>
-      <c r="F23" s="230"/>
-      <c r="G23" s="230"/>
-      <c r="H23" s="231"/>
-      <c r="I23" s="157" t="s">
+      <c r="E23" s="139"/>
+      <c r="F23" s="139"/>
+      <c r="G23" s="139"/>
+      <c r="H23" s="140"/>
+      <c r="I23" s="193" t="s">
         <v>43</v>
       </c>
-      <c r="J23" s="230"/>
+      <c r="J23" s="139"/>
       <c r="K23" s="59"/>
       <c r="L23" s="86"/>
       <c r="M23" s="86"/>
@@ -3067,107 +3080,107 @@
       <c r="Q23" s="59"/>
       <c r="R23" s="59"/>
     </row>
-    <row r="24" spans="2:19" ht="21.95" customHeight="1" thickBot="1">
+    <row r="24" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="78"/>
       <c r="C24" s="78"/>
-      <c r="D24" s="179" t="s">
+      <c r="D24" s="138" t="s">
         <v>44</v>
       </c>
-      <c r="E24" s="230"/>
-      <c r="F24" s="230"/>
-      <c r="G24" s="230"/>
-      <c r="H24" s="231"/>
-      <c r="I24" s="147" t="s">
+      <c r="E24" s="139"/>
+      <c r="F24" s="139"/>
+      <c r="G24" s="139"/>
+      <c r="H24" s="140"/>
+      <c r="I24" s="161" t="s">
         <v>45</v>
       </c>
-      <c r="J24" s="230"/>
+      <c r="J24" s="139"/>
       <c r="K24" s="59"/>
-      <c r="L24" s="170" t="s">
+      <c r="L24" s="219" t="s">
         <v>46</v>
       </c>
-      <c r="M24" s="228"/>
-      <c r="N24" s="228"/>
-      <c r="O24" s="228"/>
-      <c r="P24" s="229"/>
+      <c r="M24" s="154"/>
+      <c r="N24" s="154"/>
+      <c r="O24" s="154"/>
+      <c r="P24" s="155"/>
       <c r="Q24" s="59"/>
       <c r="R24" s="59"/>
     </row>
-    <row r="25" spans="2:19" ht="39" customHeight="1" thickBot="1">
+    <row r="25" spans="2:19" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="78"/>
       <c r="C25" s="78"/>
-      <c r="D25" s="150" t="s">
+      <c r="D25" s="217" t="s">
         <v>47</v>
       </c>
-      <c r="E25" s="230"/>
-      <c r="F25" s="230"/>
-      <c r="G25" s="230"/>
-      <c r="H25" s="231"/>
-      <c r="I25" s="157" t="s">
+      <c r="E25" s="139"/>
+      <c r="F25" s="139"/>
+      <c r="G25" s="139"/>
+      <c r="H25" s="140"/>
+      <c r="I25" s="193" t="s">
         <v>45</v>
       </c>
-      <c r="J25" s="230"/>
+      <c r="J25" s="139"/>
       <c r="K25" s="59"/>
-      <c r="L25" s="134" t="s">
+      <c r="L25" s="153" t="s">
         <v>48</v>
       </c>
-      <c r="M25" s="228"/>
-      <c r="N25" s="228"/>
-      <c r="O25" s="229"/>
+      <c r="M25" s="154"/>
+      <c r="N25" s="154"/>
+      <c r="O25" s="155"/>
       <c r="P25" s="88" t="s">
         <v>49</v>
       </c>
       <c r="Q25" s="59"/>
       <c r="R25" s="59"/>
     </row>
-    <row r="26" spans="2:19" ht="39" customHeight="1" thickBot="1">
+    <row r="26" spans="2:19" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B26" s="78"/>
       <c r="C26" s="78"/>
-      <c r="D26" s="137" t="s">
+      <c r="D26" s="252" t="s">
         <v>50</v>
       </c>
-      <c r="E26" s="228"/>
-      <c r="F26" s="228"/>
-      <c r="G26" s="228"/>
-      <c r="H26" s="228"/>
-      <c r="I26" s="228"/>
-      <c r="J26" s="228"/>
+      <c r="E26" s="154"/>
+      <c r="F26" s="154"/>
+      <c r="G26" s="154"/>
+      <c r="H26" s="154"/>
+      <c r="I26" s="154"/>
+      <c r="J26" s="154"/>
       <c r="K26" s="59"/>
-      <c r="L26" s="182" t="s">
+      <c r="L26" s="218" t="s">
         <v>51</v>
       </c>
-      <c r="M26" s="228"/>
-      <c r="N26" s="228"/>
-      <c r="O26" s="229"/>
+      <c r="M26" s="154"/>
+      <c r="N26" s="154"/>
+      <c r="O26" s="155"/>
       <c r="P26" s="89" t="s">
         <v>52</v>
       </c>
       <c r="Q26" s="59"/>
       <c r="R26" s="59"/>
     </row>
-    <row r="27" spans="2:19" ht="39" customHeight="1" thickBot="1">
+    <row r="27" spans="2:19" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="78"/>
       <c r="C27" s="78"/>
-      <c r="D27" s="177"/>
-      <c r="E27" s="234"/>
-      <c r="F27" s="234"/>
-      <c r="G27" s="234"/>
-      <c r="H27" s="234"/>
-      <c r="I27" s="234"/>
-      <c r="J27" s="234"/>
+      <c r="D27" s="240"/>
+      <c r="E27" s="241"/>
+      <c r="F27" s="241"/>
+      <c r="G27" s="241"/>
+      <c r="H27" s="241"/>
+      <c r="I27" s="241"/>
+      <c r="J27" s="241"/>
       <c r="K27" s="59"/>
-      <c r="L27" s="134" t="s">
+      <c r="L27" s="153" t="s">
         <v>53</v>
       </c>
-      <c r="M27" s="228"/>
-      <c r="N27" s="228"/>
-      <c r="O27" s="229"/>
+      <c r="M27" s="154"/>
+      <c r="N27" s="154"/>
+      <c r="O27" s="155"/>
       <c r="P27" s="88" t="s">
         <v>49</v>
       </c>
       <c r="Q27" s="72"/>
       <c r="R27" s="72"/>
     </row>
-    <row r="28" spans="2:19" ht="12.95" customHeight="1">
+    <row r="28" spans="2:19" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B28" s="78"/>
       <c r="C28" s="78"/>
       <c r="D28" s="85"/>
@@ -3186,150 +3199,150 @@
       <c r="Q28" s="73"/>
       <c r="R28" s="74"/>
     </row>
-    <row r="29" spans="2:19" ht="21.95" customHeight="1" thickBot="1">
+    <row r="29" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B29" s="78"/>
       <c r="C29" s="78"/>
-      <c r="D29" s="198" t="s">
+      <c r="D29" s="160" t="s">
         <v>54</v>
       </c>
-      <c r="E29" s="144"/>
-      <c r="F29" s="144"/>
-      <c r="G29" s="144"/>
-      <c r="H29" s="144"/>
-      <c r="I29" s="144"/>
+      <c r="E29" s="152"/>
+      <c r="F29" s="152"/>
+      <c r="G29" s="152"/>
+      <c r="H29" s="152"/>
+      <c r="I29" s="152"/>
       <c r="J29" s="91" t="s">
         <v>55</v>
       </c>
       <c r="K29" s="59"/>
-      <c r="L29" s="197" t="s">
+      <c r="L29" s="222" t="s">
         <v>56</v>
       </c>
-      <c r="M29" s="227"/>
-      <c r="N29" s="227"/>
-      <c r="O29" s="227"/>
-      <c r="P29" s="227"/>
+      <c r="M29" s="210"/>
+      <c r="N29" s="210"/>
+      <c r="O29" s="210"/>
+      <c r="P29" s="210"/>
       <c r="Q29" s="59"/>
       <c r="R29" s="59"/>
     </row>
-    <row r="30" spans="2:19" ht="21.95" customHeight="1" thickBot="1">
+    <row r="30" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B30" s="78"/>
       <c r="C30" s="78"/>
-      <c r="D30" s="176" t="s">
+      <c r="D30" s="168" t="s">
         <v>57</v>
       </c>
-      <c r="E30" s="235"/>
-      <c r="F30" s="235"/>
-      <c r="G30" s="235"/>
-      <c r="H30" s="235"/>
-      <c r="I30" s="236"/>
+      <c r="E30" s="169"/>
+      <c r="F30" s="169"/>
+      <c r="G30" s="169"/>
+      <c r="H30" s="169"/>
+      <c r="I30" s="170"/>
       <c r="J30" s="13" t="s">
         <v>58</v>
       </c>
       <c r="K30" s="59"/>
-      <c r="L30" s="178" t="s">
+      <c r="L30" s="189" t="s">
         <v>59</v>
       </c>
-      <c r="M30" s="230"/>
-      <c r="N30" s="230"/>
-      <c r="O30" s="237"/>
+      <c r="M30" s="139"/>
+      <c r="N30" s="139"/>
+      <c r="O30" s="190"/>
       <c r="P30" s="10" t="s">
         <v>60</v>
       </c>
       <c r="Q30" s="59"/>
       <c r="R30" s="59"/>
     </row>
-    <row r="31" spans="2:19" ht="21.95" customHeight="1" thickBot="1">
+    <row r="31" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B31" s="78"/>
       <c r="C31" s="78"/>
-      <c r="D31" s="135" t="s">
+      <c r="D31" s="171" t="s">
         <v>61</v>
       </c>
-      <c r="E31" s="238"/>
-      <c r="F31" s="238"/>
-      <c r="G31" s="238"/>
-      <c r="H31" s="238"/>
-      <c r="I31" s="239"/>
+      <c r="E31" s="142"/>
+      <c r="F31" s="142"/>
+      <c r="G31" s="142"/>
+      <c r="H31" s="142"/>
+      <c r="I31" s="143"/>
       <c r="J31" s="14" t="s">
         <v>58</v>
       </c>
       <c r="K31" s="59"/>
-      <c r="L31" s="152" t="s">
+      <c r="L31" s="244" t="s">
         <v>62</v>
       </c>
-      <c r="M31" s="230"/>
-      <c r="N31" s="230"/>
-      <c r="O31" s="237"/>
+      <c r="M31" s="139"/>
+      <c r="N31" s="139"/>
+      <c r="O31" s="190"/>
       <c r="P31" s="11" t="s">
         <v>63</v>
       </c>
       <c r="Q31" s="59"/>
       <c r="R31" s="59"/>
     </row>
-    <row r="32" spans="2:19" ht="21.95" customHeight="1" thickBot="1">
+    <row r="32" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B32" s="78"/>
       <c r="C32" s="78"/>
-      <c r="D32" s="173" t="s">
+      <c r="D32" s="141" t="s">
         <v>64</v>
       </c>
-      <c r="E32" s="238"/>
-      <c r="F32" s="238"/>
-      <c r="G32" s="238"/>
-      <c r="H32" s="238"/>
-      <c r="I32" s="239"/>
+      <c r="E32" s="142"/>
+      <c r="F32" s="142"/>
+      <c r="G32" s="142"/>
+      <c r="H32" s="142"/>
+      <c r="I32" s="143"/>
       <c r="J32" s="15" t="s">
         <v>58</v>
       </c>
       <c r="K32" s="59"/>
-      <c r="L32" s="178" t="s">
+      <c r="L32" s="189" t="s">
         <v>65</v>
       </c>
-      <c r="M32" s="230"/>
-      <c r="N32" s="230"/>
-      <c r="O32" s="237"/>
+      <c r="M32" s="139"/>
+      <c r="N32" s="139"/>
+      <c r="O32" s="190"/>
       <c r="P32" s="10" t="s">
         <v>66</v>
       </c>
       <c r="Q32" s="59"/>
       <c r="R32" s="59"/>
     </row>
-    <row r="33" spans="2:20" ht="36.75" customHeight="1">
+    <row r="33" spans="2:20" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="78"/>
       <c r="C33" s="78"/>
-      <c r="D33" s="135" t="s">
+      <c r="D33" s="171" t="s">
         <v>67</v>
       </c>
-      <c r="E33" s="238"/>
-      <c r="F33" s="238"/>
-      <c r="G33" s="238"/>
-      <c r="H33" s="238"/>
-      <c r="I33" s="239"/>
+      <c r="E33" s="142"/>
+      <c r="F33" s="142"/>
+      <c r="G33" s="142"/>
+      <c r="H33" s="142"/>
+      <c r="I33" s="143"/>
       <c r="J33" s="14" t="s">
         <v>58</v>
       </c>
       <c r="K33" s="59"/>
-      <c r="L33" s="192" t="s">
+      <c r="L33" s="199" t="s">
         <v>68</v>
       </c>
-      <c r="M33" s="240"/>
-      <c r="N33" s="240"/>
-      <c r="O33" s="241"/>
+      <c r="M33" s="200"/>
+      <c r="N33" s="200"/>
+      <c r="O33" s="201"/>
       <c r="P33" s="12" t="s">
         <v>63</v>
       </c>
       <c r="Q33" s="59"/>
       <c r="R33" s="59"/>
     </row>
-    <row r="34" spans="2:20" ht="21.95" customHeight="1">
+    <row r="34" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="78"/>
       <c r="C34" s="78"/>
-      <c r="D34" s="173" t="s">
+      <c r="D34" s="141" t="s">
         <v>69</v>
       </c>
-      <c r="E34" s="238"/>
-      <c r="F34" s="238"/>
-      <c r="G34" s="238"/>
-      <c r="H34" s="238"/>
-      <c r="I34" s="239"/>
+      <c r="E34" s="142"/>
+      <c r="F34" s="142"/>
+      <c r="G34" s="142"/>
+      <c r="H34" s="142"/>
+      <c r="I34" s="143"/>
       <c r="J34" s="15" t="s">
         <v>58</v>
       </c>
@@ -3342,32 +3355,32 @@
       <c r="Q34" s="59"/>
       <c r="R34" s="59"/>
     </row>
-    <row r="35" spans="2:20" ht="21.95" customHeight="1">
+    <row r="35" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="78"/>
       <c r="C35" s="78"/>
-      <c r="D35" s="175" t="s">
+      <c r="D35" s="239" t="s">
         <v>70</v>
       </c>
-      <c r="E35" s="242"/>
-      <c r="F35" s="242"/>
-      <c r="G35" s="242"/>
-      <c r="H35" s="242"/>
-      <c r="I35" s="243"/>
+      <c r="E35" s="136"/>
+      <c r="F35" s="136"/>
+      <c r="G35" s="136"/>
+      <c r="H35" s="136"/>
+      <c r="I35" s="137"/>
       <c r="J35" s="19" t="s">
         <v>58</v>
       </c>
       <c r="K35" s="59"/>
-      <c r="L35" s="181" t="s">
+      <c r="L35" s="227" t="s">
         <v>71</v>
       </c>
-      <c r="M35" s="144"/>
-      <c r="N35" s="144"/>
-      <c r="O35" s="144"/>
-      <c r="P35" s="144"/>
+      <c r="M35" s="152"/>
+      <c r="N35" s="152"/>
+      <c r="O35" s="152"/>
+      <c r="P35" s="152"/>
       <c r="Q35" s="59"/>
       <c r="R35" s="59"/>
     </row>
-    <row r="36" spans="2:20" ht="18" customHeight="1" thickBot="1">
+    <row r="36" spans="2:20" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B36" s="78"/>
       <c r="C36" s="78"/>
       <c r="D36" s="20"/>
@@ -3378,137 +3391,137 @@
       <c r="I36" s="20"/>
       <c r="J36" s="20"/>
       <c r="K36" s="59"/>
-      <c r="L36" s="136" t="s">
+      <c r="L36" s="249" t="s">
         <v>72</v>
       </c>
-      <c r="M36" s="244"/>
-      <c r="N36" s="244"/>
-      <c r="O36" s="245"/>
+      <c r="M36" s="250"/>
+      <c r="N36" s="250"/>
+      <c r="O36" s="251"/>
       <c r="P36" s="21" t="s">
         <v>73</v>
       </c>
       <c r="Q36" s="59"/>
       <c r="R36" s="59"/>
     </row>
-    <row r="37" spans="2:20" ht="21.95" customHeight="1" thickBot="1">
+    <row r="37" spans="2:20" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="78"/>
       <c r="C37" s="78"/>
-      <c r="D37" s="198" t="s">
+      <c r="D37" s="160" t="s">
         <v>74</v>
       </c>
-      <c r="E37" s="144"/>
-      <c r="F37" s="144"/>
-      <c r="G37" s="144"/>
-      <c r="H37" s="144"/>
-      <c r="I37" s="144"/>
+      <c r="E37" s="152"/>
+      <c r="F37" s="152"/>
+      <c r="G37" s="152"/>
+      <c r="H37" s="152"/>
+      <c r="I37" s="152"/>
       <c r="J37" s="91" t="s">
         <v>55</v>
       </c>
       <c r="K37" s="59"/>
-      <c r="L37" s="179" t="s">
+      <c r="L37" s="138" t="s">
         <v>75</v>
       </c>
-      <c r="M37" s="230"/>
-      <c r="N37" s="230"/>
-      <c r="O37" s="231"/>
+      <c r="M37" s="139"/>
+      <c r="N37" s="139"/>
+      <c r="O37" s="140"/>
       <c r="P37" s="11" t="s">
         <v>73</v>
       </c>
       <c r="Q37" s="59"/>
       <c r="R37" s="59"/>
     </row>
-    <row r="38" spans="2:20" ht="21.95" customHeight="1" thickBot="1">
+    <row r="38" spans="2:20" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B38" s="78"/>
       <c r="C38" s="78"/>
-      <c r="D38" s="176" t="s">
+      <c r="D38" s="168" t="s">
         <v>76</v>
       </c>
-      <c r="E38" s="235"/>
-      <c r="F38" s="235"/>
-      <c r="G38" s="235"/>
-      <c r="H38" s="235"/>
-      <c r="I38" s="236"/>
+      <c r="E38" s="169"/>
+      <c r="F38" s="169"/>
+      <c r="G38" s="169"/>
+      <c r="H38" s="169"/>
+      <c r="I38" s="170"/>
       <c r="J38" s="13" t="s">
         <v>58</v>
       </c>
       <c r="K38" s="59"/>
-      <c r="L38" s="150" t="s">
+      <c r="L38" s="217" t="s">
         <v>77</v>
       </c>
-      <c r="M38" s="230"/>
-      <c r="N38" s="230"/>
-      <c r="O38" s="231"/>
+      <c r="M38" s="139"/>
+      <c r="N38" s="139"/>
+      <c r="O38" s="140"/>
       <c r="P38" s="10" t="s">
         <v>73</v>
       </c>
       <c r="Q38" s="59"/>
       <c r="R38" s="59"/>
     </row>
-    <row r="39" spans="2:20" ht="21.95" customHeight="1" thickBot="1">
+    <row r="39" spans="2:20" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B39" s="78"/>
       <c r="C39" s="78"/>
-      <c r="D39" s="135" t="s">
+      <c r="D39" s="171" t="s">
         <v>78</v>
       </c>
-      <c r="E39" s="238"/>
-      <c r="F39" s="238"/>
-      <c r="G39" s="238"/>
-      <c r="H39" s="238"/>
-      <c r="I39" s="239"/>
+      <c r="E39" s="142"/>
+      <c r="F39" s="142"/>
+      <c r="G39" s="142"/>
+      <c r="H39" s="142"/>
+      <c r="I39" s="143"/>
       <c r="J39" s="14" t="s">
         <v>58</v>
       </c>
       <c r="K39" s="59"/>
-      <c r="L39" s="179" t="s">
+      <c r="L39" s="138" t="s">
         <v>79</v>
       </c>
-      <c r="M39" s="230"/>
-      <c r="N39" s="230"/>
-      <c r="O39" s="231"/>
+      <c r="M39" s="139"/>
+      <c r="N39" s="139"/>
+      <c r="O39" s="140"/>
       <c r="P39" s="11" t="s">
         <v>73</v>
       </c>
       <c r="Q39" s="59"/>
       <c r="R39" s="59"/>
     </row>
-    <row r="40" spans="2:20" ht="21.95" customHeight="1">
+    <row r="40" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="78"/>
       <c r="C40" s="78"/>
-      <c r="D40" s="173" t="s">
+      <c r="D40" s="141" t="s">
         <v>80</v>
       </c>
-      <c r="E40" s="238"/>
-      <c r="F40" s="238"/>
-      <c r="G40" s="238"/>
-      <c r="H40" s="238"/>
-      <c r="I40" s="239"/>
+      <c r="E40" s="142"/>
+      <c r="F40" s="142"/>
+      <c r="G40" s="142"/>
+      <c r="H40" s="142"/>
+      <c r="I40" s="143"/>
       <c r="J40" s="15" t="s">
         <v>58</v>
       </c>
       <c r="K40" s="59"/>
-      <c r="L40" s="153" t="s">
+      <c r="L40" s="245" t="s">
         <v>81</v>
       </c>
-      <c r="M40" s="240"/>
-      <c r="N40" s="240"/>
-      <c r="O40" s="241"/>
+      <c r="M40" s="200"/>
+      <c r="N40" s="200"/>
+      <c r="O40" s="201"/>
       <c r="P40" s="22" t="s">
         <v>73</v>
       </c>
       <c r="Q40" s="59"/>
       <c r="R40" s="59"/>
     </row>
-    <row r="41" spans="2:20" ht="21.95" customHeight="1">
+    <row r="41" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="78"/>
       <c r="C41" s="78"/>
-      <c r="D41" s="135" t="s">
+      <c r="D41" s="171" t="s">
         <v>82</v>
       </c>
-      <c r="E41" s="238"/>
-      <c r="F41" s="238"/>
-      <c r="G41" s="238"/>
-      <c r="H41" s="238"/>
-      <c r="I41" s="239"/>
+      <c r="E41" s="142"/>
+      <c r="F41" s="142"/>
+      <c r="G41" s="142"/>
+      <c r="H41" s="142"/>
+      <c r="I41" s="143"/>
       <c r="J41" s="14" t="s">
         <v>58</v>
       </c>
@@ -3521,17 +3534,17 @@
       <c r="Q41" s="59"/>
       <c r="R41" s="59"/>
     </row>
-    <row r="42" spans="2:20" ht="21.95" customHeight="1">
+    <row r="42" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="78"/>
       <c r="C42" s="78"/>
-      <c r="D42" s="173" t="s">
+      <c r="D42" s="141" t="s">
         <v>83</v>
       </c>
-      <c r="E42" s="238"/>
-      <c r="F42" s="238"/>
-      <c r="G42" s="238"/>
-      <c r="H42" s="238"/>
-      <c r="I42" s="239"/>
+      <c r="E42" s="142"/>
+      <c r="F42" s="142"/>
+      <c r="G42" s="142"/>
+      <c r="H42" s="142"/>
+      <c r="I42" s="143"/>
       <c r="J42" s="15" t="s">
         <v>58</v>
       </c>
@@ -3544,17 +3557,17 @@
       <c r="Q42" s="59"/>
       <c r="R42" s="59"/>
     </row>
-    <row r="43" spans="2:20" ht="21.95" customHeight="1">
+    <row r="43" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="78"/>
       <c r="C43" s="78"/>
-      <c r="D43" s="135" t="s">
+      <c r="D43" s="171" t="s">
         <v>84</v>
       </c>
-      <c r="E43" s="238"/>
-      <c r="F43" s="238"/>
-      <c r="G43" s="238"/>
-      <c r="H43" s="238"/>
-      <c r="I43" s="239"/>
+      <c r="E43" s="142"/>
+      <c r="F43" s="142"/>
+      <c r="G43" s="142"/>
+      <c r="H43" s="142"/>
+      <c r="I43" s="143"/>
       <c r="J43" s="14" t="s">
         <v>58</v>
       </c>
@@ -3567,17 +3580,17 @@
       <c r="Q43" s="59"/>
       <c r="R43" s="59"/>
     </row>
-    <row r="44" spans="2:20" ht="21.95" customHeight="1">
+    <row r="44" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="78"/>
       <c r="C44" s="78"/>
-      <c r="D44" s="176" t="s">
+      <c r="D44" s="168" t="s">
         <v>85</v>
       </c>
-      <c r="E44" s="235"/>
-      <c r="F44" s="235"/>
-      <c r="G44" s="235"/>
-      <c r="H44" s="235"/>
-      <c r="I44" s="236"/>
+      <c r="E44" s="169"/>
+      <c r="F44" s="169"/>
+      <c r="G44" s="169"/>
+      <c r="H44" s="169"/>
+      <c r="I44" s="170"/>
       <c r="J44" s="13" t="s">
         <v>58</v>
       </c>
@@ -3590,17 +3603,17 @@
       <c r="Q44" s="59"/>
       <c r="R44" s="59"/>
     </row>
-    <row r="45" spans="2:20" ht="21.95" customHeight="1">
+    <row r="45" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="78"/>
       <c r="C45" s="78"/>
-      <c r="D45" s="135" t="s">
+      <c r="D45" s="171" t="s">
         <v>86</v>
       </c>
-      <c r="E45" s="238"/>
-      <c r="F45" s="238"/>
-      <c r="G45" s="238"/>
-      <c r="H45" s="238"/>
-      <c r="I45" s="239"/>
+      <c r="E45" s="142"/>
+      <c r="F45" s="142"/>
+      <c r="G45" s="142"/>
+      <c r="H45" s="142"/>
+      <c r="I45" s="143"/>
       <c r="J45" s="14" t="s">
         <v>58</v>
       </c>
@@ -3613,32 +3626,32 @@
       <c r="Q45" s="59"/>
       <c r="R45" s="59"/>
     </row>
-    <row r="46" spans="2:20" ht="21.95" customHeight="1">
+    <row r="46" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="78"/>
       <c r="C46" s="78"/>
-      <c r="D46" s="208" t="s">
+      <c r="D46" s="135" t="s">
         <v>87</v>
       </c>
-      <c r="E46" s="242"/>
-      <c r="F46" s="242"/>
-      <c r="G46" s="242"/>
-      <c r="H46" s="242"/>
-      <c r="I46" s="243"/>
+      <c r="E46" s="136"/>
+      <c r="F46" s="136"/>
+      <c r="G46" s="136"/>
+      <c r="H46" s="136"/>
+      <c r="I46" s="137"/>
       <c r="J46" s="23" t="s">
         <v>58</v>
       </c>
       <c r="K46" s="59"/>
-      <c r="L46" s="138" t="s">
+      <c r="L46" s="243" t="s">
         <v>88</v>
       </c>
-      <c r="M46" s="144"/>
-      <c r="N46" s="144"/>
-      <c r="O46" s="144"/>
-      <c r="P46" s="144"/>
+      <c r="M46" s="152"/>
+      <c r="N46" s="152"/>
+      <c r="O46" s="152"/>
+      <c r="P46" s="152"/>
       <c r="Q46" s="59"/>
       <c r="R46" s="59"/>
     </row>
-    <row r="47" spans="2:20" s="3" customFormat="1" ht="23.1" customHeight="1" thickBot="1">
+    <row r="47" spans="2:20" s="3" customFormat="1" ht="23.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B47" s="78"/>
       <c r="C47" s="78"/>
       <c r="D47" s="59"/>
@@ -3657,44 +3670,44 @@
       <c r="Q47" s="59"/>
       <c r="R47" s="59"/>
     </row>
-    <row r="48" spans="2:20" ht="21.95" customHeight="1" thickTop="1">
+    <row r="48" spans="2:20" ht="21.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B48" s="78"/>
       <c r="C48" s="80"/>
-      <c r="D48" s="180" t="s">
+      <c r="D48" s="224" t="s">
         <v>89</v>
       </c>
-      <c r="E48" s="246"/>
-      <c r="F48" s="246"/>
-      <c r="G48" s="246"/>
-      <c r="H48" s="246"/>
-      <c r="I48" s="246"/>
-      <c r="J48" s="246"/>
-      <c r="K48" s="246"/>
-      <c r="L48" s="246"/>
-      <c r="M48" s="246"/>
-      <c r="N48" s="246"/>
-      <c r="O48" s="246"/>
-      <c r="P48" s="247"/>
+      <c r="E48" s="225"/>
+      <c r="F48" s="225"/>
+      <c r="G48" s="225"/>
+      <c r="H48" s="225"/>
+      <c r="I48" s="225"/>
+      <c r="J48" s="225"/>
+      <c r="K48" s="225"/>
+      <c r="L48" s="225"/>
+      <c r="M48" s="225"/>
+      <c r="N48" s="225"/>
+      <c r="O48" s="225"/>
+      <c r="P48" s="226"/>
       <c r="Q48" s="59"/>
       <c r="R48" s="59"/>
       <c r="T48" s="105" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="49" spans="2:23" s="25" customFormat="1" ht="21.95" customHeight="1">
+    <row r="49" spans="2:23" s="25" customFormat="1" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B49" s="80"/>
       <c r="C49" s="80"/>
       <c r="D49" s="95" t="s">
         <v>91</v>
       </c>
-      <c r="E49" s="162" t="s">
+      <c r="E49" s="146" t="s">
         <v>92</v>
       </c>
-      <c r="F49" s="163"/>
-      <c r="G49" s="163"/>
-      <c r="H49" s="163"/>
-      <c r="I49" s="163"/>
-      <c r="J49" s="163"/>
+      <c r="F49" s="147"/>
+      <c r="G49" s="147"/>
+      <c r="H49" s="147"/>
+      <c r="I49" s="147"/>
+      <c r="J49" s="147"/>
       <c r="K49" s="95" t="s">
         <v>93</v>
       </c>
@@ -3704,10 +3717,10 @@
       <c r="M49" s="95" t="s">
         <v>95</v>
       </c>
-      <c r="N49" s="162" t="s">
+      <c r="N49" s="146" t="s">
         <v>96</v>
       </c>
-      <c r="O49" s="163"/>
+      <c r="O49" s="147"/>
       <c r="P49" s="95" t="s">
         <v>97</v>
       </c>
@@ -3715,108 +3728,108 @@
       <c r="R49" s="75"/>
       <c r="T49" s="1"/>
     </row>
-    <row r="50" spans="2:23" ht="69.95" customHeight="1">
+    <row r="50" spans="2:23" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B50" s="9"/>
       <c r="C50" s="24"/>
       <c r="D50" s="26"/>
-      <c r="E50" s="186"/>
-      <c r="F50" s="214"/>
-      <c r="G50" s="214"/>
-      <c r="H50" s="214"/>
-      <c r="I50" s="214"/>
-      <c r="J50" s="248"/>
+      <c r="E50" s="162"/>
+      <c r="F50" s="134"/>
+      <c r="G50" s="134"/>
+      <c r="H50" s="134"/>
+      <c r="I50" s="134"/>
+      <c r="J50" s="163"/>
       <c r="K50" s="27"/>
       <c r="L50" s="28"/>
       <c r="M50" s="29"/>
-      <c r="N50" s="154"/>
-      <c r="O50" s="248"/>
+      <c r="N50" s="229"/>
+      <c r="O50" s="163"/>
       <c r="P50" s="30"/>
     </row>
-    <row r="51" spans="2:23" ht="68.099999999999994" customHeight="1">
+    <row r="51" spans="2:23" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="9"/>
       <c r="C51" s="24"/>
       <c r="D51" s="31"/>
-      <c r="E51" s="151"/>
-      <c r="F51" s="214"/>
-      <c r="G51" s="214"/>
-      <c r="H51" s="214"/>
-      <c r="I51" s="214"/>
-      <c r="J51" s="248"/>
+      <c r="E51" s="194"/>
+      <c r="F51" s="134"/>
+      <c r="G51" s="134"/>
+      <c r="H51" s="134"/>
+      <c r="I51" s="134"/>
+      <c r="J51" s="163"/>
       <c r="K51" s="32"/>
       <c r="L51" s="33"/>
       <c r="M51" s="34"/>
-      <c r="N51" s="160"/>
-      <c r="O51" s="248"/>
+      <c r="N51" s="221"/>
+      <c r="O51" s="163"/>
       <c r="P51" s="35"/>
     </row>
-    <row r="52" spans="2:23" ht="68.099999999999994" customHeight="1">
+    <row r="52" spans="2:23" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="9"/>
       <c r="C52" s="24"/>
       <c r="D52" s="26"/>
-      <c r="E52" s="186"/>
-      <c r="F52" s="214"/>
-      <c r="G52" s="214"/>
-      <c r="H52" s="214"/>
-      <c r="I52" s="214"/>
-      <c r="J52" s="248"/>
+      <c r="E52" s="162"/>
+      <c r="F52" s="134"/>
+      <c r="G52" s="134"/>
+      <c r="H52" s="134"/>
+      <c r="I52" s="134"/>
+      <c r="J52" s="163"/>
       <c r="K52" s="27"/>
       <c r="L52" s="28"/>
       <c r="M52" s="29"/>
-      <c r="N52" s="154"/>
-      <c r="O52" s="248"/>
+      <c r="N52" s="229"/>
+      <c r="O52" s="163"/>
       <c r="P52" s="30"/>
     </row>
-    <row r="53" spans="2:23" ht="69.95" customHeight="1">
+    <row r="53" spans="2:23" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="9"/>
       <c r="C53" s="24"/>
       <c r="D53" s="31"/>
-      <c r="E53" s="151"/>
-      <c r="F53" s="214"/>
-      <c r="G53" s="214"/>
-      <c r="H53" s="214"/>
-      <c r="I53" s="214"/>
-      <c r="J53" s="248"/>
+      <c r="E53" s="194"/>
+      <c r="F53" s="134"/>
+      <c r="G53" s="134"/>
+      <c r="H53" s="134"/>
+      <c r="I53" s="134"/>
+      <c r="J53" s="163"/>
       <c r="K53" s="32"/>
       <c r="L53" s="33"/>
       <c r="M53" s="34"/>
-      <c r="N53" s="160"/>
-      <c r="O53" s="248"/>
+      <c r="N53" s="221"/>
+      <c r="O53" s="163"/>
       <c r="P53" s="35"/>
     </row>
-    <row r="54" spans="2:23" ht="69.95" customHeight="1">
+    <row r="54" spans="2:23" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="24"/>
       <c r="D54" s="26"/>
-      <c r="E54" s="186"/>
-      <c r="F54" s="214"/>
-      <c r="G54" s="214"/>
-      <c r="H54" s="214"/>
-      <c r="I54" s="214"/>
-      <c r="J54" s="248"/>
+      <c r="E54" s="162"/>
+      <c r="F54" s="134"/>
+      <c r="G54" s="134"/>
+      <c r="H54" s="134"/>
+      <c r="I54" s="134"/>
+      <c r="J54" s="163"/>
       <c r="K54" s="27"/>
       <c r="L54" s="28"/>
       <c r="M54" s="29"/>
-      <c r="N54" s="154"/>
-      <c r="O54" s="248"/>
+      <c r="N54" s="229"/>
+      <c r="O54" s="163"/>
       <c r="P54" s="30"/>
     </row>
-    <row r="55" spans="2:23" ht="66.95" customHeight="1">
+    <row r="55" spans="2:23" ht="66.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="9"/>
       <c r="C55" s="24"/>
       <c r="D55" s="31"/>
-      <c r="E55" s="151"/>
-      <c r="F55" s="214"/>
-      <c r="G55" s="214"/>
-      <c r="H55" s="214"/>
-      <c r="I55" s="214"/>
-      <c r="J55" s="248"/>
+      <c r="E55" s="194"/>
+      <c r="F55" s="134"/>
+      <c r="G55" s="134"/>
+      <c r="H55" s="134"/>
+      <c r="I55" s="134"/>
+      <c r="J55" s="163"/>
       <c r="K55" s="32"/>
       <c r="L55" s="33"/>
       <c r="M55" s="34"/>
-      <c r="N55" s="160"/>
-      <c r="O55" s="248"/>
+      <c r="N55" s="221"/>
+      <c r="O55" s="163"/>
       <c r="P55" s="35"/>
     </row>
-    <row r="56" spans="2:23" ht="21.95" customHeight="1">
+    <row r="56" spans="2:23" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B56" s="9"/>
       <c r="C56" s="24"/>
       <c r="D56" s="3"/>
@@ -3831,14 +3844,14 @@
       <c r="M56" s="103" t="s">
         <v>98</v>
       </c>
-      <c r="N56" s="185">
+      <c r="N56" s="215">
         <f>SUM(N50:N55)</f>
         <v>0</v>
       </c>
-      <c r="O56" s="249"/>
+      <c r="O56" s="216"/>
       <c r="P56" s="3"/>
     </row>
-    <row r="57" spans="2:23" ht="21.95" customHeight="1" thickBot="1">
+    <row r="57" spans="2:23" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B57" s="9"/>
       <c r="C57" s="24"/>
       <c r="D57" s="3"/>
@@ -3853,14 +3866,14 @@
       <c r="M57" s="104" t="s">
         <v>99</v>
       </c>
-      <c r="N57" s="200">
+      <c r="N57" s="232">
         <f>+N56*0.12</f>
         <v>0</v>
       </c>
-      <c r="O57" s="250"/>
+      <c r="O57" s="233"/>
       <c r="P57" s="3"/>
     </row>
-    <row r="58" spans="2:23" ht="21.95" customHeight="1" thickTop="1">
+    <row r="58" spans="2:23" ht="21.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B58" s="9"/>
       <c r="C58" s="24"/>
       <c r="D58" s="3"/>
@@ -3879,10 +3892,10 @@
         <f>+N57+N56</f>
         <v>0</v>
       </c>
-      <c r="O58" s="214"/>
+      <c r="O58" s="134"/>
       <c r="P58" s="3"/>
     </row>
-    <row r="59" spans="2:23" s="3" customFormat="1" ht="11.1" customHeight="1">
+    <row r="59" spans="2:23" s="3" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B59" s="78"/>
       <c r="C59" s="78"/>
       <c r="D59" s="59"/>
@@ -3901,28 +3914,28 @@
       <c r="Q59" s="60"/>
       <c r="R59" s="60"/>
     </row>
-    <row r="60" spans="2:23" ht="21" customHeight="1">
+    <row r="60" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="78"/>
       <c r="C60" s="78"/>
-      <c r="D60" s="168" t="s">
+      <c r="D60" s="220" t="s">
         <v>101</v>
       </c>
-      <c r="E60" s="144"/>
-      <c r="F60" s="144"/>
-      <c r="G60" s="144"/>
-      <c r="H60" s="144"/>
-      <c r="I60" s="144"/>
-      <c r="J60" s="144"/>
-      <c r="K60" s="144"/>
-      <c r="L60" s="144"/>
-      <c r="M60" s="144"/>
-      <c r="N60" s="144"/>
-      <c r="O60" s="144"/>
-      <c r="P60" s="144"/>
+      <c r="E60" s="152"/>
+      <c r="F60" s="152"/>
+      <c r="G60" s="152"/>
+      <c r="H60" s="152"/>
+      <c r="I60" s="152"/>
+      <c r="J60" s="152"/>
+      <c r="K60" s="152"/>
+      <c r="L60" s="152"/>
+      <c r="M60" s="152"/>
+      <c r="N60" s="152"/>
+      <c r="O60" s="152"/>
+      <c r="P60" s="152"/>
       <c r="Q60" s="60"/>
       <c r="R60" s="60"/>
     </row>
-    <row r="61" spans="2:23" s="3" customFormat="1">
+    <row r="61" spans="2:23" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B61" s="78"/>
       <c r="C61" s="78"/>
       <c r="D61" s="116" t="s">
@@ -3930,9 +3943,6 @@
       </c>
       <c r="H61" s="117" t="s">
         <v>103</v>
-      </c>
-      <c r="J61" s="3" t="s">
-        <v>104</v>
       </c>
       <c r="L61" s="117" t="s">
         <v>105</v>
@@ -3946,24 +3956,24 @@
       <c r="V61" s="36"/>
       <c r="W61" s="36"/>
     </row>
-    <row r="62" spans="2:23" ht="120" customHeight="1">
+    <row r="62" spans="2:23" ht="120" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="78"/>
       <c r="C62" s="78"/>
-      <c r="D62" s="141" t="s">
+      <c r="D62" s="253" t="s">
         <v>104</v>
       </c>
-      <c r="E62" s="251"/>
+      <c r="E62" s="198"/>
       <c r="F62" s="119"/>
       <c r="G62" s="120"/>
       <c r="H62" s="121"/>
       <c r="I62" s="121"/>
       <c r="J62" s="121"/>
-      <c r="K62" s="174"/>
-      <c r="L62" s="251"/>
-      <c r="M62" s="251"/>
+      <c r="K62" s="238"/>
+      <c r="L62" s="198"/>
+      <c r="M62" s="198"/>
       <c r="N62" s="122"/>
-      <c r="O62" s="191"/>
-      <c r="P62" s="251"/>
+      <c r="O62" s="197"/>
+      <c r="P62" s="198"/>
       <c r="Q62" s="123"/>
       <c r="R62" s="123"/>
       <c r="S62" s="118"/>
@@ -3972,22 +3982,22 @@
       <c r="V62" s="36"/>
       <c r="W62" s="36"/>
     </row>
-    <row r="63" spans="2:23">
+    <row r="63" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B63" s="78"/>
       <c r="C63" s="78"/>
-      <c r="D63" s="148"/>
-      <c r="E63" s="252"/>
+      <c r="D63" s="207"/>
+      <c r="E63" s="208"/>
       <c r="F63" s="124"/>
       <c r="G63" s="122"/>
       <c r="H63" s="125"/>
       <c r="I63" s="125"/>
       <c r="J63" s="126"/>
-      <c r="K63" s="158"/>
-      <c r="L63" s="252"/>
-      <c r="M63" s="252"/>
+      <c r="K63" s="247"/>
+      <c r="L63" s="208"/>
+      <c r="M63" s="208"/>
       <c r="N63" s="122"/>
-      <c r="O63" s="251"/>
-      <c r="P63" s="251"/>
+      <c r="O63" s="198"/>
+      <c r="P63" s="198"/>
       <c r="Q63" s="127"/>
       <c r="R63" s="127"/>
       <c r="S63" s="118"/>
@@ -3996,22 +4006,22 @@
       <c r="V63" s="36"/>
       <c r="W63" s="36"/>
     </row>
-    <row r="64" spans="2:23">
+    <row r="64" spans="2:23" x14ac:dyDescent="0.3">
       <c r="B64" s="78"/>
       <c r="C64" s="78"/>
-      <c r="D64" s="148"/>
-      <c r="E64" s="252"/>
+      <c r="D64" s="207"/>
+      <c r="E64" s="208"/>
       <c r="F64" s="124"/>
       <c r="G64" s="122"/>
       <c r="H64" s="125"/>
       <c r="I64" s="125"/>
       <c r="J64" s="126"/>
-      <c r="K64" s="252"/>
-      <c r="L64" s="252"/>
-      <c r="M64" s="252"/>
+      <c r="K64" s="208"/>
+      <c r="L64" s="208"/>
+      <c r="M64" s="208"/>
       <c r="N64" s="122"/>
-      <c r="O64" s="251"/>
-      <c r="P64" s="251"/>
+      <c r="O64" s="198"/>
+      <c r="P64" s="198"/>
       <c r="Q64" s="123"/>
       <c r="R64" s="123"/>
       <c r="S64" s="118"/>
@@ -4020,7 +4030,7 @@
       <c r="V64" s="36"/>
       <c r="W64" s="36"/>
     </row>
-    <row r="65" spans="2:20" s="3" customFormat="1" ht="24" customHeight="1">
+    <row r="65" spans="2:20" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B65" s="78"/>
       <c r="C65" s="78"/>
       <c r="D65" s="128"/>
@@ -4034,14 +4044,14 @@
       <c r="L65" s="122"/>
       <c r="M65" s="122"/>
       <c r="N65" s="122"/>
-      <c r="O65" s="165"/>
-      <c r="P65" s="251"/>
+      <c r="O65" s="257"/>
+      <c r="P65" s="198"/>
       <c r="Q65" s="123"/>
       <c r="R65" s="123"/>
       <c r="S65" s="118"/>
       <c r="T65" s="118"/>
     </row>
-    <row r="66" spans="2:20" s="3" customFormat="1" ht="15" customHeight="1">
+    <row r="66" spans="2:20" s="3" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="78"/>
       <c r="C66" s="78"/>
       <c r="D66" s="4"/>
@@ -4051,7 +4061,7 @@
       <c r="Q66" s="60"/>
       <c r="R66" s="60"/>
     </row>
-    <row r="67" spans="2:20" s="3" customFormat="1" ht="18" customHeight="1">
+    <row r="67" spans="2:20" s="3" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="78"/>
       <c r="C67" s="78"/>
       <c r="D67" s="60"/>
@@ -4070,28 +4080,28 @@
       <c r="Q67" s="59"/>
       <c r="R67" s="59"/>
     </row>
-    <row r="68" spans="2:20" ht="24.95" customHeight="1">
+    <row r="68" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="78"/>
       <c r="C68" s="78"/>
-      <c r="D68" s="168" t="s">
+      <c r="D68" s="220" t="s">
         <v>107</v>
       </c>
-      <c r="E68" s="144"/>
-      <c r="F68" s="144"/>
-      <c r="G68" s="144"/>
-      <c r="H68" s="144"/>
-      <c r="I68" s="144"/>
-      <c r="J68" s="144"/>
-      <c r="K68" s="144"/>
-      <c r="L68" s="144"/>
-      <c r="M68" s="144"/>
-      <c r="N68" s="144"/>
-      <c r="O68" s="144"/>
-      <c r="P68" s="144"/>
+      <c r="E68" s="152"/>
+      <c r="F68" s="152"/>
+      <c r="G68" s="152"/>
+      <c r="H68" s="152"/>
+      <c r="I68" s="152"/>
+      <c r="J68" s="152"/>
+      <c r="K68" s="152"/>
+      <c r="L68" s="152"/>
+      <c r="M68" s="152"/>
+      <c r="N68" s="152"/>
+      <c r="O68" s="152"/>
+      <c r="P68" s="152"/>
       <c r="Q68" s="59"/>
       <c r="R68" s="59"/>
     </row>
-    <row r="69" spans="2:20" ht="24.95" customHeight="1">
+    <row r="69" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="78"/>
       <c r="C69" s="107"/>
       <c r="D69" s="108"/>
@@ -4112,77 +4122,77 @@
       <c r="Q69" s="107"/>
       <c r="R69" s="107"/>
     </row>
-    <row r="70" spans="2:20" ht="140.1" customHeight="1">
+    <row r="70" spans="2:20" ht="140.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="78"/>
       <c r="C70" s="78"/>
       <c r="D70" s="130"/>
-      <c r="E70" s="171"/>
-      <c r="F70" s="144"/>
-      <c r="G70" s="144"/>
-      <c r="H70" s="144"/>
-      <c r="I70" s="144"/>
-      <c r="J70" s="144"/>
-      <c r="K70" s="144"/>
-      <c r="L70" s="144"/>
-      <c r="M70" s="144"/>
-      <c r="N70" s="144"/>
-      <c r="O70" s="144"/>
-      <c r="P70" s="144"/>
+      <c r="E70" s="223"/>
+      <c r="F70" s="152"/>
+      <c r="G70" s="152"/>
+      <c r="H70" s="152"/>
+      <c r="I70" s="152"/>
+      <c r="J70" s="152"/>
+      <c r="K70" s="152"/>
+      <c r="L70" s="152"/>
+      <c r="M70" s="152"/>
+      <c r="N70" s="152"/>
+      <c r="O70" s="152"/>
+      <c r="P70" s="152"/>
       <c r="Q70" s="59"/>
       <c r="R70" s="59"/>
     </row>
-    <row r="71" spans="2:20" ht="24.95" customHeight="1">
+    <row r="71" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="9"/>
       <c r="C71" s="9"/>
       <c r="D71" s="112"/>
-      <c r="E71" s="140"/>
-      <c r="F71" s="214"/>
-      <c r="G71" s="214"/>
-      <c r="H71" s="214"/>
-      <c r="I71" s="214"/>
-      <c r="J71" s="214"/>
-      <c r="K71" s="214"/>
-      <c r="L71" s="214"/>
-      <c r="M71" s="214"/>
-      <c r="N71" s="214"/>
-      <c r="O71" s="214"/>
-      <c r="P71" s="214"/>
-    </row>
-    <row r="72" spans="2:20" ht="24.95" customHeight="1">
+      <c r="E71" s="195"/>
+      <c r="F71" s="134"/>
+      <c r="G71" s="134"/>
+      <c r="H71" s="134"/>
+      <c r="I71" s="134"/>
+      <c r="J71" s="134"/>
+      <c r="K71" s="134"/>
+      <c r="L71" s="134"/>
+      <c r="M71" s="134"/>
+      <c r="N71" s="134"/>
+      <c r="O71" s="134"/>
+      <c r="P71" s="134"/>
+    </row>
+    <row r="72" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="9"/>
       <c r="C72" s="9"/>
       <c r="D72" s="112"/>
-      <c r="E72" s="133"/>
-      <c r="F72" s="214"/>
-      <c r="G72" s="214"/>
-      <c r="H72" s="214"/>
-      <c r="I72" s="214"/>
-      <c r="J72" s="214"/>
-      <c r="K72" s="214"/>
-      <c r="L72" s="214"/>
-      <c r="M72" s="214"/>
-      <c r="N72" s="214"/>
-      <c r="O72" s="214"/>
-      <c r="P72" s="214"/>
-    </row>
-    <row r="73" spans="2:20" ht="24" customHeight="1">
+      <c r="E72" s="150"/>
+      <c r="F72" s="134"/>
+      <c r="G72" s="134"/>
+      <c r="H72" s="134"/>
+      <c r="I72" s="134"/>
+      <c r="J72" s="134"/>
+      <c r="K72" s="134"/>
+      <c r="L72" s="134"/>
+      <c r="M72" s="134"/>
+      <c r="N72" s="134"/>
+      <c r="O72" s="134"/>
+      <c r="P72" s="134"/>
+    </row>
+    <row r="73" spans="2:20" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="9"/>
       <c r="C73" s="9"/>
       <c r="D73" s="112"/>
-      <c r="E73" s="133"/>
-      <c r="F73" s="214"/>
-      <c r="G73" s="214"/>
-      <c r="H73" s="214"/>
-      <c r="I73" s="214"/>
-      <c r="J73" s="214"/>
-      <c r="K73" s="214"/>
-      <c r="L73" s="214"/>
-      <c r="M73" s="214"/>
-      <c r="N73" s="214"/>
-      <c r="O73" s="214"/>
-      <c r="P73" s="214"/>
-    </row>
-    <row r="74" spans="2:20" ht="24.95" customHeight="1">
+      <c r="E73" s="150"/>
+      <c r="F73" s="134"/>
+      <c r="G73" s="134"/>
+      <c r="H73" s="134"/>
+      <c r="I73" s="134"/>
+      <c r="J73" s="134"/>
+      <c r="K73" s="134"/>
+      <c r="L73" s="134"/>
+      <c r="M73" s="134"/>
+      <c r="N73" s="134"/>
+      <c r="O73" s="134"/>
+      <c r="P73" s="134"/>
+    </row>
+    <row r="74" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="9"/>
       <c r="C74" s="9"/>
       <c r="D74" s="37"/>
@@ -4199,30 +4209,30 @@
       <c r="O74" s="39"/>
       <c r="P74" s="40"/>
     </row>
-    <row r="75" spans="2:20" ht="24.95" customHeight="1">
+    <row r="75" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="78"/>
       <c r="C75" s="78"/>
       <c r="D75" s="131" t="s">
         <v>109</v>
       </c>
-      <c r="E75" s="199" t="s">
+      <c r="E75" s="230" t="s">
         <v>110</v>
       </c>
-      <c r="F75" s="253"/>
-      <c r="G75" s="253"/>
-      <c r="H75" s="253"/>
-      <c r="I75" s="253"/>
-      <c r="J75" s="253"/>
-      <c r="K75" s="253"/>
-      <c r="L75" s="253"/>
-      <c r="M75" s="253"/>
-      <c r="N75" s="253"/>
-      <c r="O75" s="253"/>
-      <c r="P75" s="253"/>
+      <c r="F75" s="231"/>
+      <c r="G75" s="231"/>
+      <c r="H75" s="231"/>
+      <c r="I75" s="231"/>
+      <c r="J75" s="231"/>
+      <c r="K75" s="231"/>
+      <c r="L75" s="231"/>
+      <c r="M75" s="231"/>
+      <c r="N75" s="231"/>
+      <c r="O75" s="231"/>
+      <c r="P75" s="231"/>
       <c r="Q75" s="59"/>
       <c r="R75" s="59"/>
     </row>
-    <row r="76" spans="2:20" ht="24.95" customHeight="1">
+    <row r="76" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="78"/>
       <c r="C76" s="78"/>
       <c r="D76" s="113"/>
@@ -4230,12 +4240,12 @@
       <c r="F76" s="115"/>
       <c r="G76" s="115"/>
       <c r="H76" s="115"/>
-      <c r="I76" s="142" t="s">
+      <c r="I76" s="254" t="s">
         <v>111</v>
       </c>
-      <c r="J76" s="254"/>
-      <c r="K76" s="254"/>
-      <c r="L76" s="254"/>
+      <c r="J76" s="255"/>
+      <c r="K76" s="255"/>
+      <c r="L76" s="255"/>
       <c r="M76" s="115"/>
       <c r="N76" s="115"/>
       <c r="O76" s="115"/>
@@ -4243,58 +4253,58 @@
       <c r="Q76" s="59"/>
       <c r="R76" s="59"/>
     </row>
-    <row r="77" spans="2:20" ht="140.1" customHeight="1">
+    <row r="77" spans="2:20" ht="140.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="9"/>
       <c r="C77" s="9"/>
       <c r="D77" s="132"/>
-      <c r="E77" s="140"/>
-      <c r="F77" s="214"/>
-      <c r="G77" s="214"/>
-      <c r="H77" s="214"/>
-      <c r="I77" s="214"/>
-      <c r="J77" s="214"/>
-      <c r="K77" s="214"/>
-      <c r="L77" s="214"/>
-      <c r="M77" s="214"/>
-      <c r="N77" s="214"/>
-      <c r="O77" s="214"/>
-      <c r="P77" s="214"/>
-    </row>
-    <row r="78" spans="2:20" ht="24.95" customHeight="1">
+      <c r="E77" s="195"/>
+      <c r="F77" s="134"/>
+      <c r="G77" s="134"/>
+      <c r="H77" s="134"/>
+      <c r="I77" s="134"/>
+      <c r="J77" s="134"/>
+      <c r="K77" s="134"/>
+      <c r="L77" s="134"/>
+      <c r="M77" s="134"/>
+      <c r="N77" s="134"/>
+      <c r="O77" s="134"/>
+      <c r="P77" s="134"/>
+    </row>
+    <row r="78" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="9"/>
       <c r="C78" s="9"/>
       <c r="D78" s="112"/>
-      <c r="E78" s="133"/>
-      <c r="F78" s="214"/>
-      <c r="G78" s="214"/>
-      <c r="H78" s="214"/>
-      <c r="I78" s="214"/>
-      <c r="J78" s="214"/>
-      <c r="K78" s="214"/>
-      <c r="L78" s="214"/>
-      <c r="M78" s="214"/>
-      <c r="N78" s="214"/>
-      <c r="O78" s="214"/>
-      <c r="P78" s="214"/>
-    </row>
-    <row r="79" spans="2:20" ht="24.95" customHeight="1">
+      <c r="E78" s="150"/>
+      <c r="F78" s="134"/>
+      <c r="G78" s="134"/>
+      <c r="H78" s="134"/>
+      <c r="I78" s="134"/>
+      <c r="J78" s="134"/>
+      <c r="K78" s="134"/>
+      <c r="L78" s="134"/>
+      <c r="M78" s="134"/>
+      <c r="N78" s="134"/>
+      <c r="O78" s="134"/>
+      <c r="P78" s="134"/>
+    </row>
+    <row r="79" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="9"/>
       <c r="C79" s="9"/>
       <c r="D79" s="112"/>
-      <c r="E79" s="133"/>
-      <c r="F79" s="214"/>
-      <c r="G79" s="214"/>
-      <c r="H79" s="214"/>
-      <c r="I79" s="214"/>
-      <c r="J79" s="214"/>
-      <c r="K79" s="214"/>
-      <c r="L79" s="214"/>
-      <c r="M79" s="214"/>
-      <c r="N79" s="214"/>
-      <c r="O79" s="214"/>
-      <c r="P79" s="214"/>
-    </row>
-    <row r="80" spans="2:20">
+      <c r="E79" s="150"/>
+      <c r="F79" s="134"/>
+      <c r="G79" s="134"/>
+      <c r="H79" s="134"/>
+      <c r="I79" s="134"/>
+      <c r="J79" s="134"/>
+      <c r="K79" s="134"/>
+      <c r="L79" s="134"/>
+      <c r="M79" s="134"/>
+      <c r="N79" s="134"/>
+      <c r="O79" s="134"/>
+      <c r="P79" s="134"/>
+    </row>
+    <row r="80" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B80" s="78"/>
       <c r="C80" s="78"/>
       <c r="D80" s="41"/>
@@ -4313,28 +4323,28 @@
       <c r="Q80" s="59"/>
       <c r="R80" s="59"/>
     </row>
-    <row r="81" spans="2:20" ht="24.95" customHeight="1">
+    <row r="81" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="9"/>
       <c r="C81" s="9"/>
-      <c r="D81" s="190" t="s">
+      <c r="D81" s="192" t="s">
         <v>112</v>
       </c>
-      <c r="E81" s="144"/>
-      <c r="F81" s="144"/>
-      <c r="G81" s="144"/>
-      <c r="H81" s="144"/>
-      <c r="I81" s="144"/>
-      <c r="J81" s="144"/>
-      <c r="K81" s="144"/>
-      <c r="L81" s="144"/>
-      <c r="M81" s="144"/>
-      <c r="N81" s="144"/>
-      <c r="O81" s="144"/>
-      <c r="P81" s="144"/>
+      <c r="E81" s="152"/>
+      <c r="F81" s="152"/>
+      <c r="G81" s="152"/>
+      <c r="H81" s="152"/>
+      <c r="I81" s="152"/>
+      <c r="J81" s="152"/>
+      <c r="K81" s="152"/>
+      <c r="L81" s="152"/>
+      <c r="M81" s="152"/>
+      <c r="N81" s="152"/>
+      <c r="O81" s="152"/>
+      <c r="P81" s="152"/>
       <c r="Q81" s="76"/>
       <c r="R81" s="76"/>
     </row>
-    <row r="82" spans="2:20" ht="24.95" customHeight="1">
+    <row r="82" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B82" s="9"/>
       <c r="C82" s="9"/>
       <c r="D82" s="51"/>
@@ -4342,12 +4352,12 @@
       <c r="F82" s="51"/>
       <c r="G82" s="51"/>
       <c r="H82" s="51"/>
-      <c r="I82" s="183" t="s">
+      <c r="I82" s="228" t="s">
         <v>113</v>
       </c>
-      <c r="J82" s="144"/>
-      <c r="K82" s="144"/>
-      <c r="L82" s="144"/>
+      <c r="J82" s="152"/>
+      <c r="K82" s="152"/>
+      <c r="L82" s="152"/>
       <c r="M82" s="51"/>
       <c r="N82" s="51"/>
       <c r="O82" s="51"/>
@@ -4355,563 +4365,563 @@
       <c r="Q82" s="76"/>
       <c r="R82" s="76"/>
     </row>
-    <row r="83" spans="2:20" ht="140.1" customHeight="1">
+    <row r="83" spans="2:20" ht="140.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="9"/>
       <c r="C83" s="9"/>
       <c r="D83" s="130"/>
-      <c r="E83" s="171"/>
-      <c r="F83" s="144"/>
-      <c r="G83" s="144"/>
-      <c r="H83" s="144"/>
-      <c r="I83" s="144"/>
-      <c r="J83" s="144"/>
-      <c r="K83" s="144"/>
-      <c r="L83" s="144"/>
-      <c r="M83" s="144"/>
+      <c r="E83" s="223"/>
+      <c r="F83" s="152"/>
+      <c r="G83" s="152"/>
+      <c r="H83" s="152"/>
+      <c r="I83" s="152"/>
+      <c r="J83" s="152"/>
+      <c r="K83" s="152"/>
+      <c r="L83" s="152"/>
+      <c r="M83" s="152"/>
       <c r="N83" s="50"/>
       <c r="O83" s="51"/>
       <c r="P83" s="51"/>
       <c r="Q83" s="76"/>
       <c r="R83" s="76"/>
     </row>
-    <row r="84" spans="2:20" ht="24.95" customHeight="1">
+    <row r="84" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="9"/>
       <c r="C84" s="9"/>
       <c r="D84" s="112"/>
-      <c r="E84" s="140"/>
-      <c r="F84" s="214"/>
-      <c r="G84" s="214"/>
-      <c r="H84" s="214"/>
-      <c r="I84" s="214"/>
-      <c r="J84" s="214"/>
-      <c r="K84" s="214"/>
-      <c r="L84" s="214"/>
-      <c r="M84" s="214"/>
+      <c r="E84" s="195"/>
+      <c r="F84" s="134"/>
+      <c r="G84" s="134"/>
+      <c r="H84" s="134"/>
+      <c r="I84" s="134"/>
+      <c r="J84" s="134"/>
+      <c r="K84" s="134"/>
+      <c r="L84" s="134"/>
+      <c r="M84" s="134"/>
       <c r="N84" s="5"/>
-      <c r="O84" s="162" t="s">
+      <c r="O84" s="146" t="s">
         <v>114</v>
       </c>
-      <c r="P84" s="144"/>
+      <c r="P84" s="152"/>
       <c r="Q84" s="45"/>
       <c r="R84" s="45"/>
       <c r="T84" s="105" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="85" spans="2:20" ht="24.95" customHeight="1">
+    <row r="85" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="9"/>
       <c r="C85" s="9"/>
       <c r="D85" s="112"/>
-      <c r="E85" s="133"/>
-      <c r="F85" s="214"/>
-      <c r="G85" s="214"/>
-      <c r="H85" s="214"/>
-      <c r="I85" s="214"/>
-      <c r="J85" s="214"/>
-      <c r="K85" s="214"/>
-      <c r="L85" s="214"/>
-      <c r="M85" s="214"/>
+      <c r="E85" s="150"/>
+      <c r="F85" s="134"/>
+      <c r="G85" s="134"/>
+      <c r="H85" s="134"/>
+      <c r="I85" s="134"/>
+      <c r="J85" s="134"/>
+      <c r="K85" s="134"/>
+      <c r="L85" s="134"/>
+      <c r="M85" s="134"/>
       <c r="N85" s="6"/>
-      <c r="O85" s="184" t="s">
+      <c r="O85" s="213" t="s">
         <v>116</v>
       </c>
-      <c r="P85" s="144"/>
+      <c r="P85" s="152"/>
       <c r="Q85" s="45"/>
       <c r="R85" s="45"/>
     </row>
-    <row r="86" spans="2:20" ht="24.95" customHeight="1">
+    <row r="86" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="9"/>
       <c r="C86" s="9"/>
       <c r="D86" s="112"/>
-      <c r="E86" s="140"/>
-      <c r="F86" s="214"/>
-      <c r="G86" s="214"/>
-      <c r="H86" s="214"/>
-      <c r="I86" s="214"/>
-      <c r="J86" s="214"/>
-      <c r="K86" s="214"/>
-      <c r="L86" s="214"/>
-      <c r="M86" s="214"/>
+      <c r="E86" s="195"/>
+      <c r="F86" s="134"/>
+      <c r="G86" s="134"/>
+      <c r="H86" s="134"/>
+      <c r="I86" s="134"/>
+      <c r="J86" s="134"/>
+      <c r="K86" s="134"/>
+      <c r="L86" s="134"/>
+      <c r="M86" s="134"/>
       <c r="N86" s="6"/>
-      <c r="O86" s="144"/>
-      <c r="P86" s="144"/>
+      <c r="O86" s="152"/>
+      <c r="P86" s="152"/>
       <c r="Q86" s="45"/>
       <c r="R86" s="45"/>
     </row>
-    <row r="87" spans="2:20" ht="24.95" customHeight="1">
+    <row r="87" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="9"/>
       <c r="C87" s="9"/>
       <c r="D87" s="112"/>
-      <c r="E87" s="133"/>
-      <c r="F87" s="214"/>
-      <c r="G87" s="214"/>
-      <c r="H87" s="214"/>
-      <c r="I87" s="214"/>
-      <c r="J87" s="214"/>
-      <c r="K87" s="214"/>
-      <c r="L87" s="214"/>
-      <c r="M87" s="214"/>
+      <c r="E87" s="150"/>
+      <c r="F87" s="134"/>
+      <c r="G87" s="134"/>
+      <c r="H87" s="134"/>
+      <c r="I87" s="134"/>
+      <c r="J87" s="134"/>
+      <c r="K87" s="134"/>
+      <c r="L87" s="134"/>
+      <c r="M87" s="134"/>
       <c r="N87" s="6"/>
-      <c r="O87" s="144"/>
-      <c r="P87" s="144"/>
+      <c r="O87" s="152"/>
+      <c r="P87" s="152"/>
       <c r="Q87" s="45"/>
       <c r="R87" s="45"/>
     </row>
-    <row r="88" spans="2:20" ht="24.95" customHeight="1">
+    <row r="88" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="9"/>
       <c r="C88" s="9"/>
       <c r="D88" s="112"/>
-      <c r="E88" s="140"/>
-      <c r="F88" s="214"/>
-      <c r="G88" s="214"/>
-      <c r="H88" s="214"/>
-      <c r="I88" s="214"/>
-      <c r="J88" s="214"/>
-      <c r="K88" s="214"/>
-      <c r="L88" s="214"/>
-      <c r="M88" s="214"/>
+      <c r="E88" s="195"/>
+      <c r="F88" s="134"/>
+      <c r="G88" s="134"/>
+      <c r="H88" s="134"/>
+      <c r="I88" s="134"/>
+      <c r="J88" s="134"/>
+      <c r="K88" s="134"/>
+      <c r="L88" s="134"/>
+      <c r="M88" s="134"/>
       <c r="N88" s="6"/>
-      <c r="O88" s="255"/>
-      <c r="P88" s="255"/>
+      <c r="O88" s="214"/>
+      <c r="P88" s="214"/>
       <c r="Q88" s="45"/>
       <c r="R88" s="45"/>
     </row>
-    <row r="89" spans="2:20" ht="24.95" customHeight="1">
+    <row r="89" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B89" s="9"/>
       <c r="C89" s="9"/>
       <c r="D89" s="112"/>
-      <c r="E89" s="133"/>
-      <c r="F89" s="214"/>
-      <c r="G89" s="214"/>
-      <c r="H89" s="214"/>
-      <c r="I89" s="214"/>
-      <c r="J89" s="214"/>
-      <c r="K89" s="214"/>
-      <c r="L89" s="214"/>
-      <c r="M89" s="214"/>
+      <c r="E89" s="150"/>
+      <c r="F89" s="134"/>
+      <c r="G89" s="134"/>
+      <c r="H89" s="134"/>
+      <c r="I89" s="134"/>
+      <c r="J89" s="134"/>
+      <c r="K89" s="134"/>
+      <c r="L89" s="134"/>
+      <c r="M89" s="134"/>
       <c r="N89" s="6"/>
       <c r="O89" s="3"/>
       <c r="P89" s="3"/>
       <c r="Q89" s="45"/>
       <c r="R89" s="45"/>
     </row>
-    <row r="90" spans="2:20" ht="24.95" customHeight="1">
+    <row r="90" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B90" s="9"/>
       <c r="C90" s="9"/>
       <c r="D90" s="112"/>
-      <c r="E90" s="140"/>
-      <c r="F90" s="214"/>
-      <c r="G90" s="214"/>
-      <c r="H90" s="214"/>
-      <c r="I90" s="214"/>
-      <c r="J90" s="214"/>
-      <c r="K90" s="214"/>
-      <c r="L90" s="214"/>
-      <c r="M90" s="214"/>
+      <c r="E90" s="195"/>
+      <c r="F90" s="134"/>
+      <c r="G90" s="134"/>
+      <c r="H90" s="134"/>
+      <c r="I90" s="134"/>
+      <c r="J90" s="134"/>
+      <c r="K90" s="134"/>
+      <c r="L90" s="134"/>
+      <c r="M90" s="134"/>
       <c r="N90" s="6"/>
-      <c r="O90" s="162" t="s">
+      <c r="O90" s="146" t="s">
         <v>117</v>
       </c>
-      <c r="P90" s="144"/>
+      <c r="P90" s="152"/>
       <c r="Q90" s="45"/>
       <c r="R90" s="45"/>
     </row>
-    <row r="91" spans="2:20" ht="24.95" customHeight="1">
+    <row r="91" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B91" s="9"/>
       <c r="C91" s="9"/>
       <c r="D91" s="112"/>
-      <c r="E91" s="133"/>
-      <c r="F91" s="214"/>
-      <c r="G91" s="214"/>
-      <c r="H91" s="214"/>
-      <c r="I91" s="214"/>
-      <c r="J91" s="214"/>
-      <c r="K91" s="214"/>
-      <c r="L91" s="214"/>
-      <c r="M91" s="214"/>
+      <c r="E91" s="150"/>
+      <c r="F91" s="134"/>
+      <c r="G91" s="134"/>
+      <c r="H91" s="134"/>
+      <c r="I91" s="134"/>
+      <c r="J91" s="134"/>
+      <c r="K91" s="134"/>
+      <c r="L91" s="134"/>
+      <c r="M91" s="134"/>
       <c r="N91" s="6"/>
-      <c r="O91" s="184" t="s">
+      <c r="O91" s="213" t="s">
         <v>118</v>
       </c>
-      <c r="P91" s="144"/>
+      <c r="P91" s="152"/>
       <c r="Q91" s="45"/>
       <c r="R91" s="45"/>
     </row>
-    <row r="92" spans="2:20" ht="24.95" customHeight="1">
+    <row r="92" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B92" s="9"/>
       <c r="C92" s="9"/>
       <c r="D92" s="112"/>
-      <c r="E92" s="140"/>
-      <c r="F92" s="214"/>
-      <c r="G92" s="214"/>
-      <c r="H92" s="214"/>
-      <c r="I92" s="214"/>
-      <c r="J92" s="214"/>
-      <c r="K92" s="214"/>
-      <c r="L92" s="214"/>
-      <c r="M92" s="214"/>
+      <c r="E92" s="195"/>
+      <c r="F92" s="134"/>
+      <c r="G92" s="134"/>
+      <c r="H92" s="134"/>
+      <c r="I92" s="134"/>
+      <c r="J92" s="134"/>
+      <c r="K92" s="134"/>
+      <c r="L92" s="134"/>
+      <c r="M92" s="134"/>
       <c r="N92" s="6"/>
-      <c r="O92" s="144"/>
-      <c r="P92" s="144"/>
+      <c r="O92" s="152"/>
+      <c r="P92" s="152"/>
       <c r="Q92" s="45"/>
       <c r="R92" s="45"/>
     </row>
-    <row r="93" spans="2:20" ht="24.95" customHeight="1">
+    <row r="93" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B93" s="9"/>
       <c r="C93" s="9"/>
       <c r="D93" s="112"/>
-      <c r="E93" s="133"/>
-      <c r="F93" s="214"/>
-      <c r="G93" s="214"/>
-      <c r="H93" s="214"/>
-      <c r="I93" s="214"/>
-      <c r="J93" s="214"/>
-      <c r="K93" s="214"/>
-      <c r="L93" s="214"/>
-      <c r="M93" s="214"/>
+      <c r="E93" s="150"/>
+      <c r="F93" s="134"/>
+      <c r="G93" s="134"/>
+      <c r="H93" s="134"/>
+      <c r="I93" s="134"/>
+      <c r="J93" s="134"/>
+      <c r="K93" s="134"/>
+      <c r="L93" s="134"/>
+      <c r="M93" s="134"/>
       <c r="N93" s="6"/>
-      <c r="O93" s="144"/>
-      <c r="P93" s="144"/>
+      <c r="O93" s="152"/>
+      <c r="P93" s="152"/>
       <c r="Q93" s="45"/>
       <c r="R93" s="45"/>
     </row>
-    <row r="94" spans="2:20" ht="24.95" customHeight="1">
+    <row r="94" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B94" s="9"/>
       <c r="C94" s="9"/>
       <c r="D94" s="112"/>
-      <c r="E94" s="140"/>
-      <c r="F94" s="214"/>
-      <c r="G94" s="214"/>
-      <c r="H94" s="214"/>
-      <c r="I94" s="214"/>
-      <c r="J94" s="214"/>
-      <c r="K94" s="214"/>
-      <c r="L94" s="214"/>
-      <c r="M94" s="214"/>
+      <c r="E94" s="195"/>
+      <c r="F94" s="134"/>
+      <c r="G94" s="134"/>
+      <c r="H94" s="134"/>
+      <c r="I94" s="134"/>
+      <c r="J94" s="134"/>
+      <c r="K94" s="134"/>
+      <c r="L94" s="134"/>
+      <c r="M94" s="134"/>
       <c r="N94" s="6"/>
-      <c r="O94" s="144"/>
-      <c r="P94" s="144"/>
+      <c r="O94" s="152"/>
+      <c r="P94" s="152"/>
       <c r="Q94" s="45"/>
       <c r="R94" s="45"/>
     </row>
-    <row r="95" spans="2:20" ht="24.95" customHeight="1">
+    <row r="95" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B95" s="9"/>
       <c r="C95" s="9"/>
       <c r="D95" s="112"/>
-      <c r="E95" s="133"/>
-      <c r="F95" s="214"/>
-      <c r="G95" s="214"/>
-      <c r="H95" s="214"/>
-      <c r="I95" s="214"/>
-      <c r="J95" s="214"/>
-      <c r="K95" s="214"/>
-      <c r="L95" s="214"/>
-      <c r="M95" s="214"/>
+      <c r="E95" s="150"/>
+      <c r="F95" s="134"/>
+      <c r="G95" s="134"/>
+      <c r="H95" s="134"/>
+      <c r="I95" s="134"/>
+      <c r="J95" s="134"/>
+      <c r="K95" s="134"/>
+      <c r="L95" s="134"/>
+      <c r="M95" s="134"/>
       <c r="N95" s="6"/>
-      <c r="O95" s="144"/>
-      <c r="P95" s="144"/>
+      <c r="O95" s="152"/>
+      <c r="P95" s="152"/>
       <c r="Q95" s="45"/>
       <c r="R95" s="45"/>
     </row>
-    <row r="96" spans="2:20" ht="24.95" customHeight="1">
+    <row r="96" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B96" s="9"/>
       <c r="C96" s="9"/>
       <c r="D96" s="112"/>
-      <c r="E96" s="140"/>
-      <c r="F96" s="214"/>
-      <c r="G96" s="214"/>
-      <c r="H96" s="214"/>
-      <c r="I96" s="214"/>
-      <c r="J96" s="214"/>
-      <c r="K96" s="214"/>
-      <c r="L96" s="214"/>
-      <c r="M96" s="214"/>
+      <c r="E96" s="195"/>
+      <c r="F96" s="134"/>
+      <c r="G96" s="134"/>
+      <c r="H96" s="134"/>
+      <c r="I96" s="134"/>
+      <c r="J96" s="134"/>
+      <c r="K96" s="134"/>
+      <c r="L96" s="134"/>
+      <c r="M96" s="134"/>
       <c r="N96" s="6"/>
-      <c r="O96" s="255"/>
-      <c r="P96" s="255"/>
+      <c r="O96" s="214"/>
+      <c r="P96" s="214"/>
       <c r="Q96" s="45"/>
       <c r="R96" s="45"/>
     </row>
-    <row r="97" spans="2:18" ht="24.95" customHeight="1">
+    <row r="97" spans="2:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B97" s="9"/>
       <c r="C97" s="9"/>
       <c r="D97" s="112"/>
-      <c r="E97" s="133"/>
-      <c r="F97" s="214"/>
-      <c r="G97" s="214"/>
-      <c r="H97" s="214"/>
-      <c r="I97" s="214"/>
-      <c r="J97" s="214"/>
-      <c r="K97" s="214"/>
-      <c r="L97" s="214"/>
-      <c r="M97" s="214"/>
+      <c r="E97" s="150"/>
+      <c r="F97" s="134"/>
+      <c r="G97" s="134"/>
+      <c r="H97" s="134"/>
+      <c r="I97" s="134"/>
+      <c r="J97" s="134"/>
+      <c r="K97" s="134"/>
+      <c r="L97" s="134"/>
+      <c r="M97" s="134"/>
       <c r="N97" s="6"/>
       <c r="O97" s="3"/>
       <c r="P97" s="3"/>
       <c r="Q97" s="45"/>
       <c r="R97" s="45"/>
     </row>
-    <row r="98" spans="2:18" ht="24.95" customHeight="1">
+    <row r="98" spans="2:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="9"/>
       <c r="C98" s="9"/>
       <c r="D98" s="112"/>
-      <c r="E98" s="140"/>
-      <c r="F98" s="214"/>
-      <c r="G98" s="214"/>
-      <c r="H98" s="214"/>
-      <c r="I98" s="214"/>
-      <c r="J98" s="214"/>
-      <c r="K98" s="214"/>
-      <c r="L98" s="214"/>
-      <c r="M98" s="214"/>
+      <c r="E98" s="195"/>
+      <c r="F98" s="134"/>
+      <c r="G98" s="134"/>
+      <c r="H98" s="134"/>
+      <c r="I98" s="134"/>
+      <c r="J98" s="134"/>
+      <c r="K98" s="134"/>
+      <c r="L98" s="134"/>
+      <c r="M98" s="134"/>
       <c r="N98" s="6"/>
-      <c r="O98" s="162" t="s">
+      <c r="O98" s="146" t="s">
         <v>119</v>
       </c>
-      <c r="P98" s="144"/>
+      <c r="P98" s="152"/>
       <c r="Q98" s="45"/>
       <c r="R98" s="45"/>
     </row>
-    <row r="99" spans="2:18" ht="24.95" customHeight="1">
+    <row r="99" spans="2:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B99" s="9"/>
       <c r="C99" s="9"/>
       <c r="D99" s="112"/>
-      <c r="E99" s="133"/>
-      <c r="F99" s="214"/>
-      <c r="G99" s="214"/>
-      <c r="H99" s="214"/>
-      <c r="I99" s="214"/>
-      <c r="J99" s="214"/>
-      <c r="K99" s="214"/>
-      <c r="L99" s="214"/>
-      <c r="M99" s="214"/>
+      <c r="E99" s="150"/>
+      <c r="F99" s="134"/>
+      <c r="G99" s="134"/>
+      <c r="H99" s="134"/>
+      <c r="I99" s="134"/>
+      <c r="J99" s="134"/>
+      <c r="K99" s="134"/>
+      <c r="L99" s="134"/>
+      <c r="M99" s="134"/>
       <c r="N99" s="6"/>
-      <c r="O99" s="184" t="s">
+      <c r="O99" s="213" t="s">
         <v>120</v>
       </c>
-      <c r="P99" s="144"/>
+      <c r="P99" s="152"/>
       <c r="Q99" s="45"/>
       <c r="R99" s="45"/>
     </row>
-    <row r="100" spans="2:18" ht="24.95" customHeight="1">
+    <row r="100" spans="2:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B100" s="9"/>
       <c r="C100" s="9"/>
       <c r="D100" s="112"/>
-      <c r="E100" s="140"/>
-      <c r="F100" s="214"/>
-      <c r="G100" s="214"/>
-      <c r="H100" s="214"/>
-      <c r="I100" s="214"/>
-      <c r="J100" s="214"/>
-      <c r="K100" s="214"/>
-      <c r="L100" s="214"/>
-      <c r="M100" s="214"/>
+      <c r="E100" s="195"/>
+      <c r="F100" s="134"/>
+      <c r="G100" s="134"/>
+      <c r="H100" s="134"/>
+      <c r="I100" s="134"/>
+      <c r="J100" s="134"/>
+      <c r="K100" s="134"/>
+      <c r="L100" s="134"/>
+      <c r="M100" s="134"/>
       <c r="N100" s="6"/>
-      <c r="O100" s="144"/>
-      <c r="P100" s="144"/>
+      <c r="O100" s="152"/>
+      <c r="P100" s="152"/>
       <c r="Q100" s="45"/>
       <c r="R100" s="45"/>
     </row>
-    <row r="101" spans="2:18" ht="24.95" customHeight="1">
+    <row r="101" spans="2:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B101" s="9"/>
       <c r="C101" s="9"/>
       <c r="D101" s="112"/>
-      <c r="E101" s="133"/>
-      <c r="F101" s="214"/>
-      <c r="G101" s="214"/>
-      <c r="H101" s="214"/>
-      <c r="I101" s="214"/>
-      <c r="J101" s="214"/>
-      <c r="K101" s="214"/>
-      <c r="L101" s="214"/>
-      <c r="M101" s="214"/>
+      <c r="E101" s="150"/>
+      <c r="F101" s="134"/>
+      <c r="G101" s="134"/>
+      <c r="H101" s="134"/>
+      <c r="I101" s="134"/>
+      <c r="J101" s="134"/>
+      <c r="K101" s="134"/>
+      <c r="L101" s="134"/>
+      <c r="M101" s="134"/>
       <c r="N101" s="6"/>
-      <c r="O101" s="144"/>
-      <c r="P101" s="144"/>
+      <c r="O101" s="152"/>
+      <c r="P101" s="152"/>
       <c r="Q101" s="45"/>
       <c r="R101" s="45"/>
     </row>
-    <row r="102" spans="2:18" ht="24.95" customHeight="1">
+    <row r="102" spans="2:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B102" s="9"/>
       <c r="C102" s="9"/>
       <c r="D102" s="112"/>
-      <c r="E102" s="140"/>
-      <c r="F102" s="214"/>
-      <c r="G102" s="214"/>
-      <c r="H102" s="214"/>
-      <c r="I102" s="214"/>
-      <c r="J102" s="214"/>
-      <c r="K102" s="214"/>
-      <c r="L102" s="214"/>
-      <c r="M102" s="214"/>
+      <c r="E102" s="195"/>
+      <c r="F102" s="134"/>
+      <c r="G102" s="134"/>
+      <c r="H102" s="134"/>
+      <c r="I102" s="134"/>
+      <c r="J102" s="134"/>
+      <c r="K102" s="134"/>
+      <c r="L102" s="134"/>
+      <c r="M102" s="134"/>
       <c r="N102" s="6"/>
-      <c r="O102" s="144"/>
-      <c r="P102" s="144"/>
+      <c r="O102" s="152"/>
+      <c r="P102" s="152"/>
       <c r="Q102" s="45"/>
       <c r="R102" s="45"/>
     </row>
-    <row r="103" spans="2:18" ht="24.95" customHeight="1">
+    <row r="103" spans="2:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B103" s="9"/>
       <c r="C103" s="9"/>
       <c r="D103" s="112"/>
-      <c r="E103" s="133"/>
-      <c r="F103" s="214"/>
-      <c r="G103" s="214"/>
-      <c r="H103" s="214"/>
-      <c r="I103" s="214"/>
-      <c r="J103" s="214"/>
-      <c r="K103" s="214"/>
-      <c r="L103" s="214"/>
-      <c r="M103" s="214"/>
+      <c r="E103" s="150"/>
+      <c r="F103" s="134"/>
+      <c r="G103" s="134"/>
+      <c r="H103" s="134"/>
+      <c r="I103" s="134"/>
+      <c r="J103" s="134"/>
+      <c r="K103" s="134"/>
+      <c r="L103" s="134"/>
+      <c r="M103" s="134"/>
       <c r="N103" s="6"/>
-      <c r="O103" s="144"/>
-      <c r="P103" s="144"/>
+      <c r="O103" s="152"/>
+      <c r="P103" s="152"/>
       <c r="Q103" s="45"/>
       <c r="R103" s="45"/>
     </row>
-    <row r="104" spans="2:18" ht="24.95" customHeight="1">
+    <row r="104" spans="2:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B104" s="9"/>
       <c r="C104" s="9"/>
       <c r="D104" s="112"/>
-      <c r="E104" s="140"/>
-      <c r="F104" s="214"/>
-      <c r="G104" s="214"/>
-      <c r="H104" s="214"/>
-      <c r="I104" s="214"/>
-      <c r="J104" s="214"/>
-      <c r="K104" s="214"/>
-      <c r="L104" s="214"/>
-      <c r="M104" s="214"/>
+      <c r="E104" s="195"/>
+      <c r="F104" s="134"/>
+      <c r="G104" s="134"/>
+      <c r="H104" s="134"/>
+      <c r="I104" s="134"/>
+      <c r="J104" s="134"/>
+      <c r="K104" s="134"/>
+      <c r="L104" s="134"/>
+      <c r="M104" s="134"/>
       <c r="N104" s="6"/>
-      <c r="O104" s="255"/>
-      <c r="P104" s="255"/>
+      <c r="O104" s="214"/>
+      <c r="P104" s="214"/>
       <c r="Q104" s="45"/>
       <c r="R104" s="45"/>
     </row>
-    <row r="105" spans="2:18" ht="24.95" customHeight="1">
+    <row r="105" spans="2:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B105" s="9"/>
       <c r="C105" s="9"/>
       <c r="D105" s="112"/>
-      <c r="E105" s="133"/>
-      <c r="F105" s="214"/>
-      <c r="G105" s="214"/>
-      <c r="H105" s="214"/>
-      <c r="I105" s="214"/>
-      <c r="J105" s="214"/>
-      <c r="K105" s="214"/>
-      <c r="L105" s="214"/>
-      <c r="M105" s="214"/>
+      <c r="E105" s="150"/>
+      <c r="F105" s="134"/>
+      <c r="G105" s="134"/>
+      <c r="H105" s="134"/>
+      <c r="I105" s="134"/>
+      <c r="J105" s="134"/>
+      <c r="K105" s="134"/>
+      <c r="L105" s="134"/>
+      <c r="M105" s="134"/>
       <c r="N105" s="6"/>
       <c r="O105" s="3"/>
       <c r="P105" s="3"/>
       <c r="Q105" s="45"/>
       <c r="R105" s="45"/>
     </row>
-    <row r="106" spans="2:18" ht="24.95" customHeight="1">
+    <row r="106" spans="2:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B106" s="9"/>
       <c r="C106" s="9"/>
       <c r="D106" s="112"/>
-      <c r="E106" s="140"/>
-      <c r="F106" s="214"/>
-      <c r="G106" s="214"/>
-      <c r="H106" s="214"/>
-      <c r="I106" s="214"/>
-      <c r="J106" s="214"/>
-      <c r="K106" s="214"/>
-      <c r="L106" s="214"/>
-      <c r="M106" s="214"/>
+      <c r="E106" s="195"/>
+      <c r="F106" s="134"/>
+      <c r="G106" s="134"/>
+      <c r="H106" s="134"/>
+      <c r="I106" s="134"/>
+      <c r="J106" s="134"/>
+      <c r="K106" s="134"/>
+      <c r="L106" s="134"/>
+      <c r="M106" s="134"/>
       <c r="N106" s="6"/>
       <c r="O106" s="92"/>
       <c r="P106" s="92"/>
       <c r="Q106" s="45"/>
       <c r="R106" s="45"/>
     </row>
-    <row r="107" spans="2:18" ht="39" customHeight="1">
+    <row r="107" spans="2:18" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B107" s="9"/>
       <c r="C107" s="9"/>
       <c r="D107" s="112"/>
-      <c r="E107" s="166"/>
-      <c r="F107" s="144"/>
-      <c r="G107" s="144"/>
-      <c r="H107" s="144"/>
-      <c r="I107" s="144"/>
-      <c r="J107" s="144"/>
-      <c r="K107" s="144"/>
-      <c r="L107" s="144"/>
-      <c r="M107" s="144"/>
+      <c r="E107" s="236"/>
+      <c r="F107" s="152"/>
+      <c r="G107" s="152"/>
+      <c r="H107" s="152"/>
+      <c r="I107" s="152"/>
+      <c r="J107" s="152"/>
+      <c r="K107" s="152"/>
+      <c r="L107" s="152"/>
+      <c r="M107" s="152"/>
       <c r="N107" s="6"/>
       <c r="O107" s="92"/>
       <c r="P107" s="92"/>
       <c r="Q107" s="45"/>
       <c r="R107" s="45"/>
     </row>
-    <row r="108" spans="2:18" s="48" customFormat="1" ht="57.75" customHeight="1">
+    <row r="108" spans="2:18" s="48" customFormat="1" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B108" s="46"/>
       <c r="C108" s="46"/>
       <c r="D108" s="112"/>
-      <c r="E108" s="166"/>
-      <c r="F108" s="167"/>
-      <c r="G108" s="167"/>
-      <c r="H108" s="167"/>
-      <c r="I108" s="167"/>
-      <c r="J108" s="167"/>
-      <c r="K108" s="167"/>
-      <c r="L108" s="167"/>
-      <c r="M108" s="167"/>
+      <c r="E108" s="236"/>
+      <c r="F108" s="258"/>
+      <c r="G108" s="258"/>
+      <c r="H108" s="258"/>
+      <c r="I108" s="258"/>
+      <c r="J108" s="258"/>
+      <c r="K108" s="258"/>
+      <c r="L108" s="258"/>
+      <c r="M108" s="258"/>
       <c r="N108" s="47"/>
       <c r="O108" s="96"/>
       <c r="P108" s="96"/>
       <c r="Q108" s="76"/>
       <c r="R108" s="76"/>
     </row>
-    <row r="109" spans="2:18" ht="33" customHeight="1">
+    <row r="109" spans="2:18" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B109" s="9"/>
       <c r="C109" s="9"/>
       <c r="D109" s="112"/>
-      <c r="E109" s="166"/>
-      <c r="F109" s="144"/>
-      <c r="G109" s="144"/>
-      <c r="H109" s="144"/>
-      <c r="I109" s="144"/>
-      <c r="J109" s="144"/>
-      <c r="K109" s="144"/>
-      <c r="L109" s="144"/>
-      <c r="M109" s="144"/>
+      <c r="E109" s="236"/>
+      <c r="F109" s="152"/>
+      <c r="G109" s="152"/>
+      <c r="H109" s="152"/>
+      <c r="I109" s="152"/>
+      <c r="J109" s="152"/>
+      <c r="K109" s="152"/>
+      <c r="L109" s="152"/>
+      <c r="M109" s="152"/>
       <c r="N109" s="6"/>
       <c r="O109" s="97"/>
       <c r="P109" s="97"/>
       <c r="Q109" s="76"/>
       <c r="R109" s="76"/>
     </row>
-    <row r="110" spans="2:18" ht="63.75" customHeight="1">
+    <row r="110" spans="2:18" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B110" s="9"/>
       <c r="C110" s="9"/>
       <c r="D110" s="112"/>
-      <c r="E110" s="166"/>
-      <c r="F110" s="144"/>
-      <c r="G110" s="144"/>
-      <c r="H110" s="144"/>
-      <c r="I110" s="144"/>
-      <c r="J110" s="144"/>
-      <c r="K110" s="144"/>
-      <c r="L110" s="144"/>
-      <c r="M110" s="144"/>
+      <c r="E110" s="236"/>
+      <c r="F110" s="152"/>
+      <c r="G110" s="152"/>
+      <c r="H110" s="152"/>
+      <c r="I110" s="152"/>
+      <c r="J110" s="152"/>
+      <c r="K110" s="152"/>
+      <c r="L110" s="152"/>
+      <c r="M110" s="152"/>
       <c r="N110" s="6"/>
-      <c r="O110" s="143" t="s">
+      <c r="O110" s="256" t="s">
         <v>88</v>
       </c>
-      <c r="P110" s="144"/>
+      <c r="P110" s="152"/>
       <c r="Q110" s="76"/>
       <c r="R110" s="76"/>
     </row>
-    <row r="111" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1">
+    <row r="111" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B111" s="9"/>
       <c r="C111" s="9"/>
       <c r="D111" s="4"/>
       <c r="Q111" s="59"/>
       <c r="R111" s="59"/>
     </row>
-    <row r="112" spans="2:18" s="3" customFormat="1">
+    <row r="112" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B112" s="78"/>
       <c r="C112" s="78"/>
       <c r="D112" s="98"/>
@@ -4919,11 +4929,11 @@
       <c r="F112" s="99"/>
       <c r="G112" s="99"/>
       <c r="H112" s="99"/>
-      <c r="I112" s="169" t="s">
+      <c r="I112" s="234" t="s">
         <v>121</v>
       </c>
-      <c r="J112" s="256"/>
-      <c r="K112" s="256"/>
+      <c r="J112" s="235"/>
+      <c r="K112" s="235"/>
       <c r="L112" s="99"/>
       <c r="M112" s="99"/>
       <c r="N112" s="99"/>
@@ -4932,28 +4942,28 @@
       <c r="Q112" s="59"/>
       <c r="R112" s="59"/>
     </row>
-    <row r="113" spans="2:18" ht="140.1" customHeight="1">
+    <row r="113" spans="2:18" ht="140.1" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B113" s="78"/>
       <c r="C113" s="78"/>
-      <c r="D113" s="161" t="s">
+      <c r="D113" s="248" t="s">
         <v>122</v>
       </c>
-      <c r="E113" s="144"/>
-      <c r="F113" s="144"/>
-      <c r="G113" s="144"/>
-      <c r="H113" s="144"/>
-      <c r="I113" s="144"/>
-      <c r="J113" s="144"/>
-      <c r="K113" s="144"/>
-      <c r="L113" s="144"/>
-      <c r="M113" s="144"/>
-      <c r="N113" s="144"/>
-      <c r="O113" s="144"/>
-      <c r="P113" s="144"/>
+      <c r="E113" s="152"/>
+      <c r="F113" s="152"/>
+      <c r="G113" s="152"/>
+      <c r="H113" s="152"/>
+      <c r="I113" s="152"/>
+      <c r="J113" s="152"/>
+      <c r="K113" s="152"/>
+      <c r="L113" s="152"/>
+      <c r="M113" s="152"/>
+      <c r="N113" s="152"/>
+      <c r="O113" s="152"/>
+      <c r="P113" s="152"/>
       <c r="Q113" s="59"/>
       <c r="R113" s="59"/>
     </row>
-    <row r="114" spans="2:18">
+    <row r="114" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B114" s="78"/>
       <c r="C114" s="78"/>
       <c r="D114" s="60"/>
@@ -4972,34 +4982,34 @@
       <c r="Q114" s="59"/>
       <c r="R114" s="59"/>
     </row>
-    <row r="115" spans="2:18" ht="24" customHeight="1">
+    <row r="115" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B115" s="78"/>
       <c r="C115" s="78"/>
-      <c r="D115" s="159" t="s">
+      <c r="D115" s="196" t="s">
         <v>123</v>
       </c>
-      <c r="E115" s="144"/>
-      <c r="F115" s="144"/>
+      <c r="E115" s="152"/>
+      <c r="F115" s="152"/>
       <c r="G115" s="59"/>
-      <c r="H115" s="159" t="s">
+      <c r="H115" s="196" t="s">
         <v>123</v>
       </c>
-      <c r="I115" s="144"/>
-      <c r="J115" s="144"/>
+      <c r="I115" s="152"/>
+      <c r="J115" s="152"/>
       <c r="K115" s="59"/>
-      <c r="L115" s="159" t="s">
+      <c r="L115" s="196" t="s">
         <v>123</v>
       </c>
-      <c r="M115" s="144"/>
+      <c r="M115" s="152"/>
       <c r="N115" s="59"/>
-      <c r="O115" s="159" t="s">
+      <c r="O115" s="196" t="s">
         <v>124</v>
       </c>
-      <c r="P115" s="144"/>
+      <c r="P115" s="152"/>
       <c r="Q115" s="59"/>
       <c r="R115" s="59"/>
     </row>
-    <row r="116" spans="2:18" s="3" customFormat="1" ht="24" customHeight="1">
+    <row r="116" spans="2:18" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B116" s="78"/>
       <c r="C116" s="78"/>
       <c r="D116" s="59"/>
@@ -5018,7 +5028,7 @@
       <c r="Q116" s="59"/>
       <c r="R116" s="59"/>
     </row>
-    <row r="117" spans="2:18" ht="24" customHeight="1">
+    <row r="117" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B117" s="78"/>
       <c r="C117" s="78"/>
       <c r="D117" s="100"/>
@@ -5037,7 +5047,7 @@
       <c r="Q117" s="59"/>
       <c r="R117" s="59"/>
     </row>
-    <row r="118" spans="2:18" ht="24" customHeight="1">
+    <row r="118" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B118" s="78"/>
       <c r="C118" s="78"/>
       <c r="D118" s="100"/>
@@ -5056,7 +5066,7 @@
       <c r="Q118" s="59"/>
       <c r="R118" s="59"/>
     </row>
-    <row r="119" spans="2:18" ht="24" customHeight="1">
+    <row r="119" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B119" s="78"/>
       <c r="C119" s="78"/>
       <c r="D119" s="100"/>
@@ -5075,7 +5085,7 @@
       <c r="Q119" s="59"/>
       <c r="R119" s="59"/>
     </row>
-    <row r="120" spans="2:18" ht="24" customHeight="1">
+    <row r="120" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B120" s="78"/>
       <c r="C120" s="78"/>
       <c r="D120" s="101"/>
@@ -5094,61 +5104,61 @@
       <c r="Q120" s="59"/>
       <c r="R120" s="59"/>
     </row>
-    <row r="121" spans="2:18" s="3" customFormat="1" ht="24" customHeight="1">
+    <row r="121" spans="2:18" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B121" s="78"/>
       <c r="C121" s="78"/>
-      <c r="D121" s="189" t="s">
+      <c r="D121" s="191" t="s">
         <v>125</v>
       </c>
-      <c r="E121" s="139"/>
-      <c r="F121" s="139"/>
+      <c r="E121" s="145"/>
+      <c r="F121" s="145"/>
       <c r="G121" s="102"/>
-      <c r="H121" s="209" t="s">
+      <c r="H121" s="144" t="s">
         <v>126</v>
       </c>
-      <c r="I121" s="139"/>
-      <c r="J121" s="139"/>
+      <c r="I121" s="145"/>
+      <c r="J121" s="145"/>
       <c r="K121" s="102"/>
-      <c r="L121" s="164" t="s">
+      <c r="L121" s="148" t="s">
         <v>127</v>
       </c>
-      <c r="M121" s="257"/>
+      <c r="M121" s="149"/>
       <c r="N121" s="102"/>
-      <c r="O121" s="164" t="s">
+      <c r="O121" s="148" t="s">
         <v>128</v>
       </c>
-      <c r="P121" s="257"/>
+      <c r="P121" s="149"/>
       <c r="Q121" s="59"/>
       <c r="R121" s="59"/>
     </row>
-    <row r="122" spans="2:18" s="3" customFormat="1" ht="24.95" customHeight="1">
+    <row r="122" spans="2:18" s="3" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B122" s="78"/>
       <c r="C122" s="78"/>
-      <c r="D122" s="149" t="s">
+      <c r="D122" s="133" t="s">
         <v>129</v>
       </c>
-      <c r="E122" s="214"/>
-      <c r="F122" s="214"/>
+      <c r="E122" s="134"/>
+      <c r="F122" s="134"/>
       <c r="G122" s="94"/>
-      <c r="H122" s="149" t="s">
+      <c r="H122" s="133" t="s">
         <v>129</v>
       </c>
-      <c r="I122" s="214"/>
-      <c r="J122" s="214"/>
+      <c r="I122" s="134"/>
+      <c r="J122" s="134"/>
       <c r="K122" s="102"/>
-      <c r="L122" s="138" t="s">
+      <c r="L122" s="243" t="s">
         <v>130</v>
       </c>
-      <c r="M122" s="139"/>
+      <c r="M122" s="145"/>
       <c r="N122" s="102"/>
-      <c r="O122" s="149" t="s">
+      <c r="O122" s="133" t="s">
         <v>129</v>
       </c>
-      <c r="P122" s="214"/>
+      <c r="P122" s="134"/>
       <c r="Q122" s="59"/>
       <c r="R122" s="59"/>
     </row>
-    <row r="123" spans="2:18" s="3" customFormat="1">
+    <row r="123" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B123" s="78"/>
       <c r="C123" s="78"/>
       <c r="D123" s="59"/>
@@ -5167,7 +5177,7 @@
       <c r="Q123" s="59"/>
       <c r="R123" s="59"/>
     </row>
-    <row r="124" spans="2:18" s="3" customFormat="1" ht="18" customHeight="1" thickBot="1">
+    <row r="124" spans="2:18" s="3" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B124" s="78"/>
       <c r="C124" s="78"/>
       <c r="D124" s="83"/>
@@ -5186,12 +5196,157 @@
       <c r="Q124" s="59"/>
       <c r="R124" s="59"/>
     </row>
-    <row r="125" spans="2:18">
+    <row r="125" spans="2:18" x14ac:dyDescent="0.3">
       <c r="Q125" s="59"/>
       <c r="R125" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="169">
+    <mergeCell ref="E102:M102"/>
+    <mergeCell ref="D62:E62"/>
+    <mergeCell ref="I76:L76"/>
+    <mergeCell ref="O110:P110"/>
+    <mergeCell ref="E104:M104"/>
+    <mergeCell ref="E49:J49"/>
+    <mergeCell ref="L121:M121"/>
+    <mergeCell ref="O65:P65"/>
+    <mergeCell ref="E92:M92"/>
+    <mergeCell ref="O115:P115"/>
+    <mergeCell ref="N55:O55"/>
+    <mergeCell ref="E107:M107"/>
+    <mergeCell ref="E108:M108"/>
+    <mergeCell ref="L115:M115"/>
+    <mergeCell ref="E109:M109"/>
+    <mergeCell ref="E93:M93"/>
+    <mergeCell ref="E101:M101"/>
+    <mergeCell ref="H122:J122"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="L46:P46"/>
+    <mergeCell ref="D45:I45"/>
+    <mergeCell ref="D23:H23"/>
+    <mergeCell ref="L38:O38"/>
+    <mergeCell ref="E51:J51"/>
+    <mergeCell ref="L31:O31"/>
+    <mergeCell ref="L40:O40"/>
+    <mergeCell ref="N50:O50"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="K63:M64"/>
+    <mergeCell ref="H115:J115"/>
+    <mergeCell ref="N51:O51"/>
+    <mergeCell ref="D113:P113"/>
+    <mergeCell ref="E90:M90"/>
+    <mergeCell ref="E77:P77"/>
+    <mergeCell ref="E105:M105"/>
+    <mergeCell ref="L27:O27"/>
+    <mergeCell ref="E99:M99"/>
+    <mergeCell ref="D43:I43"/>
+    <mergeCell ref="L36:O36"/>
+    <mergeCell ref="D26:J26"/>
+    <mergeCell ref="L122:M122"/>
+    <mergeCell ref="E85:M85"/>
+    <mergeCell ref="E100:M100"/>
+    <mergeCell ref="E78:P78"/>
+    <mergeCell ref="I112:K112"/>
+    <mergeCell ref="E110:M110"/>
+    <mergeCell ref="L16:O16"/>
+    <mergeCell ref="L18:P18"/>
+    <mergeCell ref="E70:P70"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="D42:I42"/>
+    <mergeCell ref="E72:P72"/>
+    <mergeCell ref="K62:M62"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="D35:I35"/>
+    <mergeCell ref="D44:I44"/>
+    <mergeCell ref="D27:J27"/>
+    <mergeCell ref="D34:I34"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="L30:O30"/>
+    <mergeCell ref="L39:O39"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="D64:E64"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="D48:P48"/>
+    <mergeCell ref="L19:O19"/>
+    <mergeCell ref="L35:P35"/>
+    <mergeCell ref="L20:O20"/>
+    <mergeCell ref="I82:L82"/>
+    <mergeCell ref="N54:O54"/>
+    <mergeCell ref="E84:M84"/>
+    <mergeCell ref="E75:P75"/>
+    <mergeCell ref="N57:O57"/>
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="D60:P60"/>
+    <mergeCell ref="L21:O21"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="L13:O13"/>
+    <mergeCell ref="O99:P104"/>
+    <mergeCell ref="N56:O56"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="E55:J55"/>
+    <mergeCell ref="E98:M98"/>
+    <mergeCell ref="E52:J52"/>
+    <mergeCell ref="L26:O26"/>
+    <mergeCell ref="E71:P71"/>
+    <mergeCell ref="O90:P90"/>
+    <mergeCell ref="E88:M88"/>
+    <mergeCell ref="O85:P88"/>
+    <mergeCell ref="O84:P84"/>
+    <mergeCell ref="O91:P96"/>
+    <mergeCell ref="E97:M97"/>
+    <mergeCell ref="L24:P24"/>
+    <mergeCell ref="D32:I32"/>
+    <mergeCell ref="D41:I41"/>
+    <mergeCell ref="O98:P98"/>
+    <mergeCell ref="D68:P68"/>
+    <mergeCell ref="N53:O53"/>
+    <mergeCell ref="E86:M86"/>
+    <mergeCell ref="E95:M95"/>
+    <mergeCell ref="D122:F122"/>
+    <mergeCell ref="E89:M89"/>
+    <mergeCell ref="N58:O58"/>
+    <mergeCell ref="L32:O32"/>
+    <mergeCell ref="D121:F121"/>
+    <mergeCell ref="D81:P81"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="D38:I38"/>
+    <mergeCell ref="E53:J53"/>
+    <mergeCell ref="E96:M96"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="D115:F115"/>
+    <mergeCell ref="E50:J50"/>
+    <mergeCell ref="O62:P64"/>
+    <mergeCell ref="L33:O33"/>
+    <mergeCell ref="E106:M106"/>
+    <mergeCell ref="E103:M103"/>
+    <mergeCell ref="E94:M94"/>
+    <mergeCell ref="L22:O22"/>
+    <mergeCell ref="D63:E63"/>
+    <mergeCell ref="L29:P29"/>
+    <mergeCell ref="D29:I29"/>
+    <mergeCell ref="E83:M83"/>
+    <mergeCell ref="E91:M91"/>
+    <mergeCell ref="L15:O15"/>
+    <mergeCell ref="F13:J13"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="F15:J15"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="L12:O12"/>
+    <mergeCell ref="F14:J14"/>
+    <mergeCell ref="F12:J12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="L4:N5"/>
+    <mergeCell ref="L14:O14"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="D13:E13"/>
     <mergeCell ref="O122:P122"/>
     <mergeCell ref="D46:I46"/>
     <mergeCell ref="D24:H24"/>
@@ -5216,155 +5371,10 @@
     <mergeCell ref="D30:I30"/>
     <mergeCell ref="D39:I39"/>
     <mergeCell ref="L37:O37"/>
-    <mergeCell ref="L15:O15"/>
-    <mergeCell ref="F13:J13"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="F15:J15"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="L12:O12"/>
-    <mergeCell ref="F14:J14"/>
-    <mergeCell ref="F12:J12"/>
-    <mergeCell ref="D122:F122"/>
-    <mergeCell ref="E89:M89"/>
-    <mergeCell ref="N58:O58"/>
-    <mergeCell ref="L32:O32"/>
-    <mergeCell ref="D121:F121"/>
-    <mergeCell ref="D81:P81"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="D38:I38"/>
-    <mergeCell ref="E53:J53"/>
-    <mergeCell ref="E96:M96"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="D115:F115"/>
-    <mergeCell ref="E50:J50"/>
-    <mergeCell ref="O62:P64"/>
-    <mergeCell ref="L33:O33"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="E106:M106"/>
-    <mergeCell ref="E103:M103"/>
-    <mergeCell ref="E94:M94"/>
-    <mergeCell ref="L22:O22"/>
-    <mergeCell ref="D63:E63"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="L13:O13"/>
-    <mergeCell ref="O99:P104"/>
-    <mergeCell ref="N56:O56"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="E55:J55"/>
-    <mergeCell ref="E98:M98"/>
-    <mergeCell ref="E52:J52"/>
-    <mergeCell ref="L26:O26"/>
-    <mergeCell ref="E71:P71"/>
-    <mergeCell ref="O90:P90"/>
-    <mergeCell ref="E88:M88"/>
-    <mergeCell ref="O85:P88"/>
-    <mergeCell ref="O84:P84"/>
-    <mergeCell ref="O91:P96"/>
-    <mergeCell ref="E97:M97"/>
-    <mergeCell ref="L24:P24"/>
-    <mergeCell ref="D32:I32"/>
-    <mergeCell ref="D41:I41"/>
-    <mergeCell ref="O98:P98"/>
-    <mergeCell ref="D68:P68"/>
-    <mergeCell ref="N53:O53"/>
-    <mergeCell ref="E86:M86"/>
-    <mergeCell ref="E95:M95"/>
-    <mergeCell ref="L29:P29"/>
-    <mergeCell ref="D29:I29"/>
-    <mergeCell ref="E83:M83"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="D48:P48"/>
-    <mergeCell ref="L19:O19"/>
-    <mergeCell ref="L35:P35"/>
-    <mergeCell ref="L20:O20"/>
-    <mergeCell ref="I82:L82"/>
-    <mergeCell ref="N54:O54"/>
-    <mergeCell ref="E84:M84"/>
-    <mergeCell ref="E75:P75"/>
-    <mergeCell ref="N57:O57"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="D60:P60"/>
-    <mergeCell ref="E91:M91"/>
-    <mergeCell ref="E85:M85"/>
-    <mergeCell ref="E100:M100"/>
-    <mergeCell ref="E78:P78"/>
-    <mergeCell ref="I112:K112"/>
-    <mergeCell ref="E110:M110"/>
-    <mergeCell ref="L16:O16"/>
-    <mergeCell ref="L18:P18"/>
-    <mergeCell ref="E70:P70"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="D42:I42"/>
-    <mergeCell ref="E72:P72"/>
-    <mergeCell ref="K62:M62"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="D35:I35"/>
-    <mergeCell ref="D44:I44"/>
-    <mergeCell ref="D27:J27"/>
-    <mergeCell ref="D34:I34"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="L30:O30"/>
-    <mergeCell ref="L39:O39"/>
-    <mergeCell ref="L4:N5"/>
-    <mergeCell ref="L14:O14"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="D64:E64"/>
-    <mergeCell ref="H122:J122"/>
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="L46:P46"/>
-    <mergeCell ref="D45:I45"/>
-    <mergeCell ref="D23:H23"/>
-    <mergeCell ref="L38:O38"/>
-    <mergeCell ref="E51:J51"/>
-    <mergeCell ref="L31:O31"/>
-    <mergeCell ref="L40:O40"/>
-    <mergeCell ref="N50:O50"/>
-    <mergeCell ref="L21:O21"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="K63:M64"/>
-    <mergeCell ref="H115:J115"/>
-    <mergeCell ref="N51:O51"/>
-    <mergeCell ref="D113:P113"/>
-    <mergeCell ref="E90:M90"/>
-    <mergeCell ref="E77:P77"/>
-    <mergeCell ref="E105:M105"/>
-    <mergeCell ref="L27:O27"/>
-    <mergeCell ref="E99:M99"/>
-    <mergeCell ref="D43:I43"/>
-    <mergeCell ref="L36:O36"/>
-    <mergeCell ref="D26:J26"/>
-    <mergeCell ref="L122:M122"/>
-    <mergeCell ref="E102:M102"/>
-    <mergeCell ref="D62:E62"/>
-    <mergeCell ref="I76:L76"/>
-    <mergeCell ref="O110:P110"/>
-    <mergeCell ref="E104:M104"/>
-    <mergeCell ref="E49:J49"/>
-    <mergeCell ref="L121:M121"/>
-    <mergeCell ref="O65:P65"/>
-    <mergeCell ref="E92:M92"/>
-    <mergeCell ref="O115:P115"/>
-    <mergeCell ref="N55:O55"/>
-    <mergeCell ref="E107:M107"/>
-    <mergeCell ref="E108:M108"/>
-    <mergeCell ref="L115:M115"/>
-    <mergeCell ref="E109:M109"/>
-    <mergeCell ref="E93:M93"/>
-    <mergeCell ref="E101:M101"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="50" fitToHeight="0" orientation="portrait" horizontalDpi="4294967293"/>
+  <pageSetup scale="50" fitToHeight="0" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
   <headerFooter>
     <oddFooter>&amp;CPágina &amp;P de &amp;N</oddFooter>
   </headerFooter>
@@ -5372,16 +5382,16 @@
     <brk id="46" min="1" max="17" man="1"/>
     <brk id="79" min="1" max="17" man="1"/>
   </rowBreaks>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:K19"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="14.45"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="2" spans="2:11">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B2" s="109"/>
       <c r="C2" s="109"/>
       <c r="D2" s="109"/>
@@ -5393,7 +5403,7 @@
       <c r="J2" s="109"/>
       <c r="K2" s="109"/>
     </row>
-    <row r="3" spans="2:11">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B3" s="109"/>
       <c r="C3" s="109"/>
       <c r="D3" s="109"/>
@@ -5405,7 +5415,7 @@
       <c r="J3" s="109"/>
       <c r="K3" s="109"/>
     </row>
-    <row r="4" spans="2:11">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B4" s="109"/>
       <c r="C4" s="109"/>
       <c r="D4" s="109"/>
@@ -5417,7 +5427,7 @@
       <c r="J4" s="109"/>
       <c r="K4" s="109"/>
     </row>
-    <row r="5" spans="2:11">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B5" s="109"/>
       <c r="C5" s="109"/>
       <c r="D5" s="109"/>
@@ -5429,7 +5439,7 @@
       <c r="J5" s="109"/>
       <c r="K5" s="109"/>
     </row>
-    <row r="6" spans="2:11">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B6" s="109"/>
       <c r="C6" s="109"/>
       <c r="D6" s="109"/>
@@ -5441,7 +5451,7 @@
       <c r="J6" s="109"/>
       <c r="K6" s="109"/>
     </row>
-    <row r="7" spans="2:11">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B7" s="109"/>
       <c r="C7" s="109"/>
       <c r="D7" s="109"/>
@@ -5453,7 +5463,7 @@
       <c r="J7" s="109"/>
       <c r="K7" s="109"/>
     </row>
-    <row r="8" spans="2:11">
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B8" s="109"/>
       <c r="C8" s="109"/>
       <c r="D8" s="109"/>
@@ -5465,7 +5475,7 @@
       <c r="J8" s="109"/>
       <c r="K8" s="109"/>
     </row>
-    <row r="9" spans="2:11">
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B9" s="109"/>
       <c r="C9" s="109"/>
       <c r="D9" s="109"/>
@@ -5477,7 +5487,7 @@
       <c r="J9" s="109"/>
       <c r="K9" s="109"/>
     </row>
-    <row r="10" spans="2:11">
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B10" s="109"/>
       <c r="C10" s="109"/>
       <c r="D10" s="109"/>
@@ -5489,7 +5499,7 @@
       <c r="J10" s="109"/>
       <c r="K10" s="109"/>
     </row>
-    <row r="11" spans="2:11">
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B11" s="109"/>
       <c r="C11" s="109"/>
       <c r="D11" s="109"/>
@@ -5501,7 +5511,7 @@
       <c r="J11" s="109"/>
       <c r="K11" s="109"/>
     </row>
-    <row r="12" spans="2:11">
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B12" s="109"/>
       <c r="C12" s="109"/>
       <c r="D12" s="109"/>
@@ -5513,7 +5523,7 @@
       <c r="J12" s="109"/>
       <c r="K12" s="109"/>
     </row>
-    <row r="13" spans="2:11">
+    <row r="13" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B13" s="109"/>
       <c r="C13" s="109"/>
       <c r="D13" s="109"/>
@@ -5525,7 +5535,7 @@
       <c r="J13" s="109"/>
       <c r="K13" s="109"/>
     </row>
-    <row r="14" spans="2:11">
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B14" s="109"/>
       <c r="C14" s="109"/>
       <c r="D14" s="109"/>
@@ -5537,7 +5547,7 @@
       <c r="J14" s="109"/>
       <c r="K14" s="109"/>
     </row>
-    <row r="15" spans="2:11">
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B15" s="109"/>
       <c r="C15" s="109"/>
       <c r="D15" s="109"/>
@@ -5549,7 +5559,7 @@
       <c r="J15" s="109"/>
       <c r="K15" s="109"/>
     </row>
-    <row r="16" spans="2:11">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B16" s="109"/>
       <c r="C16" s="109"/>
       <c r="D16" s="109"/>
@@ -5561,7 +5571,7 @@
       <c r="J16" s="109"/>
       <c r="K16" s="109"/>
     </row>
-    <row r="17" spans="2:11">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B17" s="109"/>
       <c r="C17" s="109"/>
       <c r="D17" s="109"/>
@@ -5573,7 +5583,7 @@
       <c r="J17" s="109"/>
       <c r="K17" s="109"/>
     </row>
-    <row r="18" spans="2:11">
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B18" s="109"/>
       <c r="C18" s="109"/>
       <c r="D18" s="109"/>
@@ -5585,7 +5595,7 @@
       <c r="J18" s="109"/>
       <c r="K18" s="109"/>
     </row>
-    <row r="19" spans="2:11">
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B19" s="109"/>
       <c r="C19" s="109"/>
       <c r="D19" s="109"/>

--- a/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
+++ b/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xoi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{98105D56-1CB3-4410-A731-5F58A06E101B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B8AF3C9-A55E-40B2-8E03-0099C936F370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3956,7 +3956,7 @@
       <c r="V61" s="36"/>
       <c r="W61" s="36"/>
     </row>
-    <row r="62" spans="2:23" ht="120" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="2:23" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="78"/>
       <c r="C62" s="78"/>
       <c r="D62" s="253" t="s">

--- a/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
+++ b/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xoi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{528F35A0-4B03-4CD1-A094-EB7E96FF532D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D42E797-2BFC-4B9E-B4DD-0C07E6480C88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
     <definedName name="AGUA">#REF!</definedName>
     <definedName name="ANTICIPO" localSheetId="0">#REF!</definedName>
     <definedName name="ANTICIPO">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'C-9-12'!$B$2:$R$127</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'C-9-12'!$B$2:$R$129</definedName>
     <definedName name="AZULEJO">#REF!</definedName>
     <definedName name="BASE">#REF!</definedName>
     <definedName name="BASE1">#REF!</definedName>
@@ -109,7 +109,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="131">
   <si>
     <t>PUNTO DE ACTA DE CONTRATO</t>
   </si>
@@ -436,9 +436,6 @@
   </si>
   <si>
     <t>{{TRABAJOS_PREVIOS}}</t>
-  </si>
-  <si>
-    <t>SERVICIOS BÁSICOS NECESARIOS PARA TRABAJAR</t>
   </si>
   <si>
     <t>SERVICIOS BASICOS NECESARIOS PARA TRABAJAR</t>
@@ -514,7 +511,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="_-&quot;Q&quot;* #,##0.00_-;\-&quot;Q&quot;* #,##0.00_-;_-&quot;Q&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="32" x14ac:knownFonts="1">
+  <fonts count="33" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -652,12 +649,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FFE05900"/>
-      <name val="Open Sans"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
       <color theme="0"/>
@@ -725,8 +716,22 @@
       <name val="Open Sans"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -777,17 +782,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE67E22"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="58">
+  <borders count="65">
     <border>
       <left/>
       <right/>
@@ -802,32 +802,6 @@
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0"/>
-      </right>
-      <top style="thin">
-        <color theme="0"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1422,12 +1396,111 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color theme="2" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="2" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="274">
+  <cellXfs count="297">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
@@ -1440,15 +1513,15 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="9" fontId="11" fillId="5" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="9" fontId="11" fillId="5" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1460,35 +1533,35 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="9" fontId="10" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="9" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
@@ -1496,7 +1569,7 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1504,15 +1577,15 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="9" fontId="10" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="5" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="9" fontId="10" fillId="5" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="5" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1524,7 +1597,7 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1532,7 +1605,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="5" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="2" fillId="5" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1544,7 +1617,7 @@
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="2" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="2" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1552,7 +1625,7 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="2" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="2" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1568,27 +1641,27 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -1641,19 +1714,19 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1665,19 +1738,19 @@
     <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1689,7 +1762,7 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1707,13 +1780,13 @@
     <xf numFmtId="14" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1722,13 +1795,13 @@
     <xf numFmtId="9" fontId="10" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="10" fillId="5" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="9" fontId="10" fillId="2" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="2" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1737,7 +1810,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1749,7 +1822,7 @@
     <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1759,556 +1832,641 @@
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="20" fillId="7" borderId="36" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="20" fillId="7" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="21" fillId="5" borderId="46" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="25" fillId="9" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="9" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="25" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="14" fontId="23" fillId="7" borderId="40" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="22" fillId="7" borderId="38" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="39" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="32" fillId="4" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="37" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="37" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="5" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="44" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="10" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="49" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="46" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2736,7 +2894,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:W128"/>
+  <dimension ref="B2:W130"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.109375" style="1" customWidth="1"/>
@@ -2785,19 +2943,19 @@
       <c r="C3" s="48"/>
       <c r="D3" s="49"/>
       <c r="E3" s="48"/>
-      <c r="F3" s="139" t="s">
+      <c r="F3" s="210" t="s">
         <v>0</v>
       </c>
-      <c r="G3" s="121"/>
-      <c r="H3" s="121"/>
-      <c r="I3" s="121"/>
-      <c r="J3" s="121"/>
+      <c r="G3" s="142"/>
+      <c r="H3" s="142"/>
+      <c r="I3" s="142"/>
+      <c r="J3" s="142"/>
       <c r="K3" s="52"/>
-      <c r="L3" s="139" t="s">
+      <c r="L3" s="210" t="s">
         <v>1</v>
       </c>
-      <c r="M3" s="121"/>
-      <c r="N3" s="121"/>
+      <c r="M3" s="142"/>
+      <c r="N3" s="142"/>
       <c r="O3" s="53"/>
       <c r="P3" s="52"/>
       <c r="Q3" s="48"/>
@@ -2814,11 +2972,11 @@
       <c r="I4" s="51"/>
       <c r="J4" s="52"/>
       <c r="K4" s="52"/>
-      <c r="L4" s="155" t="s">
+      <c r="L4" s="204" t="s">
         <v>2</v>
       </c>
-      <c r="M4" s="113"/>
-      <c r="N4" s="113"/>
+      <c r="M4" s="135"/>
+      <c r="N4" s="135"/>
       <c r="O4" s="53"/>
       <c r="P4" s="52"/>
       <c r="Q4" s="48"/>
@@ -2829,19 +2987,19 @@
       <c r="C5" s="48"/>
       <c r="D5" s="49"/>
       <c r="E5" s="48"/>
-      <c r="F5" s="147" t="s">
+      <c r="F5" s="226" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="148"/>
-      <c r="H5" s="143" t="s">
+      <c r="G5" s="227"/>
+      <c r="H5" s="224" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="144"/>
-      <c r="J5" s="144"/>
+      <c r="I5" s="225"/>
+      <c r="J5" s="225"/>
       <c r="K5" s="52"/>
-      <c r="L5" s="113"/>
-      <c r="M5" s="113"/>
-      <c r="N5" s="113"/>
+      <c r="L5" s="135"/>
+      <c r="M5" s="135"/>
+      <c r="N5" s="135"/>
       <c r="O5" s="53"/>
       <c r="P5" s="52"/>
       <c r="Q5" s="48"/>
@@ -2853,23 +3011,23 @@
       <c r="C6" s="48"/>
       <c r="D6" s="49"/>
       <c r="E6" s="48"/>
-      <c r="F6" s="156" t="s">
+      <c r="F6" s="207" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="121"/>
-      <c r="H6" s="143" t="s">
+      <c r="G6" s="142"/>
+      <c r="H6" s="224" t="s">
         <v>6</v>
       </c>
-      <c r="I6" s="144"/>
-      <c r="J6" s="144"/>
+      <c r="I6" s="225"/>
+      <c r="J6" s="225"/>
       <c r="K6" s="52"/>
-      <c r="L6" s="120" t="s">
+      <c r="L6" s="234" t="s">
         <v>7</v>
       </c>
-      <c r="M6" s="126" t="s">
+      <c r="M6" s="235" t="s">
         <v>8</v>
       </c>
-      <c r="N6" s="127"/>
+      <c r="N6" s="236"/>
       <c r="O6" s="53"/>
       <c r="P6" s="52"/>
       <c r="Q6" s="48"/>
@@ -2886,9 +3044,9 @@
       <c r="I7" s="57"/>
       <c r="J7" s="58"/>
       <c r="K7" s="52"/>
-      <c r="L7" s="121"/>
-      <c r="M7" s="128"/>
-      <c r="N7" s="128"/>
+      <c r="L7" s="142"/>
+      <c r="M7" s="237"/>
+      <c r="N7" s="237"/>
       <c r="O7" s="53"/>
       <c r="P7" s="52"/>
       <c r="Q7" s="48"/>
@@ -2899,19 +3057,19 @@
       <c r="C8" s="48"/>
       <c r="D8" s="49"/>
       <c r="E8" s="48"/>
-      <c r="F8" s="140" t="s">
+      <c r="F8" s="221" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="121"/>
-      <c r="H8" s="141" t="s">
+      <c r="G8" s="142"/>
+      <c r="H8" s="222" t="s">
         <v>10</v>
       </c>
-      <c r="I8" s="142"/>
-      <c r="J8" s="142"/>
+      <c r="I8" s="223"/>
+      <c r="J8" s="223"/>
       <c r="K8" s="52"/>
-      <c r="L8" s="121"/>
-      <c r="M8" s="129"/>
-      <c r="N8" s="129"/>
+      <c r="L8" s="142"/>
+      <c r="M8" s="238"/>
+      <c r="N8" s="238"/>
       <c r="O8" s="52"/>
       <c r="P8" s="52"/>
       <c r="Q8" s="48"/>
@@ -2978,24 +3136,24 @@
     <row r="12" spans="2:21" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="59"/>
       <c r="C12" s="59"/>
-      <c r="D12" s="153" t="s">
+      <c r="D12" s="230" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="154"/>
-      <c r="F12" s="151" t="s">
+      <c r="E12" s="231"/>
+      <c r="F12" s="228" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="152"/>
-      <c r="H12" s="152"/>
-      <c r="I12" s="152"/>
-      <c r="J12" s="152"/>
+      <c r="G12" s="229"/>
+      <c r="H12" s="229"/>
+      <c r="I12" s="229"/>
+      <c r="J12" s="229"/>
       <c r="K12" s="65"/>
-      <c r="L12" s="149" t="s">
+      <c r="L12" s="239" t="s">
         <v>13</v>
       </c>
-      <c r="M12" s="121"/>
-      <c r="N12" s="121"/>
-      <c r="O12" s="150"/>
+      <c r="M12" s="142"/>
+      <c r="N12" s="142"/>
+      <c r="O12" s="240"/>
       <c r="P12" s="98" t="s">
         <v>14</v>
       </c>
@@ -3005,24 +3163,24 @@
     <row r="13" spans="2:21" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="59"/>
       <c r="C13" s="59"/>
-      <c r="D13" s="145" t="s">
+      <c r="D13" s="208" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="146"/>
-      <c r="F13" s="138" t="s">
+      <c r="E13" s="209"/>
+      <c r="F13" s="219" t="s">
         <v>16</v>
       </c>
-      <c r="G13" s="119"/>
-      <c r="H13" s="119"/>
-      <c r="I13" s="119"/>
-      <c r="J13" s="119"/>
+      <c r="G13" s="220"/>
+      <c r="H13" s="220"/>
+      <c r="I13" s="220"/>
+      <c r="J13" s="220"/>
       <c r="K13" s="66"/>
-      <c r="L13" s="192" t="s">
+      <c r="L13" s="242" t="s">
         <v>17</v>
       </c>
-      <c r="M13" s="193"/>
-      <c r="N13" s="193"/>
-      <c r="O13" s="193"/>
+      <c r="M13" s="243"/>
+      <c r="N13" s="243"/>
+      <c r="O13" s="243"/>
       <c r="P13" s="6" t="s">
         <v>18</v>
       </c>
@@ -3032,24 +3190,24 @@
     <row r="14" spans="2:21" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="59"/>
       <c r="C14" s="59"/>
-      <c r="D14" s="145" t="s">
+      <c r="D14" s="208" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="146"/>
-      <c r="F14" s="138" t="s">
+      <c r="E14" s="209"/>
+      <c r="F14" s="219" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="119"/>
-      <c r="H14" s="119"/>
-      <c r="I14" s="119"/>
-      <c r="J14" s="119"/>
+      <c r="G14" s="220"/>
+      <c r="H14" s="220"/>
+      <c r="I14" s="220"/>
+      <c r="J14" s="220"/>
       <c r="K14" s="67"/>
-      <c r="L14" s="136" t="s">
+      <c r="L14" s="205" t="s">
         <v>21</v>
       </c>
-      <c r="M14" s="137"/>
-      <c r="N14" s="137"/>
-      <c r="O14" s="137"/>
+      <c r="M14" s="206"/>
+      <c r="N14" s="206"/>
+      <c r="O14" s="206"/>
       <c r="P14" s="6" t="s">
         <v>22</v>
       </c>
@@ -3059,24 +3217,24 @@
     <row r="15" spans="2:21" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="59"/>
       <c r="C15" s="59"/>
-      <c r="D15" s="145" t="s">
+      <c r="D15" s="208" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="146"/>
-      <c r="F15" s="138" t="s">
+      <c r="E15" s="209"/>
+      <c r="F15" s="219" t="s">
         <v>24</v>
       </c>
-      <c r="G15" s="119"/>
-      <c r="H15" s="119"/>
-      <c r="I15" s="119"/>
-      <c r="J15" s="119"/>
+      <c r="G15" s="220"/>
+      <c r="H15" s="220"/>
+      <c r="I15" s="220"/>
+      <c r="J15" s="220"/>
       <c r="K15" s="55"/>
-      <c r="L15" s="136" t="s">
+      <c r="L15" s="205" t="s">
         <v>25</v>
       </c>
-      <c r="M15" s="137"/>
-      <c r="N15" s="137"/>
-      <c r="O15" s="137"/>
+      <c r="M15" s="206"/>
+      <c r="N15" s="206"/>
+      <c r="O15" s="206"/>
       <c r="P15" s="6" t="s">
         <v>26</v>
       </c>
@@ -3086,24 +3244,24 @@
     <row r="16" spans="2:21" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="59"/>
       <c r="C16" s="59"/>
-      <c r="D16" s="191" t="s">
+      <c r="D16" s="241" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="172"/>
-      <c r="F16" s="118" t="s">
+      <c r="E16" s="217"/>
+      <c r="F16" s="233" t="s">
         <v>28</v>
       </c>
-      <c r="G16" s="119"/>
-      <c r="H16" s="119"/>
-      <c r="I16" s="119"/>
-      <c r="J16" s="119"/>
+      <c r="G16" s="220"/>
+      <c r="H16" s="220"/>
+      <c r="I16" s="220"/>
+      <c r="J16" s="220"/>
       <c r="K16" s="65"/>
-      <c r="L16" s="136" t="s">
+      <c r="L16" s="205" t="s">
         <v>29</v>
       </c>
-      <c r="M16" s="137"/>
-      <c r="N16" s="137"/>
-      <c r="O16" s="137"/>
+      <c r="M16" s="206"/>
+      <c r="N16" s="206"/>
+      <c r="O16" s="206"/>
       <c r="P16" s="6" t="s">
         <v>30</v>
       </c>
@@ -3117,8 +3275,8 @@
       <c r="E17" s="62"/>
       <c r="F17" s="63"/>
       <c r="G17" s="63"/>
-      <c r="H17" s="201"/>
-      <c r="I17" s="160"/>
+      <c r="H17" s="162"/>
+      <c r="I17" s="161"/>
       <c r="J17" s="64"/>
       <c r="K17" s="66"/>
       <c r="L17" s="55"/>
@@ -3131,23 +3289,23 @@
     <row r="18" spans="2:19" s="7" customFormat="1" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="75"/>
       <c r="C18" s="75"/>
-      <c r="D18" s="117" t="s">
+      <c r="D18" s="232" t="s">
         <v>31</v>
       </c>
-      <c r="E18" s="110"/>
-      <c r="F18" s="110"/>
-      <c r="G18" s="110"/>
-      <c r="H18" s="110"/>
-      <c r="I18" s="110"/>
-      <c r="J18" s="111"/>
+      <c r="E18" s="155"/>
+      <c r="F18" s="155"/>
+      <c r="G18" s="155"/>
+      <c r="H18" s="155"/>
+      <c r="I18" s="155"/>
+      <c r="J18" s="156"/>
       <c r="K18" s="73"/>
-      <c r="L18" s="199" t="s">
+      <c r="L18" s="200" t="s">
         <v>32</v>
       </c>
-      <c r="M18" s="110"/>
-      <c r="N18" s="110"/>
-      <c r="O18" s="110"/>
-      <c r="P18" s="111"/>
+      <c r="M18" s="155"/>
+      <c r="N18" s="155"/>
+      <c r="O18" s="155"/>
+      <c r="P18" s="156"/>
       <c r="Q18" s="55"/>
       <c r="R18" s="55"/>
       <c r="S18" s="1"/>
@@ -3155,24 +3313,24 @@
     <row r="19" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="74"/>
       <c r="C19" s="74"/>
-      <c r="D19" s="190" t="s">
+      <c r="D19" s="143" t="s">
         <v>33</v>
       </c>
-      <c r="E19" s="115"/>
-      <c r="F19" s="115"/>
-      <c r="G19" s="115"/>
-      <c r="H19" s="116"/>
-      <c r="I19" s="161" t="s">
+      <c r="E19" s="144"/>
+      <c r="F19" s="144"/>
+      <c r="G19" s="144"/>
+      <c r="H19" s="145"/>
+      <c r="I19" s="152" t="s">
         <v>34</v>
       </c>
-      <c r="J19" s="115"/>
+      <c r="J19" s="144"/>
       <c r="K19" s="55"/>
-      <c r="L19" s="109" t="s">
+      <c r="L19" s="154" t="s">
         <v>17</v>
       </c>
-      <c r="M19" s="110"/>
-      <c r="N19" s="110"/>
-      <c r="O19" s="111"/>
+      <c r="M19" s="155"/>
+      <c r="N19" s="155"/>
+      <c r="O19" s="156"/>
       <c r="P19" s="84" t="s">
         <v>35</v>
       </c>
@@ -3182,24 +3340,24 @@
     <row r="20" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="74"/>
       <c r="C20" s="74"/>
-      <c r="D20" s="114" t="s">
+      <c r="D20" s="174" t="s">
         <v>36</v>
       </c>
-      <c r="E20" s="115"/>
-      <c r="F20" s="115"/>
-      <c r="G20" s="115"/>
-      <c r="H20" s="116"/>
-      <c r="I20" s="123" t="s">
+      <c r="E20" s="144"/>
+      <c r="F20" s="144"/>
+      <c r="G20" s="144"/>
+      <c r="H20" s="145"/>
+      <c r="I20" s="164" t="s">
         <v>34</v>
       </c>
-      <c r="J20" s="115"/>
+      <c r="J20" s="144"/>
       <c r="K20" s="55"/>
-      <c r="L20" s="198" t="s">
+      <c r="L20" s="179" t="s">
         <v>21</v>
       </c>
-      <c r="M20" s="110"/>
-      <c r="N20" s="110"/>
-      <c r="O20" s="111"/>
+      <c r="M20" s="155"/>
+      <c r="N20" s="155"/>
+      <c r="O20" s="156"/>
       <c r="P20" s="85" t="s">
         <v>37</v>
       </c>
@@ -3209,24 +3367,24 @@
     <row r="21" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="74"/>
       <c r="C21" s="74"/>
-      <c r="D21" s="190" t="s">
+      <c r="D21" s="143" t="s">
         <v>38</v>
       </c>
-      <c r="E21" s="115"/>
-      <c r="F21" s="115"/>
-      <c r="G21" s="115"/>
-      <c r="H21" s="116"/>
-      <c r="I21" s="161" t="s">
+      <c r="E21" s="144"/>
+      <c r="F21" s="144"/>
+      <c r="G21" s="144"/>
+      <c r="H21" s="145"/>
+      <c r="I21" s="152" t="s">
         <v>39</v>
       </c>
-      <c r="J21" s="115"/>
+      <c r="J21" s="144"/>
       <c r="K21" s="55"/>
-      <c r="L21" s="109" t="s">
+      <c r="L21" s="154" t="s">
         <v>25</v>
       </c>
-      <c r="M21" s="110"/>
-      <c r="N21" s="110"/>
-      <c r="O21" s="111"/>
+      <c r="M21" s="155"/>
+      <c r="N21" s="155"/>
+      <c r="O21" s="156"/>
       <c r="P21" s="84" t="s">
         <v>37</v>
       </c>
@@ -3236,24 +3394,24 @@
     <row r="22" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="74"/>
       <c r="C22" s="74"/>
-      <c r="D22" s="114" t="s">
+      <c r="D22" s="174" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="115"/>
-      <c r="F22" s="115"/>
-      <c r="G22" s="115"/>
-      <c r="H22" s="116"/>
-      <c r="I22" s="123" t="s">
+      <c r="E22" s="144"/>
+      <c r="F22" s="144"/>
+      <c r="G22" s="144"/>
+      <c r="H22" s="145"/>
+      <c r="I22" s="164" t="s">
         <v>34</v>
       </c>
-      <c r="J22" s="115"/>
+      <c r="J22" s="144"/>
       <c r="K22" s="55"/>
-      <c r="L22" s="168" t="s">
+      <c r="L22" s="213" t="s">
         <v>29</v>
       </c>
-      <c r="M22" s="169"/>
-      <c r="N22" s="169"/>
-      <c r="O22" s="170"/>
+      <c r="M22" s="214"/>
+      <c r="N22" s="214"/>
+      <c r="O22" s="215"/>
       <c r="P22" s="86" t="s">
         <v>41</v>
       </c>
@@ -3263,17 +3421,17 @@
     <row r="23" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="74"/>
       <c r="C23" s="74"/>
-      <c r="D23" s="190" t="s">
+      <c r="D23" s="143" t="s">
         <v>42</v>
       </c>
-      <c r="E23" s="115"/>
-      <c r="F23" s="115"/>
-      <c r="G23" s="115"/>
-      <c r="H23" s="116"/>
-      <c r="I23" s="161" t="s">
+      <c r="E23" s="144"/>
+      <c r="F23" s="144"/>
+      <c r="G23" s="144"/>
+      <c r="H23" s="145"/>
+      <c r="I23" s="152" t="s">
         <v>43</v>
       </c>
-      <c r="J23" s="115"/>
+      <c r="J23" s="144"/>
       <c r="K23" s="55"/>
       <c r="L23" s="82"/>
       <c r="M23" s="82"/>
@@ -3286,49 +3444,49 @@
     <row r="24" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="74"/>
       <c r="C24" s="74"/>
-      <c r="D24" s="114" t="s">
+      <c r="D24" s="174" t="s">
         <v>44</v>
       </c>
-      <c r="E24" s="115"/>
-      <c r="F24" s="115"/>
-      <c r="G24" s="115"/>
-      <c r="H24" s="116"/>
-      <c r="I24" s="123" t="s">
+      <c r="E24" s="144"/>
+      <c r="F24" s="144"/>
+      <c r="G24" s="144"/>
+      <c r="H24" s="145"/>
+      <c r="I24" s="164" t="s">
         <v>45</v>
       </c>
-      <c r="J24" s="115"/>
+      <c r="J24" s="144"/>
       <c r="K24" s="55"/>
-      <c r="L24" s="199" t="s">
+      <c r="L24" s="200" t="s">
         <v>46</v>
       </c>
-      <c r="M24" s="110"/>
-      <c r="N24" s="110"/>
-      <c r="O24" s="110"/>
-      <c r="P24" s="111"/>
+      <c r="M24" s="155"/>
+      <c r="N24" s="155"/>
+      <c r="O24" s="155"/>
+      <c r="P24" s="156"/>
       <c r="Q24" s="55"/>
       <c r="R24" s="55"/>
     </row>
     <row r="25" spans="2:19" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="74"/>
       <c r="C25" s="74"/>
-      <c r="D25" s="190" t="s">
+      <c r="D25" s="143" t="s">
         <v>47</v>
       </c>
-      <c r="E25" s="115"/>
-      <c r="F25" s="115"/>
-      <c r="G25" s="115"/>
-      <c r="H25" s="116"/>
-      <c r="I25" s="161" t="s">
+      <c r="E25" s="144"/>
+      <c r="F25" s="144"/>
+      <c r="G25" s="144"/>
+      <c r="H25" s="145"/>
+      <c r="I25" s="152" t="s">
         <v>45</v>
       </c>
-      <c r="J25" s="115"/>
+      <c r="J25" s="144"/>
       <c r="K25" s="55"/>
-      <c r="L25" s="109" t="s">
+      <c r="L25" s="154" t="s">
         <v>48</v>
       </c>
-      <c r="M25" s="110"/>
-      <c r="N25" s="110"/>
-      <c r="O25" s="111"/>
+      <c r="M25" s="155"/>
+      <c r="N25" s="155"/>
+      <c r="O25" s="156"/>
       <c r="P25" s="84" t="s">
         <v>49</v>
       </c>
@@ -3338,22 +3496,22 @@
     <row r="26" spans="2:19" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B26" s="74"/>
       <c r="C26" s="74"/>
-      <c r="D26" s="215" t="s">
+      <c r="D26" s="160" t="s">
         <v>50</v>
       </c>
-      <c r="E26" s="110"/>
-      <c r="F26" s="110"/>
-      <c r="G26" s="110"/>
-      <c r="H26" s="110"/>
-      <c r="I26" s="110"/>
-      <c r="J26" s="110"/>
+      <c r="E26" s="155"/>
+      <c r="F26" s="155"/>
+      <c r="G26" s="155"/>
+      <c r="H26" s="155"/>
+      <c r="I26" s="155"/>
+      <c r="J26" s="155"/>
       <c r="K26" s="55"/>
-      <c r="L26" s="198" t="s">
+      <c r="L26" s="179" t="s">
         <v>51</v>
       </c>
-      <c r="M26" s="110"/>
-      <c r="N26" s="110"/>
-      <c r="O26" s="111"/>
+      <c r="M26" s="155"/>
+      <c r="N26" s="155"/>
+      <c r="O26" s="156"/>
       <c r="P26" s="85" t="s">
         <v>52</v>
       </c>
@@ -3363,20 +3521,20 @@
     <row r="27" spans="2:19" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="74"/>
       <c r="C27" s="74"/>
-      <c r="D27" s="203"/>
-      <c r="E27" s="204"/>
-      <c r="F27" s="204"/>
-      <c r="G27" s="204"/>
-      <c r="H27" s="204"/>
-      <c r="I27" s="204"/>
-      <c r="J27" s="204"/>
+      <c r="D27" s="171"/>
+      <c r="E27" s="172"/>
+      <c r="F27" s="172"/>
+      <c r="G27" s="172"/>
+      <c r="H27" s="172"/>
+      <c r="I27" s="172"/>
+      <c r="J27" s="172"/>
       <c r="K27" s="55"/>
-      <c r="L27" s="109" t="s">
+      <c r="L27" s="154" t="s">
         <v>53</v>
       </c>
-      <c r="M27" s="110"/>
-      <c r="N27" s="110"/>
-      <c r="O27" s="111"/>
+      <c r="M27" s="155"/>
+      <c r="N27" s="155"/>
+      <c r="O27" s="156"/>
       <c r="P27" s="84" t="s">
         <v>49</v>
       </c>
@@ -3405,49 +3563,49 @@
     <row r="29" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B29" s="74"/>
       <c r="C29" s="74"/>
-      <c r="D29" s="122" t="s">
+      <c r="D29" s="218" t="s">
         <v>54</v>
       </c>
-      <c r="E29" s="121"/>
-      <c r="F29" s="121"/>
-      <c r="G29" s="121"/>
-      <c r="H29" s="121"/>
-      <c r="I29" s="121"/>
+      <c r="E29" s="142"/>
+      <c r="F29" s="142"/>
+      <c r="G29" s="142"/>
+      <c r="H29" s="142"/>
+      <c r="I29" s="142"/>
       <c r="J29" s="87" t="s">
         <v>55</v>
       </c>
       <c r="K29" s="55"/>
-      <c r="L29" s="171" t="s">
+      <c r="L29" s="216" t="s">
         <v>56</v>
       </c>
-      <c r="M29" s="172"/>
-      <c r="N29" s="172"/>
-      <c r="O29" s="172"/>
-      <c r="P29" s="172"/>
+      <c r="M29" s="217"/>
+      <c r="N29" s="217"/>
+      <c r="O29" s="217"/>
+      <c r="P29" s="217"/>
       <c r="Q29" s="55"/>
       <c r="R29" s="55"/>
     </row>
     <row r="30" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B30" s="74"/>
       <c r="C30" s="74"/>
-      <c r="D30" s="130" t="s">
+      <c r="D30" s="168" t="s">
         <v>57</v>
       </c>
-      <c r="E30" s="131"/>
-      <c r="F30" s="131"/>
-      <c r="G30" s="131"/>
-      <c r="H30" s="131"/>
-      <c r="I30" s="132"/>
+      <c r="E30" s="169"/>
+      <c r="F30" s="169"/>
+      <c r="G30" s="169"/>
+      <c r="H30" s="169"/>
+      <c r="I30" s="170"/>
       <c r="J30" s="12" t="s">
         <v>58</v>
       </c>
       <c r="K30" s="55"/>
-      <c r="L30" s="157" t="s">
+      <c r="L30" s="173" t="s">
         <v>59</v>
       </c>
-      <c r="M30" s="115"/>
-      <c r="N30" s="115"/>
-      <c r="O30" s="158"/>
+      <c r="M30" s="144"/>
+      <c r="N30" s="144"/>
+      <c r="O30" s="148"/>
       <c r="P30" s="9" t="s">
         <v>60</v>
       </c>
@@ -3457,24 +3615,24 @@
     <row r="31" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B31" s="74"/>
       <c r="C31" s="74"/>
-      <c r="D31" s="133" t="s">
+      <c r="D31" s="138" t="s">
         <v>61</v>
       </c>
-      <c r="E31" s="134"/>
-      <c r="F31" s="134"/>
-      <c r="G31" s="134"/>
-      <c r="H31" s="134"/>
-      <c r="I31" s="135"/>
+      <c r="E31" s="139"/>
+      <c r="F31" s="139"/>
+      <c r="G31" s="139"/>
+      <c r="H31" s="139"/>
+      <c r="I31" s="140"/>
       <c r="J31" s="13" t="s">
         <v>58</v>
       </c>
       <c r="K31" s="55"/>
-      <c r="L31" s="210" t="s">
+      <c r="L31" s="147" t="s">
         <v>62</v>
       </c>
-      <c r="M31" s="115"/>
-      <c r="N31" s="115"/>
-      <c r="O31" s="158"/>
+      <c r="M31" s="144"/>
+      <c r="N31" s="144"/>
+      <c r="O31" s="148"/>
       <c r="P31" s="10" t="s">
         <v>63</v>
       </c>
@@ -3484,24 +3642,24 @@
     <row r="32" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B32" s="74"/>
       <c r="C32" s="74"/>
-      <c r="D32" s="177" t="s">
+      <c r="D32" s="163" t="s">
         <v>64</v>
       </c>
-      <c r="E32" s="134"/>
-      <c r="F32" s="134"/>
-      <c r="G32" s="134"/>
-      <c r="H32" s="134"/>
-      <c r="I32" s="135"/>
+      <c r="E32" s="139"/>
+      <c r="F32" s="139"/>
+      <c r="G32" s="139"/>
+      <c r="H32" s="139"/>
+      <c r="I32" s="140"/>
       <c r="J32" s="14" t="s">
         <v>58</v>
       </c>
       <c r="K32" s="55"/>
-      <c r="L32" s="157" t="s">
+      <c r="L32" s="173" t="s">
         <v>65</v>
       </c>
-      <c r="M32" s="115"/>
-      <c r="N32" s="115"/>
-      <c r="O32" s="158"/>
+      <c r="M32" s="144"/>
+      <c r="N32" s="144"/>
+      <c r="O32" s="148"/>
       <c r="P32" s="9" t="s">
         <v>66</v>
       </c>
@@ -3511,24 +3669,24 @@
     <row r="33" spans="2:20" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="74"/>
       <c r="C33" s="74"/>
-      <c r="D33" s="133" t="s">
+      <c r="D33" s="138" t="s">
         <v>67</v>
       </c>
-      <c r="E33" s="134"/>
-      <c r="F33" s="134"/>
-      <c r="G33" s="134"/>
-      <c r="H33" s="134"/>
-      <c r="I33" s="135"/>
+      <c r="E33" s="139"/>
+      <c r="F33" s="139"/>
+      <c r="G33" s="139"/>
+      <c r="H33" s="139"/>
+      <c r="I33" s="140"/>
       <c r="J33" s="13" t="s">
         <v>58</v>
       </c>
       <c r="K33" s="55"/>
-      <c r="L33" s="165" t="s">
+      <c r="L33" s="212" t="s">
         <v>68</v>
       </c>
-      <c r="M33" s="166"/>
-      <c r="N33" s="166"/>
-      <c r="O33" s="167"/>
+      <c r="M33" s="150"/>
+      <c r="N33" s="150"/>
+      <c r="O33" s="151"/>
       <c r="P33" s="11" t="s">
         <v>63</v>
       </c>
@@ -3538,14 +3696,14 @@
     <row r="34" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="74"/>
       <c r="C34" s="74"/>
-      <c r="D34" s="177" t="s">
+      <c r="D34" s="163" t="s">
         <v>69</v>
       </c>
-      <c r="E34" s="134"/>
-      <c r="F34" s="134"/>
-      <c r="G34" s="134"/>
-      <c r="H34" s="134"/>
-      <c r="I34" s="135"/>
+      <c r="E34" s="139"/>
+      <c r="F34" s="139"/>
+      <c r="G34" s="139"/>
+      <c r="H34" s="139"/>
+      <c r="I34" s="140"/>
       <c r="J34" s="14" t="s">
         <v>58</v>
       </c>
@@ -3561,25 +3719,25 @@
     <row r="35" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="74"/>
       <c r="C35" s="74"/>
-      <c r="D35" s="202" t="s">
+      <c r="D35" s="165" t="s">
         <v>70</v>
       </c>
-      <c r="E35" s="175"/>
-      <c r="F35" s="175"/>
-      <c r="G35" s="175"/>
-      <c r="H35" s="175"/>
-      <c r="I35" s="176"/>
+      <c r="E35" s="166"/>
+      <c r="F35" s="166"/>
+      <c r="G35" s="166"/>
+      <c r="H35" s="166"/>
+      <c r="I35" s="167"/>
       <c r="J35" s="18" t="s">
         <v>58</v>
       </c>
       <c r="K35" s="55"/>
-      <c r="L35" s="208" t="s">
+      <c r="L35" s="178" t="s">
         <v>71</v>
       </c>
-      <c r="M35" s="121"/>
-      <c r="N35" s="121"/>
-      <c r="O35" s="121"/>
-      <c r="P35" s="121"/>
+      <c r="M35" s="142"/>
+      <c r="N35" s="142"/>
+      <c r="O35" s="142"/>
+      <c r="P35" s="142"/>
       <c r="Q35" s="55"/>
       <c r="R35" s="55"/>
     </row>
@@ -3594,12 +3752,12 @@
       <c r="I36" s="19"/>
       <c r="J36" s="19"/>
       <c r="K36" s="55"/>
-      <c r="L36" s="212" t="s">
+      <c r="L36" s="157" t="s">
         <v>72</v>
       </c>
-      <c r="M36" s="213"/>
-      <c r="N36" s="213"/>
-      <c r="O36" s="214"/>
+      <c r="M36" s="158"/>
+      <c r="N36" s="158"/>
+      <c r="O36" s="159"/>
       <c r="P36" s="20" t="s">
         <v>73</v>
       </c>
@@ -3609,24 +3767,24 @@
     <row r="37" spans="2:20" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="74"/>
       <c r="C37" s="74"/>
-      <c r="D37" s="122" t="s">
+      <c r="D37" s="218" t="s">
         <v>74</v>
       </c>
-      <c r="E37" s="121"/>
-      <c r="F37" s="121"/>
-      <c r="G37" s="121"/>
-      <c r="H37" s="121"/>
-      <c r="I37" s="121"/>
+      <c r="E37" s="142"/>
+      <c r="F37" s="142"/>
+      <c r="G37" s="142"/>
+      <c r="H37" s="142"/>
+      <c r="I37" s="142"/>
       <c r="J37" s="87" t="s">
         <v>55</v>
       </c>
       <c r="K37" s="55"/>
-      <c r="L37" s="114" t="s">
+      <c r="L37" s="174" t="s">
         <v>75</v>
       </c>
-      <c r="M37" s="115"/>
-      <c r="N37" s="115"/>
-      <c r="O37" s="116"/>
+      <c r="M37" s="144"/>
+      <c r="N37" s="144"/>
+      <c r="O37" s="145"/>
       <c r="P37" s="10" t="s">
         <v>73</v>
       </c>
@@ -3636,24 +3794,24 @@
     <row r="38" spans="2:20" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B38" s="74"/>
       <c r="C38" s="74"/>
-      <c r="D38" s="130" t="s">
+      <c r="D38" s="168" t="s">
         <v>76</v>
       </c>
-      <c r="E38" s="131"/>
-      <c r="F38" s="131"/>
-      <c r="G38" s="131"/>
-      <c r="H38" s="131"/>
-      <c r="I38" s="132"/>
+      <c r="E38" s="169"/>
+      <c r="F38" s="169"/>
+      <c r="G38" s="169"/>
+      <c r="H38" s="169"/>
+      <c r="I38" s="170"/>
       <c r="J38" s="12" t="s">
         <v>58</v>
       </c>
       <c r="K38" s="55"/>
-      <c r="L38" s="190" t="s">
+      <c r="L38" s="143" t="s">
         <v>77</v>
       </c>
-      <c r="M38" s="115"/>
-      <c r="N38" s="115"/>
-      <c r="O38" s="116"/>
+      <c r="M38" s="144"/>
+      <c r="N38" s="144"/>
+      <c r="O38" s="145"/>
       <c r="P38" s="9" t="s">
         <v>73</v>
       </c>
@@ -3663,24 +3821,24 @@
     <row r="39" spans="2:20" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B39" s="74"/>
       <c r="C39" s="74"/>
-      <c r="D39" s="133" t="s">
+      <c r="D39" s="138" t="s">
         <v>78</v>
       </c>
-      <c r="E39" s="134"/>
-      <c r="F39" s="134"/>
-      <c r="G39" s="134"/>
-      <c r="H39" s="134"/>
-      <c r="I39" s="135"/>
+      <c r="E39" s="139"/>
+      <c r="F39" s="139"/>
+      <c r="G39" s="139"/>
+      <c r="H39" s="139"/>
+      <c r="I39" s="140"/>
       <c r="J39" s="13" t="s">
         <v>58</v>
       </c>
       <c r="K39" s="55"/>
-      <c r="L39" s="114" t="s">
+      <c r="L39" s="174" t="s">
         <v>79</v>
       </c>
-      <c r="M39" s="115"/>
-      <c r="N39" s="115"/>
-      <c r="O39" s="116"/>
+      <c r="M39" s="144"/>
+      <c r="N39" s="144"/>
+      <c r="O39" s="145"/>
       <c r="P39" s="10" t="s">
         <v>73</v>
       </c>
@@ -3690,24 +3848,24 @@
     <row r="40" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="74"/>
       <c r="C40" s="74"/>
-      <c r="D40" s="177" t="s">
+      <c r="D40" s="163" t="s">
         <v>80</v>
       </c>
-      <c r="E40" s="134"/>
-      <c r="F40" s="134"/>
-      <c r="G40" s="134"/>
-      <c r="H40" s="134"/>
-      <c r="I40" s="135"/>
+      <c r="E40" s="139"/>
+      <c r="F40" s="139"/>
+      <c r="G40" s="139"/>
+      <c r="H40" s="139"/>
+      <c r="I40" s="140"/>
       <c r="J40" s="14" t="s">
         <v>58</v>
       </c>
       <c r="K40" s="55"/>
-      <c r="L40" s="211" t="s">
+      <c r="L40" s="149" t="s">
         <v>81</v>
       </c>
-      <c r="M40" s="166"/>
-      <c r="N40" s="166"/>
-      <c r="O40" s="167"/>
+      <c r="M40" s="150"/>
+      <c r="N40" s="150"/>
+      <c r="O40" s="151"/>
       <c r="P40" s="21" t="s">
         <v>73</v>
       </c>
@@ -3717,14 +3875,14 @@
     <row r="41" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="74"/>
       <c r="C41" s="74"/>
-      <c r="D41" s="133" t="s">
+      <c r="D41" s="138" t="s">
         <v>82</v>
       </c>
-      <c r="E41" s="134"/>
-      <c r="F41" s="134"/>
-      <c r="G41" s="134"/>
-      <c r="H41" s="134"/>
-      <c r="I41" s="135"/>
+      <c r="E41" s="139"/>
+      <c r="F41" s="139"/>
+      <c r="G41" s="139"/>
+      <c r="H41" s="139"/>
+      <c r="I41" s="140"/>
       <c r="J41" s="13" t="s">
         <v>58</v>
       </c>
@@ -3740,14 +3898,14 @@
     <row r="42" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="74"/>
       <c r="C42" s="74"/>
-      <c r="D42" s="177" t="s">
+      <c r="D42" s="163" t="s">
         <v>83</v>
       </c>
-      <c r="E42" s="134"/>
-      <c r="F42" s="134"/>
-      <c r="G42" s="134"/>
-      <c r="H42" s="134"/>
-      <c r="I42" s="135"/>
+      <c r="E42" s="139"/>
+      <c r="F42" s="139"/>
+      <c r="G42" s="139"/>
+      <c r="H42" s="139"/>
+      <c r="I42" s="140"/>
       <c r="J42" s="14" t="s">
         <v>58</v>
       </c>
@@ -3763,14 +3921,14 @@
     <row r="43" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="74"/>
       <c r="C43" s="74"/>
-      <c r="D43" s="133" t="s">
+      <c r="D43" s="138" t="s">
         <v>84</v>
       </c>
-      <c r="E43" s="134"/>
-      <c r="F43" s="134"/>
-      <c r="G43" s="134"/>
-      <c r="H43" s="134"/>
-      <c r="I43" s="135"/>
+      <c r="E43" s="139"/>
+      <c r="F43" s="139"/>
+      <c r="G43" s="139"/>
+      <c r="H43" s="139"/>
+      <c r="I43" s="140"/>
       <c r="J43" s="13" t="s">
         <v>58</v>
       </c>
@@ -3786,14 +3944,14 @@
     <row r="44" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="74"/>
       <c r="C44" s="74"/>
-      <c r="D44" s="130" t="s">
+      <c r="D44" s="168" t="s">
         <v>85</v>
       </c>
-      <c r="E44" s="131"/>
-      <c r="F44" s="131"/>
-      <c r="G44" s="131"/>
-      <c r="H44" s="131"/>
-      <c r="I44" s="132"/>
+      <c r="E44" s="169"/>
+      <c r="F44" s="169"/>
+      <c r="G44" s="169"/>
+      <c r="H44" s="169"/>
+      <c r="I44" s="170"/>
       <c r="J44" s="12" t="s">
         <v>58</v>
       </c>
@@ -3809,14 +3967,14 @@
     <row r="45" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="74"/>
       <c r="C45" s="74"/>
-      <c r="D45" s="133" t="s">
+      <c r="D45" s="138" t="s">
         <v>86</v>
       </c>
-      <c r="E45" s="134"/>
-      <c r="F45" s="134"/>
-      <c r="G45" s="134"/>
-      <c r="H45" s="134"/>
-      <c r="I45" s="135"/>
+      <c r="E45" s="139"/>
+      <c r="F45" s="139"/>
+      <c r="G45" s="139"/>
+      <c r="H45" s="139"/>
+      <c r="I45" s="140"/>
       <c r="J45" s="13" t="s">
         <v>58</v>
       </c>
@@ -3832,25 +3990,25 @@
     <row r="46" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="74"/>
       <c r="C46" s="74"/>
-      <c r="D46" s="174" t="s">
+      <c r="D46" s="199" t="s">
         <v>87</v>
       </c>
-      <c r="E46" s="175"/>
-      <c r="F46" s="175"/>
-      <c r="G46" s="175"/>
-      <c r="H46" s="175"/>
-      <c r="I46" s="176"/>
+      <c r="E46" s="166"/>
+      <c r="F46" s="166"/>
+      <c r="G46" s="166"/>
+      <c r="H46" s="166"/>
+      <c r="I46" s="167"/>
       <c r="J46" s="22" t="s">
         <v>58</v>
       </c>
       <c r="K46" s="55"/>
-      <c r="L46" s="209" t="s">
+      <c r="L46" s="141" t="s">
         <v>88</v>
       </c>
-      <c r="M46" s="121"/>
-      <c r="N46" s="121"/>
-      <c r="O46" s="121"/>
-      <c r="P46" s="121"/>
+      <c r="M46" s="142"/>
+      <c r="N46" s="142"/>
+      <c r="O46" s="142"/>
+      <c r="P46" s="142"/>
       <c r="Q46" s="55"/>
       <c r="R46" s="55"/>
     </row>
@@ -3876,21 +4034,21 @@
     <row r="48" spans="2:20" ht="21.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B48" s="74"/>
       <c r="C48" s="76"/>
-      <c r="D48" s="205" t="s">
+      <c r="D48" s="175" t="s">
         <v>89</v>
       </c>
-      <c r="E48" s="206"/>
-      <c r="F48" s="206"/>
-      <c r="G48" s="206"/>
-      <c r="H48" s="206"/>
-      <c r="I48" s="206"/>
-      <c r="J48" s="206"/>
-      <c r="K48" s="206"/>
-      <c r="L48" s="206"/>
-      <c r="M48" s="206"/>
-      <c r="N48" s="206"/>
-      <c r="O48" s="206"/>
-      <c r="P48" s="207"/>
+      <c r="E48" s="176"/>
+      <c r="F48" s="176"/>
+      <c r="G48" s="176"/>
+      <c r="H48" s="176"/>
+      <c r="I48" s="176"/>
+      <c r="J48" s="176"/>
+      <c r="K48" s="176"/>
+      <c r="L48" s="176"/>
+      <c r="M48" s="176"/>
+      <c r="N48" s="176"/>
+      <c r="O48" s="176"/>
+      <c r="P48" s="177"/>
       <c r="Q48" s="55"/>
       <c r="R48" s="55"/>
       <c r="T48" s="97" t="s">
@@ -3903,14 +4061,14 @@
       <c r="D49" s="91" t="s">
         <v>91</v>
       </c>
-      <c r="E49" s="178" t="s">
+      <c r="E49" s="125" t="s">
         <v>92</v>
       </c>
-      <c r="F49" s="183"/>
-      <c r="G49" s="183"/>
-      <c r="H49" s="183"/>
-      <c r="I49" s="183"/>
-      <c r="J49" s="183"/>
+      <c r="F49" s="126"/>
+      <c r="G49" s="126"/>
+      <c r="H49" s="126"/>
+      <c r="I49" s="126"/>
+      <c r="J49" s="126"/>
       <c r="K49" s="91" t="s">
         <v>93</v>
       </c>
@@ -3920,10 +4078,10 @@
       <c r="M49" s="91" t="s">
         <v>95</v>
       </c>
-      <c r="N49" s="178" t="s">
+      <c r="N49" s="125" t="s">
         <v>96</v>
       </c>
-      <c r="O49" s="183"/>
+      <c r="O49" s="126"/>
       <c r="P49" s="91" t="s">
         <v>97</v>
       </c>
@@ -3935,101 +4093,101 @@
       <c r="B50" s="8"/>
       <c r="C50" s="23"/>
       <c r="D50" s="25"/>
-      <c r="E50" s="124"/>
-      <c r="F50" s="113"/>
-      <c r="G50" s="113"/>
-      <c r="H50" s="113"/>
-      <c r="I50" s="113"/>
-      <c r="J50" s="125"/>
+      <c r="E50" s="197"/>
+      <c r="F50" s="135"/>
+      <c r="G50" s="135"/>
+      <c r="H50" s="135"/>
+      <c r="I50" s="135"/>
+      <c r="J50" s="132"/>
       <c r="K50" s="26"/>
       <c r="L50" s="27"/>
       <c r="M50" s="28"/>
-      <c r="N50" s="200"/>
-      <c r="O50" s="125"/>
+      <c r="N50" s="136"/>
+      <c r="O50" s="132"/>
       <c r="P50" s="29"/>
     </row>
     <row r="51" spans="2:23" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="8"/>
       <c r="C51" s="23"/>
       <c r="D51" s="30"/>
-      <c r="E51" s="162"/>
-      <c r="F51" s="113"/>
-      <c r="G51" s="113"/>
-      <c r="H51" s="113"/>
-      <c r="I51" s="113"/>
-      <c r="J51" s="125"/>
+      <c r="E51" s="146"/>
+      <c r="F51" s="135"/>
+      <c r="G51" s="135"/>
+      <c r="H51" s="135"/>
+      <c r="I51" s="135"/>
+      <c r="J51" s="132"/>
       <c r="K51" s="31"/>
       <c r="L51" s="32"/>
       <c r="M51" s="33"/>
-      <c r="N51" s="179"/>
-      <c r="O51" s="125"/>
+      <c r="N51" s="131"/>
+      <c r="O51" s="132"/>
       <c r="P51" s="34"/>
     </row>
     <row r="52" spans="2:23" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="8"/>
       <c r="C52" s="23"/>
       <c r="D52" s="25"/>
-      <c r="E52" s="124"/>
-      <c r="F52" s="113"/>
-      <c r="G52" s="113"/>
-      <c r="H52" s="113"/>
-      <c r="I52" s="113"/>
-      <c r="J52" s="125"/>
+      <c r="E52" s="197"/>
+      <c r="F52" s="135"/>
+      <c r="G52" s="135"/>
+      <c r="H52" s="135"/>
+      <c r="I52" s="135"/>
+      <c r="J52" s="132"/>
       <c r="K52" s="26"/>
       <c r="L52" s="27"/>
       <c r="M52" s="28"/>
-      <c r="N52" s="200"/>
-      <c r="O52" s="125"/>
+      <c r="N52" s="136"/>
+      <c r="O52" s="132"/>
       <c r="P52" s="29"/>
     </row>
     <row r="53" spans="2:23" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="8"/>
       <c r="C53" s="23"/>
       <c r="D53" s="30"/>
-      <c r="E53" s="162"/>
-      <c r="F53" s="113"/>
-      <c r="G53" s="113"/>
-      <c r="H53" s="113"/>
-      <c r="I53" s="113"/>
-      <c r="J53" s="125"/>
+      <c r="E53" s="146"/>
+      <c r="F53" s="135"/>
+      <c r="G53" s="135"/>
+      <c r="H53" s="135"/>
+      <c r="I53" s="135"/>
+      <c r="J53" s="132"/>
       <c r="K53" s="31"/>
       <c r="L53" s="32"/>
       <c r="M53" s="33"/>
-      <c r="N53" s="179"/>
-      <c r="O53" s="125"/>
+      <c r="N53" s="131"/>
+      <c r="O53" s="132"/>
       <c r="P53" s="34"/>
     </row>
     <row r="54" spans="2:23" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="23"/>
       <c r="D54" s="25"/>
-      <c r="E54" s="124"/>
-      <c r="F54" s="113"/>
-      <c r="G54" s="113"/>
-      <c r="H54" s="113"/>
-      <c r="I54" s="113"/>
-      <c r="J54" s="125"/>
+      <c r="E54" s="197"/>
+      <c r="F54" s="135"/>
+      <c r="G54" s="135"/>
+      <c r="H54" s="135"/>
+      <c r="I54" s="135"/>
+      <c r="J54" s="132"/>
       <c r="K54" s="26"/>
       <c r="L54" s="27"/>
       <c r="M54" s="28"/>
-      <c r="N54" s="200"/>
-      <c r="O54" s="125"/>
+      <c r="N54" s="136"/>
+      <c r="O54" s="132"/>
       <c r="P54" s="29"/>
     </row>
     <row r="55" spans="2:23" ht="66.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="8"/>
       <c r="C55" s="23"/>
       <c r="D55" s="30"/>
-      <c r="E55" s="162"/>
-      <c r="F55" s="113"/>
-      <c r="G55" s="113"/>
-      <c r="H55" s="113"/>
-      <c r="I55" s="113"/>
-      <c r="J55" s="125"/>
+      <c r="E55" s="146"/>
+      <c r="F55" s="135"/>
+      <c r="G55" s="135"/>
+      <c r="H55" s="135"/>
+      <c r="I55" s="135"/>
+      <c r="J55" s="132"/>
       <c r="K55" s="31"/>
       <c r="L55" s="32"/>
       <c r="M55" s="33"/>
-      <c r="N55" s="179"/>
-      <c r="O55" s="125"/>
+      <c r="N55" s="131"/>
+      <c r="O55" s="132"/>
       <c r="P55" s="34"/>
     </row>
     <row r="56" spans="2:23" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -4047,11 +4205,11 @@
       <c r="M56" s="95" t="s">
         <v>98</v>
       </c>
-      <c r="N56" s="196">
+      <c r="N56" s="195">
         <f>SUM(N50:N55)</f>
         <v>0</v>
       </c>
-      <c r="O56" s="197"/>
+      <c r="O56" s="196"/>
       <c r="P56" s="3"/>
     </row>
     <row r="57" spans="2:23" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4069,11 +4227,11 @@
       <c r="M57" s="96" t="s">
         <v>99</v>
       </c>
-      <c r="N57" s="188">
+      <c r="N57" s="190">
         <f>+N56*0.12</f>
         <v>0</v>
       </c>
-      <c r="O57" s="189"/>
+      <c r="O57" s="191"/>
       <c r="P57" s="3"/>
     </row>
     <row r="58" spans="2:23" ht="21.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
@@ -4091,11 +4249,11 @@
       <c r="M58" s="95" t="s">
         <v>100</v>
       </c>
-      <c r="N58" s="181">
+      <c r="N58" s="188">
         <f>+N57+N56</f>
         <v>0</v>
       </c>
-      <c r="O58" s="113"/>
+      <c r="O58" s="135"/>
       <c r="P58" s="3"/>
     </row>
     <row r="59" spans="2:23" s="3" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4120,48 +4278,48 @@
     <row r="60" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="74"/>
       <c r="C60" s="74"/>
-      <c r="D60" s="255" t="s">
+      <c r="D60" s="192" t="s">
         <v>101</v>
       </c>
-      <c r="E60" s="255"/>
-      <c r="F60" s="255"/>
-      <c r="G60" s="255"/>
-      <c r="H60" s="255"/>
-      <c r="I60" s="255"/>
-      <c r="J60" s="255"/>
-      <c r="K60" s="255"/>
-      <c r="L60" s="255"/>
-      <c r="M60" s="255"/>
-      <c r="N60" s="255"/>
-      <c r="O60" s="255"/>
-      <c r="P60" s="255"/>
+      <c r="E60" s="192"/>
+      <c r="F60" s="192"/>
+      <c r="G60" s="192"/>
+      <c r="H60" s="192"/>
+      <c r="I60" s="192"/>
+      <c r="J60" s="192"/>
+      <c r="K60" s="192"/>
+      <c r="L60" s="192"/>
+      <c r="M60" s="192"/>
+      <c r="N60" s="192"/>
+      <c r="O60" s="192"/>
+      <c r="P60" s="192"/>
       <c r="Q60" s="56"/>
       <c r="R60" s="56"/>
     </row>
     <row r="61" spans="2:23" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B61" s="74"/>
       <c r="C61" s="74"/>
-      <c r="D61" s="256" t="s">
+      <c r="D61" s="180" t="s">
         <v>102</v>
       </c>
-      <c r="E61" s="256"/>
-      <c r="F61" s="256"/>
-      <c r="G61" s="257" t="s">
+      <c r="E61" s="180"/>
+      <c r="F61" s="180"/>
+      <c r="G61" s="181" t="s">
         <v>103</v>
       </c>
-      <c r="H61" s="257"/>
-      <c r="I61" s="257"/>
-      <c r="J61" s="258" t="s">
+      <c r="H61" s="181"/>
+      <c r="I61" s="181"/>
+      <c r="J61" s="182" t="s">
         <v>105</v>
       </c>
-      <c r="K61" s="259"/>
-      <c r="L61" s="260"/>
-      <c r="M61" s="261" t="s">
+      <c r="K61" s="183"/>
+      <c r="L61" s="184"/>
+      <c r="M61" s="185" t="s">
         <v>106</v>
       </c>
-      <c r="N61" s="262"/>
-      <c r="O61" s="262"/>
-      <c r="P61" s="263"/>
+      <c r="N61" s="186"/>
+      <c r="O61" s="186"/>
+      <c r="P61" s="187"/>
       <c r="Q61" s="56"/>
       <c r="R61" s="56"/>
       <c r="U61" s="35"/>
@@ -4171,122 +4329,118 @@
     <row r="62" spans="2:23" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="74"/>
       <c r="C62" s="74"/>
-      <c r="D62" s="220" t="s">
+      <c r="D62" s="277" t="s">
         <v>104</v>
       </c>
-      <c r="E62" s="220"/>
-      <c r="F62" s="220"/>
-      <c r="G62" s="218"/>
-      <c r="H62" s="218"/>
-      <c r="I62" s="218"/>
-      <c r="J62" s="221"/>
-      <c r="K62" s="221"/>
-      <c r="L62" s="221"/>
-      <c r="M62" s="221"/>
-      <c r="N62" s="221"/>
-      <c r="O62" s="221"/>
-      <c r="P62" s="221"/>
-      <c r="Q62" s="223"/>
-      <c r="R62" s="223"/>
-      <c r="S62" s="224"/>
-      <c r="T62" s="224"/>
-      <c r="U62" s="225"/>
+      <c r="E62" s="277"/>
+      <c r="F62" s="277"/>
+      <c r="G62" s="123"/>
+      <c r="H62" s="123"/>
+      <c r="I62" s="123"/>
+      <c r="J62" s="201"/>
+      <c r="K62" s="201"/>
+      <c r="L62" s="201"/>
+      <c r="M62" s="201"/>
+      <c r="N62" s="201"/>
+      <c r="O62" s="201"/>
+      <c r="P62" s="201"/>
+      <c r="Q62" s="56"/>
+      <c r="R62" s="56"/>
+      <c r="S62"/>
+      <c r="T62"/>
+      <c r="U62" s="35"/>
       <c r="V62" s="35"/>
       <c r="W62" s="35"/>
     </row>
     <row r="63" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="74"/>
       <c r="C63" s="74"/>
-      <c r="D63" s="235"/>
-      <c r="E63" s="235"/>
-      <c r="F63" s="235"/>
-      <c r="G63" s="236"/>
-      <c r="H63" s="236"/>
-      <c r="I63" s="236"/>
-      <c r="J63" s="237"/>
-      <c r="K63" s="237"/>
-      <c r="L63" s="237"/>
-      <c r="M63" s="236"/>
-      <c r="N63" s="236"/>
-      <c r="O63" s="236"/>
-      <c r="P63" s="236"/>
-      <c r="Q63" s="226"/>
-      <c r="R63" s="226"/>
-      <c r="S63" s="224"/>
-      <c r="T63" s="224"/>
-      <c r="U63" s="225"/>
+      <c r="D63" s="202"/>
+      <c r="E63" s="202"/>
+      <c r="F63" s="202"/>
+      <c r="G63" s="122"/>
+      <c r="H63" s="122"/>
+      <c r="I63" s="122"/>
+      <c r="J63" s="203"/>
+      <c r="K63" s="203"/>
+      <c r="L63" s="203"/>
+      <c r="M63" s="122"/>
+      <c r="N63" s="122"/>
+      <c r="O63" s="122"/>
+      <c r="P63" s="122"/>
+      <c r="Q63" s="103"/>
+      <c r="R63" s="103"/>
+      <c r="S63"/>
+      <c r="T63"/>
+      <c r="U63" s="35"/>
       <c r="V63" s="35"/>
       <c r="W63" s="35"/>
     </row>
     <row r="64" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="74"/>
       <c r="C64" s="74"/>
-      <c r="D64" s="218"/>
-      <c r="E64" s="218"/>
-      <c r="F64" s="218"/>
-      <c r="G64" s="219"/>
-      <c r="H64" s="219"/>
-      <c r="I64" s="219"/>
-      <c r="J64" s="222"/>
-      <c r="K64" s="222"/>
-      <c r="L64" s="222"/>
-      <c r="M64" s="219"/>
-      <c r="N64" s="219"/>
-      <c r="O64" s="219"/>
-      <c r="P64" s="219"/>
-      <c r="Q64" s="223"/>
-      <c r="R64" s="223"/>
-      <c r="S64" s="224"/>
-      <c r="T64" s="224"/>
-      <c r="U64" s="225"/>
+      <c r="D64" s="123"/>
+      <c r="E64" s="123"/>
+      <c r="F64" s="123"/>
+      <c r="G64" s="116"/>
+      <c r="H64" s="116"/>
+      <c r="I64" s="116"/>
+      <c r="J64" s="124"/>
+      <c r="K64" s="124"/>
+      <c r="L64" s="124"/>
+      <c r="M64" s="116"/>
+      <c r="N64" s="116"/>
+      <c r="O64" s="116"/>
+      <c r="P64" s="116"/>
+      <c r="Q64" s="56"/>
+      <c r="R64" s="56"/>
+      <c r="S64"/>
+      <c r="T64"/>
+      <c r="U64" s="35"/>
       <c r="V64" s="35"/>
       <c r="W64" s="35"/>
     </row>
-    <row r="65" spans="2:21" s="3" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="2:20" s="3" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="74"/>
       <c r="C65" s="74"/>
-      <c r="D65" s="238"/>
-      <c r="E65" s="239"/>
-      <c r="F65" s="240"/>
-      <c r="G65" s="238"/>
-      <c r="H65" s="239"/>
-      <c r="I65" s="240"/>
-      <c r="J65" s="238"/>
-      <c r="K65" s="239"/>
-      <c r="L65" s="240"/>
-      <c r="M65" s="238"/>
-      <c r="N65" s="239"/>
-      <c r="O65" s="239"/>
-      <c r="P65" s="240"/>
-      <c r="Q65" s="223"/>
-      <c r="R65" s="223"/>
-      <c r="S65" s="224"/>
-      <c r="T65" s="224"/>
-      <c r="U65" s="227"/>
-    </row>
-    <row r="66" spans="2:21" s="3" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D65" s="118"/>
+      <c r="E65" s="119"/>
+      <c r="F65" s="120"/>
+      <c r="G65" s="118"/>
+      <c r="H65" s="119"/>
+      <c r="I65" s="120"/>
+      <c r="J65" s="118"/>
+      <c r="K65" s="119"/>
+      <c r="L65" s="120"/>
+      <c r="M65" s="118"/>
+      <c r="N65" s="119"/>
+      <c r="O65" s="119"/>
+      <c r="P65" s="120"/>
+      <c r="Q65" s="56"/>
+      <c r="R65" s="56"/>
+      <c r="S65"/>
+      <c r="T65"/>
+    </row>
+    <row r="66" spans="2:20" s="3" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="74"/>
       <c r="C66" s="74"/>
-      <c r="D66" s="219"/>
-      <c r="E66" s="219"/>
-      <c r="F66" s="219"/>
-      <c r="G66" s="219"/>
-      <c r="H66" s="219"/>
-      <c r="I66" s="219"/>
-      <c r="J66" s="219"/>
-      <c r="K66" s="219"/>
-      <c r="L66" s="219"/>
-      <c r="M66" s="219"/>
-      <c r="N66" s="219"/>
-      <c r="O66" s="219"/>
-      <c r="P66" s="219"/>
-      <c r="Q66" s="223"/>
-      <c r="R66" s="223"/>
-      <c r="S66" s="227"/>
-      <c r="T66" s="227"/>
-      <c r="U66" s="227"/>
-    </row>
-    <row r="67" spans="2:21" s="3" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D66" s="116"/>
+      <c r="E66" s="116"/>
+      <c r="F66" s="116"/>
+      <c r="G66" s="116"/>
+      <c r="H66" s="116"/>
+      <c r="I66" s="116"/>
+      <c r="J66" s="116"/>
+      <c r="K66" s="116"/>
+      <c r="L66" s="116"/>
+      <c r="M66" s="116"/>
+      <c r="N66" s="116"/>
+      <c r="O66" s="116"/>
+      <c r="P66" s="116"/>
+      <c r="Q66" s="56"/>
+      <c r="R66" s="56"/>
+    </row>
+    <row r="67" spans="2:20" s="3" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B67" s="74"/>
       <c r="C67" s="74"/>
       <c r="D67" s="56"/>
@@ -4302,125 +4456,134 @@
       <c r="N67" s="55"/>
       <c r="O67" s="55"/>
       <c r="P67" s="55"/>
-      <c r="Q67" s="228"/>
-      <c r="R67" s="228"/>
-      <c r="S67" s="227"/>
-      <c r="T67" s="227"/>
-      <c r="U67" s="227"/>
-    </row>
-    <row r="68" spans="2:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="Q67" s="55"/>
+      <c r="R67" s="55"/>
+    </row>
+    <row r="68" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="74"/>
       <c r="C68" s="74"/>
-      <c r="D68" s="255" t="s">
+      <c r="D68" s="258" t="s">
+        <v>91</v>
+      </c>
+      <c r="E68" s="259" t="s">
         <v>107</v>
       </c>
-      <c r="E68" s="264"/>
-      <c r="F68" s="264"/>
-      <c r="G68" s="264"/>
-      <c r="H68" s="264"/>
-      <c r="I68" s="264"/>
-      <c r="J68" s="264"/>
-      <c r="K68" s="264"/>
-      <c r="L68" s="264"/>
-      <c r="M68" s="264"/>
-      <c r="N68" s="264"/>
-      <c r="O68" s="264"/>
-      <c r="P68" s="264"/>
+      <c r="F68" s="260"/>
+      <c r="G68" s="260"/>
+      <c r="H68" s="260"/>
+      <c r="I68" s="260"/>
+      <c r="J68" s="260"/>
+      <c r="K68" s="260"/>
+      <c r="L68" s="260"/>
+      <c r="M68" s="260"/>
+      <c r="N68" s="260"/>
+      <c r="O68" s="260"/>
+      <c r="P68" s="261"/>
       <c r="Q68" s="55"/>
       <c r="R68" s="55"/>
     </row>
-    <row r="69" spans="2:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="74"/>
       <c r="C69" s="99"/>
-      <c r="D69" s="100"/>
-      <c r="E69" s="100"/>
-      <c r="F69" s="100"/>
-      <c r="G69" s="100"/>
-      <c r="H69" s="100"/>
-      <c r="I69" s="100"/>
-      <c r="J69" s="100" t="s">
+      <c r="D69" s="262">
+        <v>1</v>
+      </c>
+      <c r="E69" s="264" t="s">
         <v>108</v>
       </c>
-      <c r="K69" s="100"/>
-      <c r="L69" s="100"/>
-      <c r="M69" s="100"/>
-      <c r="N69" s="100"/>
-      <c r="O69" s="100"/>
-      <c r="P69" s="100"/>
+      <c r="F69" s="265"/>
+      <c r="G69" s="265"/>
+      <c r="H69" s="265"/>
+      <c r="I69" s="265"/>
+      <c r="J69" s="265"/>
+      <c r="K69" s="265"/>
+      <c r="L69" s="265"/>
+      <c r="M69" s="265"/>
+      <c r="N69" s="265"/>
+      <c r="O69" s="265"/>
+      <c r="P69" s="266"/>
       <c r="Q69" s="99"/>
       <c r="R69" s="99"/>
     </row>
-    <row r="70" spans="2:21" ht="140.1" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="2:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="74"/>
       <c r="C70" s="74"/>
-      <c r="D70" s="106"/>
-      <c r="E70" s="173"/>
-      <c r="F70" s="121"/>
-      <c r="G70" s="121"/>
-      <c r="H70" s="121"/>
-      <c r="I70" s="121"/>
-      <c r="J70" s="121"/>
-      <c r="K70" s="121"/>
-      <c r="L70" s="121"/>
-      <c r="M70" s="121"/>
-      <c r="N70" s="121"/>
-      <c r="O70" s="121"/>
-      <c r="P70" s="121"/>
+      <c r="D70" s="278">
+        <v>2</v>
+      </c>
+      <c r="E70" s="279"/>
+      <c r="F70" s="198"/>
+      <c r="G70" s="198"/>
+      <c r="H70" s="198"/>
+      <c r="I70" s="198"/>
+      <c r="J70" s="198"/>
+      <c r="K70" s="198"/>
+      <c r="L70" s="198"/>
+      <c r="M70" s="198"/>
+      <c r="N70" s="198"/>
+      <c r="O70" s="198"/>
+      <c r="P70" s="198"/>
       <c r="Q70" s="55"/>
       <c r="R70" s="55"/>
     </row>
-    <row r="71" spans="2:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="8"/>
       <c r="C71" s="8"/>
-      <c r="D71" s="102"/>
-      <c r="E71" s="163"/>
-      <c r="F71" s="113"/>
-      <c r="G71" s="113"/>
-      <c r="H71" s="113"/>
-      <c r="I71" s="113"/>
-      <c r="J71" s="113"/>
-      <c r="K71" s="113"/>
-      <c r="L71" s="113"/>
-      <c r="M71" s="113"/>
-      <c r="N71" s="113"/>
-      <c r="O71" s="113"/>
-      <c r="P71" s="113"/>
-    </row>
-    <row r="72" spans="2:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D71" s="262">
+        <v>3</v>
+      </c>
+      <c r="E71" s="267"/>
+      <c r="F71" s="268"/>
+      <c r="G71" s="268"/>
+      <c r="H71" s="268"/>
+      <c r="I71" s="268"/>
+      <c r="J71" s="268"/>
+      <c r="K71" s="268"/>
+      <c r="L71" s="268"/>
+      <c r="M71" s="268"/>
+      <c r="N71" s="268"/>
+      <c r="O71" s="268"/>
+      <c r="P71" s="268"/>
+    </row>
+    <row r="72" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="8"/>
       <c r="C72" s="8"/>
-      <c r="D72" s="102"/>
-      <c r="E72" s="112"/>
-      <c r="F72" s="113"/>
-      <c r="G72" s="113"/>
-      <c r="H72" s="113"/>
-      <c r="I72" s="113"/>
-      <c r="J72" s="113"/>
-      <c r="K72" s="113"/>
-      <c r="L72" s="113"/>
-      <c r="M72" s="113"/>
-      <c r="N72" s="113"/>
-      <c r="O72" s="113"/>
-      <c r="P72" s="113"/>
-    </row>
-    <row r="73" spans="2:21" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D72" s="278">
+        <v>4</v>
+      </c>
+      <c r="E72" s="280"/>
+      <c r="F72" s="281"/>
+      <c r="G72" s="281"/>
+      <c r="H72" s="281"/>
+      <c r="I72" s="281"/>
+      <c r="J72" s="281"/>
+      <c r="K72" s="281"/>
+      <c r="L72" s="281"/>
+      <c r="M72" s="281"/>
+      <c r="N72" s="281"/>
+      <c r="O72" s="281"/>
+      <c r="P72" s="281"/>
+    </row>
+    <row r="73" spans="2:20" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="8"/>
       <c r="C73" s="8"/>
-      <c r="D73" s="102"/>
-      <c r="E73" s="112"/>
-      <c r="F73" s="113"/>
-      <c r="G73" s="113"/>
-      <c r="H73" s="113"/>
-      <c r="I73" s="113"/>
-      <c r="J73" s="113"/>
-      <c r="K73" s="113"/>
-      <c r="L73" s="113"/>
-      <c r="M73" s="113"/>
-      <c r="N73" s="113"/>
-      <c r="O73" s="113"/>
-      <c r="P73" s="113"/>
-    </row>
-    <row r="74" spans="2:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D73" s="262">
+        <v>5</v>
+      </c>
+      <c r="E73" s="269"/>
+      <c r="F73" s="268"/>
+      <c r="G73" s="268"/>
+      <c r="H73" s="268"/>
+      <c r="I73" s="268"/>
+      <c r="J73" s="268"/>
+      <c r="K73" s="268"/>
+      <c r="L73" s="268"/>
+      <c r="M73" s="268"/>
+      <c r="N73" s="268"/>
+      <c r="O73" s="268"/>
+      <c r="P73" s="268"/>
+    </row>
+    <row r="74" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="8"/>
       <c r="C74" s="8"/>
       <c r="D74" s="36"/>
@@ -4437,927 +4600,915 @@
       <c r="O74" s="38"/>
       <c r="P74" s="39"/>
     </row>
-    <row r="75" spans="2:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="74"/>
       <c r="C75" s="74"/>
-      <c r="D75" s="107" t="s">
+      <c r="D75" s="270" t="s">
+        <v>91</v>
+      </c>
+      <c r="E75" s="271" t="s">
         <v>109</v>
       </c>
-      <c r="E75" s="186" t="s">
-        <v>110</v>
-      </c>
-      <c r="F75" s="187"/>
-      <c r="G75" s="187"/>
-      <c r="H75" s="187"/>
-      <c r="I75" s="187"/>
-      <c r="J75" s="187"/>
-      <c r="K75" s="187"/>
-      <c r="L75" s="187"/>
-      <c r="M75" s="187"/>
-      <c r="N75" s="187"/>
-      <c r="O75" s="187"/>
-      <c r="P75" s="187"/>
+      <c r="F75" s="272"/>
+      <c r="G75" s="272"/>
+      <c r="H75" s="272"/>
+      <c r="I75" s="272"/>
+      <c r="J75" s="272"/>
+      <c r="K75" s="272"/>
+      <c r="L75" s="272"/>
+      <c r="M75" s="272"/>
+      <c r="N75" s="272"/>
+      <c r="O75" s="272"/>
+      <c r="P75" s="272"/>
       <c r="Q75" s="55"/>
       <c r="R75" s="55"/>
     </row>
-    <row r="76" spans="2:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="74"/>
       <c r="C76" s="74"/>
-      <c r="D76" s="103"/>
-      <c r="E76" s="104"/>
-      <c r="F76" s="105"/>
-      <c r="G76" s="105"/>
-      <c r="H76" s="105"/>
-      <c r="I76" s="216" t="s">
-        <v>111</v>
-      </c>
-      <c r="J76" s="217"/>
-      <c r="K76" s="217"/>
-      <c r="L76" s="217"/>
-      <c r="M76" s="105"/>
-      <c r="N76" s="105"/>
-      <c r="O76" s="105"/>
-      <c r="P76" s="105"/>
+      <c r="D76" s="262">
+        <v>1</v>
+      </c>
+      <c r="E76" s="273" t="s">
+        <v>110</v>
+      </c>
+      <c r="F76" s="273"/>
+      <c r="G76" s="273"/>
+      <c r="H76" s="273"/>
+      <c r="I76" s="273"/>
+      <c r="J76" s="273"/>
+      <c r="K76" s="273"/>
+      <c r="L76" s="273"/>
+      <c r="M76" s="273"/>
+      <c r="N76" s="273"/>
+      <c r="O76" s="273"/>
+      <c r="P76" s="273"/>
       <c r="Q76" s="55"/>
       <c r="R76" s="55"/>
     </row>
-    <row r="77" spans="2:21" ht="140.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B77" s="8"/>
-      <c r="C77" s="8"/>
-      <c r="D77" s="108"/>
-      <c r="E77" s="163"/>
-      <c r="F77" s="113"/>
-      <c r="G77" s="113"/>
-      <c r="H77" s="113"/>
-      <c r="I77" s="113"/>
-      <c r="J77" s="113"/>
-      <c r="K77" s="113"/>
-      <c r="L77" s="113"/>
-      <c r="M77" s="113"/>
-      <c r="N77" s="113"/>
-      <c r="O77" s="113"/>
-      <c r="P77" s="113"/>
-    </row>
-    <row r="78" spans="2:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B78" s="8"/>
-      <c r="C78" s="8"/>
-      <c r="D78" s="102"/>
-      <c r="E78" s="112"/>
-      <c r="F78" s="113"/>
-      <c r="G78" s="113"/>
-      <c r="H78" s="113"/>
-      <c r="I78" s="113"/>
-      <c r="J78" s="113"/>
-      <c r="K78" s="113"/>
-      <c r="L78" s="113"/>
-      <c r="M78" s="113"/>
-      <c r="N78" s="113"/>
-      <c r="O78" s="113"/>
-      <c r="P78" s="113"/>
-    </row>
-    <row r="79" spans="2:21" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B77" s="74"/>
+      <c r="C77" s="74"/>
+      <c r="D77" s="278">
+        <v>2</v>
+      </c>
+      <c r="E77" s="282"/>
+      <c r="F77" s="283"/>
+      <c r="G77" s="283"/>
+      <c r="H77" s="283"/>
+      <c r="I77" s="283"/>
+      <c r="J77" s="283"/>
+      <c r="K77" s="283"/>
+      <c r="L77" s="283"/>
+      <c r="M77" s="283"/>
+      <c r="N77" s="283"/>
+      <c r="O77" s="283"/>
+      <c r="P77" s="284"/>
+      <c r="Q77" s="55"/>
+      <c r="R77" s="55"/>
+    </row>
+    <row r="78" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B78" s="74"/>
+      <c r="C78" s="74"/>
+      <c r="D78" s="262">
+        <v>3</v>
+      </c>
+      <c r="E78" s="274"/>
+      <c r="F78" s="275"/>
+      <c r="G78" s="275"/>
+      <c r="H78" s="275"/>
+      <c r="I78" s="275"/>
+      <c r="J78" s="275"/>
+      <c r="K78" s="275"/>
+      <c r="L78" s="275"/>
+      <c r="M78" s="275"/>
+      <c r="N78" s="275"/>
+      <c r="O78" s="275"/>
+      <c r="P78" s="276"/>
+      <c r="Q78" s="55"/>
+      <c r="R78" s="55"/>
+    </row>
+    <row r="79" spans="2:20" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="8"/>
       <c r="C79" s="8"/>
-      <c r="D79" s="102"/>
-      <c r="E79" s="112"/>
-      <c r="F79" s="113"/>
-      <c r="G79" s="113"/>
-      <c r="H79" s="113"/>
-      <c r="I79" s="113"/>
-      <c r="J79" s="113"/>
-      <c r="K79" s="113"/>
-      <c r="L79" s="113"/>
-      <c r="M79" s="113"/>
-      <c r="N79" s="113"/>
-      <c r="O79" s="113"/>
-      <c r="P79" s="113"/>
-    </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.3">
-      <c r="B80" s="74"/>
-      <c r="C80" s="74"/>
-      <c r="D80" s="40"/>
-      <c r="E80" s="41"/>
-      <c r="F80" s="41"/>
-      <c r="G80" s="41"/>
-      <c r="H80" s="41"/>
-      <c r="I80" s="41"/>
-      <c r="J80" s="41"/>
-      <c r="K80" s="41"/>
-      <c r="L80" s="41"/>
-      <c r="M80" s="42"/>
-      <c r="N80" s="42"/>
-      <c r="O80" s="42"/>
-      <c r="P80" s="43"/>
-      <c r="Q80" s="55"/>
-      <c r="R80" s="55"/>
+      <c r="D79" s="278">
+        <v>4</v>
+      </c>
+      <c r="E79" s="285"/>
+      <c r="F79" s="133"/>
+      <c r="G79" s="133"/>
+      <c r="H79" s="133"/>
+      <c r="I79" s="133"/>
+      <c r="J79" s="133"/>
+      <c r="K79" s="133"/>
+      <c r="L79" s="133"/>
+      <c r="M79" s="133"/>
+      <c r="N79" s="133"/>
+      <c r="O79" s="133"/>
+      <c r="P79" s="133"/>
+    </row>
+    <row r="80" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B80" s="8"/>
+      <c r="C80" s="8"/>
+      <c r="D80" s="262">
+        <v>5</v>
+      </c>
+      <c r="E80" s="263"/>
+      <c r="F80" s="129"/>
+      <c r="G80" s="129"/>
+      <c r="H80" s="129"/>
+      <c r="I80" s="129"/>
+      <c r="J80" s="129"/>
+      <c r="K80" s="129"/>
+      <c r="L80" s="129"/>
+      <c r="M80" s="129"/>
+      <c r="N80" s="129"/>
+      <c r="O80" s="129"/>
+      <c r="P80" s="129"/>
     </row>
     <row r="81" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="8"/>
       <c r="C81" s="8"/>
-      <c r="D81" s="265" t="s">
-        <v>91</v>
-      </c>
-      <c r="E81" s="266" t="s">
-        <v>112</v>
-      </c>
-      <c r="F81" s="266"/>
-      <c r="G81" s="266"/>
-      <c r="H81" s="266"/>
-      <c r="I81" s="266"/>
-      <c r="J81" s="266"/>
-      <c r="K81" s="266"/>
-      <c r="L81" s="266"/>
-      <c r="M81" s="266"/>
-      <c r="N81" s="266"/>
-      <c r="O81" s="266"/>
-      <c r="P81" s="266"/>
-      <c r="Q81" s="72"/>
-      <c r="R81" s="72"/>
-    </row>
-    <row r="82" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B82" s="8"/>
-      <c r="C82" s="8"/>
-      <c r="D82" s="231">
-        <v>1</v>
-      </c>
-      <c r="E82" s="232" t="s">
-        <v>113</v>
-      </c>
-      <c r="F82" s="233"/>
-      <c r="G82" s="233"/>
-      <c r="H82" s="233"/>
-      <c r="I82" s="233"/>
-      <c r="J82" s="233"/>
-      <c r="K82" s="233"/>
-      <c r="L82" s="233"/>
-      <c r="M82" s="234"/>
-      <c r="N82" s="47"/>
-      <c r="O82" s="47"/>
-      <c r="P82" s="47"/>
-      <c r="Q82" s="72"/>
-      <c r="R82" s="72"/>
-    </row>
-    <row r="83" spans="2:20" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D81" s="101"/>
+      <c r="E81" s="134"/>
+      <c r="F81" s="135"/>
+      <c r="G81" s="135"/>
+      <c r="H81" s="135"/>
+      <c r="I81" s="135"/>
+      <c r="J81" s="135"/>
+      <c r="K81" s="135"/>
+      <c r="L81" s="135"/>
+      <c r="M81" s="135"/>
+      <c r="N81" s="135"/>
+      <c r="O81" s="135"/>
+      <c r="P81" s="135"/>
+    </row>
+    <row r="82" spans="2:20" x14ac:dyDescent="0.3">
+      <c r="B82" s="74"/>
+      <c r="C82" s="74"/>
+      <c r="D82" s="40"/>
+      <c r="E82" s="41"/>
+      <c r="F82" s="41"/>
+      <c r="G82" s="41"/>
+      <c r="H82" s="41"/>
+      <c r="I82" s="41"/>
+      <c r="J82" s="41"/>
+      <c r="K82" s="41"/>
+      <c r="L82" s="41"/>
+      <c r="M82" s="42"/>
+      <c r="N82" s="42"/>
+      <c r="O82" s="42"/>
+      <c r="P82" s="43"/>
+      <c r="Q82" s="55"/>
+      <c r="R82" s="55"/>
+    </row>
+    <row r="83" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="8"/>
       <c r="C83" s="8"/>
-      <c r="D83" s="245">
-        <v>2</v>
-      </c>
-      <c r="E83" s="241"/>
-      <c r="F83" s="242"/>
-      <c r="G83" s="242"/>
-      <c r="H83" s="242"/>
-      <c r="I83" s="242"/>
-      <c r="J83" s="242"/>
-      <c r="K83" s="242"/>
-      <c r="L83" s="242"/>
-      <c r="M83" s="242"/>
-      <c r="N83" s="46"/>
-      <c r="O83" s="47"/>
-      <c r="P83" s="47"/>
+      <c r="D83" s="109" t="s">
+        <v>91</v>
+      </c>
+      <c r="E83" s="121" t="s">
+        <v>111</v>
+      </c>
+      <c r="F83" s="121"/>
+      <c r="G83" s="121"/>
+      <c r="H83" s="121"/>
+      <c r="I83" s="121"/>
+      <c r="J83" s="121"/>
+      <c r="K83" s="121"/>
+      <c r="L83" s="121"/>
+      <c r="M83" s="121"/>
+      <c r="N83" s="121"/>
+      <c r="O83" s="121"/>
+      <c r="P83" s="121"/>
       <c r="Q83" s="72"/>
       <c r="R83" s="72"/>
     </row>
-    <row r="84" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:20" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="8"/>
       <c r="C84" s="8"/>
-      <c r="D84" s="231">
-        <v>3</v>
-      </c>
-      <c r="E84" s="229"/>
-      <c r="F84" s="230"/>
-      <c r="G84" s="230"/>
-      <c r="H84" s="230"/>
-      <c r="I84" s="230"/>
-      <c r="J84" s="230"/>
-      <c r="K84" s="230"/>
-      <c r="L84" s="230"/>
-      <c r="M84" s="230"/>
-      <c r="N84" s="4"/>
-      <c r="O84" s="178" t="s">
-        <v>114</v>
-      </c>
-      <c r="P84" s="121"/>
-      <c r="Q84" s="44"/>
-      <c r="R84" s="44"/>
-      <c r="T84" s="97" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="85" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D84" s="250">
+        <v>1</v>
+      </c>
+      <c r="E84" s="244" t="s">
+        <v>112</v>
+      </c>
+      <c r="F84" s="245"/>
+      <c r="G84" s="245"/>
+      <c r="H84" s="245"/>
+      <c r="I84" s="245"/>
+      <c r="J84" s="245"/>
+      <c r="K84" s="245"/>
+      <c r="L84" s="245"/>
+      <c r="M84" s="246"/>
+      <c r="N84" s="47"/>
+      <c r="O84" s="47"/>
+      <c r="P84" s="47"/>
+      <c r="Q84" s="72"/>
+      <c r="R84" s="72"/>
+    </row>
+    <row r="85" spans="2:20" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="8"/>
       <c r="C85" s="8"/>
-      <c r="D85" s="245">
-        <v>4</v>
-      </c>
-      <c r="E85" s="243"/>
-      <c r="F85" s="244"/>
-      <c r="G85" s="244"/>
-      <c r="H85" s="244"/>
-      <c r="I85" s="244"/>
-      <c r="J85" s="244"/>
-      <c r="K85" s="244"/>
-      <c r="L85" s="244"/>
-      <c r="M85" s="244"/>
-      <c r="N85" s="5"/>
-      <c r="O85" s="194" t="s">
-        <v>116</v>
-      </c>
-      <c r="P85" s="121"/>
-      <c r="Q85" s="44"/>
-      <c r="R85" s="44"/>
-    </row>
-    <row r="86" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D85" s="251"/>
+      <c r="E85" s="247"/>
+      <c r="F85" s="248"/>
+      <c r="G85" s="248"/>
+      <c r="H85" s="248"/>
+      <c r="I85" s="248"/>
+      <c r="J85" s="248"/>
+      <c r="K85" s="248"/>
+      <c r="L85" s="248"/>
+      <c r="M85" s="249"/>
+      <c r="N85" s="46"/>
+      <c r="O85" s="47"/>
+      <c r="P85" s="47"/>
+      <c r="Q85" s="72"/>
+      <c r="R85" s="72"/>
+    </row>
+    <row r="86" spans="2:20" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="8"/>
       <c r="C86" s="8"/>
-      <c r="D86" s="231">
-        <v>5</v>
-      </c>
-      <c r="E86" s="229"/>
-      <c r="F86" s="230"/>
-      <c r="G86" s="230"/>
-      <c r="H86" s="230"/>
-      <c r="I86" s="230"/>
-      <c r="J86" s="230"/>
-      <c r="K86" s="230"/>
-      <c r="L86" s="230"/>
-      <c r="M86" s="230"/>
-      <c r="N86" s="5"/>
-      <c r="O86" s="121"/>
-      <c r="P86" s="121"/>
+      <c r="D86" s="286">
+        <v>2</v>
+      </c>
+      <c r="E86" s="287"/>
+      <c r="F86" s="288"/>
+      <c r="G86" s="288"/>
+      <c r="H86" s="288"/>
+      <c r="I86" s="288"/>
+      <c r="J86" s="288"/>
+      <c r="K86" s="288"/>
+      <c r="L86" s="288"/>
+      <c r="M86" s="289"/>
+      <c r="N86" s="4"/>
+      <c r="O86" s="125" t="s">
+        <v>113</v>
+      </c>
+      <c r="P86" s="142"/>
       <c r="Q86" s="44"/>
       <c r="R86" s="44"/>
-    </row>
-    <row r="87" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="T86" s="97" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="87" spans="2:20" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="8"/>
       <c r="C87" s="8"/>
-      <c r="D87" s="245">
-        <v>6</v>
-      </c>
-      <c r="E87" s="243"/>
-      <c r="F87" s="244"/>
-      <c r="G87" s="244"/>
-      <c r="H87" s="244"/>
-      <c r="I87" s="244"/>
-      <c r="J87" s="244"/>
-      <c r="K87" s="244"/>
-      <c r="L87" s="244"/>
-      <c r="M87" s="244"/>
+      <c r="D87" s="290"/>
+      <c r="E87" s="291"/>
+      <c r="F87" s="292"/>
+      <c r="G87" s="292"/>
+      <c r="H87" s="292"/>
+      <c r="I87" s="292"/>
+      <c r="J87" s="292"/>
+      <c r="K87" s="292"/>
+      <c r="L87" s="292"/>
+      <c r="M87" s="293"/>
       <c r="N87" s="5"/>
-      <c r="O87" s="121"/>
-      <c r="P87" s="121"/>
+      <c r="O87" s="193" t="s">
+        <v>115</v>
+      </c>
+      <c r="P87" s="142"/>
       <c r="Q87" s="44"/>
       <c r="R87" s="44"/>
     </row>
     <row r="88" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="8"/>
       <c r="C88" s="8"/>
-      <c r="D88" s="231">
-        <v>7</v>
-      </c>
-      <c r="E88" s="229"/>
-      <c r="F88" s="230"/>
-      <c r="G88" s="230"/>
-      <c r="H88" s="230"/>
-      <c r="I88" s="230"/>
-      <c r="J88" s="230"/>
-      <c r="K88" s="230"/>
-      <c r="L88" s="230"/>
-      <c r="M88" s="230"/>
+      <c r="D88" s="250">
+        <v>3</v>
+      </c>
+      <c r="E88" s="252"/>
+      <c r="F88" s="253"/>
+      <c r="G88" s="253"/>
+      <c r="H88" s="253"/>
+      <c r="I88" s="253"/>
+      <c r="J88" s="253"/>
+      <c r="K88" s="253"/>
+      <c r="L88" s="253"/>
+      <c r="M88" s="254"/>
       <c r="N88" s="5"/>
-      <c r="O88" s="195"/>
-      <c r="P88" s="195"/>
+      <c r="O88" s="142"/>
+      <c r="P88" s="142"/>
       <c r="Q88" s="44"/>
       <c r="R88" s="44"/>
     </row>
     <row r="89" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B89" s="8"/>
       <c r="C89" s="8"/>
-      <c r="D89" s="245">
-        <v>8</v>
-      </c>
-      <c r="E89" s="243"/>
-      <c r="F89" s="244"/>
-      <c r="G89" s="244"/>
-      <c r="H89" s="244"/>
-      <c r="I89" s="244"/>
-      <c r="J89" s="244"/>
-      <c r="K89" s="244"/>
-      <c r="L89" s="244"/>
-      <c r="M89" s="244"/>
+      <c r="D89" s="251"/>
+      <c r="E89" s="255"/>
+      <c r="F89" s="256"/>
+      <c r="G89" s="256"/>
+      <c r="H89" s="256"/>
+      <c r="I89" s="256"/>
+      <c r="J89" s="256"/>
+      <c r="K89" s="256"/>
+      <c r="L89" s="256"/>
+      <c r="M89" s="257"/>
       <c r="N89" s="5"/>
-      <c r="O89" s="3"/>
-      <c r="P89" s="3"/>
+      <c r="O89" s="142"/>
+      <c r="P89" s="142"/>
       <c r="Q89" s="44"/>
       <c r="R89" s="44"/>
     </row>
     <row r="90" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B90" s="8"/>
       <c r="C90" s="8"/>
-      <c r="D90" s="231">
-        <v>9</v>
-      </c>
-      <c r="E90" s="229"/>
-      <c r="F90" s="230"/>
-      <c r="G90" s="230"/>
-      <c r="H90" s="230"/>
-      <c r="I90" s="230"/>
-      <c r="J90" s="230"/>
-      <c r="K90" s="230"/>
-      <c r="L90" s="230"/>
-      <c r="M90" s="230"/>
+      <c r="D90" s="286">
+        <v>4</v>
+      </c>
+      <c r="E90" s="287"/>
+      <c r="F90" s="288"/>
+      <c r="G90" s="288"/>
+      <c r="H90" s="288"/>
+      <c r="I90" s="288"/>
+      <c r="J90" s="288"/>
+      <c r="K90" s="288"/>
+      <c r="L90" s="288"/>
+      <c r="M90" s="289"/>
       <c r="N90" s="5"/>
-      <c r="O90" s="178" t="s">
-        <v>117</v>
-      </c>
-      <c r="P90" s="121"/>
+      <c r="O90" s="194"/>
+      <c r="P90" s="194"/>
       <c r="Q90" s="44"/>
       <c r="R90" s="44"/>
     </row>
     <row r="91" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B91" s="8"/>
       <c r="C91" s="8"/>
-      <c r="D91" s="245">
-        <v>10</v>
-      </c>
-      <c r="E91" s="243"/>
-      <c r="F91" s="244"/>
-      <c r="G91" s="244"/>
-      <c r="H91" s="244"/>
-      <c r="I91" s="244"/>
-      <c r="J91" s="244"/>
-      <c r="K91" s="244"/>
-      <c r="L91" s="244"/>
-      <c r="M91" s="244"/>
+      <c r="D91" s="290"/>
+      <c r="E91" s="291"/>
+      <c r="F91" s="292"/>
+      <c r="G91" s="292"/>
+      <c r="H91" s="292"/>
+      <c r="I91" s="292"/>
+      <c r="J91" s="292"/>
+      <c r="K91" s="292"/>
+      <c r="L91" s="292"/>
+      <c r="M91" s="293"/>
       <c r="N91" s="5"/>
-      <c r="O91" s="194" t="s">
-        <v>118</v>
-      </c>
-      <c r="P91" s="121"/>
+      <c r="O91" s="3"/>
+      <c r="P91" s="3"/>
       <c r="Q91" s="44"/>
       <c r="R91" s="44"/>
     </row>
     <row r="92" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B92" s="8"/>
       <c r="C92" s="8"/>
-      <c r="D92" s="231">
-        <v>11</v>
-      </c>
-      <c r="E92" s="229"/>
-      <c r="F92" s="230"/>
-      <c r="G92" s="230"/>
-      <c r="H92" s="230"/>
-      <c r="I92" s="230"/>
-      <c r="J92" s="230"/>
-      <c r="K92" s="230"/>
-      <c r="L92" s="230"/>
-      <c r="M92" s="230"/>
+      <c r="D92" s="250">
+        <v>5</v>
+      </c>
+      <c r="E92" s="252"/>
+      <c r="F92" s="253"/>
+      <c r="G92" s="253"/>
+      <c r="H92" s="253"/>
+      <c r="I92" s="253"/>
+      <c r="J92" s="253"/>
+      <c r="K92" s="253"/>
+      <c r="L92" s="253"/>
+      <c r="M92" s="254"/>
       <c r="N92" s="5"/>
-      <c r="O92" s="121"/>
-      <c r="P92" s="121"/>
+      <c r="O92" s="125" t="s">
+        <v>116</v>
+      </c>
+      <c r="P92" s="142"/>
       <c r="Q92" s="44"/>
       <c r="R92" s="44"/>
     </row>
     <row r="93" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B93" s="8"/>
       <c r="C93" s="8"/>
-      <c r="D93" s="245">
-        <v>12</v>
-      </c>
-      <c r="E93" s="243"/>
-      <c r="F93" s="244"/>
-      <c r="G93" s="244"/>
-      <c r="H93" s="244"/>
-      <c r="I93" s="244"/>
-      <c r="J93" s="244"/>
-      <c r="K93" s="244"/>
-      <c r="L93" s="244"/>
-      <c r="M93" s="244"/>
+      <c r="D93" s="251"/>
+      <c r="E93" s="255"/>
+      <c r="F93" s="256"/>
+      <c r="G93" s="256"/>
+      <c r="H93" s="256"/>
+      <c r="I93" s="256"/>
+      <c r="J93" s="256"/>
+      <c r="K93" s="256"/>
+      <c r="L93" s="256"/>
+      <c r="M93" s="257"/>
       <c r="N93" s="5"/>
-      <c r="O93" s="121"/>
-      <c r="P93" s="121"/>
+      <c r="O93" s="193" t="s">
+        <v>117</v>
+      </c>
+      <c r="P93" s="142"/>
       <c r="Q93" s="44"/>
       <c r="R93" s="44"/>
     </row>
     <row r="94" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B94" s="8"/>
       <c r="C94" s="8"/>
-      <c r="D94" s="231">
-        <v>13</v>
-      </c>
-      <c r="E94" s="229"/>
-      <c r="F94" s="230"/>
-      <c r="G94" s="230"/>
-      <c r="H94" s="230"/>
-      <c r="I94" s="230"/>
-      <c r="J94" s="230"/>
-      <c r="K94" s="230"/>
-      <c r="L94" s="230"/>
-      <c r="M94" s="230"/>
+      <c r="D94" s="286">
+        <v>6</v>
+      </c>
+      <c r="E94" s="287"/>
+      <c r="F94" s="288"/>
+      <c r="G94" s="288"/>
+      <c r="H94" s="288"/>
+      <c r="I94" s="288"/>
+      <c r="J94" s="288"/>
+      <c r="K94" s="288"/>
+      <c r="L94" s="288"/>
+      <c r="M94" s="289"/>
       <c r="N94" s="5"/>
-      <c r="O94" s="121"/>
-      <c r="P94" s="121"/>
+      <c r="O94" s="142"/>
+      <c r="P94" s="142"/>
       <c r="Q94" s="44"/>
       <c r="R94" s="44"/>
     </row>
     <row r="95" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B95" s="8"/>
       <c r="C95" s="8"/>
-      <c r="D95" s="245">
-        <v>14</v>
-      </c>
-      <c r="E95" s="243"/>
-      <c r="F95" s="244"/>
-      <c r="G95" s="244"/>
-      <c r="H95" s="244"/>
-      <c r="I95" s="244"/>
-      <c r="J95" s="244"/>
-      <c r="K95" s="244"/>
-      <c r="L95" s="244"/>
-      <c r="M95" s="244"/>
+      <c r="D95" s="290"/>
+      <c r="E95" s="291"/>
+      <c r="F95" s="292"/>
+      <c r="G95" s="292"/>
+      <c r="H95" s="292"/>
+      <c r="I95" s="292"/>
+      <c r="J95" s="292"/>
+      <c r="K95" s="292"/>
+      <c r="L95" s="292"/>
+      <c r="M95" s="293"/>
       <c r="N95" s="5"/>
-      <c r="O95" s="121"/>
-      <c r="P95" s="121"/>
+      <c r="O95" s="142"/>
+      <c r="P95" s="142"/>
       <c r="Q95" s="44"/>
       <c r="R95" s="44"/>
     </row>
     <row r="96" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B96" s="8"/>
       <c r="C96" s="8"/>
-      <c r="D96" s="231">
-        <v>15</v>
-      </c>
-      <c r="E96" s="229"/>
-      <c r="F96" s="230"/>
-      <c r="G96" s="230"/>
-      <c r="H96" s="230"/>
-      <c r="I96" s="230"/>
-      <c r="J96" s="230"/>
-      <c r="K96" s="230"/>
-      <c r="L96" s="230"/>
-      <c r="M96" s="230"/>
+      <c r="D96" s="250">
+        <v>7</v>
+      </c>
+      <c r="E96" s="252"/>
+      <c r="F96" s="253"/>
+      <c r="G96" s="253"/>
+      <c r="H96" s="253"/>
+      <c r="I96" s="253"/>
+      <c r="J96" s="253"/>
+      <c r="K96" s="253"/>
+      <c r="L96" s="253"/>
+      <c r="M96" s="254"/>
       <c r="N96" s="5"/>
-      <c r="O96" s="195"/>
-      <c r="P96" s="195"/>
+      <c r="O96" s="142"/>
+      <c r="P96" s="142"/>
       <c r="Q96" s="44"/>
       <c r="R96" s="44"/>
     </row>
     <row r="97" spans="2:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B97" s="8"/>
       <c r="C97" s="8"/>
-      <c r="D97" s="247"/>
-      <c r="E97" s="248"/>
-      <c r="F97" s="249"/>
-      <c r="G97" s="249"/>
-      <c r="H97" s="249"/>
-      <c r="I97" s="249"/>
-      <c r="J97" s="249"/>
-      <c r="K97" s="249"/>
-      <c r="L97" s="249"/>
-      <c r="M97" s="249"/>
+      <c r="D97" s="251"/>
+      <c r="E97" s="255"/>
+      <c r="F97" s="256"/>
+      <c r="G97" s="256"/>
+      <c r="H97" s="256"/>
+      <c r="I97" s="256"/>
+      <c r="J97" s="256"/>
+      <c r="K97" s="256"/>
+      <c r="L97" s="256"/>
+      <c r="M97" s="257"/>
       <c r="N97" s="5"/>
-      <c r="O97" s="3"/>
-      <c r="P97" s="3"/>
+      <c r="O97" s="142"/>
+      <c r="P97" s="142"/>
       <c r="Q97" s="44"/>
       <c r="R97" s="44"/>
     </row>
-    <row r="98" spans="2:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:18" ht="42" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="8"/>
       <c r="C98" s="8"/>
-      <c r="D98" s="246"/>
-      <c r="E98" s="251"/>
-      <c r="F98" s="251"/>
-      <c r="G98" s="251"/>
-      <c r="H98" s="249"/>
-      <c r="I98" s="249"/>
-      <c r="J98" s="249"/>
-      <c r="K98" s="249"/>
-      <c r="L98" s="249"/>
-      <c r="M98" s="249"/>
+      <c r="D98" s="294">
+        <v>8</v>
+      </c>
+      <c r="E98" s="285"/>
+      <c r="F98" s="133"/>
+      <c r="G98" s="133"/>
+      <c r="H98" s="133"/>
+      <c r="I98" s="133"/>
+      <c r="J98" s="133"/>
+      <c r="K98" s="133"/>
+      <c r="L98" s="133"/>
+      <c r="M98" s="133"/>
       <c r="N98" s="5"/>
-      <c r="O98" s="178" t="s">
-        <v>119</v>
-      </c>
-      <c r="P98" s="121"/>
+      <c r="O98" s="194"/>
+      <c r="P98" s="194"/>
       <c r="Q98" s="44"/>
       <c r="R98" s="44"/>
     </row>
     <row r="99" spans="2:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B99" s="8"/>
       <c r="C99" s="8"/>
-      <c r="D99" s="247"/>
-      <c r="E99" s="252"/>
-      <c r="F99" s="252"/>
-      <c r="G99" s="252"/>
-      <c r="H99" s="249"/>
-      <c r="I99" s="249"/>
-      <c r="J99" s="249"/>
-      <c r="K99" s="249"/>
-      <c r="L99" s="249"/>
-      <c r="M99" s="249"/>
+      <c r="D99" s="105"/>
+      <c r="E99" s="102"/>
+      <c r="F99" s="106"/>
+      <c r="G99" s="106"/>
+      <c r="H99" s="106"/>
+      <c r="I99" s="106"/>
+      <c r="J99" s="106"/>
+      <c r="K99" s="106"/>
+      <c r="L99" s="106"/>
+      <c r="M99" s="106"/>
       <c r="N99" s="5"/>
-      <c r="O99" s="194" t="s">
-        <v>120</v>
-      </c>
-      <c r="P99" s="121"/>
+      <c r="O99" s="3"/>
+      <c r="P99" s="3"/>
       <c r="Q99" s="44"/>
       <c r="R99" s="44"/>
     </row>
     <row r="100" spans="2:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B100" s="8"/>
       <c r="C100" s="8"/>
-      <c r="D100" s="246"/>
-      <c r="E100" s="252"/>
-      <c r="F100" s="252"/>
-      <c r="G100" s="252"/>
-      <c r="H100" s="249"/>
-      <c r="I100" s="249"/>
-      <c r="J100" s="249"/>
-      <c r="K100" s="249"/>
-      <c r="L100" s="249"/>
-      <c r="M100" s="249"/>
+      <c r="D100" s="104"/>
+      <c r="E100" s="107"/>
+      <c r="F100" s="107"/>
+      <c r="G100" s="107"/>
+      <c r="H100" s="107"/>
+      <c r="I100" s="106"/>
+      <c r="J100" s="106"/>
+      <c r="K100" s="106"/>
+      <c r="L100" s="106"/>
+      <c r="M100" s="106"/>
       <c r="N100" s="5"/>
-      <c r="O100" s="121"/>
-      <c r="P100" s="121"/>
+      <c r="O100" s="125" t="s">
+        <v>118</v>
+      </c>
+      <c r="P100" s="142"/>
       <c r="Q100" s="44"/>
       <c r="R100" s="44"/>
     </row>
     <row r="101" spans="2:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B101" s="8"/>
       <c r="C101" s="8"/>
-      <c r="D101" s="247"/>
-      <c r="E101" s="252"/>
-      <c r="F101" s="252"/>
-      <c r="G101" s="252"/>
-      <c r="H101" s="249"/>
-      <c r="I101" s="249"/>
-      <c r="J101" s="249"/>
-      <c r="K101" s="249"/>
-      <c r="L101" s="249"/>
-      <c r="M101" s="249"/>
+      <c r="D101" s="105"/>
+      <c r="E101" s="88"/>
+      <c r="F101" s="88"/>
+      <c r="G101" s="88"/>
+      <c r="H101" s="88"/>
+      <c r="I101" s="106"/>
+      <c r="J101" s="106"/>
+      <c r="K101" s="106"/>
+      <c r="L101" s="106"/>
+      <c r="M101" s="106"/>
       <c r="N101" s="5"/>
-      <c r="O101" s="121"/>
-      <c r="P101" s="121"/>
+      <c r="O101" s="193" t="s">
+        <v>119</v>
+      </c>
+      <c r="P101" s="142"/>
       <c r="Q101" s="44"/>
       <c r="R101" s="44"/>
     </row>
-    <row r="102" spans="2:18" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B102" s="8"/>
       <c r="C102" s="8"/>
-      <c r="D102" s="246"/>
-      <c r="E102" s="251"/>
-      <c r="F102" s="251"/>
-      <c r="G102" s="251"/>
-      <c r="H102" s="249"/>
-      <c r="I102" s="249"/>
-      <c r="J102" s="249"/>
-      <c r="K102" s="249"/>
-      <c r="L102" s="249"/>
-      <c r="M102" s="249"/>
+      <c r="D102" s="104"/>
+      <c r="E102" s="88"/>
+      <c r="F102" s="88"/>
+      <c r="G102" s="88"/>
+      <c r="H102" s="88"/>
+      <c r="I102" s="106"/>
+      <c r="J102" s="106"/>
+      <c r="K102" s="106"/>
+      <c r="L102" s="106"/>
+      <c r="M102" s="106"/>
       <c r="N102" s="5"/>
-      <c r="O102" s="121"/>
-      <c r="P102" s="121"/>
+      <c r="O102" s="142"/>
+      <c r="P102" s="142"/>
       <c r="Q102" s="44"/>
       <c r="R102" s="44"/>
     </row>
-    <row r="103" spans="2:18" ht="24.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B103" s="8"/>
       <c r="C103" s="8"/>
-      <c r="D103" s="247"/>
-      <c r="E103" s="253"/>
-      <c r="F103" s="253"/>
-      <c r="G103" s="253"/>
-      <c r="H103" s="249"/>
-      <c r="I103" s="249"/>
-      <c r="J103" s="249"/>
-      <c r="K103" s="249"/>
-      <c r="L103" s="249"/>
-      <c r="M103" s="249"/>
+      <c r="D103" s="105"/>
+      <c r="E103" s="88"/>
+      <c r="F103" s="88"/>
+      <c r="G103" s="88"/>
+      <c r="H103" s="88"/>
+      <c r="I103" s="106"/>
+      <c r="J103" s="106"/>
+      <c r="K103" s="106"/>
+      <c r="L103" s="106"/>
+      <c r="M103" s="106"/>
       <c r="N103" s="5"/>
-      <c r="O103" s="121"/>
-      <c r="P103" s="121"/>
+      <c r="O103" s="142"/>
+      <c r="P103" s="142"/>
       <c r="Q103" s="44"/>
       <c r="R103" s="44"/>
     </row>
-    <row r="104" spans="2:18" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:18" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B104" s="8"/>
       <c r="C104" s="8"/>
-      <c r="D104" s="246"/>
-      <c r="E104" s="250" t="s">
-        <v>88</v>
-      </c>
-      <c r="F104" s="250"/>
-      <c r="G104" s="250"/>
-      <c r="H104" s="249"/>
-      <c r="I104" s="249"/>
-      <c r="J104" s="249"/>
-      <c r="K104" s="249"/>
-      <c r="L104" s="249"/>
-      <c r="M104" s="249"/>
+      <c r="D104" s="104"/>
+      <c r="E104" s="107"/>
+      <c r="F104" s="107"/>
+      <c r="G104" s="107"/>
+      <c r="H104" s="107"/>
+      <c r="I104" s="106"/>
+      <c r="J104" s="106"/>
+      <c r="K104" s="106"/>
+      <c r="L104" s="106"/>
+      <c r="M104" s="106"/>
       <c r="N104" s="5"/>
-      <c r="O104" s="195"/>
-      <c r="P104" s="195"/>
+      <c r="O104" s="142"/>
+      <c r="P104" s="142"/>
       <c r="Q104" s="44"/>
       <c r="R104" s="44"/>
     </row>
-    <row r="105" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="2:18" ht="24.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B105" s="8"/>
       <c r="C105" s="8"/>
-      <c r="D105" s="247"/>
-      <c r="E105" s="248"/>
-      <c r="F105" s="249"/>
-      <c r="G105" s="249"/>
-      <c r="H105" s="249"/>
-      <c r="I105" s="249"/>
-      <c r="J105" s="249"/>
-      <c r="K105" s="249"/>
-      <c r="L105" s="249"/>
-      <c r="M105" s="249"/>
+      <c r="D105" s="105"/>
+      <c r="E105" s="108"/>
+      <c r="F105" s="108"/>
+      <c r="G105" s="108"/>
+      <c r="H105" s="108"/>
+      <c r="I105" s="106"/>
+      <c r="J105" s="106"/>
+      <c r="K105" s="106"/>
+      <c r="L105" s="106"/>
+      <c r="M105" s="106"/>
       <c r="N105" s="5"/>
-      <c r="O105" s="3"/>
-      <c r="P105" s="3"/>
+      <c r="O105" s="142"/>
+      <c r="P105" s="142"/>
       <c r="Q105" s="44"/>
       <c r="R105" s="44"/>
     </row>
-    <row r="106" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:18" ht="39" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B106" s="8"/>
       <c r="C106" s="8"/>
-      <c r="D106" s="269" t="s">
-        <v>91</v>
-      </c>
-      <c r="E106" s="267" t="s">
-        <v>131</v>
-      </c>
-      <c r="F106" s="268"/>
-      <c r="G106" s="268"/>
-      <c r="H106" s="268"/>
-      <c r="I106" s="268"/>
-      <c r="J106" s="268"/>
-      <c r="K106" s="268"/>
-      <c r="L106" s="268"/>
-      <c r="M106" s="268"/>
-      <c r="N106" s="268"/>
-      <c r="O106" s="268"/>
-      <c r="P106" s="268"/>
+      <c r="D106" s="104"/>
+      <c r="E106" s="296" t="s">
+        <v>88</v>
+      </c>
+      <c r="F106" s="296"/>
+      <c r="G106" s="296"/>
+      <c r="H106" s="296"/>
+      <c r="I106" s="106"/>
+      <c r="J106" s="106"/>
+      <c r="K106" s="106"/>
+      <c r="L106" s="106"/>
+      <c r="M106" s="106"/>
+      <c r="N106" s="5"/>
+      <c r="O106" s="194"/>
+      <c r="P106" s="194"/>
       <c r="Q106" s="44"/>
       <c r="R106" s="44"/>
     </row>
-    <row r="107" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B107" s="8"/>
       <c r="C107" s="8"/>
-      <c r="D107" s="272">
-        <v>1</v>
-      </c>
-      <c r="E107" s="271" t="s">
-        <v>121</v>
-      </c>
-      <c r="F107" s="271"/>
-      <c r="G107" s="271"/>
-      <c r="H107" s="271"/>
-      <c r="I107" s="271"/>
-      <c r="J107" s="271"/>
-      <c r="K107" s="271"/>
-      <c r="L107" s="271"/>
-      <c r="M107" s="271"/>
-      <c r="N107" s="271"/>
-      <c r="O107" s="271"/>
-      <c r="P107" s="271"/>
-      <c r="Q107" s="55"/>
-      <c r="R107" s="55"/>
-    </row>
-    <row r="108" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D107" s="105"/>
+      <c r="E107" s="102"/>
+      <c r="F107" s="106"/>
+      <c r="G107" s="106"/>
+      <c r="H107" s="106"/>
+      <c r="I107" s="106"/>
+      <c r="J107" s="106"/>
+      <c r="K107" s="106"/>
+      <c r="L107" s="106"/>
+      <c r="M107" s="106"/>
+      <c r="N107" s="5"/>
+      <c r="O107" s="3"/>
+      <c r="P107" s="3"/>
+      <c r="Q107" s="44"/>
+      <c r="R107" s="44"/>
+    </row>
+    <row r="108" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B108" s="8"/>
       <c r="C108" s="8"/>
-      <c r="D108" s="272">
-        <v>2</v>
-      </c>
-      <c r="E108" s="219"/>
-      <c r="F108" s="219"/>
-      <c r="G108" s="219"/>
-      <c r="H108" s="219"/>
-      <c r="I108" s="219"/>
-      <c r="J108" s="219"/>
-      <c r="K108" s="219"/>
-      <c r="L108" s="219"/>
-      <c r="M108" s="219"/>
-      <c r="N108" s="219"/>
-      <c r="O108" s="219"/>
-      <c r="P108" s="219"/>
-      <c r="Q108" s="55"/>
-      <c r="R108" s="55"/>
+      <c r="D108" s="110" t="s">
+        <v>91</v>
+      </c>
+      <c r="E108" s="113" t="s">
+        <v>130</v>
+      </c>
+      <c r="F108" s="114"/>
+      <c r="G108" s="114"/>
+      <c r="H108" s="114"/>
+      <c r="I108" s="114"/>
+      <c r="J108" s="114"/>
+      <c r="K108" s="114"/>
+      <c r="L108" s="114"/>
+      <c r="M108" s="114"/>
+      <c r="N108" s="114"/>
+      <c r="O108" s="114"/>
+      <c r="P108" s="114"/>
+      <c r="Q108" s="44"/>
+      <c r="R108" s="44"/>
     </row>
     <row r="109" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B109" s="8"/>
       <c r="C109" s="8"/>
-      <c r="D109" s="272">
-        <v>3</v>
-      </c>
-      <c r="E109" s="219"/>
-      <c r="F109" s="219"/>
-      <c r="G109" s="219"/>
-      <c r="H109" s="219"/>
-      <c r="I109" s="219"/>
-      <c r="J109" s="219"/>
-      <c r="K109" s="219"/>
-      <c r="L109" s="219"/>
-      <c r="M109" s="219"/>
-      <c r="N109" s="219"/>
-      <c r="O109" s="219"/>
-      <c r="P109" s="219"/>
+      <c r="D109" s="111">
+        <v>1</v>
+      </c>
+      <c r="E109" s="115" t="s">
+        <v>120</v>
+      </c>
+      <c r="F109" s="115"/>
+      <c r="G109" s="115"/>
+      <c r="H109" s="115"/>
+      <c r="I109" s="115"/>
+      <c r="J109" s="115"/>
+      <c r="K109" s="115"/>
+      <c r="L109" s="115"/>
+      <c r="M109" s="115"/>
+      <c r="N109" s="115"/>
+      <c r="O109" s="115"/>
+      <c r="P109" s="115"/>
       <c r="Q109" s="55"/>
       <c r="R109" s="55"/>
     </row>
-    <row r="110" spans="2:18" ht="24" x14ac:dyDescent="0.3">
-      <c r="B110" s="3"/>
-      <c r="C110" s="3"/>
-      <c r="D110" s="272">
+    <row r="110" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B110" s="8"/>
+      <c r="C110" s="8"/>
+      <c r="D110" s="295">
+        <v>2</v>
+      </c>
+      <c r="E110" s="122"/>
+      <c r="F110" s="122"/>
+      <c r="G110" s="122"/>
+      <c r="H110" s="122"/>
+      <c r="I110" s="122"/>
+      <c r="J110" s="122"/>
+      <c r="K110" s="122"/>
+      <c r="L110" s="122"/>
+      <c r="M110" s="122"/>
+      <c r="N110" s="122"/>
+      <c r="O110" s="122"/>
+      <c r="P110" s="122"/>
+      <c r="Q110" s="55"/>
+      <c r="R110" s="55"/>
+    </row>
+    <row r="111" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B111" s="8"/>
+      <c r="C111" s="8"/>
+      <c r="D111" s="111">
+        <v>3</v>
+      </c>
+      <c r="E111" s="116"/>
+      <c r="F111" s="116"/>
+      <c r="G111" s="116"/>
+      <c r="H111" s="116"/>
+      <c r="I111" s="116"/>
+      <c r="J111" s="116"/>
+      <c r="K111" s="116"/>
+      <c r="L111" s="116"/>
+      <c r="M111" s="116"/>
+      <c r="N111" s="116"/>
+      <c r="O111" s="116"/>
+      <c r="P111" s="116"/>
+      <c r="Q111" s="55"/>
+      <c r="R111" s="55"/>
+    </row>
+    <row r="112" spans="2:18" ht="24" x14ac:dyDescent="0.3">
+      <c r="B112" s="3"/>
+      <c r="C112" s="3"/>
+      <c r="D112" s="295">
         <v>4</v>
       </c>
-      <c r="E110" s="273"/>
-      <c r="F110" s="273"/>
-      <c r="G110" s="273"/>
-      <c r="H110" s="273"/>
-      <c r="I110" s="273"/>
-      <c r="J110" s="273"/>
-      <c r="K110" s="273"/>
-      <c r="L110" s="273"/>
-      <c r="M110" s="273"/>
-      <c r="N110" s="273"/>
-      <c r="O110" s="273"/>
-      <c r="P110" s="273"/>
-    </row>
-    <row r="111" spans="2:18" ht="24" x14ac:dyDescent="0.3">
-      <c r="B111" s="3"/>
-      <c r="C111" s="3"/>
-      <c r="D111" s="272">
+      <c r="E112" s="122"/>
+      <c r="F112" s="122"/>
+      <c r="G112" s="122"/>
+      <c r="H112" s="122"/>
+      <c r="I112" s="122"/>
+      <c r="J112" s="122"/>
+      <c r="K112" s="122"/>
+      <c r="L112" s="122"/>
+      <c r="M112" s="122"/>
+      <c r="N112" s="122"/>
+      <c r="O112" s="122"/>
+      <c r="P112" s="122"/>
+    </row>
+    <row r="113" spans="2:18" ht="24" x14ac:dyDescent="0.3">
+      <c r="B113" s="3"/>
+      <c r="C113" s="3"/>
+      <c r="D113" s="111">
         <v>5</v>
       </c>
-      <c r="E111" s="273"/>
-      <c r="F111" s="273"/>
-      <c r="G111" s="273"/>
-      <c r="H111" s="273"/>
-      <c r="I111" s="273"/>
-      <c r="J111" s="273"/>
-      <c r="K111" s="273"/>
-      <c r="L111" s="273"/>
-      <c r="M111" s="273"/>
-      <c r="N111" s="273"/>
-      <c r="O111" s="273"/>
-      <c r="P111" s="273"/>
-    </row>
-    <row r="112" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B112" s="8"/>
-      <c r="C112" s="8"/>
-      <c r="D112" s="272">
-        <v>6</v>
-      </c>
-      <c r="E112" s="219"/>
-      <c r="F112" s="219"/>
-      <c r="G112" s="219"/>
-      <c r="H112" s="219"/>
-      <c r="I112" s="219"/>
-      <c r="J112" s="219"/>
-      <c r="K112" s="219"/>
-      <c r="L112" s="219"/>
-      <c r="M112" s="219"/>
-      <c r="N112" s="219"/>
-      <c r="O112" s="219"/>
-      <c r="P112" s="219"/>
-      <c r="Q112" s="55"/>
-      <c r="R112" s="55"/>
-    </row>
-    <row r="113" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B113" s="8"/>
-      <c r="C113" s="8"/>
-      <c r="D113" s="272">
-        <v>7</v>
-      </c>
-      <c r="E113" s="219"/>
-      <c r="F113" s="219"/>
-      <c r="G113" s="219"/>
-      <c r="H113" s="219"/>
-      <c r="I113" s="219"/>
-      <c r="J113" s="219"/>
-      <c r="K113" s="219"/>
-      <c r="L113" s="219"/>
-      <c r="M113" s="219"/>
-      <c r="N113" s="219"/>
-      <c r="O113" s="219"/>
-      <c r="P113" s="219"/>
-      <c r="Q113" s="55"/>
-      <c r="R113" s="55"/>
+      <c r="E113" s="117"/>
+      <c r="F113" s="117"/>
+      <c r="G113" s="117"/>
+      <c r="H113" s="117"/>
+      <c r="I113" s="117"/>
+      <c r="J113" s="117"/>
+      <c r="K113" s="117"/>
+      <c r="L113" s="117"/>
+      <c r="M113" s="117"/>
+      <c r="N113" s="117"/>
+      <c r="O113" s="117"/>
+      <c r="P113" s="117"/>
     </row>
     <row r="114" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="8"/>
       <c r="C114" s="8"/>
-      <c r="D114" s="272">
-        <v>8</v>
-      </c>
-      <c r="E114" s="219"/>
-      <c r="F114" s="219"/>
-      <c r="G114" s="219"/>
-      <c r="H114" s="219"/>
-      <c r="I114" s="219"/>
-      <c r="J114" s="219"/>
-      <c r="K114" s="219"/>
-      <c r="L114" s="219"/>
-      <c r="M114" s="219"/>
-      <c r="N114" s="219"/>
-      <c r="O114" s="219"/>
-      <c r="P114" s="219"/>
+      <c r="D114" s="295">
+        <v>6</v>
+      </c>
+      <c r="E114" s="122"/>
+      <c r="F114" s="122"/>
+      <c r="G114" s="122"/>
+      <c r="H114" s="122"/>
+      <c r="I114" s="122"/>
+      <c r="J114" s="122"/>
+      <c r="K114" s="122"/>
+      <c r="L114" s="122"/>
+      <c r="M114" s="122"/>
+      <c r="N114" s="122"/>
+      <c r="O114" s="122"/>
+      <c r="P114" s="122"/>
       <c r="Q114" s="55"/>
       <c r="R114" s="55"/>
     </row>
-    <row r="115" spans="2:18" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B115" s="74"/>
-      <c r="C115" s="74"/>
-      <c r="D115" s="270"/>
-      <c r="E115" s="270"/>
-      <c r="F115" s="270"/>
-      <c r="G115" s="270"/>
-      <c r="H115" s="270"/>
-      <c r="I115" s="270"/>
-      <c r="J115" s="270"/>
-      <c r="K115" s="270"/>
-      <c r="L115" s="270"/>
-      <c r="M115" s="270"/>
-      <c r="N115" s="270"/>
-      <c r="O115" s="270"/>
-      <c r="P115" s="270"/>
+    <row r="115" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B115" s="8"/>
+      <c r="C115" s="8"/>
+      <c r="D115" s="111">
+        <v>7</v>
+      </c>
+      <c r="E115" s="116"/>
+      <c r="F115" s="116"/>
+      <c r="G115" s="116"/>
+      <c r="H115" s="116"/>
+      <c r="I115" s="116"/>
+      <c r="J115" s="116"/>
+      <c r="K115" s="116"/>
+      <c r="L115" s="116"/>
+      <c r="M115" s="116"/>
+      <c r="N115" s="116"/>
+      <c r="O115" s="116"/>
+      <c r="P115" s="116"/>
       <c r="Q115" s="55"/>
       <c r="R115" s="55"/>
     </row>
-    <row r="116" spans="2:18" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B116" s="74"/>
-      <c r="C116" s="74"/>
-      <c r="D116" s="254" t="s">
-        <v>122</v>
-      </c>
-      <c r="E116" s="254"/>
-      <c r="F116" s="254"/>
-      <c r="G116" s="254"/>
-      <c r="H116" s="254"/>
-      <c r="I116" s="254"/>
-      <c r="J116" s="254"/>
-      <c r="K116" s="254"/>
-      <c r="L116" s="254"/>
-      <c r="M116" s="254"/>
-      <c r="N116" s="254"/>
-      <c r="O116" s="254"/>
-      <c r="P116" s="254"/>
+    <row r="116" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B116" s="8"/>
+      <c r="C116" s="8"/>
+      <c r="D116" s="295">
+        <v>8</v>
+      </c>
+      <c r="E116" s="122"/>
+      <c r="F116" s="122"/>
+      <c r="G116" s="122"/>
+      <c r="H116" s="122"/>
+      <c r="I116" s="122"/>
+      <c r="J116" s="122"/>
+      <c r="K116" s="122"/>
+      <c r="L116" s="122"/>
+      <c r="M116" s="122"/>
+      <c r="N116" s="122"/>
+      <c r="O116" s="122"/>
+      <c r="P116" s="122"/>
       <c r="Q116" s="55"/>
       <c r="R116" s="55"/>
     </row>
-    <row r="117" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="117" spans="2:18" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B117" s="74"/>
       <c r="C117" s="74"/>
-      <c r="D117" s="56"/>
-      <c r="E117" s="55"/>
-      <c r="F117" s="55"/>
-      <c r="G117" s="55"/>
-      <c r="H117" s="55"/>
-      <c r="I117" s="55"/>
-      <c r="J117" s="55"/>
-      <c r="K117" s="55"/>
-      <c r="L117" s="55"/>
-      <c r="M117" s="55"/>
-      <c r="N117" s="55"/>
-      <c r="O117" s="55"/>
-      <c r="P117" s="55"/>
+      <c r="D117" s="112"/>
+      <c r="E117" s="112"/>
+      <c r="F117" s="112"/>
+      <c r="G117" s="112"/>
+      <c r="H117" s="112"/>
+      <c r="I117" s="112"/>
+      <c r="J117" s="112"/>
+      <c r="K117" s="112"/>
+      <c r="L117" s="112"/>
+      <c r="M117" s="112"/>
+      <c r="N117" s="112"/>
+      <c r="O117" s="112"/>
+      <c r="P117" s="112"/>
       <c r="Q117" s="55"/>
       <c r="R117" s="55"/>
     </row>
-    <row r="118" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="2:18" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B118" s="74"/>
       <c r="C118" s="74"/>
-      <c r="D118" s="164" t="s">
-        <v>123</v>
-      </c>
-      <c r="E118" s="164"/>
-      <c r="F118" s="164"/>
-      <c r="G118" s="55"/>
-      <c r="H118" s="164" t="s">
-        <v>123</v>
-      </c>
-      <c r="I118" s="164"/>
-      <c r="J118" s="164"/>
-      <c r="K118" s="55"/>
-      <c r="L118" s="164" t="s">
-        <v>123</v>
-      </c>
-      <c r="M118" s="164"/>
-      <c r="N118" s="55"/>
-      <c r="O118" s="164" t="s">
-        <v>124</v>
-      </c>
-      <c r="P118" s="164"/>
+      <c r="D118" s="153" t="s">
+        <v>121</v>
+      </c>
+      <c r="E118" s="153"/>
+      <c r="F118" s="153"/>
+      <c r="G118" s="153"/>
+      <c r="H118" s="153"/>
+      <c r="I118" s="153"/>
+      <c r="J118" s="153"/>
+      <c r="K118" s="153"/>
+      <c r="L118" s="153"/>
+      <c r="M118" s="153"/>
+      <c r="N118" s="153"/>
+      <c r="O118" s="153"/>
+      <c r="P118" s="153"/>
       <c r="Q118" s="55"/>
       <c r="R118" s="55"/>
     </row>
-    <row r="119" spans="2:18" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B119" s="74"/>
       <c r="C119" s="74"/>
-      <c r="D119" s="55"/>
+      <c r="D119" s="56"/>
       <c r="E119" s="55"/>
       <c r="F119" s="55"/>
       <c r="G119" s="55"/>
@@ -5376,38 +5527,46 @@
     <row r="120" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B120" s="74"/>
       <c r="C120" s="74"/>
-      <c r="D120" s="92"/>
-      <c r="E120" s="92"/>
-      <c r="F120" s="92"/>
+      <c r="D120" s="130" t="s">
+        <v>122</v>
+      </c>
+      <c r="E120" s="130"/>
+      <c r="F120" s="130"/>
       <c r="G120" s="55"/>
-      <c r="H120" s="92"/>
-      <c r="I120" s="92"/>
-      <c r="J120" s="92"/>
+      <c r="H120" s="130" t="s">
+        <v>122</v>
+      </c>
+      <c r="I120" s="130"/>
+      <c r="J120" s="130"/>
       <c r="K120" s="55"/>
-      <c r="L120" s="92"/>
-      <c r="M120" s="92"/>
+      <c r="L120" s="130" t="s">
+        <v>122</v>
+      </c>
+      <c r="M120" s="130"/>
       <c r="N120" s="55"/>
-      <c r="O120" s="92"/>
-      <c r="P120" s="92"/>
+      <c r="O120" s="130" t="s">
+        <v>123</v>
+      </c>
+      <c r="P120" s="130"/>
       <c r="Q120" s="55"/>
       <c r="R120" s="55"/>
     </row>
-    <row r="121" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="2:18" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B121" s="74"/>
       <c r="C121" s="74"/>
-      <c r="D121" s="92"/>
-      <c r="E121" s="92"/>
-      <c r="F121" s="92"/>
+      <c r="D121" s="55"/>
+      <c r="E121" s="55"/>
+      <c r="F121" s="55"/>
       <c r="G121" s="55"/>
-      <c r="H121" s="92"/>
-      <c r="I121" s="92"/>
-      <c r="J121" s="92"/>
+      <c r="H121" s="55"/>
+      <c r="I121" s="55"/>
+      <c r="J121" s="55"/>
       <c r="K121" s="55"/>
-      <c r="L121" s="92"/>
-      <c r="M121" s="92"/>
+      <c r="L121" s="55"/>
+      <c r="M121" s="55"/>
       <c r="N121" s="55"/>
-      <c r="O121" s="92"/>
-      <c r="P121" s="92"/>
+      <c r="O121" s="55"/>
+      <c r="P121" s="55"/>
       <c r="Q121" s="55"/>
       <c r="R121" s="55"/>
     </row>
@@ -5433,270 +5592,172 @@
     <row r="123" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B123" s="74"/>
       <c r="C123" s="74"/>
-      <c r="D123" s="93"/>
-      <c r="E123" s="93"/>
-      <c r="F123" s="93"/>
+      <c r="D123" s="92"/>
+      <c r="E123" s="92"/>
+      <c r="F123" s="92"/>
       <c r="G123" s="55"/>
-      <c r="H123" s="93"/>
-      <c r="I123" s="93"/>
-      <c r="J123" s="93"/>
+      <c r="H123" s="92"/>
+      <c r="I123" s="92"/>
+      <c r="J123" s="92"/>
       <c r="K123" s="55"/>
-      <c r="L123" s="93"/>
-      <c r="M123" s="93"/>
+      <c r="L123" s="92"/>
+      <c r="M123" s="92"/>
       <c r="N123" s="55"/>
-      <c r="O123" s="93"/>
-      <c r="P123" s="93"/>
+      <c r="O123" s="92"/>
+      <c r="P123" s="92"/>
       <c r="Q123" s="55"/>
       <c r="R123" s="55"/>
     </row>
-    <row r="124" spans="2:18" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="124" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B124" s="74"/>
       <c r="C124" s="74"/>
-      <c r="D124" s="159" t="s">
-        <v>125</v>
-      </c>
-      <c r="E124" s="160"/>
-      <c r="F124" s="160"/>
-      <c r="G124" s="94"/>
-      <c r="H124" s="182" t="s">
-        <v>126</v>
-      </c>
-      <c r="I124" s="160"/>
-      <c r="J124" s="160"/>
-      <c r="K124" s="94"/>
-      <c r="L124" s="184" t="s">
-        <v>127</v>
-      </c>
-      <c r="M124" s="185"/>
-      <c r="N124" s="94"/>
-      <c r="O124" s="184" t="s">
-        <v>128</v>
-      </c>
-      <c r="P124" s="185"/>
+      <c r="D124" s="92"/>
+      <c r="E124" s="92"/>
+      <c r="F124" s="92"/>
+      <c r="G124" s="55"/>
+      <c r="H124" s="92"/>
+      <c r="I124" s="92"/>
+      <c r="J124" s="92"/>
+      <c r="K124" s="55"/>
+      <c r="L124" s="92"/>
+      <c r="M124" s="92"/>
+      <c r="N124" s="55"/>
+      <c r="O124" s="92"/>
+      <c r="P124" s="92"/>
       <c r="Q124" s="55"/>
       <c r="R124" s="55"/>
     </row>
-    <row r="125" spans="2:18" s="3" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="125" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B125" s="74"/>
       <c r="C125" s="74"/>
-      <c r="D125" s="180" t="s">
-        <v>129</v>
-      </c>
-      <c r="E125" s="113"/>
-      <c r="F125" s="113"/>
-      <c r="G125" s="90"/>
-      <c r="H125" s="180" t="s">
-        <v>129</v>
-      </c>
-      <c r="I125" s="113"/>
-      <c r="J125" s="113"/>
-      <c r="K125" s="94"/>
-      <c r="L125" s="209" t="s">
-        <v>130</v>
-      </c>
-      <c r="M125" s="160"/>
-      <c r="N125" s="94"/>
-      <c r="O125" s="180" t="s">
-        <v>129</v>
-      </c>
-      <c r="P125" s="113"/>
+      <c r="D125" s="93"/>
+      <c r="E125" s="93"/>
+      <c r="F125" s="93"/>
+      <c r="G125" s="55"/>
+      <c r="H125" s="93"/>
+      <c r="I125" s="93"/>
+      <c r="J125" s="93"/>
+      <c r="K125" s="55"/>
+      <c r="L125" s="93"/>
+      <c r="M125" s="93"/>
+      <c r="N125" s="55"/>
+      <c r="O125" s="93"/>
+      <c r="P125" s="93"/>
       <c r="Q125" s="55"/>
       <c r="R125" s="55"/>
     </row>
-    <row r="126" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="2:18" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B126" s="74"/>
       <c r="C126" s="74"/>
-      <c r="D126" s="55"/>
-      <c r="E126" s="55"/>
-      <c r="F126" s="55"/>
-      <c r="G126" s="55"/>
-      <c r="H126" s="55"/>
-      <c r="I126" s="55"/>
-      <c r="J126" s="55"/>
-      <c r="K126" s="55"/>
-      <c r="L126" s="77"/>
-      <c r="M126" s="77"/>
-      <c r="N126" s="55"/>
-      <c r="O126" s="77"/>
-      <c r="P126" s="78"/>
+      <c r="D126" s="211" t="s">
+        <v>124</v>
+      </c>
+      <c r="E126" s="161"/>
+      <c r="F126" s="161"/>
+      <c r="G126" s="94"/>
+      <c r="H126" s="189" t="s">
+        <v>125</v>
+      </c>
+      <c r="I126" s="161"/>
+      <c r="J126" s="161"/>
+      <c r="K126" s="94"/>
+      <c r="L126" s="127" t="s">
+        <v>126</v>
+      </c>
+      <c r="M126" s="128"/>
+      <c r="N126" s="94"/>
+      <c r="O126" s="127" t="s">
+        <v>127</v>
+      </c>
+      <c r="P126" s="128"/>
       <c r="Q126" s="55"/>
       <c r="R126" s="55"/>
     </row>
-    <row r="127" spans="2:18" s="3" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="2:18" s="3" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B127" s="74"/>
       <c r="C127" s="74"/>
-      <c r="D127" s="79"/>
-      <c r="E127" s="80"/>
-      <c r="F127" s="80"/>
-      <c r="G127" s="80"/>
-      <c r="H127" s="80"/>
-      <c r="I127" s="80"/>
-      <c r="J127" s="80"/>
-      <c r="K127" s="80"/>
-      <c r="L127" s="80"/>
-      <c r="M127" s="80"/>
-      <c r="N127" s="80"/>
-      <c r="O127" s="80"/>
-      <c r="P127" s="80"/>
+      <c r="D127" s="137" t="s">
+        <v>16</v>
+      </c>
+      <c r="E127" s="135"/>
+      <c r="F127" s="135"/>
+      <c r="G127" s="90"/>
+      <c r="H127" s="137" t="s">
+        <v>128</v>
+      </c>
+      <c r="I127" s="135"/>
+      <c r="J127" s="135"/>
+      <c r="K127" s="94"/>
+      <c r="L127" s="141" t="s">
+        <v>129</v>
+      </c>
+      <c r="M127" s="161"/>
+      <c r="N127" s="94"/>
+      <c r="O127" s="137" t="s">
+        <v>128</v>
+      </c>
+      <c r="P127" s="135"/>
       <c r="Q127" s="55"/>
       <c r="R127" s="55"/>
     </row>
-    <row r="128" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B128" s="74"/>
+      <c r="C128" s="74"/>
+      <c r="D128" s="55"/>
+      <c r="E128" s="55"/>
+      <c r="F128" s="55"/>
+      <c r="G128" s="55"/>
+      <c r="H128" s="55"/>
+      <c r="I128" s="55"/>
+      <c r="J128" s="55"/>
+      <c r="K128" s="55"/>
+      <c r="L128" s="77"/>
+      <c r="M128" s="77"/>
+      <c r="N128" s="55"/>
+      <c r="O128" s="77"/>
+      <c r="P128" s="78"/>
       <c r="Q128" s="55"/>
       <c r="R128" s="55"/>
     </row>
+    <row r="129" spans="2:18" s="3" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B129" s="74"/>
+      <c r="C129" s="74"/>
+      <c r="D129" s="79"/>
+      <c r="E129" s="80"/>
+      <c r="F129" s="80"/>
+      <c r="G129" s="80"/>
+      <c r="H129" s="80"/>
+      <c r="I129" s="80"/>
+      <c r="J129" s="80"/>
+      <c r="K129" s="80"/>
+      <c r="L129" s="80"/>
+      <c r="M129" s="80"/>
+      <c r="N129" s="80"/>
+      <c r="O129" s="80"/>
+      <c r="P129" s="80"/>
+      <c r="Q129" s="55"/>
+      <c r="R129" s="55"/>
+    </row>
+    <row r="130" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="Q130" s="55"/>
+      <c r="R130" s="55"/>
+    </row>
   </sheetData>
-  <mergeCells count="181">
-    <mergeCell ref="E82:M82"/>
-    <mergeCell ref="E104:G104"/>
-    <mergeCell ref="D115:P115"/>
-    <mergeCell ref="E106:P106"/>
-    <mergeCell ref="E107:P107"/>
-    <mergeCell ref="E113:P113"/>
-    <mergeCell ref="E114:P114"/>
-    <mergeCell ref="E108:P108"/>
-    <mergeCell ref="E109:P109"/>
-    <mergeCell ref="E110:P110"/>
-    <mergeCell ref="E111:P111"/>
-    <mergeCell ref="E112:P112"/>
-    <mergeCell ref="D66:F66"/>
-    <mergeCell ref="G66:I66"/>
-    <mergeCell ref="J66:L66"/>
-    <mergeCell ref="M66:P66"/>
-    <mergeCell ref="M65:P65"/>
-    <mergeCell ref="J65:L65"/>
-    <mergeCell ref="G65:I65"/>
-    <mergeCell ref="D65:F65"/>
-    <mergeCell ref="E81:P81"/>
-    <mergeCell ref="M63:P63"/>
-    <mergeCell ref="D64:F64"/>
-    <mergeCell ref="G64:I64"/>
-    <mergeCell ref="J64:L64"/>
-    <mergeCell ref="M64:P64"/>
-    <mergeCell ref="I76:L76"/>
-    <mergeCell ref="E49:J49"/>
-    <mergeCell ref="L124:M124"/>
-    <mergeCell ref="E92:M92"/>
-    <mergeCell ref="O118:P118"/>
-    <mergeCell ref="N55:O55"/>
-    <mergeCell ref="L118:M118"/>
-    <mergeCell ref="E93:M93"/>
-    <mergeCell ref="E85:M85"/>
+  <mergeCells count="184">
+    <mergeCell ref="D19:H19"/>
+    <mergeCell ref="L21:O21"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="L13:O13"/>
+    <mergeCell ref="D21:H21"/>
+    <mergeCell ref="L16:O16"/>
+    <mergeCell ref="L18:P18"/>
+    <mergeCell ref="E84:M85"/>
+    <mergeCell ref="D84:D85"/>
+    <mergeCell ref="E68:P68"/>
+    <mergeCell ref="E69:P69"/>
+    <mergeCell ref="E76:P76"/>
+    <mergeCell ref="E77:P77"/>
     <mergeCell ref="E78:P78"/>
-    <mergeCell ref="N54:O54"/>
-    <mergeCell ref="H125:J125"/>
-    <mergeCell ref="D31:I31"/>
-    <mergeCell ref="L46:P46"/>
-    <mergeCell ref="D45:I45"/>
-    <mergeCell ref="D23:H23"/>
-    <mergeCell ref="L38:O38"/>
-    <mergeCell ref="E51:J51"/>
-    <mergeCell ref="L31:O31"/>
-    <mergeCell ref="L40:O40"/>
-    <mergeCell ref="N50:O50"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="H118:J118"/>
-    <mergeCell ref="N51:O51"/>
-    <mergeCell ref="D116:P116"/>
-    <mergeCell ref="E90:M90"/>
-    <mergeCell ref="E77:P77"/>
-    <mergeCell ref="L27:O27"/>
-    <mergeCell ref="D43:I43"/>
-    <mergeCell ref="L36:O36"/>
-    <mergeCell ref="D26:J26"/>
-    <mergeCell ref="L125:M125"/>
-    <mergeCell ref="H17:I17"/>
-    <mergeCell ref="D33:I33"/>
-    <mergeCell ref="D42:I42"/>
-    <mergeCell ref="E72:P72"/>
-    <mergeCell ref="I24:J24"/>
-    <mergeCell ref="D35:I35"/>
-    <mergeCell ref="D44:I44"/>
-    <mergeCell ref="D27:J27"/>
-    <mergeCell ref="D34:I34"/>
-    <mergeCell ref="D25:H25"/>
-    <mergeCell ref="L30:O30"/>
-    <mergeCell ref="L39:O39"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="D48:P48"/>
-    <mergeCell ref="L19:O19"/>
-    <mergeCell ref="L35:P35"/>
-    <mergeCell ref="L20:O20"/>
-    <mergeCell ref="D61:F61"/>
-    <mergeCell ref="G61:I61"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="M61:P61"/>
-    <mergeCell ref="D125:F125"/>
-    <mergeCell ref="E89:M89"/>
-    <mergeCell ref="N58:O58"/>
-    <mergeCell ref="O125:P125"/>
-    <mergeCell ref="H124:J124"/>
-    <mergeCell ref="N49:O49"/>
-    <mergeCell ref="O124:P124"/>
-    <mergeCell ref="E87:M87"/>
-    <mergeCell ref="E79:P79"/>
-    <mergeCell ref="E84:M84"/>
-    <mergeCell ref="E75:P75"/>
-    <mergeCell ref="N57:O57"/>
-    <mergeCell ref="D60:P60"/>
-    <mergeCell ref="O99:P104"/>
-    <mergeCell ref="N56:O56"/>
-    <mergeCell ref="E55:J55"/>
-    <mergeCell ref="E52:J52"/>
-    <mergeCell ref="E71:P71"/>
-    <mergeCell ref="O90:P90"/>
-    <mergeCell ref="E88:M88"/>
-    <mergeCell ref="O85:P88"/>
-    <mergeCell ref="O84:P84"/>
-    <mergeCell ref="O91:P96"/>
-    <mergeCell ref="E83:M83"/>
-    <mergeCell ref="E91:M91"/>
-    <mergeCell ref="D46:I46"/>
-    <mergeCell ref="D24:H24"/>
-    <mergeCell ref="D40:I40"/>
-    <mergeCell ref="D41:I41"/>
-    <mergeCell ref="O98:P98"/>
-    <mergeCell ref="D68:P68"/>
-    <mergeCell ref="N53:O53"/>
-    <mergeCell ref="E86:M86"/>
-    <mergeCell ref="E95:M95"/>
-    <mergeCell ref="L26:O26"/>
-    <mergeCell ref="L24:P24"/>
-    <mergeCell ref="D32:I32"/>
-    <mergeCell ref="E70:P70"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="G62:I62"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="M62:P62"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="G63:I63"/>
-    <mergeCell ref="J63:L63"/>
-    <mergeCell ref="L4:N5"/>
-    <mergeCell ref="L14:O14"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="D13:E13"/>
-    <mergeCell ref="L3:N3"/>
-    <mergeCell ref="L32:O32"/>
-    <mergeCell ref="D124:F124"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="D38:I38"/>
-    <mergeCell ref="E53:J53"/>
-    <mergeCell ref="E96:M96"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="D118:F118"/>
-    <mergeCell ref="E50:J50"/>
-    <mergeCell ref="L33:O33"/>
-    <mergeCell ref="E94:M94"/>
-    <mergeCell ref="L22:O22"/>
-    <mergeCell ref="L29:P29"/>
-    <mergeCell ref="D29:I29"/>
-    <mergeCell ref="F3:J3"/>
-    <mergeCell ref="F15:J15"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="H6:J6"/>
     <mergeCell ref="D14:E14"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="D15:E15"/>
@@ -5721,13 +5782,152 @@
     <mergeCell ref="L15:O15"/>
     <mergeCell ref="F13:J13"/>
     <mergeCell ref="L12:O12"/>
-    <mergeCell ref="D19:H19"/>
-    <mergeCell ref="L21:O21"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="L13:O13"/>
-    <mergeCell ref="D21:H21"/>
-    <mergeCell ref="L16:O16"/>
-    <mergeCell ref="L18:P18"/>
+    <mergeCell ref="L4:N5"/>
+    <mergeCell ref="L14:O14"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="D13:E13"/>
+    <mergeCell ref="L3:N3"/>
+    <mergeCell ref="L32:O32"/>
+    <mergeCell ref="D126:F126"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="D38:I38"/>
+    <mergeCell ref="E53:J53"/>
+    <mergeCell ref="E98:M98"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="D120:F120"/>
+    <mergeCell ref="E50:J50"/>
+    <mergeCell ref="L33:O33"/>
+    <mergeCell ref="L22:O22"/>
+    <mergeCell ref="L29:P29"/>
+    <mergeCell ref="D29:I29"/>
+    <mergeCell ref="F3:J3"/>
+    <mergeCell ref="F15:J15"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:J8"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="D46:I46"/>
+    <mergeCell ref="D24:H24"/>
+    <mergeCell ref="D40:I40"/>
+    <mergeCell ref="D41:I41"/>
+    <mergeCell ref="O100:P100"/>
+    <mergeCell ref="N53:O53"/>
+    <mergeCell ref="L26:O26"/>
+    <mergeCell ref="L24:P24"/>
+    <mergeCell ref="D32:I32"/>
+    <mergeCell ref="E70:P70"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="G62:I62"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="M62:P62"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="G63:I63"/>
+    <mergeCell ref="J63:L63"/>
+    <mergeCell ref="E86:M87"/>
+    <mergeCell ref="D86:D87"/>
+    <mergeCell ref="E88:M89"/>
+    <mergeCell ref="N56:O56"/>
+    <mergeCell ref="E55:J55"/>
+    <mergeCell ref="E52:J52"/>
+    <mergeCell ref="E71:P71"/>
+    <mergeCell ref="O92:P92"/>
+    <mergeCell ref="O87:P90"/>
+    <mergeCell ref="O86:P86"/>
+    <mergeCell ref="O93:P98"/>
+    <mergeCell ref="E90:M91"/>
+    <mergeCell ref="E92:M93"/>
+    <mergeCell ref="E94:M95"/>
+    <mergeCell ref="E96:M97"/>
+    <mergeCell ref="H17:I17"/>
+    <mergeCell ref="D33:I33"/>
+    <mergeCell ref="D42:I42"/>
+    <mergeCell ref="E72:P72"/>
+    <mergeCell ref="I24:J24"/>
+    <mergeCell ref="D35:I35"/>
+    <mergeCell ref="D44:I44"/>
+    <mergeCell ref="D27:J27"/>
+    <mergeCell ref="D34:I34"/>
+    <mergeCell ref="D25:H25"/>
+    <mergeCell ref="L30:O30"/>
+    <mergeCell ref="L39:O39"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="D48:P48"/>
+    <mergeCell ref="L19:O19"/>
+    <mergeCell ref="L35:P35"/>
+    <mergeCell ref="L20:O20"/>
+    <mergeCell ref="D61:F61"/>
+    <mergeCell ref="G61:I61"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="M61:P61"/>
+    <mergeCell ref="N58:O58"/>
+    <mergeCell ref="N49:O49"/>
+    <mergeCell ref="H127:J127"/>
+    <mergeCell ref="D31:I31"/>
+    <mergeCell ref="L46:P46"/>
+    <mergeCell ref="D45:I45"/>
+    <mergeCell ref="D23:H23"/>
+    <mergeCell ref="L38:O38"/>
+    <mergeCell ref="E51:J51"/>
+    <mergeCell ref="L31:O31"/>
+    <mergeCell ref="L40:O40"/>
+    <mergeCell ref="N50:O50"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="H120:J120"/>
+    <mergeCell ref="N51:O51"/>
+    <mergeCell ref="D118:P118"/>
+    <mergeCell ref="E79:P79"/>
+    <mergeCell ref="L27:O27"/>
+    <mergeCell ref="D43:I43"/>
+    <mergeCell ref="L36:O36"/>
+    <mergeCell ref="D26:J26"/>
+    <mergeCell ref="L127:M127"/>
+    <mergeCell ref="D127:F127"/>
+    <mergeCell ref="O127:P127"/>
+    <mergeCell ref="M63:P63"/>
+    <mergeCell ref="D64:F64"/>
+    <mergeCell ref="G64:I64"/>
+    <mergeCell ref="J64:L64"/>
+    <mergeCell ref="M64:P64"/>
+    <mergeCell ref="E49:J49"/>
+    <mergeCell ref="L126:M126"/>
+    <mergeCell ref="O120:P120"/>
+    <mergeCell ref="N55:O55"/>
+    <mergeCell ref="L120:M120"/>
+    <mergeCell ref="E80:P80"/>
+    <mergeCell ref="N54:O54"/>
+    <mergeCell ref="H126:J126"/>
+    <mergeCell ref="O126:P126"/>
+    <mergeCell ref="E81:P81"/>
+    <mergeCell ref="E75:P75"/>
+    <mergeCell ref="N57:O57"/>
+    <mergeCell ref="D60:P60"/>
+    <mergeCell ref="D66:F66"/>
+    <mergeCell ref="G66:I66"/>
+    <mergeCell ref="J66:L66"/>
+    <mergeCell ref="M66:P66"/>
+    <mergeCell ref="M65:P65"/>
+    <mergeCell ref="J65:L65"/>
+    <mergeCell ref="G65:I65"/>
+    <mergeCell ref="D65:F65"/>
+    <mergeCell ref="E83:P83"/>
+    <mergeCell ref="D117:P117"/>
+    <mergeCell ref="E108:P108"/>
+    <mergeCell ref="E109:P109"/>
+    <mergeCell ref="E115:P115"/>
+    <mergeCell ref="E116:P116"/>
+    <mergeCell ref="E110:P110"/>
+    <mergeCell ref="E111:P111"/>
+    <mergeCell ref="E112:P112"/>
+    <mergeCell ref="E113:P113"/>
+    <mergeCell ref="E114:P114"/>
+    <mergeCell ref="O101:P106"/>
+    <mergeCell ref="D88:D89"/>
+    <mergeCell ref="D90:D91"/>
+    <mergeCell ref="D92:D93"/>
+    <mergeCell ref="D94:D95"/>
+    <mergeCell ref="D96:D97"/>
+    <mergeCell ref="E106:H106"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5737,7 +5937,7 @@
   </headerFooter>
   <rowBreaks count="2" manualBreakCount="2">
     <brk id="46" min="1" max="17" man="1"/>
-    <brk id="79" min="1" max="17" man="1"/>
+    <brk id="81" min="1" max="17" man="1"/>
   </rowBreaks>
   <drawing r:id="rId2"/>
 </worksheet>
@@ -5749,220 +5949,220 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B2" s="101"/>
-      <c r="C2" s="101"/>
-      <c r="D2" s="101"/>
-      <c r="E2" s="101"/>
-      <c r="F2" s="101"/>
-      <c r="G2" s="101"/>
-      <c r="H2" s="101"/>
-      <c r="I2" s="101"/>
-      <c r="J2" s="101"/>
-      <c r="K2" s="101"/>
+      <c r="B2" s="100"/>
+      <c r="C2" s="100"/>
+      <c r="D2" s="100"/>
+      <c r="E2" s="100"/>
+      <c r="F2" s="100"/>
+      <c r="G2" s="100"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B3" s="101"/>
-      <c r="C3" s="101"/>
-      <c r="D3" s="101"/>
-      <c r="E3" s="101"/>
-      <c r="F3" s="101"/>
-      <c r="G3" s="101"/>
-      <c r="H3" s="101"/>
-      <c r="I3" s="101"/>
-      <c r="J3" s="101"/>
-      <c r="K3" s="101"/>
+      <c r="B3" s="100"/>
+      <c r="C3" s="100"/>
+      <c r="D3" s="100"/>
+      <c r="E3" s="100"/>
+      <c r="F3" s="100"/>
+      <c r="G3" s="100"/>
+      <c r="H3" s="100"/>
+      <c r="I3" s="100"/>
+      <c r="J3" s="100"/>
+      <c r="K3" s="100"/>
     </row>
     <row r="4" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B4" s="101"/>
-      <c r="C4" s="101"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="101"/>
-      <c r="F4" s="101"/>
-      <c r="G4" s="101"/>
-      <c r="H4" s="101"/>
-      <c r="I4" s="101"/>
-      <c r="J4" s="101"/>
-      <c r="K4" s="101"/>
+      <c r="B4" s="100"/>
+      <c r="C4" s="100"/>
+      <c r="D4" s="100"/>
+      <c r="E4" s="100"/>
+      <c r="F4" s="100"/>
+      <c r="G4" s="100"/>
+      <c r="H4" s="100"/>
+      <c r="I4" s="100"/>
+      <c r="J4" s="100"/>
+      <c r="K4" s="100"/>
     </row>
     <row r="5" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B5" s="101"/>
-      <c r="C5" s="101"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="101"/>
-      <c r="F5" s="101"/>
-      <c r="G5" s="101"/>
-      <c r="H5" s="101"/>
-      <c r="I5" s="101"/>
-      <c r="J5" s="101"/>
-      <c r="K5" s="101"/>
+      <c r="B5" s="100"/>
+      <c r="C5" s="100"/>
+      <c r="D5" s="100"/>
+      <c r="E5" s="100"/>
+      <c r="F5" s="100"/>
+      <c r="G5" s="100"/>
+      <c r="H5" s="100"/>
+      <c r="I5" s="100"/>
+      <c r="J5" s="100"/>
+      <c r="K5" s="100"/>
     </row>
     <row r="6" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B6" s="101"/>
-      <c r="C6" s="101"/>
-      <c r="D6" s="101"/>
-      <c r="E6" s="101"/>
-      <c r="F6" s="101"/>
-      <c r="G6" s="101"/>
-      <c r="H6" s="101"/>
-      <c r="I6" s="101"/>
-      <c r="J6" s="101"/>
-      <c r="K6" s="101"/>
+      <c r="B6" s="100"/>
+      <c r="C6" s="100"/>
+      <c r="D6" s="100"/>
+      <c r="E6" s="100"/>
+      <c r="F6" s="100"/>
+      <c r="G6" s="100"/>
+      <c r="H6" s="100"/>
+      <c r="I6" s="100"/>
+      <c r="J6" s="100"/>
+      <c r="K6" s="100"/>
     </row>
     <row r="7" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B7" s="101"/>
-      <c r="C7" s="101"/>
-      <c r="D7" s="101"/>
-      <c r="E7" s="101"/>
-      <c r="F7" s="101"/>
-      <c r="G7" s="101"/>
-      <c r="H7" s="101"/>
-      <c r="I7" s="101"/>
-      <c r="J7" s="101"/>
-      <c r="K7" s="101"/>
+      <c r="B7" s="100"/>
+      <c r="C7" s="100"/>
+      <c r="D7" s="100"/>
+      <c r="E7" s="100"/>
+      <c r="F7" s="100"/>
+      <c r="G7" s="100"/>
+      <c r="H7" s="100"/>
+      <c r="I7" s="100"/>
+      <c r="J7" s="100"/>
+      <c r="K7" s="100"/>
     </row>
     <row r="8" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B8" s="101"/>
-      <c r="C8" s="101"/>
-      <c r="D8" s="101"/>
-      <c r="E8" s="101"/>
-      <c r="F8" s="101"/>
-      <c r="G8" s="101"/>
-      <c r="H8" s="101"/>
-      <c r="I8" s="101"/>
-      <c r="J8" s="101"/>
-      <c r="K8" s="101"/>
+      <c r="B8" s="100"/>
+      <c r="C8" s="100"/>
+      <c r="D8" s="100"/>
+      <c r="E8" s="100"/>
+      <c r="F8" s="100"/>
+      <c r="G8" s="100"/>
+      <c r="H8" s="100"/>
+      <c r="I8" s="100"/>
+      <c r="J8" s="100"/>
+      <c r="K8" s="100"/>
     </row>
     <row r="9" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B9" s="101"/>
-      <c r="C9" s="101"/>
-      <c r="D9" s="101"/>
-      <c r="E9" s="101"/>
-      <c r="F9" s="101"/>
-      <c r="G9" s="101"/>
-      <c r="H9" s="101"/>
-      <c r="I9" s="101"/>
-      <c r="J9" s="101"/>
-      <c r="K9" s="101"/>
+      <c r="B9" s="100"/>
+      <c r="C9" s="100"/>
+      <c r="D9" s="100"/>
+      <c r="E9" s="100"/>
+      <c r="F9" s="100"/>
+      <c r="G9" s="100"/>
+      <c r="H9" s="100"/>
+      <c r="I9" s="100"/>
+      <c r="J9" s="100"/>
+      <c r="K9" s="100"/>
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B10" s="101"/>
-      <c r="C10" s="101"/>
-      <c r="D10" s="101"/>
-      <c r="E10" s="101"/>
-      <c r="F10" s="101"/>
-      <c r="G10" s="101"/>
-      <c r="H10" s="101"/>
-      <c r="I10" s="101"/>
-      <c r="J10" s="101"/>
-      <c r="K10" s="101"/>
+      <c r="B10" s="100"/>
+      <c r="C10" s="100"/>
+      <c r="D10" s="100"/>
+      <c r="E10" s="100"/>
+      <c r="F10" s="100"/>
+      <c r="G10" s="100"/>
+      <c r="H10" s="100"/>
+      <c r="I10" s="100"/>
+      <c r="J10" s="100"/>
+      <c r="K10" s="100"/>
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B11" s="101"/>
-      <c r="C11" s="101"/>
-      <c r="D11" s="101"/>
-      <c r="E11" s="101"/>
-      <c r="F11" s="101"/>
-      <c r="G11" s="101"/>
-      <c r="H11" s="101"/>
-      <c r="I11" s="101"/>
-      <c r="J11" s="101"/>
-      <c r="K11" s="101"/>
+      <c r="B11" s="100"/>
+      <c r="C11" s="100"/>
+      <c r="D11" s="100"/>
+      <c r="E11" s="100"/>
+      <c r="F11" s="100"/>
+      <c r="G11" s="100"/>
+      <c r="H11" s="100"/>
+      <c r="I11" s="100"/>
+      <c r="J11" s="100"/>
+      <c r="K11" s="100"/>
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B12" s="101"/>
-      <c r="C12" s="101"/>
-      <c r="D12" s="101"/>
-      <c r="E12" s="101"/>
-      <c r="F12" s="101"/>
-      <c r="G12" s="101"/>
-      <c r="H12" s="101"/>
-      <c r="I12" s="101"/>
-      <c r="J12" s="101"/>
-      <c r="K12" s="101"/>
+      <c r="B12" s="100"/>
+      <c r="C12" s="100"/>
+      <c r="D12" s="100"/>
+      <c r="E12" s="100"/>
+      <c r="F12" s="100"/>
+      <c r="G12" s="100"/>
+      <c r="H12" s="100"/>
+      <c r="I12" s="100"/>
+      <c r="J12" s="100"/>
+      <c r="K12" s="100"/>
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B13" s="101"/>
-      <c r="C13" s="101"/>
-      <c r="D13" s="101"/>
-      <c r="E13" s="101"/>
-      <c r="F13" s="101"/>
-      <c r="G13" s="101"/>
-      <c r="H13" s="101"/>
-      <c r="I13" s="101"/>
-      <c r="J13" s="101"/>
-      <c r="K13" s="101"/>
+      <c r="B13" s="100"/>
+      <c r="C13" s="100"/>
+      <c r="D13" s="100"/>
+      <c r="E13" s="100"/>
+      <c r="F13" s="100"/>
+      <c r="G13" s="100"/>
+      <c r="H13" s="100"/>
+      <c r="I13" s="100"/>
+      <c r="J13" s="100"/>
+      <c r="K13" s="100"/>
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B14" s="101"/>
-      <c r="C14" s="101"/>
-      <c r="D14" s="101"/>
-      <c r="E14" s="101"/>
-      <c r="F14" s="101"/>
-      <c r="G14" s="101"/>
-      <c r="H14" s="101"/>
-      <c r="I14" s="101"/>
-      <c r="J14" s="101"/>
-      <c r="K14" s="101"/>
+      <c r="B14" s="100"/>
+      <c r="C14" s="100"/>
+      <c r="D14" s="100"/>
+      <c r="E14" s="100"/>
+      <c r="F14" s="100"/>
+      <c r="G14" s="100"/>
+      <c r="H14" s="100"/>
+      <c r="I14" s="100"/>
+      <c r="J14" s="100"/>
+      <c r="K14" s="100"/>
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B15" s="101"/>
-      <c r="C15" s="101"/>
-      <c r="D15" s="101"/>
-      <c r="E15" s="101"/>
-      <c r="F15" s="101"/>
-      <c r="G15" s="101"/>
-      <c r="H15" s="101"/>
-      <c r="I15" s="101"/>
-      <c r="J15" s="101"/>
-      <c r="K15" s="101"/>
+      <c r="B15" s="100"/>
+      <c r="C15" s="100"/>
+      <c r="D15" s="100"/>
+      <c r="E15" s="100"/>
+      <c r="F15" s="100"/>
+      <c r="G15" s="100"/>
+      <c r="H15" s="100"/>
+      <c r="I15" s="100"/>
+      <c r="J15" s="100"/>
+      <c r="K15" s="100"/>
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B16" s="101"/>
-      <c r="C16" s="101"/>
-      <c r="D16" s="101"/>
-      <c r="E16" s="101"/>
-      <c r="F16" s="101"/>
-      <c r="G16" s="101"/>
-      <c r="H16" s="101"/>
-      <c r="I16" s="101"/>
-      <c r="J16" s="101"/>
-      <c r="K16" s="101"/>
+      <c r="B16" s="100"/>
+      <c r="C16" s="100"/>
+      <c r="D16" s="100"/>
+      <c r="E16" s="100"/>
+      <c r="F16" s="100"/>
+      <c r="G16" s="100"/>
+      <c r="H16" s="100"/>
+      <c r="I16" s="100"/>
+      <c r="J16" s="100"/>
+      <c r="K16" s="100"/>
     </row>
     <row r="17" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B17" s="101"/>
-      <c r="C17" s="101"/>
-      <c r="D17" s="101"/>
-      <c r="E17" s="101"/>
-      <c r="F17" s="101"/>
-      <c r="G17" s="101"/>
-      <c r="H17" s="101"/>
-      <c r="I17" s="101"/>
-      <c r="J17" s="101"/>
-      <c r="K17" s="101"/>
+      <c r="B17" s="100"/>
+      <c r="C17" s="100"/>
+      <c r="D17" s="100"/>
+      <c r="E17" s="100"/>
+      <c r="F17" s="100"/>
+      <c r="G17" s="100"/>
+      <c r="H17" s="100"/>
+      <c r="I17" s="100"/>
+      <c r="J17" s="100"/>
+      <c r="K17" s="100"/>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B18" s="101"/>
-      <c r="C18" s="101"/>
-      <c r="D18" s="101"/>
-      <c r="E18" s="101"/>
-      <c r="F18" s="101"/>
-      <c r="G18" s="101"/>
-      <c r="H18" s="101"/>
-      <c r="I18" s="101"/>
-      <c r="J18" s="101"/>
-      <c r="K18" s="101"/>
+      <c r="B18" s="100"/>
+      <c r="C18" s="100"/>
+      <c r="D18" s="100"/>
+      <c r="E18" s="100"/>
+      <c r="F18" s="100"/>
+      <c r="G18" s="100"/>
+      <c r="H18" s="100"/>
+      <c r="I18" s="100"/>
+      <c r="J18" s="100"/>
+      <c r="K18" s="100"/>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B19" s="101"/>
-      <c r="C19" s="101"/>
-      <c r="D19" s="101"/>
-      <c r="E19" s="101"/>
-      <c r="F19" s="101"/>
-      <c r="G19" s="101"/>
-      <c r="H19" s="101"/>
-      <c r="I19" s="101"/>
-      <c r="J19" s="101"/>
-      <c r="K19" s="101"/>
+      <c r="B19" s="100"/>
+      <c r="C19" s="100"/>
+      <c r="D19" s="100"/>
+      <c r="E19" s="100"/>
+      <c r="F19" s="100"/>
+      <c r="G19" s="100"/>
+      <c r="H19" s="100"/>
+      <c r="I19" s="100"/>
+      <c r="J19" s="100"/>
+      <c r="K19" s="100"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
+++ b/templates/100_PUNTO_DE_ACTA_PLANTILLA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xoi\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5D42E797-2BFC-4B9E-B4DD-0C07E6480C88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AA85A58-F18D-441D-BE3D-F6532E314643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24,7 +24,7 @@
     <definedName name="AGUA">#REF!</definedName>
     <definedName name="ANTICIPO" localSheetId="0">#REF!</definedName>
     <definedName name="ANTICIPO">#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'C-9-12'!$B$2:$R$129</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'C-9-12'!$B$2:$R$135</definedName>
     <definedName name="AZULEJO">#REF!</definedName>
     <definedName name="BASE">#REF!</definedName>
     <definedName name="BASE1">#REF!</definedName>
@@ -1857,20 +1857,11 @@
     <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyProtection="1">
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1883,7 +1874,105 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="32" fillId="4" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
@@ -1902,10 +1991,71 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="5" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -1921,55 +2071,8 @@
     <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="5" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="5" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -2029,6 +2132,13 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyProtection="1">
+      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
@@ -2048,8 +2158,8 @@
     <xf numFmtId="0" fontId="19" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2057,6 +2167,10 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2110,48 +2224,30 @@
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="35" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" xfId="0" applyBorder="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="36" xfId="0" applyBorder="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="9" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="33" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
@@ -2163,36 +2259,10 @@
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="2" fillId="9" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -2243,6 +2313,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -2258,6 +2332,10 @@
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2281,10 +2359,18 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="6" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
@@ -2310,40 +2396,6 @@
     <xf numFmtId="0" fontId="22" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2353,13 +2405,6 @@
     <xf numFmtId="0" fontId="24" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="22" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2369,27 +2414,18 @@
     <xf numFmtId="0" fontId="22" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="47" xfId="0" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="32" fillId="4" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="27" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="27" fillId="5" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2399,74 +2435,41 @@
     <xf numFmtId="0" fontId="27" fillId="5" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="47" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="53" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="54" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" indent="2"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="62" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="5" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="57" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="22" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="58" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="63" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="59" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="60" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="61" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="47" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2588,10 +2591,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2894,7 +2893,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:W130"/>
+  <dimension ref="B2:W136"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.44140625" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.109375" style="1" customWidth="1"/>
@@ -2943,19 +2942,19 @@
       <c r="C3" s="48"/>
       <c r="D3" s="49"/>
       <c r="E3" s="48"/>
-      <c r="F3" s="210" t="s">
+      <c r="F3" s="228" t="s">
         <v>0</v>
       </c>
-      <c r="G3" s="142"/>
-      <c r="H3" s="142"/>
-      <c r="I3" s="142"/>
-      <c r="J3" s="142"/>
+      <c r="G3" s="172"/>
+      <c r="H3" s="172"/>
+      <c r="I3" s="172"/>
+      <c r="J3" s="172"/>
       <c r="K3" s="52"/>
-      <c r="L3" s="210" t="s">
+      <c r="L3" s="228" t="s">
         <v>1</v>
       </c>
-      <c r="M3" s="142"/>
-      <c r="N3" s="142"/>
+      <c r="M3" s="172"/>
+      <c r="N3" s="172"/>
       <c r="O3" s="53"/>
       <c r="P3" s="52"/>
       <c r="Q3" s="48"/>
@@ -2972,11 +2971,11 @@
       <c r="I4" s="51"/>
       <c r="J4" s="52"/>
       <c r="K4" s="52"/>
-      <c r="L4" s="204" t="s">
+      <c r="L4" s="263" t="s">
         <v>2</v>
       </c>
-      <c r="M4" s="135"/>
-      <c r="N4" s="135"/>
+      <c r="M4" s="156"/>
+      <c r="N4" s="156"/>
       <c r="O4" s="53"/>
       <c r="P4" s="52"/>
       <c r="Q4" s="48"/>
@@ -2987,19 +2986,19 @@
       <c r="C5" s="48"/>
       <c r="D5" s="49"/>
       <c r="E5" s="48"/>
-      <c r="F5" s="226" t="s">
+      <c r="F5" s="245" t="s">
         <v>3</v>
       </c>
-      <c r="G5" s="227"/>
-      <c r="H5" s="224" t="s">
+      <c r="G5" s="246"/>
+      <c r="H5" s="242" t="s">
         <v>4</v>
       </c>
-      <c r="I5" s="225"/>
-      <c r="J5" s="225"/>
+      <c r="I5" s="243"/>
+      <c r="J5" s="243"/>
       <c r="K5" s="52"/>
-      <c r="L5" s="135"/>
-      <c r="M5" s="135"/>
-      <c r="N5" s="135"/>
+      <c r="L5" s="156"/>
+      <c r="M5" s="156"/>
+      <c r="N5" s="156"/>
       <c r="O5" s="53"/>
       <c r="P5" s="52"/>
       <c r="Q5" s="48"/>
@@ -3011,23 +3010,23 @@
       <c r="C6" s="48"/>
       <c r="D6" s="49"/>
       <c r="E6" s="48"/>
-      <c r="F6" s="207" t="s">
+      <c r="F6" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="142"/>
-      <c r="H6" s="224" t="s">
+      <c r="G6" s="172"/>
+      <c r="H6" s="242" t="s">
         <v>6</v>
       </c>
-      <c r="I6" s="225"/>
-      <c r="J6" s="225"/>
+      <c r="I6" s="243"/>
+      <c r="J6" s="243"/>
       <c r="K6" s="52"/>
-      <c r="L6" s="234" t="s">
+      <c r="L6" s="254" t="s">
         <v>7</v>
       </c>
-      <c r="M6" s="235" t="s">
+      <c r="M6" s="255" t="s">
         <v>8</v>
       </c>
-      <c r="N6" s="236"/>
+      <c r="N6" s="256"/>
       <c r="O6" s="53"/>
       <c r="P6" s="52"/>
       <c r="Q6" s="48"/>
@@ -3044,9 +3043,9 @@
       <c r="I7" s="57"/>
       <c r="J7" s="58"/>
       <c r="K7" s="52"/>
-      <c r="L7" s="142"/>
-      <c r="M7" s="237"/>
-      <c r="N7" s="237"/>
+      <c r="L7" s="172"/>
+      <c r="M7" s="257"/>
+      <c r="N7" s="257"/>
       <c r="O7" s="53"/>
       <c r="P7" s="52"/>
       <c r="Q7" s="48"/>
@@ -3057,19 +3056,19 @@
       <c r="C8" s="48"/>
       <c r="D8" s="49"/>
       <c r="E8" s="48"/>
-      <c r="F8" s="221" t="s">
+      <c r="F8" s="239" t="s">
         <v>9</v>
       </c>
-      <c r="G8" s="142"/>
-      <c r="H8" s="222" t="s">
+      <c r="G8" s="172"/>
+      <c r="H8" s="240" t="s">
         <v>10</v>
       </c>
-      <c r="I8" s="223"/>
-      <c r="J8" s="223"/>
+      <c r="I8" s="241"/>
+      <c r="J8" s="241"/>
       <c r="K8" s="52"/>
-      <c r="L8" s="142"/>
-      <c r="M8" s="238"/>
-      <c r="N8" s="238"/>
+      <c r="L8" s="172"/>
+      <c r="M8" s="258"/>
+      <c r="N8" s="258"/>
       <c r="O8" s="52"/>
       <c r="P8" s="52"/>
       <c r="Q8" s="48"/>
@@ -3136,24 +3135,24 @@
     <row r="12" spans="2:21" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B12" s="59"/>
       <c r="C12" s="59"/>
-      <c r="D12" s="230" t="s">
+      <c r="D12" s="249" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="231"/>
-      <c r="F12" s="228" t="s">
+      <c r="E12" s="250"/>
+      <c r="F12" s="247" t="s">
         <v>12</v>
       </c>
-      <c r="G12" s="229"/>
-      <c r="H12" s="229"/>
-      <c r="I12" s="229"/>
-      <c r="J12" s="229"/>
+      <c r="G12" s="248"/>
+      <c r="H12" s="248"/>
+      <c r="I12" s="248"/>
+      <c r="J12" s="248"/>
       <c r="K12" s="65"/>
-      <c r="L12" s="239" t="s">
+      <c r="L12" s="261" t="s">
         <v>13</v>
       </c>
-      <c r="M12" s="142"/>
-      <c r="N12" s="142"/>
-      <c r="O12" s="240"/>
+      <c r="M12" s="172"/>
+      <c r="N12" s="172"/>
+      <c r="O12" s="262"/>
       <c r="P12" s="98" t="s">
         <v>14</v>
       </c>
@@ -3163,24 +3162,24 @@
     <row r="13" spans="2:21" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B13" s="59"/>
       <c r="C13" s="59"/>
-      <c r="D13" s="208" t="s">
+      <c r="D13" s="226" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="209"/>
-      <c r="F13" s="219" t="s">
+      <c r="E13" s="227"/>
+      <c r="F13" s="237" t="s">
         <v>16</v>
       </c>
-      <c r="G13" s="220"/>
-      <c r="H13" s="220"/>
-      <c r="I13" s="220"/>
-      <c r="J13" s="220"/>
+      <c r="G13" s="238"/>
+      <c r="H13" s="238"/>
+      <c r="I13" s="238"/>
+      <c r="J13" s="238"/>
       <c r="K13" s="66"/>
-      <c r="L13" s="242" t="s">
+      <c r="L13" s="265" t="s">
         <v>17</v>
       </c>
-      <c r="M13" s="243"/>
-      <c r="N13" s="243"/>
-      <c r="O13" s="243"/>
+      <c r="M13" s="266"/>
+      <c r="N13" s="266"/>
+      <c r="O13" s="266"/>
       <c r="P13" s="6" t="s">
         <v>18</v>
       </c>
@@ -3190,24 +3189,24 @@
     <row r="14" spans="2:21" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B14" s="59"/>
       <c r="C14" s="59"/>
-      <c r="D14" s="208" t="s">
+      <c r="D14" s="226" t="s">
         <v>19</v>
       </c>
-      <c r="E14" s="209"/>
-      <c r="F14" s="219" t="s">
+      <c r="E14" s="227"/>
+      <c r="F14" s="237" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="220"/>
-      <c r="H14" s="220"/>
-      <c r="I14" s="220"/>
-      <c r="J14" s="220"/>
+      <c r="G14" s="238"/>
+      <c r="H14" s="238"/>
+      <c r="I14" s="238"/>
+      <c r="J14" s="238"/>
       <c r="K14" s="67"/>
-      <c r="L14" s="205" t="s">
+      <c r="L14" s="259" t="s">
         <v>21</v>
       </c>
-      <c r="M14" s="206"/>
-      <c r="N14" s="206"/>
-      <c r="O14" s="206"/>
+      <c r="M14" s="260"/>
+      <c r="N14" s="260"/>
+      <c r="O14" s="260"/>
       <c r="P14" s="6" t="s">
         <v>22</v>
       </c>
@@ -3217,24 +3216,24 @@
     <row r="15" spans="2:21" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="59"/>
       <c r="C15" s="59"/>
-      <c r="D15" s="208" t="s">
+      <c r="D15" s="226" t="s">
         <v>23</v>
       </c>
-      <c r="E15" s="209"/>
-      <c r="F15" s="219" t="s">
+      <c r="E15" s="227"/>
+      <c r="F15" s="237" t="s">
         <v>24</v>
       </c>
-      <c r="G15" s="220"/>
-      <c r="H15" s="220"/>
-      <c r="I15" s="220"/>
-      <c r="J15" s="220"/>
+      <c r="G15" s="238"/>
+      <c r="H15" s="238"/>
+      <c r="I15" s="238"/>
+      <c r="J15" s="238"/>
       <c r="K15" s="55"/>
-      <c r="L15" s="205" t="s">
+      <c r="L15" s="259" t="s">
         <v>25</v>
       </c>
-      <c r="M15" s="206"/>
-      <c r="N15" s="206"/>
-      <c r="O15" s="206"/>
+      <c r="M15" s="260"/>
+      <c r="N15" s="260"/>
+      <c r="O15" s="260"/>
       <c r="P15" s="6" t="s">
         <v>26</v>
       </c>
@@ -3244,24 +3243,24 @@
     <row r="16" spans="2:21" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B16" s="59"/>
       <c r="C16" s="59"/>
-      <c r="D16" s="241" t="s">
+      <c r="D16" s="264" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="217"/>
-      <c r="F16" s="233" t="s">
+      <c r="E16" s="235"/>
+      <c r="F16" s="253" t="s">
         <v>28</v>
       </c>
-      <c r="G16" s="220"/>
-      <c r="H16" s="220"/>
-      <c r="I16" s="220"/>
-      <c r="J16" s="220"/>
+      <c r="G16" s="238"/>
+      <c r="H16" s="238"/>
+      <c r="I16" s="238"/>
+      <c r="J16" s="238"/>
       <c r="K16" s="65"/>
-      <c r="L16" s="205" t="s">
+      <c r="L16" s="259" t="s">
         <v>29</v>
       </c>
-      <c r="M16" s="206"/>
-      <c r="N16" s="206"/>
-      <c r="O16" s="206"/>
+      <c r="M16" s="260"/>
+      <c r="N16" s="260"/>
+      <c r="O16" s="260"/>
       <c r="P16" s="6" t="s">
         <v>30</v>
       </c>
@@ -3275,8 +3274,8 @@
       <c r="E17" s="62"/>
       <c r="F17" s="63"/>
       <c r="G17" s="63"/>
-      <c r="H17" s="162"/>
-      <c r="I17" s="161"/>
+      <c r="H17" s="194"/>
+      <c r="I17" s="154"/>
       <c r="J17" s="64"/>
       <c r="K17" s="66"/>
       <c r="L17" s="55"/>
@@ -3289,23 +3288,23 @@
     <row r="18" spans="2:19" s="7" customFormat="1" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="75"/>
       <c r="C18" s="75"/>
-      <c r="D18" s="232" t="s">
+      <c r="D18" s="252" t="s">
         <v>31</v>
       </c>
-      <c r="E18" s="155"/>
-      <c r="F18" s="155"/>
-      <c r="G18" s="155"/>
-      <c r="H18" s="155"/>
-      <c r="I18" s="155"/>
-      <c r="J18" s="156"/>
+      <c r="E18" s="187"/>
+      <c r="F18" s="187"/>
+      <c r="G18" s="187"/>
+      <c r="H18" s="187"/>
+      <c r="I18" s="187"/>
+      <c r="J18" s="188"/>
       <c r="K18" s="73"/>
-      <c r="L18" s="200" t="s">
+      <c r="L18" s="214" t="s">
         <v>32</v>
       </c>
-      <c r="M18" s="155"/>
-      <c r="N18" s="155"/>
-      <c r="O18" s="155"/>
-      <c r="P18" s="156"/>
+      <c r="M18" s="187"/>
+      <c r="N18" s="187"/>
+      <c r="O18" s="187"/>
+      <c r="P18" s="188"/>
       <c r="Q18" s="55"/>
       <c r="R18" s="55"/>
       <c r="S18" s="1"/>
@@ -3313,24 +3312,24 @@
     <row r="19" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B19" s="74"/>
       <c r="C19" s="74"/>
-      <c r="D19" s="143" t="s">
+      <c r="D19" s="173" t="s">
         <v>33</v>
       </c>
-      <c r="E19" s="144"/>
-      <c r="F19" s="144"/>
-      <c r="G19" s="144"/>
-      <c r="H19" s="145"/>
-      <c r="I19" s="152" t="s">
+      <c r="E19" s="174"/>
+      <c r="F19" s="174"/>
+      <c r="G19" s="174"/>
+      <c r="H19" s="175"/>
+      <c r="I19" s="182" t="s">
         <v>34</v>
       </c>
-      <c r="J19" s="144"/>
+      <c r="J19" s="174"/>
       <c r="K19" s="55"/>
-      <c r="L19" s="154" t="s">
+      <c r="L19" s="186" t="s">
         <v>17</v>
       </c>
-      <c r="M19" s="155"/>
-      <c r="N19" s="155"/>
-      <c r="O19" s="156"/>
+      <c r="M19" s="187"/>
+      <c r="N19" s="187"/>
+      <c r="O19" s="188"/>
       <c r="P19" s="84" t="s">
         <v>35</v>
       </c>
@@ -3340,24 +3339,24 @@
     <row r="20" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B20" s="74"/>
       <c r="C20" s="74"/>
-      <c r="D20" s="174" t="s">
+      <c r="D20" s="207" t="s">
         <v>36</v>
       </c>
-      <c r="E20" s="144"/>
-      <c r="F20" s="144"/>
-      <c r="G20" s="144"/>
-      <c r="H20" s="145"/>
-      <c r="I20" s="164" t="s">
+      <c r="E20" s="174"/>
+      <c r="F20" s="174"/>
+      <c r="G20" s="174"/>
+      <c r="H20" s="175"/>
+      <c r="I20" s="197" t="s">
         <v>34</v>
       </c>
-      <c r="J20" s="144"/>
+      <c r="J20" s="174"/>
       <c r="K20" s="55"/>
-      <c r="L20" s="179" t="s">
+      <c r="L20" s="212" t="s">
         <v>21</v>
       </c>
-      <c r="M20" s="155"/>
-      <c r="N20" s="155"/>
-      <c r="O20" s="156"/>
+      <c r="M20" s="187"/>
+      <c r="N20" s="187"/>
+      <c r="O20" s="188"/>
       <c r="P20" s="85" t="s">
         <v>37</v>
       </c>
@@ -3367,24 +3366,24 @@
     <row r="21" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="74"/>
       <c r="C21" s="74"/>
-      <c r="D21" s="143" t="s">
+      <c r="D21" s="173" t="s">
         <v>38</v>
       </c>
-      <c r="E21" s="144"/>
-      <c r="F21" s="144"/>
-      <c r="G21" s="144"/>
-      <c r="H21" s="145"/>
-      <c r="I21" s="152" t="s">
+      <c r="E21" s="174"/>
+      <c r="F21" s="174"/>
+      <c r="G21" s="174"/>
+      <c r="H21" s="175"/>
+      <c r="I21" s="182" t="s">
         <v>39</v>
       </c>
-      <c r="J21" s="144"/>
+      <c r="J21" s="174"/>
       <c r="K21" s="55"/>
-      <c r="L21" s="154" t="s">
+      <c r="L21" s="186" t="s">
         <v>25</v>
       </c>
-      <c r="M21" s="155"/>
-      <c r="N21" s="155"/>
-      <c r="O21" s="156"/>
+      <c r="M21" s="187"/>
+      <c r="N21" s="187"/>
+      <c r="O21" s="188"/>
       <c r="P21" s="84" t="s">
         <v>37</v>
       </c>
@@ -3394,24 +3393,24 @@
     <row r="22" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22" s="74"/>
       <c r="C22" s="74"/>
-      <c r="D22" s="174" t="s">
+      <c r="D22" s="207" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="144"/>
-      <c r="F22" s="144"/>
-      <c r="G22" s="144"/>
-      <c r="H22" s="145"/>
-      <c r="I22" s="164" t="s">
+      <c r="E22" s="174"/>
+      <c r="F22" s="174"/>
+      <c r="G22" s="174"/>
+      <c r="H22" s="175"/>
+      <c r="I22" s="197" t="s">
         <v>34</v>
       </c>
-      <c r="J22" s="144"/>
+      <c r="J22" s="174"/>
       <c r="K22" s="55"/>
-      <c r="L22" s="213" t="s">
+      <c r="L22" s="231" t="s">
         <v>29</v>
       </c>
-      <c r="M22" s="214"/>
-      <c r="N22" s="214"/>
-      <c r="O22" s="215"/>
+      <c r="M22" s="232"/>
+      <c r="N22" s="232"/>
+      <c r="O22" s="233"/>
       <c r="P22" s="86" t="s">
         <v>41</v>
       </c>
@@ -3421,17 +3420,17 @@
     <row r="23" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B23" s="74"/>
       <c r="C23" s="74"/>
-      <c r="D23" s="143" t="s">
+      <c r="D23" s="173" t="s">
         <v>42</v>
       </c>
-      <c r="E23" s="144"/>
-      <c r="F23" s="144"/>
-      <c r="G23" s="144"/>
-      <c r="H23" s="145"/>
-      <c r="I23" s="152" t="s">
+      <c r="E23" s="174"/>
+      <c r="F23" s="174"/>
+      <c r="G23" s="174"/>
+      <c r="H23" s="175"/>
+      <c r="I23" s="182" t="s">
         <v>43</v>
       </c>
-      <c r="J23" s="144"/>
+      <c r="J23" s="174"/>
       <c r="K23" s="55"/>
       <c r="L23" s="82"/>
       <c r="M23" s="82"/>
@@ -3444,49 +3443,49 @@
     <row r="24" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B24" s="74"/>
       <c r="C24" s="74"/>
-      <c r="D24" s="174" t="s">
+      <c r="D24" s="207" t="s">
         <v>44</v>
       </c>
-      <c r="E24" s="144"/>
-      <c r="F24" s="144"/>
-      <c r="G24" s="144"/>
-      <c r="H24" s="145"/>
-      <c r="I24" s="164" t="s">
+      <c r="E24" s="174"/>
+      <c r="F24" s="174"/>
+      <c r="G24" s="174"/>
+      <c r="H24" s="175"/>
+      <c r="I24" s="197" t="s">
         <v>45</v>
       </c>
-      <c r="J24" s="144"/>
+      <c r="J24" s="174"/>
       <c r="K24" s="55"/>
-      <c r="L24" s="200" t="s">
+      <c r="L24" s="214" t="s">
         <v>46</v>
       </c>
-      <c r="M24" s="155"/>
-      <c r="N24" s="155"/>
-      <c r="O24" s="155"/>
-      <c r="P24" s="156"/>
+      <c r="M24" s="187"/>
+      <c r="N24" s="187"/>
+      <c r="O24" s="187"/>
+      <c r="P24" s="188"/>
       <c r="Q24" s="55"/>
       <c r="R24" s="55"/>
     </row>
     <row r="25" spans="2:19" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B25" s="74"/>
       <c r="C25" s="74"/>
-      <c r="D25" s="143" t="s">
+      <c r="D25" s="173" t="s">
         <v>47</v>
       </c>
-      <c r="E25" s="144"/>
-      <c r="F25" s="144"/>
-      <c r="G25" s="144"/>
-      <c r="H25" s="145"/>
-      <c r="I25" s="152" t="s">
+      <c r="E25" s="174"/>
+      <c r="F25" s="174"/>
+      <c r="G25" s="174"/>
+      <c r="H25" s="175"/>
+      <c r="I25" s="182" t="s">
         <v>45</v>
       </c>
-      <c r="J25" s="144"/>
+      <c r="J25" s="174"/>
       <c r="K25" s="55"/>
-      <c r="L25" s="154" t="s">
+      <c r="L25" s="186" t="s">
         <v>48</v>
       </c>
-      <c r="M25" s="155"/>
-      <c r="N25" s="155"/>
-      <c r="O25" s="156"/>
+      <c r="M25" s="187"/>
+      <c r="N25" s="187"/>
+      <c r="O25" s="188"/>
       <c r="P25" s="84" t="s">
         <v>49</v>
       </c>
@@ -3496,22 +3495,22 @@
     <row r="26" spans="2:19" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B26" s="74"/>
       <c r="C26" s="74"/>
-      <c r="D26" s="160" t="s">
+      <c r="D26" s="192" t="s">
         <v>50</v>
       </c>
-      <c r="E26" s="155"/>
-      <c r="F26" s="155"/>
-      <c r="G26" s="155"/>
-      <c r="H26" s="155"/>
-      <c r="I26" s="155"/>
-      <c r="J26" s="155"/>
+      <c r="E26" s="187"/>
+      <c r="F26" s="187"/>
+      <c r="G26" s="187"/>
+      <c r="H26" s="187"/>
+      <c r="I26" s="187"/>
+      <c r="J26" s="187"/>
       <c r="K26" s="55"/>
-      <c r="L26" s="179" t="s">
+      <c r="L26" s="212" t="s">
         <v>51</v>
       </c>
-      <c r="M26" s="155"/>
-      <c r="N26" s="155"/>
-      <c r="O26" s="156"/>
+      <c r="M26" s="187"/>
+      <c r="N26" s="187"/>
+      <c r="O26" s="188"/>
       <c r="P26" s="85" t="s">
         <v>52</v>
       </c>
@@ -3521,20 +3520,20 @@
     <row r="27" spans="2:19" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B27" s="74"/>
       <c r="C27" s="74"/>
-      <c r="D27" s="171"/>
-      <c r="E27" s="172"/>
-      <c r="F27" s="172"/>
-      <c r="G27" s="172"/>
-      <c r="H27" s="172"/>
-      <c r="I27" s="172"/>
-      <c r="J27" s="172"/>
+      <c r="D27" s="204"/>
+      <c r="E27" s="205"/>
+      <c r="F27" s="205"/>
+      <c r="G27" s="205"/>
+      <c r="H27" s="205"/>
+      <c r="I27" s="205"/>
+      <c r="J27" s="205"/>
       <c r="K27" s="55"/>
-      <c r="L27" s="154" t="s">
+      <c r="L27" s="186" t="s">
         <v>53</v>
       </c>
-      <c r="M27" s="155"/>
-      <c r="N27" s="155"/>
-      <c r="O27" s="156"/>
+      <c r="M27" s="187"/>
+      <c r="N27" s="187"/>
+      <c r="O27" s="188"/>
       <c r="P27" s="84" t="s">
         <v>49</v>
       </c>
@@ -3563,49 +3562,49 @@
     <row r="29" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B29" s="74"/>
       <c r="C29" s="74"/>
-      <c r="D29" s="218" t="s">
+      <c r="D29" s="236" t="s">
         <v>54</v>
       </c>
-      <c r="E29" s="142"/>
-      <c r="F29" s="142"/>
-      <c r="G29" s="142"/>
-      <c r="H29" s="142"/>
-      <c r="I29" s="142"/>
+      <c r="E29" s="172"/>
+      <c r="F29" s="172"/>
+      <c r="G29" s="172"/>
+      <c r="H29" s="172"/>
+      <c r="I29" s="172"/>
       <c r="J29" s="87" t="s">
         <v>55</v>
       </c>
       <c r="K29" s="55"/>
-      <c r="L29" s="216" t="s">
+      <c r="L29" s="234" t="s">
         <v>56</v>
       </c>
-      <c r="M29" s="217"/>
-      <c r="N29" s="217"/>
-      <c r="O29" s="217"/>
-      <c r="P29" s="217"/>
+      <c r="M29" s="235"/>
+      <c r="N29" s="235"/>
+      <c r="O29" s="235"/>
+      <c r="P29" s="235"/>
       <c r="Q29" s="55"/>
       <c r="R29" s="55"/>
     </row>
     <row r="30" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B30" s="74"/>
       <c r="C30" s="74"/>
-      <c r="D30" s="168" t="s">
+      <c r="D30" s="201" t="s">
         <v>57</v>
       </c>
-      <c r="E30" s="169"/>
-      <c r="F30" s="169"/>
-      <c r="G30" s="169"/>
-      <c r="H30" s="169"/>
-      <c r="I30" s="170"/>
+      <c r="E30" s="202"/>
+      <c r="F30" s="202"/>
+      <c r="G30" s="202"/>
+      <c r="H30" s="202"/>
+      <c r="I30" s="203"/>
       <c r="J30" s="12" t="s">
         <v>58</v>
       </c>
       <c r="K30" s="55"/>
-      <c r="L30" s="173" t="s">
+      <c r="L30" s="206" t="s">
         <v>59</v>
       </c>
-      <c r="M30" s="144"/>
-      <c r="N30" s="144"/>
-      <c r="O30" s="148"/>
+      <c r="M30" s="174"/>
+      <c r="N30" s="174"/>
+      <c r="O30" s="178"/>
       <c r="P30" s="9" t="s">
         <v>60</v>
       </c>
@@ -3615,24 +3614,24 @@
     <row r="31" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B31" s="74"/>
       <c r="C31" s="74"/>
-      <c r="D31" s="138" t="s">
+      <c r="D31" s="168" t="s">
         <v>61</v>
       </c>
-      <c r="E31" s="139"/>
-      <c r="F31" s="139"/>
-      <c r="G31" s="139"/>
-      <c r="H31" s="139"/>
-      <c r="I31" s="140"/>
+      <c r="E31" s="169"/>
+      <c r="F31" s="169"/>
+      <c r="G31" s="169"/>
+      <c r="H31" s="169"/>
+      <c r="I31" s="170"/>
       <c r="J31" s="13" t="s">
         <v>58</v>
       </c>
       <c r="K31" s="55"/>
-      <c r="L31" s="147" t="s">
+      <c r="L31" s="177" t="s">
         <v>62</v>
       </c>
-      <c r="M31" s="144"/>
-      <c r="N31" s="144"/>
-      <c r="O31" s="148"/>
+      <c r="M31" s="174"/>
+      <c r="N31" s="174"/>
+      <c r="O31" s="178"/>
       <c r="P31" s="10" t="s">
         <v>63</v>
       </c>
@@ -3642,24 +3641,24 @@
     <row r="32" spans="2:19" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B32" s="74"/>
       <c r="C32" s="74"/>
-      <c r="D32" s="163" t="s">
+      <c r="D32" s="195" t="s">
         <v>64</v>
       </c>
-      <c r="E32" s="139"/>
-      <c r="F32" s="139"/>
-      <c r="G32" s="139"/>
-      <c r="H32" s="139"/>
-      <c r="I32" s="140"/>
+      <c r="E32" s="169"/>
+      <c r="F32" s="169"/>
+      <c r="G32" s="169"/>
+      <c r="H32" s="169"/>
+      <c r="I32" s="170"/>
       <c r="J32" s="14" t="s">
         <v>58</v>
       </c>
       <c r="K32" s="55"/>
-      <c r="L32" s="173" t="s">
+      <c r="L32" s="206" t="s">
         <v>65</v>
       </c>
-      <c r="M32" s="144"/>
-      <c r="N32" s="144"/>
-      <c r="O32" s="148"/>
+      <c r="M32" s="174"/>
+      <c r="N32" s="174"/>
+      <c r="O32" s="178"/>
       <c r="P32" s="9" t="s">
         <v>66</v>
       </c>
@@ -3669,24 +3668,24 @@
     <row r="33" spans="2:20" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B33" s="74"/>
       <c r="C33" s="74"/>
-      <c r="D33" s="138" t="s">
+      <c r="D33" s="168" t="s">
         <v>67</v>
       </c>
-      <c r="E33" s="139"/>
-      <c r="F33" s="139"/>
-      <c r="G33" s="139"/>
-      <c r="H33" s="139"/>
-      <c r="I33" s="140"/>
+      <c r="E33" s="169"/>
+      <c r="F33" s="169"/>
+      <c r="G33" s="169"/>
+      <c r="H33" s="169"/>
+      <c r="I33" s="170"/>
       <c r="J33" s="13" t="s">
         <v>58</v>
       </c>
       <c r="K33" s="55"/>
-      <c r="L33" s="212" t="s">
+      <c r="L33" s="230" t="s">
         <v>68</v>
       </c>
-      <c r="M33" s="150"/>
-      <c r="N33" s="150"/>
-      <c r="O33" s="151"/>
+      <c r="M33" s="180"/>
+      <c r="N33" s="180"/>
+      <c r="O33" s="181"/>
       <c r="P33" s="11" t="s">
         <v>63</v>
       </c>
@@ -3696,14 +3695,14 @@
     <row r="34" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B34" s="74"/>
       <c r="C34" s="74"/>
-      <c r="D34" s="163" t="s">
+      <c r="D34" s="195" t="s">
         <v>69</v>
       </c>
-      <c r="E34" s="139"/>
-      <c r="F34" s="139"/>
-      <c r="G34" s="139"/>
-      <c r="H34" s="139"/>
-      <c r="I34" s="140"/>
+      <c r="E34" s="169"/>
+      <c r="F34" s="169"/>
+      <c r="G34" s="169"/>
+      <c r="H34" s="169"/>
+      <c r="I34" s="170"/>
       <c r="J34" s="14" t="s">
         <v>58</v>
       </c>
@@ -3719,25 +3718,25 @@
     <row r="35" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B35" s="74"/>
       <c r="C35" s="74"/>
-      <c r="D35" s="165" t="s">
+      <c r="D35" s="198" t="s">
         <v>70</v>
       </c>
-      <c r="E35" s="166"/>
-      <c r="F35" s="166"/>
-      <c r="G35" s="166"/>
-      <c r="H35" s="166"/>
-      <c r="I35" s="167"/>
+      <c r="E35" s="199"/>
+      <c r="F35" s="199"/>
+      <c r="G35" s="199"/>
+      <c r="H35" s="199"/>
+      <c r="I35" s="200"/>
       <c r="J35" s="18" t="s">
         <v>58</v>
       </c>
       <c r="K35" s="55"/>
-      <c r="L35" s="178" t="s">
+      <c r="L35" s="211" t="s">
         <v>71</v>
       </c>
-      <c r="M35" s="142"/>
-      <c r="N35" s="142"/>
-      <c r="O35" s="142"/>
-      <c r="P35" s="142"/>
+      <c r="M35" s="172"/>
+      <c r="N35" s="172"/>
+      <c r="O35" s="172"/>
+      <c r="P35" s="172"/>
       <c r="Q35" s="55"/>
       <c r="R35" s="55"/>
     </row>
@@ -3752,12 +3751,12 @@
       <c r="I36" s="19"/>
       <c r="J36" s="19"/>
       <c r="K36" s="55"/>
-      <c r="L36" s="157" t="s">
+      <c r="L36" s="189" t="s">
         <v>72</v>
       </c>
-      <c r="M36" s="158"/>
-      <c r="N36" s="158"/>
-      <c r="O36" s="159"/>
+      <c r="M36" s="190"/>
+      <c r="N36" s="190"/>
+      <c r="O36" s="191"/>
       <c r="P36" s="20" t="s">
         <v>73</v>
       </c>
@@ -3767,24 +3766,24 @@
     <row r="37" spans="2:20" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B37" s="74"/>
       <c r="C37" s="74"/>
-      <c r="D37" s="218" t="s">
+      <c r="D37" s="236" t="s">
         <v>74</v>
       </c>
-      <c r="E37" s="142"/>
-      <c r="F37" s="142"/>
-      <c r="G37" s="142"/>
-      <c r="H37" s="142"/>
-      <c r="I37" s="142"/>
+      <c r="E37" s="172"/>
+      <c r="F37" s="172"/>
+      <c r="G37" s="172"/>
+      <c r="H37" s="172"/>
+      <c r="I37" s="172"/>
       <c r="J37" s="87" t="s">
         <v>55</v>
       </c>
       <c r="K37" s="55"/>
-      <c r="L37" s="174" t="s">
+      <c r="L37" s="207" t="s">
         <v>75</v>
       </c>
-      <c r="M37" s="144"/>
-      <c r="N37" s="144"/>
-      <c r="O37" s="145"/>
+      <c r="M37" s="174"/>
+      <c r="N37" s="174"/>
+      <c r="O37" s="175"/>
       <c r="P37" s="10" t="s">
         <v>73</v>
       </c>
@@ -3794,24 +3793,24 @@
     <row r="38" spans="2:20" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B38" s="74"/>
       <c r="C38" s="74"/>
-      <c r="D38" s="168" t="s">
+      <c r="D38" s="201" t="s">
         <v>76</v>
       </c>
-      <c r="E38" s="169"/>
-      <c r="F38" s="169"/>
-      <c r="G38" s="169"/>
-      <c r="H38" s="169"/>
-      <c r="I38" s="170"/>
+      <c r="E38" s="202"/>
+      <c r="F38" s="202"/>
+      <c r="G38" s="202"/>
+      <c r="H38" s="202"/>
+      <c r="I38" s="203"/>
       <c r="J38" s="12" t="s">
         <v>58</v>
       </c>
       <c r="K38" s="55"/>
-      <c r="L38" s="143" t="s">
+      <c r="L38" s="173" t="s">
         <v>77</v>
       </c>
-      <c r="M38" s="144"/>
-      <c r="N38" s="144"/>
-      <c r="O38" s="145"/>
+      <c r="M38" s="174"/>
+      <c r="N38" s="174"/>
+      <c r="O38" s="175"/>
       <c r="P38" s="9" t="s">
         <v>73</v>
       </c>
@@ -3821,24 +3820,24 @@
     <row r="39" spans="2:20" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B39" s="74"/>
       <c r="C39" s="74"/>
-      <c r="D39" s="138" t="s">
+      <c r="D39" s="168" t="s">
         <v>78</v>
       </c>
-      <c r="E39" s="139"/>
-      <c r="F39" s="139"/>
-      <c r="G39" s="139"/>
-      <c r="H39" s="139"/>
-      <c r="I39" s="140"/>
+      <c r="E39" s="169"/>
+      <c r="F39" s="169"/>
+      <c r="G39" s="169"/>
+      <c r="H39" s="169"/>
+      <c r="I39" s="170"/>
       <c r="J39" s="13" t="s">
         <v>58</v>
       </c>
       <c r="K39" s="55"/>
-      <c r="L39" s="174" t="s">
+      <c r="L39" s="207" t="s">
         <v>79</v>
       </c>
-      <c r="M39" s="144"/>
-      <c r="N39" s="144"/>
-      <c r="O39" s="145"/>
+      <c r="M39" s="174"/>
+      <c r="N39" s="174"/>
+      <c r="O39" s="175"/>
       <c r="P39" s="10" t="s">
         <v>73</v>
       </c>
@@ -3848,24 +3847,24 @@
     <row r="40" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B40" s="74"/>
       <c r="C40" s="74"/>
-      <c r="D40" s="163" t="s">
+      <c r="D40" s="195" t="s">
         <v>80</v>
       </c>
-      <c r="E40" s="139"/>
-      <c r="F40" s="139"/>
-      <c r="G40" s="139"/>
-      <c r="H40" s="139"/>
-      <c r="I40" s="140"/>
+      <c r="E40" s="169"/>
+      <c r="F40" s="169"/>
+      <c r="G40" s="169"/>
+      <c r="H40" s="169"/>
+      <c r="I40" s="170"/>
       <c r="J40" s="14" t="s">
         <v>58</v>
       </c>
       <c r="K40" s="55"/>
-      <c r="L40" s="149" t="s">
+      <c r="L40" s="179" t="s">
         <v>81</v>
       </c>
-      <c r="M40" s="150"/>
-      <c r="N40" s="150"/>
-      <c r="O40" s="151"/>
+      <c r="M40" s="180"/>
+      <c r="N40" s="180"/>
+      <c r="O40" s="181"/>
       <c r="P40" s="21" t="s">
         <v>73</v>
       </c>
@@ -3875,14 +3874,14 @@
     <row r="41" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B41" s="74"/>
       <c r="C41" s="74"/>
-      <c r="D41" s="138" t="s">
+      <c r="D41" s="168" t="s">
         <v>82</v>
       </c>
-      <c r="E41" s="139"/>
-      <c r="F41" s="139"/>
-      <c r="G41" s="139"/>
-      <c r="H41" s="139"/>
-      <c r="I41" s="140"/>
+      <c r="E41" s="169"/>
+      <c r="F41" s="169"/>
+      <c r="G41" s="169"/>
+      <c r="H41" s="169"/>
+      <c r="I41" s="170"/>
       <c r="J41" s="13" t="s">
         <v>58</v>
       </c>
@@ -3898,14 +3897,14 @@
     <row r="42" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B42" s="74"/>
       <c r="C42" s="74"/>
-      <c r="D42" s="163" t="s">
+      <c r="D42" s="195" t="s">
         <v>83</v>
       </c>
-      <c r="E42" s="139"/>
-      <c r="F42" s="139"/>
-      <c r="G42" s="139"/>
-      <c r="H42" s="139"/>
-      <c r="I42" s="140"/>
+      <c r="E42" s="169"/>
+      <c r="F42" s="169"/>
+      <c r="G42" s="169"/>
+      <c r="H42" s="169"/>
+      <c r="I42" s="170"/>
       <c r="J42" s="14" t="s">
         <v>58</v>
       </c>
@@ -3921,14 +3920,14 @@
     <row r="43" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B43" s="74"/>
       <c r="C43" s="74"/>
-      <c r="D43" s="138" t="s">
+      <c r="D43" s="168" t="s">
         <v>84</v>
       </c>
-      <c r="E43" s="139"/>
-      <c r="F43" s="139"/>
-      <c r="G43" s="139"/>
-      <c r="H43" s="139"/>
-      <c r="I43" s="140"/>
+      <c r="E43" s="169"/>
+      <c r="F43" s="169"/>
+      <c r="G43" s="169"/>
+      <c r="H43" s="169"/>
+      <c r="I43" s="170"/>
       <c r="J43" s="13" t="s">
         <v>58</v>
       </c>
@@ -3944,14 +3943,14 @@
     <row r="44" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B44" s="74"/>
       <c r="C44" s="74"/>
-      <c r="D44" s="168" t="s">
+      <c r="D44" s="201" t="s">
         <v>85</v>
       </c>
-      <c r="E44" s="169"/>
-      <c r="F44" s="169"/>
-      <c r="G44" s="169"/>
-      <c r="H44" s="169"/>
-      <c r="I44" s="170"/>
+      <c r="E44" s="202"/>
+      <c r="F44" s="202"/>
+      <c r="G44" s="202"/>
+      <c r="H44" s="202"/>
+      <c r="I44" s="203"/>
       <c r="J44" s="12" t="s">
         <v>58</v>
       </c>
@@ -3967,14 +3966,14 @@
     <row r="45" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B45" s="74"/>
       <c r="C45" s="74"/>
-      <c r="D45" s="138" t="s">
+      <c r="D45" s="168" t="s">
         <v>86</v>
       </c>
-      <c r="E45" s="139"/>
-      <c r="F45" s="139"/>
-      <c r="G45" s="139"/>
-      <c r="H45" s="139"/>
-      <c r="I45" s="140"/>
+      <c r="E45" s="169"/>
+      <c r="F45" s="169"/>
+      <c r="G45" s="169"/>
+      <c r="H45" s="169"/>
+      <c r="I45" s="170"/>
       <c r="J45" s="13" t="s">
         <v>58</v>
       </c>
@@ -3990,25 +3989,25 @@
     <row r="46" spans="2:20" ht="21.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B46" s="74"/>
       <c r="C46" s="74"/>
-      <c r="D46" s="199" t="s">
+      <c r="D46" s="244" t="s">
         <v>87</v>
       </c>
-      <c r="E46" s="166"/>
-      <c r="F46" s="166"/>
-      <c r="G46" s="166"/>
-      <c r="H46" s="166"/>
-      <c r="I46" s="167"/>
+      <c r="E46" s="199"/>
+      <c r="F46" s="199"/>
+      <c r="G46" s="199"/>
+      <c r="H46" s="199"/>
+      <c r="I46" s="200"/>
       <c r="J46" s="22" t="s">
         <v>58</v>
       </c>
       <c r="K46" s="55"/>
-      <c r="L46" s="141" t="s">
+      <c r="L46" s="171" t="s">
         <v>88</v>
       </c>
-      <c r="M46" s="142"/>
-      <c r="N46" s="142"/>
-      <c r="O46" s="142"/>
-      <c r="P46" s="142"/>
+      <c r="M46" s="172"/>
+      <c r="N46" s="172"/>
+      <c r="O46" s="172"/>
+      <c r="P46" s="172"/>
       <c r="Q46" s="55"/>
       <c r="R46" s="55"/>
     </row>
@@ -4034,21 +4033,21 @@
     <row r="48" spans="2:20" ht="21.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
       <c r="B48" s="74"/>
       <c r="C48" s="76"/>
-      <c r="D48" s="175" t="s">
+      <c r="D48" s="208" t="s">
         <v>89</v>
       </c>
-      <c r="E48" s="176"/>
-      <c r="F48" s="176"/>
-      <c r="G48" s="176"/>
-      <c r="H48" s="176"/>
-      <c r="I48" s="176"/>
-      <c r="J48" s="176"/>
-      <c r="K48" s="176"/>
-      <c r="L48" s="176"/>
-      <c r="M48" s="176"/>
-      <c r="N48" s="176"/>
-      <c r="O48" s="176"/>
-      <c r="P48" s="177"/>
+      <c r="E48" s="209"/>
+      <c r="F48" s="209"/>
+      <c r="G48" s="209"/>
+      <c r="H48" s="209"/>
+      <c r="I48" s="209"/>
+      <c r="J48" s="209"/>
+      <c r="K48" s="209"/>
+      <c r="L48" s="209"/>
+      <c r="M48" s="209"/>
+      <c r="N48" s="209"/>
+      <c r="O48" s="209"/>
+      <c r="P48" s="210"/>
       <c r="Q48" s="55"/>
       <c r="R48" s="55"/>
       <c r="T48" s="97" t="s">
@@ -4061,14 +4060,14 @@
       <c r="D49" s="91" t="s">
         <v>91</v>
       </c>
-      <c r="E49" s="125" t="s">
+      <c r="E49" s="115" t="s">
         <v>92</v>
       </c>
-      <c r="F49" s="126"/>
-      <c r="G49" s="126"/>
-      <c r="H49" s="126"/>
-      <c r="I49" s="126"/>
-      <c r="J49" s="126"/>
+      <c r="F49" s="144"/>
+      <c r="G49" s="144"/>
+      <c r="H49" s="144"/>
+      <c r="I49" s="144"/>
+      <c r="J49" s="144"/>
       <c r="K49" s="91" t="s">
         <v>93</v>
       </c>
@@ -4078,10 +4077,10 @@
       <c r="M49" s="91" t="s">
         <v>95</v>
       </c>
-      <c r="N49" s="125" t="s">
+      <c r="N49" s="115" t="s">
         <v>96</v>
       </c>
-      <c r="O49" s="126"/>
+      <c r="O49" s="144"/>
       <c r="P49" s="91" t="s">
         <v>97</v>
       </c>
@@ -4093,101 +4092,101 @@
       <c r="B50" s="8"/>
       <c r="C50" s="23"/>
       <c r="D50" s="25"/>
-      <c r="E50" s="197"/>
-      <c r="F50" s="135"/>
-      <c r="G50" s="135"/>
-      <c r="H50" s="135"/>
-      <c r="I50" s="135"/>
-      <c r="J50" s="132"/>
+      <c r="E50" s="223"/>
+      <c r="F50" s="156"/>
+      <c r="G50" s="156"/>
+      <c r="H50" s="156"/>
+      <c r="I50" s="156"/>
+      <c r="J50" s="149"/>
       <c r="K50" s="26"/>
       <c r="L50" s="27"/>
       <c r="M50" s="28"/>
-      <c r="N50" s="136"/>
-      <c r="O50" s="132"/>
+      <c r="N50" s="152"/>
+      <c r="O50" s="149"/>
       <c r="P50" s="29"/>
     </row>
     <row r="51" spans="2:23" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B51" s="8"/>
       <c r="C51" s="23"/>
       <c r="D51" s="30"/>
-      <c r="E51" s="146"/>
-      <c r="F51" s="135"/>
-      <c r="G51" s="135"/>
-      <c r="H51" s="135"/>
-      <c r="I51" s="135"/>
-      <c r="J51" s="132"/>
+      <c r="E51" s="176"/>
+      <c r="F51" s="156"/>
+      <c r="G51" s="156"/>
+      <c r="H51" s="156"/>
+      <c r="I51" s="156"/>
+      <c r="J51" s="149"/>
       <c r="K51" s="31"/>
       <c r="L51" s="32"/>
       <c r="M51" s="33"/>
-      <c r="N51" s="131"/>
-      <c r="O51" s="132"/>
+      <c r="N51" s="148"/>
+      <c r="O51" s="149"/>
       <c r="P51" s="34"/>
     </row>
     <row r="52" spans="2:23" ht="68.099999999999994" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B52" s="8"/>
       <c r="C52" s="23"/>
       <c r="D52" s="25"/>
-      <c r="E52" s="197"/>
-      <c r="F52" s="135"/>
-      <c r="G52" s="135"/>
-      <c r="H52" s="135"/>
-      <c r="I52" s="135"/>
-      <c r="J52" s="132"/>
+      <c r="E52" s="223"/>
+      <c r="F52" s="156"/>
+      <c r="G52" s="156"/>
+      <c r="H52" s="156"/>
+      <c r="I52" s="156"/>
+      <c r="J52" s="149"/>
       <c r="K52" s="26"/>
       <c r="L52" s="27"/>
       <c r="M52" s="28"/>
-      <c r="N52" s="136"/>
-      <c r="O52" s="132"/>
+      <c r="N52" s="152"/>
+      <c r="O52" s="149"/>
       <c r="P52" s="29"/>
     </row>
     <row r="53" spans="2:23" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B53" s="8"/>
       <c r="C53" s="23"/>
       <c r="D53" s="30"/>
-      <c r="E53" s="146"/>
-      <c r="F53" s="135"/>
-      <c r="G53" s="135"/>
-      <c r="H53" s="135"/>
-      <c r="I53" s="135"/>
-      <c r="J53" s="132"/>
+      <c r="E53" s="176"/>
+      <c r="F53" s="156"/>
+      <c r="G53" s="156"/>
+      <c r="H53" s="156"/>
+      <c r="I53" s="156"/>
+      <c r="J53" s="149"/>
       <c r="K53" s="31"/>
       <c r="L53" s="32"/>
       <c r="M53" s="33"/>
-      <c r="N53" s="131"/>
-      <c r="O53" s="132"/>
+      <c r="N53" s="148"/>
+      <c r="O53" s="149"/>
       <c r="P53" s="34"/>
     </row>
     <row r="54" spans="2:23" ht="69.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B54" s="23"/>
       <c r="D54" s="25"/>
-      <c r="E54" s="197"/>
-      <c r="F54" s="135"/>
-      <c r="G54" s="135"/>
-      <c r="H54" s="135"/>
-      <c r="I54" s="135"/>
-      <c r="J54" s="132"/>
+      <c r="E54" s="223"/>
+      <c r="F54" s="156"/>
+      <c r="G54" s="156"/>
+      <c r="H54" s="156"/>
+      <c r="I54" s="156"/>
+      <c r="J54" s="149"/>
       <c r="K54" s="26"/>
       <c r="L54" s="27"/>
       <c r="M54" s="28"/>
-      <c r="N54" s="136"/>
-      <c r="O54" s="132"/>
+      <c r="N54" s="152"/>
+      <c r="O54" s="149"/>
       <c r="P54" s="29"/>
     </row>
     <row r="55" spans="2:23" ht="66.900000000000006" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B55" s="8"/>
       <c r="C55" s="23"/>
       <c r="D55" s="30"/>
-      <c r="E55" s="146"/>
-      <c r="F55" s="135"/>
-      <c r="G55" s="135"/>
-      <c r="H55" s="135"/>
-      <c r="I55" s="135"/>
-      <c r="J55" s="132"/>
+      <c r="E55" s="176"/>
+      <c r="F55" s="156"/>
+      <c r="G55" s="156"/>
+      <c r="H55" s="156"/>
+      <c r="I55" s="156"/>
+      <c r="J55" s="149"/>
       <c r="K55" s="31"/>
       <c r="L55" s="32"/>
       <c r="M55" s="33"/>
-      <c r="N55" s="131"/>
-      <c r="O55" s="132"/>
+      <c r="N55" s="148"/>
+      <c r="O55" s="149"/>
       <c r="P55" s="34"/>
     </row>
     <row r="56" spans="2:23" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -4205,11 +4204,11 @@
       <c r="M56" s="95" t="s">
         <v>98</v>
       </c>
-      <c r="N56" s="195">
+      <c r="N56" s="221">
         <f>SUM(N50:N55)</f>
         <v>0</v>
       </c>
-      <c r="O56" s="196"/>
+      <c r="O56" s="222"/>
       <c r="P56" s="3"/>
     </row>
     <row r="57" spans="2:23" ht="21.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -4227,11 +4226,11 @@
       <c r="M57" s="96" t="s">
         <v>99</v>
       </c>
-      <c r="N57" s="190">
+      <c r="N57" s="159">
         <f>+N56*0.12</f>
         <v>0</v>
       </c>
-      <c r="O57" s="191"/>
+      <c r="O57" s="160"/>
       <c r="P57" s="3"/>
     </row>
     <row r="58" spans="2:23" ht="21.9" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
@@ -4249,11 +4248,11 @@
       <c r="M58" s="95" t="s">
         <v>100</v>
       </c>
-      <c r="N58" s="188">
+      <c r="N58" s="293">
         <f>+N57+N56</f>
         <v>0</v>
       </c>
-      <c r="O58" s="135"/>
+      <c r="O58" s="156"/>
       <c r="P58" s="3"/>
     </row>
     <row r="59" spans="2:23" s="3" customFormat="1" ht="11.1" customHeight="1" x14ac:dyDescent="0.3">
@@ -4278,48 +4277,48 @@
     <row r="60" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B60" s="74"/>
       <c r="C60" s="74"/>
-      <c r="D60" s="192" t="s">
+      <c r="D60" s="161" t="s">
         <v>101</v>
       </c>
-      <c r="E60" s="192"/>
-      <c r="F60" s="192"/>
-      <c r="G60" s="192"/>
-      <c r="H60" s="192"/>
-      <c r="I60" s="192"/>
-      <c r="J60" s="192"/>
-      <c r="K60" s="192"/>
-      <c r="L60" s="192"/>
-      <c r="M60" s="192"/>
-      <c r="N60" s="192"/>
-      <c r="O60" s="192"/>
-      <c r="P60" s="192"/>
+      <c r="E60" s="161"/>
+      <c r="F60" s="161"/>
+      <c r="G60" s="161"/>
+      <c r="H60" s="161"/>
+      <c r="I60" s="161"/>
+      <c r="J60" s="161"/>
+      <c r="K60" s="161"/>
+      <c r="L60" s="161"/>
+      <c r="M60" s="161"/>
+      <c r="N60" s="161"/>
+      <c r="O60" s="161"/>
+      <c r="P60" s="161"/>
       <c r="Q60" s="56"/>
       <c r="R60" s="56"/>
     </row>
     <row r="61" spans="2:23" s="3" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B61" s="74"/>
       <c r="C61" s="74"/>
-      <c r="D61" s="180" t="s">
+      <c r="D61" s="213" t="s">
         <v>102</v>
       </c>
-      <c r="E61" s="180"/>
-      <c r="F61" s="180"/>
-      <c r="G61" s="181" t="s">
+      <c r="E61" s="213"/>
+      <c r="F61" s="213"/>
+      <c r="G61" s="286" t="s">
         <v>103</v>
       </c>
-      <c r="H61" s="181"/>
-      <c r="I61" s="181"/>
-      <c r="J61" s="182" t="s">
+      <c r="H61" s="286"/>
+      <c r="I61" s="286"/>
+      <c r="J61" s="287" t="s">
         <v>105</v>
       </c>
-      <c r="K61" s="183"/>
-      <c r="L61" s="184"/>
-      <c r="M61" s="185" t="s">
+      <c r="K61" s="288"/>
+      <c r="L61" s="289"/>
+      <c r="M61" s="290" t="s">
         <v>106</v>
       </c>
-      <c r="N61" s="186"/>
-      <c r="O61" s="186"/>
-      <c r="P61" s="187"/>
+      <c r="N61" s="291"/>
+      <c r="O61" s="291"/>
+      <c r="P61" s="292"/>
       <c r="Q61" s="56"/>
       <c r="R61" s="56"/>
       <c r="U61" s="35"/>
@@ -4329,21 +4328,21 @@
     <row r="62" spans="2:23" ht="21.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B62" s="74"/>
       <c r="C62" s="74"/>
-      <c r="D62" s="277" t="s">
+      <c r="D62" s="217" t="s">
         <v>104</v>
       </c>
-      <c r="E62" s="277"/>
-      <c r="F62" s="277"/>
-      <c r="G62" s="123"/>
-      <c r="H62" s="123"/>
-      <c r="I62" s="123"/>
-      <c r="J62" s="201"/>
-      <c r="K62" s="201"/>
-      <c r="L62" s="201"/>
-      <c r="M62" s="201"/>
-      <c r="N62" s="201"/>
-      <c r="O62" s="201"/>
-      <c r="P62" s="201"/>
+      <c r="E62" s="217"/>
+      <c r="F62" s="217"/>
+      <c r="G62" s="193"/>
+      <c r="H62" s="193"/>
+      <c r="I62" s="193"/>
+      <c r="J62" s="218"/>
+      <c r="K62" s="218"/>
+      <c r="L62" s="218"/>
+      <c r="M62" s="218"/>
+      <c r="N62" s="218"/>
+      <c r="O62" s="218"/>
+      <c r="P62" s="218"/>
       <c r="Q62" s="56"/>
       <c r="R62" s="56"/>
       <c r="S62"/>
@@ -4355,19 +4354,19 @@
     <row r="63" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B63" s="74"/>
       <c r="C63" s="74"/>
-      <c r="D63" s="202"/>
-      <c r="E63" s="202"/>
-      <c r="F63" s="202"/>
-      <c r="G63" s="122"/>
-      <c r="H63" s="122"/>
-      <c r="I63" s="122"/>
-      <c r="J63" s="203"/>
-      <c r="K63" s="203"/>
-      <c r="L63" s="203"/>
-      <c r="M63" s="122"/>
-      <c r="N63" s="122"/>
-      <c r="O63" s="122"/>
-      <c r="P63" s="122"/>
+      <c r="D63" s="219"/>
+      <c r="E63" s="219"/>
+      <c r="F63" s="219"/>
+      <c r="G63" s="142"/>
+      <c r="H63" s="142"/>
+      <c r="I63" s="142"/>
+      <c r="J63" s="220"/>
+      <c r="K63" s="220"/>
+      <c r="L63" s="220"/>
+      <c r="M63" s="142"/>
+      <c r="N63" s="142"/>
+      <c r="O63" s="142"/>
+      <c r="P63" s="142"/>
       <c r="Q63" s="103"/>
       <c r="R63" s="103"/>
       <c r="S63"/>
@@ -4379,19 +4378,19 @@
     <row r="64" spans="2:23" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B64" s="74"/>
       <c r="C64" s="74"/>
-      <c r="D64" s="123"/>
-      <c r="E64" s="123"/>
-      <c r="F64" s="123"/>
-      <c r="G64" s="116"/>
-      <c r="H64" s="116"/>
-      <c r="I64" s="116"/>
-      <c r="J64" s="124"/>
-      <c r="K64" s="124"/>
-      <c r="L64" s="124"/>
-      <c r="M64" s="116"/>
-      <c r="N64" s="116"/>
-      <c r="O64" s="116"/>
-      <c r="P64" s="116"/>
+      <c r="D64" s="193"/>
+      <c r="E64" s="193"/>
+      <c r="F64" s="193"/>
+      <c r="G64" s="141"/>
+      <c r="H64" s="141"/>
+      <c r="I64" s="141"/>
+      <c r="J64" s="294"/>
+      <c r="K64" s="294"/>
+      <c r="L64" s="294"/>
+      <c r="M64" s="141"/>
+      <c r="N64" s="141"/>
+      <c r="O64" s="141"/>
+      <c r="P64" s="141"/>
       <c r="Q64" s="56"/>
       <c r="R64" s="56"/>
       <c r="S64"/>
@@ -4403,19 +4402,19 @@
     <row r="65" spans="2:20" s="3" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B65" s="74"/>
       <c r="C65" s="74"/>
-      <c r="D65" s="118"/>
-      <c r="E65" s="119"/>
-      <c r="F65" s="120"/>
-      <c r="G65" s="118"/>
-      <c r="H65" s="119"/>
-      <c r="I65" s="120"/>
-      <c r="J65" s="118"/>
-      <c r="K65" s="119"/>
-      <c r="L65" s="120"/>
-      <c r="M65" s="118"/>
-      <c r="N65" s="119"/>
-      <c r="O65" s="119"/>
-      <c r="P65" s="120"/>
+      <c r="D65" s="162"/>
+      <c r="E65" s="163"/>
+      <c r="F65" s="164"/>
+      <c r="G65" s="162"/>
+      <c r="H65" s="163"/>
+      <c r="I65" s="164"/>
+      <c r="J65" s="162"/>
+      <c r="K65" s="163"/>
+      <c r="L65" s="164"/>
+      <c r="M65" s="162"/>
+      <c r="N65" s="163"/>
+      <c r="O65" s="163"/>
+      <c r="P65" s="164"/>
       <c r="Q65" s="56"/>
       <c r="R65" s="56"/>
       <c r="S65"/>
@@ -4424,19 +4423,19 @@
     <row r="66" spans="2:20" s="3" customFormat="1" ht="20.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B66" s="74"/>
       <c r="C66" s="74"/>
-      <c r="D66" s="116"/>
-      <c r="E66" s="116"/>
-      <c r="F66" s="116"/>
-      <c r="G66" s="116"/>
-      <c r="H66" s="116"/>
-      <c r="I66" s="116"/>
-      <c r="J66" s="116"/>
-      <c r="K66" s="116"/>
-      <c r="L66" s="116"/>
-      <c r="M66" s="116"/>
-      <c r="N66" s="116"/>
-      <c r="O66" s="116"/>
-      <c r="P66" s="116"/>
+      <c r="D66" s="141"/>
+      <c r="E66" s="141"/>
+      <c r="F66" s="141"/>
+      <c r="G66" s="141"/>
+      <c r="H66" s="141"/>
+      <c r="I66" s="141"/>
+      <c r="J66" s="141"/>
+      <c r="K66" s="141"/>
+      <c r="L66" s="141"/>
+      <c r="M66" s="141"/>
+      <c r="N66" s="141"/>
+      <c r="O66" s="141"/>
+      <c r="P66" s="141"/>
       <c r="Q66" s="56"/>
       <c r="R66" s="56"/>
     </row>
@@ -4462,126 +4461,126 @@
     <row r="68" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B68" s="74"/>
       <c r="C68" s="74"/>
-      <c r="D68" s="258" t="s">
+      <c r="D68" s="109" t="s">
         <v>91</v>
       </c>
-      <c r="E68" s="259" t="s">
+      <c r="E68" s="273" t="s">
         <v>107</v>
       </c>
-      <c r="F68" s="260"/>
-      <c r="G68" s="260"/>
-      <c r="H68" s="260"/>
-      <c r="I68" s="260"/>
-      <c r="J68" s="260"/>
-      <c r="K68" s="260"/>
-      <c r="L68" s="260"/>
-      <c r="M68" s="260"/>
-      <c r="N68" s="260"/>
-      <c r="O68" s="260"/>
-      <c r="P68" s="261"/>
+      <c r="F68" s="274"/>
+      <c r="G68" s="274"/>
+      <c r="H68" s="274"/>
+      <c r="I68" s="274"/>
+      <c r="J68" s="274"/>
+      <c r="K68" s="274"/>
+      <c r="L68" s="274"/>
+      <c r="M68" s="274"/>
+      <c r="N68" s="274"/>
+      <c r="O68" s="274"/>
+      <c r="P68" s="275"/>
       <c r="Q68" s="55"/>
       <c r="R68" s="55"/>
     </row>
     <row r="69" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B69" s="74"/>
       <c r="C69" s="99"/>
-      <c r="D69" s="262">
+      <c r="D69" s="110">
         <v>1</v>
       </c>
-      <c r="E69" s="264" t="s">
+      <c r="E69" s="276" t="s">
         <v>108</v>
       </c>
-      <c r="F69" s="265"/>
-      <c r="G69" s="265"/>
-      <c r="H69" s="265"/>
-      <c r="I69" s="265"/>
-      <c r="J69" s="265"/>
-      <c r="K69" s="265"/>
-      <c r="L69" s="265"/>
-      <c r="M69" s="265"/>
-      <c r="N69" s="265"/>
-      <c r="O69" s="265"/>
-      <c r="P69" s="266"/>
+      <c r="F69" s="277"/>
+      <c r="G69" s="277"/>
+      <c r="H69" s="277"/>
+      <c r="I69" s="277"/>
+      <c r="J69" s="277"/>
+      <c r="K69" s="277"/>
+      <c r="L69" s="277"/>
+      <c r="M69" s="277"/>
+      <c r="N69" s="277"/>
+      <c r="O69" s="277"/>
+      <c r="P69" s="278"/>
       <c r="Q69" s="99"/>
       <c r="R69" s="99"/>
     </row>
     <row r="70" spans="2:20" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B70" s="74"/>
       <c r="C70" s="74"/>
-      <c r="D70" s="278">
+      <c r="D70" s="112">
         <v>2</v>
       </c>
-      <c r="E70" s="279"/>
-      <c r="F70" s="198"/>
-      <c r="G70" s="198"/>
-      <c r="H70" s="198"/>
-      <c r="I70" s="198"/>
-      <c r="J70" s="198"/>
-      <c r="K70" s="198"/>
-      <c r="L70" s="198"/>
-      <c r="M70" s="198"/>
-      <c r="N70" s="198"/>
-      <c r="O70" s="198"/>
-      <c r="P70" s="198"/>
+      <c r="E70" s="215"/>
+      <c r="F70" s="216"/>
+      <c r="G70" s="216"/>
+      <c r="H70" s="216"/>
+      <c r="I70" s="216"/>
+      <c r="J70" s="216"/>
+      <c r="K70" s="216"/>
+      <c r="L70" s="216"/>
+      <c r="M70" s="216"/>
+      <c r="N70" s="216"/>
+      <c r="O70" s="216"/>
+      <c r="P70" s="216"/>
       <c r="Q70" s="55"/>
       <c r="R70" s="55"/>
     </row>
     <row r="71" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B71" s="8"/>
       <c r="C71" s="8"/>
-      <c r="D71" s="262">
+      <c r="D71" s="110">
         <v>3</v>
       </c>
-      <c r="E71" s="267"/>
-      <c r="F71" s="268"/>
-      <c r="G71" s="268"/>
-      <c r="H71" s="268"/>
-      <c r="I71" s="268"/>
-      <c r="J71" s="268"/>
-      <c r="K71" s="268"/>
-      <c r="L71" s="268"/>
-      <c r="M71" s="268"/>
-      <c r="N71" s="268"/>
-      <c r="O71" s="268"/>
-      <c r="P71" s="268"/>
+      <c r="E71" s="224"/>
+      <c r="F71" s="151"/>
+      <c r="G71" s="151"/>
+      <c r="H71" s="151"/>
+      <c r="I71" s="151"/>
+      <c r="J71" s="151"/>
+      <c r="K71" s="151"/>
+      <c r="L71" s="151"/>
+      <c r="M71" s="151"/>
+      <c r="N71" s="151"/>
+      <c r="O71" s="151"/>
+      <c r="P71" s="151"/>
     </row>
     <row r="72" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B72" s="8"/>
       <c r="C72" s="8"/>
-      <c r="D72" s="278">
+      <c r="D72" s="112">
         <v>4</v>
       </c>
-      <c r="E72" s="280"/>
-      <c r="F72" s="281"/>
-      <c r="G72" s="281"/>
-      <c r="H72" s="281"/>
-      <c r="I72" s="281"/>
-      <c r="J72" s="281"/>
-      <c r="K72" s="281"/>
-      <c r="L72" s="281"/>
-      <c r="M72" s="281"/>
-      <c r="N72" s="281"/>
-      <c r="O72" s="281"/>
-      <c r="P72" s="281"/>
+      <c r="E72" s="196"/>
+      <c r="F72" s="185"/>
+      <c r="G72" s="185"/>
+      <c r="H72" s="185"/>
+      <c r="I72" s="185"/>
+      <c r="J72" s="185"/>
+      <c r="K72" s="185"/>
+      <c r="L72" s="185"/>
+      <c r="M72" s="185"/>
+      <c r="N72" s="185"/>
+      <c r="O72" s="185"/>
+      <c r="P72" s="185"/>
     </row>
     <row r="73" spans="2:20" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B73" s="8"/>
       <c r="C73" s="8"/>
-      <c r="D73" s="262">
+      <c r="D73" s="110">
         <v>5</v>
       </c>
-      <c r="E73" s="269"/>
-      <c r="F73" s="268"/>
-      <c r="G73" s="268"/>
-      <c r="H73" s="268"/>
-      <c r="I73" s="268"/>
-      <c r="J73" s="268"/>
-      <c r="K73" s="268"/>
-      <c r="L73" s="268"/>
-      <c r="M73" s="268"/>
-      <c r="N73" s="268"/>
-      <c r="O73" s="268"/>
-      <c r="P73" s="268"/>
+      <c r="E73" s="251"/>
+      <c r="F73" s="151"/>
+      <c r="G73" s="151"/>
+      <c r="H73" s="151"/>
+      <c r="I73" s="151"/>
+      <c r="J73" s="151"/>
+      <c r="K73" s="151"/>
+      <c r="L73" s="151"/>
+      <c r="M73" s="151"/>
+      <c r="N73" s="151"/>
+      <c r="O73" s="151"/>
+      <c r="P73" s="151"/>
     </row>
     <row r="74" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B74" s="8"/>
@@ -4603,145 +4602,145 @@
     <row r="75" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B75" s="74"/>
       <c r="C75" s="74"/>
-      <c r="D75" s="270" t="s">
+      <c r="D75" s="111" t="s">
         <v>91</v>
       </c>
-      <c r="E75" s="271" t="s">
+      <c r="E75" s="157" t="s">
         <v>109</v>
       </c>
-      <c r="F75" s="272"/>
-      <c r="G75" s="272"/>
-      <c r="H75" s="272"/>
-      <c r="I75" s="272"/>
-      <c r="J75" s="272"/>
-      <c r="K75" s="272"/>
-      <c r="L75" s="272"/>
-      <c r="M75" s="272"/>
-      <c r="N75" s="272"/>
-      <c r="O75" s="272"/>
-      <c r="P75" s="272"/>
+      <c r="F75" s="158"/>
+      <c r="G75" s="158"/>
+      <c r="H75" s="158"/>
+      <c r="I75" s="158"/>
+      <c r="J75" s="158"/>
+      <c r="K75" s="158"/>
+      <c r="L75" s="158"/>
+      <c r="M75" s="158"/>
+      <c r="N75" s="158"/>
+      <c r="O75" s="158"/>
+      <c r="P75" s="158"/>
       <c r="Q75" s="55"/>
       <c r="R75" s="55"/>
     </row>
     <row r="76" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B76" s="74"/>
       <c r="C76" s="74"/>
-      <c r="D76" s="262">
+      <c r="D76" s="110">
         <v>1</v>
       </c>
-      <c r="E76" s="273" t="s">
+      <c r="E76" s="279" t="s">
         <v>110</v>
       </c>
-      <c r="F76" s="273"/>
-      <c r="G76" s="273"/>
-      <c r="H76" s="273"/>
-      <c r="I76" s="273"/>
-      <c r="J76" s="273"/>
-      <c r="K76" s="273"/>
-      <c r="L76" s="273"/>
-      <c r="M76" s="273"/>
-      <c r="N76" s="273"/>
-      <c r="O76" s="273"/>
-      <c r="P76" s="273"/>
+      <c r="F76" s="279"/>
+      <c r="G76" s="279"/>
+      <c r="H76" s="279"/>
+      <c r="I76" s="279"/>
+      <c r="J76" s="279"/>
+      <c r="K76" s="279"/>
+      <c r="L76" s="279"/>
+      <c r="M76" s="279"/>
+      <c r="N76" s="279"/>
+      <c r="O76" s="279"/>
+      <c r="P76" s="279"/>
       <c r="Q76" s="55"/>
       <c r="R76" s="55"/>
     </row>
     <row r="77" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="74"/>
       <c r="C77" s="74"/>
-      <c r="D77" s="278">
+      <c r="D77" s="112">
         <v>2</v>
       </c>
-      <c r="E77" s="282"/>
-      <c r="F77" s="283"/>
-      <c r="G77" s="283"/>
-      <c r="H77" s="283"/>
-      <c r="I77" s="283"/>
-      <c r="J77" s="283"/>
-      <c r="K77" s="283"/>
-      <c r="L77" s="283"/>
-      <c r="M77" s="283"/>
-      <c r="N77" s="283"/>
-      <c r="O77" s="283"/>
-      <c r="P77" s="284"/>
+      <c r="E77" s="280"/>
+      <c r="F77" s="281"/>
+      <c r="G77" s="281"/>
+      <c r="H77" s="281"/>
+      <c r="I77" s="281"/>
+      <c r="J77" s="281"/>
+      <c r="K77" s="281"/>
+      <c r="L77" s="281"/>
+      <c r="M77" s="281"/>
+      <c r="N77" s="281"/>
+      <c r="O77" s="281"/>
+      <c r="P77" s="282"/>
       <c r="Q77" s="55"/>
       <c r="R77" s="55"/>
     </row>
     <row r="78" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B78" s="74"/>
       <c r="C78" s="74"/>
-      <c r="D78" s="262">
+      <c r="D78" s="110">
         <v>3</v>
       </c>
-      <c r="E78" s="274"/>
-      <c r="F78" s="275"/>
-      <c r="G78" s="275"/>
-      <c r="H78" s="275"/>
-      <c r="I78" s="275"/>
-      <c r="J78" s="275"/>
-      <c r="K78" s="275"/>
-      <c r="L78" s="275"/>
-      <c r="M78" s="275"/>
-      <c r="N78" s="275"/>
-      <c r="O78" s="275"/>
-      <c r="P78" s="276"/>
+      <c r="E78" s="283"/>
+      <c r="F78" s="284"/>
+      <c r="G78" s="284"/>
+      <c r="H78" s="284"/>
+      <c r="I78" s="284"/>
+      <c r="J78" s="284"/>
+      <c r="K78" s="284"/>
+      <c r="L78" s="284"/>
+      <c r="M78" s="284"/>
+      <c r="N78" s="284"/>
+      <c r="O78" s="284"/>
+      <c r="P78" s="285"/>
       <c r="Q78" s="55"/>
       <c r="R78" s="55"/>
     </row>
     <row r="79" spans="2:20" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B79" s="8"/>
       <c r="C79" s="8"/>
-      <c r="D79" s="278">
+      <c r="D79" s="112">
         <v>4</v>
       </c>
-      <c r="E79" s="285"/>
-      <c r="F79" s="133"/>
-      <c r="G79" s="133"/>
-      <c r="H79" s="133"/>
-      <c r="I79" s="133"/>
-      <c r="J79" s="133"/>
-      <c r="K79" s="133"/>
-      <c r="L79" s="133"/>
-      <c r="M79" s="133"/>
-      <c r="N79" s="133"/>
-      <c r="O79" s="133"/>
-      <c r="P79" s="133"/>
+      <c r="E79" s="184"/>
+      <c r="F79" s="185"/>
+      <c r="G79" s="185"/>
+      <c r="H79" s="185"/>
+      <c r="I79" s="185"/>
+      <c r="J79" s="185"/>
+      <c r="K79" s="185"/>
+      <c r="L79" s="185"/>
+      <c r="M79" s="185"/>
+      <c r="N79" s="185"/>
+      <c r="O79" s="185"/>
+      <c r="P79" s="185"/>
     </row>
     <row r="80" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B80" s="8"/>
       <c r="C80" s="8"/>
-      <c r="D80" s="262">
+      <c r="D80" s="110">
         <v>5</v>
       </c>
-      <c r="E80" s="263"/>
-      <c r="F80" s="129"/>
-      <c r="G80" s="129"/>
-      <c r="H80" s="129"/>
-      <c r="I80" s="129"/>
-      <c r="J80" s="129"/>
-      <c r="K80" s="129"/>
-      <c r="L80" s="129"/>
-      <c r="M80" s="129"/>
-      <c r="N80" s="129"/>
-      <c r="O80" s="129"/>
-      <c r="P80" s="129"/>
+      <c r="E80" s="150"/>
+      <c r="F80" s="151"/>
+      <c r="G80" s="151"/>
+      <c r="H80" s="151"/>
+      <c r="I80" s="151"/>
+      <c r="J80" s="151"/>
+      <c r="K80" s="151"/>
+      <c r="L80" s="151"/>
+      <c r="M80" s="151"/>
+      <c r="N80" s="151"/>
+      <c r="O80" s="151"/>
+      <c r="P80" s="151"/>
     </row>
     <row r="81" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B81" s="8"/>
       <c r="C81" s="8"/>
       <c r="D81" s="101"/>
-      <c r="E81" s="134"/>
-      <c r="F81" s="135"/>
-      <c r="G81" s="135"/>
-      <c r="H81" s="135"/>
-      <c r="I81" s="135"/>
-      <c r="J81" s="135"/>
-      <c r="K81" s="135"/>
-      <c r="L81" s="135"/>
-      <c r="M81" s="135"/>
-      <c r="N81" s="135"/>
-      <c r="O81" s="135"/>
-      <c r="P81" s="135"/>
+      <c r="E81" s="155"/>
+      <c r="F81" s="156"/>
+      <c r="G81" s="156"/>
+      <c r="H81" s="156"/>
+      <c r="I81" s="156"/>
+      <c r="J81" s="156"/>
+      <c r="K81" s="156"/>
+      <c r="L81" s="156"/>
+      <c r="M81" s="156"/>
+      <c r="N81" s="156"/>
+      <c r="O81" s="156"/>
+      <c r="P81" s="156"/>
     </row>
     <row r="82" spans="2:20" x14ac:dyDescent="0.3">
       <c r="B82" s="74"/>
@@ -4765,985 +4764,1113 @@
     <row r="83" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B83" s="8"/>
       <c r="C83" s="8"/>
-      <c r="D83" s="109" t="s">
+      <c r="D83" s="106" t="s">
         <v>91</v>
       </c>
-      <c r="E83" s="121" t="s">
+      <c r="E83" s="165" t="s">
         <v>111</v>
       </c>
-      <c r="F83" s="121"/>
-      <c r="G83" s="121"/>
-      <c r="H83" s="121"/>
-      <c r="I83" s="121"/>
-      <c r="J83" s="121"/>
-      <c r="K83" s="121"/>
-      <c r="L83" s="121"/>
-      <c r="M83" s="121"/>
-      <c r="N83" s="121"/>
-      <c r="O83" s="121"/>
-      <c r="P83" s="121"/>
+      <c r="F83" s="165"/>
+      <c r="G83" s="165"/>
+      <c r="H83" s="165"/>
+      <c r="I83" s="165"/>
+      <c r="J83" s="165"/>
+      <c r="K83" s="165"/>
+      <c r="L83" s="165"/>
+      <c r="M83" s="165"/>
+      <c r="N83" s="165"/>
+      <c r="O83" s="165"/>
+      <c r="P83" s="165"/>
       <c r="Q83" s="72"/>
       <c r="R83" s="72"/>
     </row>
-    <row r="84" spans="2:20" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:20" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B84" s="8"/>
       <c r="C84" s="8"/>
-      <c r="D84" s="250">
+      <c r="D84" s="124">
         <v>1</v>
       </c>
-      <c r="E84" s="244" t="s">
+      <c r="E84" s="267" t="s">
         <v>112</v>
       </c>
-      <c r="F84" s="245"/>
-      <c r="G84" s="245"/>
-      <c r="H84" s="245"/>
-      <c r="I84" s="245"/>
-      <c r="J84" s="245"/>
-      <c r="K84" s="245"/>
-      <c r="L84" s="245"/>
-      <c r="M84" s="246"/>
+      <c r="F84" s="268"/>
+      <c r="G84" s="268"/>
+      <c r="H84" s="268"/>
+      <c r="I84" s="268"/>
+      <c r="J84" s="268"/>
+      <c r="K84" s="268"/>
+      <c r="L84" s="268"/>
+      <c r="M84" s="269"/>
       <c r="N84" s="47"/>
       <c r="O84" s="47"/>
       <c r="P84" s="47"/>
       <c r="Q84" s="72"/>
       <c r="R84" s="72"/>
     </row>
-    <row r="85" spans="2:20" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:20" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B85" s="8"/>
       <c r="C85" s="8"/>
-      <c r="D85" s="251"/>
-      <c r="E85" s="247"/>
-      <c r="F85" s="248"/>
-      <c r="G85" s="248"/>
-      <c r="H85" s="248"/>
-      <c r="I85" s="248"/>
-      <c r="J85" s="248"/>
-      <c r="K85" s="248"/>
-      <c r="L85" s="248"/>
-      <c r="M85" s="249"/>
+      <c r="D85" s="125"/>
+      <c r="E85" s="270"/>
+      <c r="F85" s="271"/>
+      <c r="G85" s="271"/>
+      <c r="H85" s="271"/>
+      <c r="I85" s="271"/>
+      <c r="J85" s="271"/>
+      <c r="K85" s="271"/>
+      <c r="L85" s="271"/>
+      <c r="M85" s="272"/>
       <c r="N85" s="46"/>
-      <c r="O85" s="47"/>
-      <c r="P85" s="47"/>
+      <c r="O85" s="115" t="s">
+        <v>113</v>
+      </c>
+      <c r="P85" s="115"/>
       <c r="Q85" s="72"/>
       <c r="R85" s="72"/>
     </row>
-    <row r="86" spans="2:20" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:20" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B86" s="8"/>
       <c r="C86" s="8"/>
-      <c r="D86" s="286">
+      <c r="D86" s="126">
         <v>2</v>
       </c>
-      <c r="E86" s="287"/>
-      <c r="F86" s="288"/>
-      <c r="G86" s="288"/>
-      <c r="H86" s="288"/>
-      <c r="I86" s="288"/>
-      <c r="J86" s="288"/>
-      <c r="K86" s="288"/>
-      <c r="L86" s="288"/>
-      <c r="M86" s="289"/>
+      <c r="E86" s="128"/>
+      <c r="F86" s="129"/>
+      <c r="G86" s="129"/>
+      <c r="H86" s="129"/>
+      <c r="I86" s="129"/>
+      <c r="J86" s="129"/>
+      <c r="K86" s="129"/>
+      <c r="L86" s="129"/>
+      <c r="M86" s="130"/>
       <c r="N86" s="4"/>
-      <c r="O86" s="125" t="s">
-        <v>113</v>
-      </c>
-      <c r="P86" s="142"/>
+      <c r="O86" s="116" t="s">
+        <v>115</v>
+      </c>
+      <c r="P86" s="116"/>
       <c r="Q86" s="44"/>
       <c r="R86" s="44"/>
       <c r="T86" s="97" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="87" spans="2:20" ht="24.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:20" ht="26.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B87" s="8"/>
       <c r="C87" s="8"/>
-      <c r="D87" s="290"/>
-      <c r="E87" s="291"/>
-      <c r="F87" s="292"/>
-      <c r="G87" s="292"/>
-      <c r="H87" s="292"/>
-      <c r="I87" s="292"/>
-      <c r="J87" s="292"/>
-      <c r="K87" s="292"/>
-      <c r="L87" s="292"/>
-      <c r="M87" s="293"/>
+      <c r="D87" s="127"/>
+      <c r="E87" s="131"/>
+      <c r="F87" s="132"/>
+      <c r="G87" s="132"/>
+      <c r="H87" s="132"/>
+      <c r="I87" s="132"/>
+      <c r="J87" s="132"/>
+      <c r="K87" s="132"/>
+      <c r="L87" s="132"/>
+      <c r="M87" s="133"/>
       <c r="N87" s="5"/>
-      <c r="O87" s="193" t="s">
-        <v>115</v>
-      </c>
-      <c r="P87" s="142"/>
+      <c r="O87" s="116"/>
+      <c r="P87" s="116"/>
       <c r="Q87" s="44"/>
       <c r="R87" s="44"/>
     </row>
-    <row r="88" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:20" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B88" s="8"/>
       <c r="C88" s="8"/>
-      <c r="D88" s="250">
+      <c r="D88" s="124">
         <v>3</v>
       </c>
-      <c r="E88" s="252"/>
-      <c r="F88" s="253"/>
-      <c r="G88" s="253"/>
-      <c r="H88" s="253"/>
-      <c r="I88" s="253"/>
-      <c r="J88" s="253"/>
-      <c r="K88" s="253"/>
-      <c r="L88" s="253"/>
-      <c r="M88" s="254"/>
+      <c r="E88" s="118"/>
+      <c r="F88" s="119"/>
+      <c r="G88" s="119"/>
+      <c r="H88" s="119"/>
+      <c r="I88" s="119"/>
+      <c r="J88" s="119"/>
+      <c r="K88" s="119"/>
+      <c r="L88" s="119"/>
+      <c r="M88" s="120"/>
       <c r="N88" s="5"/>
-      <c r="O88" s="142"/>
-      <c r="P88" s="142"/>
+      <c r="O88" s="116"/>
+      <c r="P88" s="116"/>
       <c r="Q88" s="44"/>
       <c r="R88" s="44"/>
     </row>
-    <row r="89" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="2:20" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B89" s="8"/>
       <c r="C89" s="8"/>
-      <c r="D89" s="251"/>
-      <c r="E89" s="255"/>
-      <c r="F89" s="256"/>
-      <c r="G89" s="256"/>
-      <c r="H89" s="256"/>
-      <c r="I89" s="256"/>
-      <c r="J89" s="256"/>
-      <c r="K89" s="256"/>
-      <c r="L89" s="256"/>
-      <c r="M89" s="257"/>
+      <c r="D89" s="125"/>
+      <c r="E89" s="121"/>
+      <c r="F89" s="122"/>
+      <c r="G89" s="122"/>
+      <c r="H89" s="122"/>
+      <c r="I89" s="122"/>
+      <c r="J89" s="122"/>
+      <c r="K89" s="122"/>
+      <c r="L89" s="122"/>
+      <c r="M89" s="123"/>
       <c r="N89" s="5"/>
-      <c r="O89" s="142"/>
-      <c r="P89" s="142"/>
+      <c r="O89" s="117"/>
+      <c r="P89" s="117"/>
       <c r="Q89" s="44"/>
       <c r="R89" s="44"/>
     </row>
-    <row r="90" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:20" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B90" s="8"/>
       <c r="C90" s="8"/>
-      <c r="D90" s="286">
+      <c r="D90" s="126">
         <v>4</v>
       </c>
-      <c r="E90" s="287"/>
-      <c r="F90" s="288"/>
-      <c r="G90" s="288"/>
-      <c r="H90" s="288"/>
-      <c r="I90" s="288"/>
-      <c r="J90" s="288"/>
-      <c r="K90" s="288"/>
-      <c r="L90" s="288"/>
-      <c r="M90" s="289"/>
+      <c r="E90" s="128"/>
+      <c r="F90" s="129"/>
+      <c r="G90" s="129"/>
+      <c r="H90" s="129"/>
+      <c r="I90" s="129"/>
+      <c r="J90" s="129"/>
+      <c r="K90" s="129"/>
+      <c r="L90" s="129"/>
+      <c r="M90" s="130"/>
       <c r="N90" s="5"/>
-      <c r="O90" s="194"/>
-      <c r="P90" s="194"/>
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
       <c r="Q90" s="44"/>
       <c r="R90" s="44"/>
     </row>
-    <row r="91" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="2:20" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B91" s="8"/>
       <c r="C91" s="8"/>
-      <c r="D91" s="290"/>
-      <c r="E91" s="291"/>
-      <c r="F91" s="292"/>
-      <c r="G91" s="292"/>
-      <c r="H91" s="292"/>
-      <c r="I91" s="292"/>
-      <c r="J91" s="292"/>
-      <c r="K91" s="292"/>
-      <c r="L91" s="292"/>
-      <c r="M91" s="293"/>
+      <c r="D91" s="127"/>
+      <c r="E91" s="131"/>
+      <c r="F91" s="132"/>
+      <c r="G91" s="132"/>
+      <c r="H91" s="132"/>
+      <c r="I91" s="132"/>
+      <c r="J91" s="132"/>
+      <c r="K91" s="132"/>
+      <c r="L91" s="132"/>
+      <c r="M91" s="133"/>
       <c r="N91" s="5"/>
-      <c r="O91" s="3"/>
-      <c r="P91" s="3"/>
+      <c r="O91" s="115" t="s">
+        <v>116</v>
+      </c>
+      <c r="P91" s="115"/>
       <c r="Q91" s="44"/>
       <c r="R91" s="44"/>
     </row>
-    <row r="92" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:20" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B92" s="8"/>
       <c r="C92" s="8"/>
-      <c r="D92" s="250">
+      <c r="D92" s="124">
         <v>5</v>
       </c>
-      <c r="E92" s="252"/>
-      <c r="F92" s="253"/>
-      <c r="G92" s="253"/>
-      <c r="H92" s="253"/>
-      <c r="I92" s="253"/>
-      <c r="J92" s="253"/>
-      <c r="K92" s="253"/>
-      <c r="L92" s="253"/>
-      <c r="M92" s="254"/>
+      <c r="E92" s="118"/>
+      <c r="F92" s="119"/>
+      <c r="G92" s="119"/>
+      <c r="H92" s="119"/>
+      <c r="I92" s="119"/>
+      <c r="J92" s="119"/>
+      <c r="K92" s="119"/>
+      <c r="L92" s="119"/>
+      <c r="M92" s="120"/>
       <c r="N92" s="5"/>
-      <c r="O92" s="125" t="s">
-        <v>116</v>
-      </c>
-      <c r="P92" s="142"/>
+      <c r="O92" s="91"/>
+      <c r="P92" s="91"/>
       <c r="Q92" s="44"/>
       <c r="R92" s="44"/>
     </row>
-    <row r="93" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="2:20" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B93" s="8"/>
       <c r="C93" s="8"/>
-      <c r="D93" s="251"/>
-      <c r="E93" s="255"/>
-      <c r="F93" s="256"/>
-      <c r="G93" s="256"/>
-      <c r="H93" s="256"/>
-      <c r="I93" s="256"/>
-      <c r="J93" s="256"/>
-      <c r="K93" s="256"/>
-      <c r="L93" s="256"/>
-      <c r="M93" s="257"/>
+      <c r="D93" s="125"/>
+      <c r="E93" s="121"/>
+      <c r="F93" s="122"/>
+      <c r="G93" s="122"/>
+      <c r="H93" s="122"/>
+      <c r="I93" s="122"/>
+      <c r="J93" s="122"/>
+      <c r="K93" s="122"/>
+      <c r="L93" s="122"/>
+      <c r="M93" s="123"/>
       <c r="N93" s="5"/>
-      <c r="O93" s="193" t="s">
+      <c r="O93" s="116" t="s">
         <v>117</v>
       </c>
-      <c r="P93" s="142"/>
+      <c r="P93" s="116"/>
       <c r="Q93" s="44"/>
       <c r="R93" s="44"/>
     </row>
-    <row r="94" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="2:20" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B94" s="8"/>
       <c r="C94" s="8"/>
-      <c r="D94" s="286">
+      <c r="D94" s="126">
         <v>6</v>
       </c>
-      <c r="E94" s="287"/>
-      <c r="F94" s="288"/>
-      <c r="G94" s="288"/>
-      <c r="H94" s="288"/>
-      <c r="I94" s="288"/>
-      <c r="J94" s="288"/>
-      <c r="K94" s="288"/>
-      <c r="L94" s="288"/>
-      <c r="M94" s="289"/>
+      <c r="E94" s="128"/>
+      <c r="F94" s="129"/>
+      <c r="G94" s="129"/>
+      <c r="H94" s="129"/>
+      <c r="I94" s="129"/>
+      <c r="J94" s="129"/>
+      <c r="K94" s="129"/>
+      <c r="L94" s="129"/>
+      <c r="M94" s="130"/>
       <c r="N94" s="5"/>
-      <c r="O94" s="142"/>
-      <c r="P94" s="142"/>
+      <c r="O94" s="116"/>
+      <c r="P94" s="116"/>
       <c r="Q94" s="44"/>
       <c r="R94" s="44"/>
     </row>
-    <row r="95" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="2:20" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B95" s="8"/>
       <c r="C95" s="8"/>
-      <c r="D95" s="290"/>
-      <c r="E95" s="291"/>
-      <c r="F95" s="292"/>
-      <c r="G95" s="292"/>
-      <c r="H95" s="292"/>
-      <c r="I95" s="292"/>
-      <c r="J95" s="292"/>
-      <c r="K95" s="292"/>
-      <c r="L95" s="292"/>
-      <c r="M95" s="293"/>
+      <c r="D95" s="127"/>
+      <c r="E95" s="131"/>
+      <c r="F95" s="132"/>
+      <c r="G95" s="132"/>
+      <c r="H95" s="132"/>
+      <c r="I95" s="132"/>
+      <c r="J95" s="132"/>
+      <c r="K95" s="132"/>
+      <c r="L95" s="132"/>
+      <c r="M95" s="133"/>
       <c r="N95" s="5"/>
-      <c r="O95" s="142"/>
-      <c r="P95" s="142"/>
+      <c r="O95" s="116"/>
+      <c r="P95" s="116"/>
       <c r="Q95" s="44"/>
       <c r="R95" s="44"/>
     </row>
-    <row r="96" spans="2:20" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="2:20" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B96" s="8"/>
       <c r="C96" s="8"/>
-      <c r="D96" s="250">
+      <c r="D96" s="124">
         <v>7</v>
       </c>
-      <c r="E96" s="252"/>
-      <c r="F96" s="253"/>
-      <c r="G96" s="253"/>
-      <c r="H96" s="253"/>
-      <c r="I96" s="253"/>
-      <c r="J96" s="253"/>
-      <c r="K96" s="253"/>
-      <c r="L96" s="253"/>
-      <c r="M96" s="254"/>
+      <c r="E96" s="118"/>
+      <c r="F96" s="119"/>
+      <c r="G96" s="119"/>
+      <c r="H96" s="119"/>
+      <c r="I96" s="119"/>
+      <c r="J96" s="119"/>
+      <c r="K96" s="119"/>
+      <c r="L96" s="119"/>
+      <c r="M96" s="120"/>
       <c r="N96" s="5"/>
-      <c r="O96" s="142"/>
-      <c r="P96" s="142"/>
+      <c r="O96" s="116"/>
+      <c r="P96" s="116"/>
       <c r="Q96" s="44"/>
       <c r="R96" s="44"/>
     </row>
-    <row r="97" spans="2:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B97" s="8"/>
       <c r="C97" s="8"/>
-      <c r="D97" s="251"/>
-      <c r="E97" s="255"/>
-      <c r="F97" s="256"/>
-      <c r="G97" s="256"/>
-      <c r="H97" s="256"/>
-      <c r="I97" s="256"/>
-      <c r="J97" s="256"/>
-      <c r="K97" s="256"/>
-      <c r="L97" s="256"/>
-      <c r="M97" s="257"/>
+      <c r="D97" s="125"/>
+      <c r="E97" s="121"/>
+      <c r="F97" s="122"/>
+      <c r="G97" s="122"/>
+      <c r="H97" s="122"/>
+      <c r="I97" s="122"/>
+      <c r="J97" s="122"/>
+      <c r="K97" s="122"/>
+      <c r="L97" s="122"/>
+      <c r="M97" s="123"/>
       <c r="N97" s="5"/>
-      <c r="O97" s="142"/>
-      <c r="P97" s="142"/>
+      <c r="O97" s="117"/>
+      <c r="P97" s="117"/>
       <c r="Q97" s="44"/>
       <c r="R97" s="44"/>
     </row>
-    <row r="98" spans="2:18" ht="42" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B98" s="8"/>
       <c r="C98" s="8"/>
-      <c r="D98" s="294">
+      <c r="D98" s="126">
         <v>8</v>
       </c>
-      <c r="E98" s="285"/>
-      <c r="F98" s="133"/>
-      <c r="G98" s="133"/>
-      <c r="H98" s="133"/>
-      <c r="I98" s="133"/>
-      <c r="J98" s="133"/>
-      <c r="K98" s="133"/>
-      <c r="L98" s="133"/>
-      <c r="M98" s="133"/>
+      <c r="E98" s="128"/>
+      <c r="F98" s="129"/>
+      <c r="G98" s="129"/>
+      <c r="H98" s="129"/>
+      <c r="I98" s="129"/>
+      <c r="J98" s="129"/>
+      <c r="K98" s="129"/>
+      <c r="L98" s="129"/>
+      <c r="M98" s="130"/>
       <c r="N98" s="5"/>
-      <c r="O98" s="194"/>
-      <c r="P98" s="194"/>
+      <c r="O98" s="114"/>
+      <c r="P98" s="114"/>
       <c r="Q98" s="44"/>
       <c r="R98" s="44"/>
     </row>
-    <row r="99" spans="2:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B99" s="8"/>
       <c r="C99" s="8"/>
-      <c r="D99" s="105"/>
-      <c r="E99" s="102"/>
-      <c r="F99" s="106"/>
-      <c r="G99" s="106"/>
-      <c r="H99" s="106"/>
-      <c r="I99" s="106"/>
-      <c r="J99" s="106"/>
-      <c r="K99" s="106"/>
-      <c r="L99" s="106"/>
-      <c r="M99" s="106"/>
+      <c r="D99" s="127"/>
+      <c r="E99" s="131"/>
+      <c r="F99" s="132"/>
+      <c r="G99" s="132"/>
+      <c r="H99" s="132"/>
+      <c r="I99" s="132"/>
+      <c r="J99" s="132"/>
+      <c r="K99" s="132"/>
+      <c r="L99" s="132"/>
+      <c r="M99" s="133"/>
       <c r="N99" s="5"/>
-      <c r="O99" s="3"/>
-      <c r="P99" s="3"/>
+      <c r="O99" s="115" t="s">
+        <v>118</v>
+      </c>
+      <c r="P99" s="115"/>
       <c r="Q99" s="44"/>
       <c r="R99" s="44"/>
     </row>
-    <row r="100" spans="2:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B100" s="8"/>
       <c r="C100" s="8"/>
-      <c r="D100" s="104"/>
-      <c r="E100" s="107"/>
-      <c r="F100" s="107"/>
-      <c r="G100" s="107"/>
-      <c r="H100" s="107"/>
-      <c r="I100" s="106"/>
-      <c r="J100" s="106"/>
-      <c r="K100" s="106"/>
-      <c r="L100" s="106"/>
-      <c r="M100" s="106"/>
+      <c r="D100" s="124">
+        <v>9</v>
+      </c>
+      <c r="E100" s="118"/>
+      <c r="F100" s="119"/>
+      <c r="G100" s="119"/>
+      <c r="H100" s="119"/>
+      <c r="I100" s="119"/>
+      <c r="J100" s="119"/>
+      <c r="K100" s="119"/>
+      <c r="L100" s="119"/>
+      <c r="M100" s="120"/>
       <c r="N100" s="5"/>
-      <c r="O100" s="125" t="s">
-        <v>118</v>
-      </c>
-      <c r="P100" s="142"/>
+      <c r="O100" s="116" t="s">
+        <v>119</v>
+      </c>
+      <c r="P100" s="116"/>
       <c r="Q100" s="44"/>
       <c r="R100" s="44"/>
     </row>
-    <row r="101" spans="2:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B101" s="8"/>
       <c r="C101" s="8"/>
-      <c r="D101" s="105"/>
-      <c r="E101" s="88"/>
-      <c r="F101" s="88"/>
-      <c r="G101" s="88"/>
-      <c r="H101" s="88"/>
-      <c r="I101" s="106"/>
-      <c r="J101" s="106"/>
-      <c r="K101" s="106"/>
-      <c r="L101" s="106"/>
-      <c r="M101" s="106"/>
+      <c r="D101" s="125"/>
+      <c r="E101" s="121"/>
+      <c r="F101" s="122"/>
+      <c r="G101" s="122"/>
+      <c r="H101" s="122"/>
+      <c r="I101" s="122"/>
+      <c r="J101" s="122"/>
+      <c r="K101" s="122"/>
+      <c r="L101" s="122"/>
+      <c r="M101" s="123"/>
       <c r="N101" s="5"/>
-      <c r="O101" s="193" t="s">
-        <v>119</v>
-      </c>
-      <c r="P101" s="142"/>
+      <c r="O101" s="116"/>
+      <c r="P101" s="116"/>
       <c r="Q101" s="44"/>
       <c r="R101" s="44"/>
     </row>
-    <row r="102" spans="2:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B102" s="8"/>
       <c r="C102" s="8"/>
-      <c r="D102" s="104"/>
-      <c r="E102" s="88"/>
-      <c r="F102" s="88"/>
-      <c r="G102" s="88"/>
-      <c r="H102" s="88"/>
-      <c r="I102" s="106"/>
-      <c r="J102" s="106"/>
-      <c r="K102" s="106"/>
-      <c r="L102" s="106"/>
-      <c r="M102" s="106"/>
+      <c r="D102" s="126">
+        <v>10</v>
+      </c>
+      <c r="E102" s="128"/>
+      <c r="F102" s="129"/>
+      <c r="G102" s="129"/>
+      <c r="H102" s="129"/>
+      <c r="I102" s="129"/>
+      <c r="J102" s="129"/>
+      <c r="K102" s="129"/>
+      <c r="L102" s="129"/>
+      <c r="M102" s="130"/>
       <c r="N102" s="5"/>
-      <c r="O102" s="142"/>
-      <c r="P102" s="142"/>
+      <c r="O102" s="116"/>
+      <c r="P102" s="116"/>
       <c r="Q102" s="44"/>
       <c r="R102" s="44"/>
     </row>
-    <row r="103" spans="2:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B103" s="8"/>
       <c r="C103" s="8"/>
-      <c r="D103" s="105"/>
-      <c r="E103" s="88"/>
-      <c r="F103" s="88"/>
-      <c r="G103" s="88"/>
-      <c r="H103" s="88"/>
-      <c r="I103" s="106"/>
-      <c r="J103" s="106"/>
-      <c r="K103" s="106"/>
-      <c r="L103" s="106"/>
-      <c r="M103" s="106"/>
+      <c r="D103" s="127"/>
+      <c r="E103" s="131"/>
+      <c r="F103" s="132"/>
+      <c r="G103" s="132"/>
+      <c r="H103" s="132"/>
+      <c r="I103" s="132"/>
+      <c r="J103" s="132"/>
+      <c r="K103" s="132"/>
+      <c r="L103" s="132"/>
+      <c r="M103" s="133"/>
       <c r="N103" s="5"/>
-      <c r="O103" s="142"/>
-      <c r="P103" s="142"/>
+      <c r="O103" s="116"/>
+      <c r="P103" s="116"/>
       <c r="Q103" s="44"/>
       <c r="R103" s="44"/>
     </row>
-    <row r="104" spans="2:18" ht="49.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B104" s="8"/>
       <c r="C104" s="8"/>
-      <c r="D104" s="104"/>
-      <c r="E104" s="107"/>
-      <c r="F104" s="107"/>
-      <c r="G104" s="107"/>
-      <c r="H104" s="107"/>
-      <c r="I104" s="106"/>
-      <c r="J104" s="106"/>
-      <c r="K104" s="106"/>
-      <c r="L104" s="106"/>
-      <c r="M104" s="106"/>
+      <c r="D104" s="124">
+        <v>11</v>
+      </c>
+      <c r="E104" s="118"/>
+      <c r="F104" s="119"/>
+      <c r="G104" s="119"/>
+      <c r="H104" s="119"/>
+      <c r="I104" s="119"/>
+      <c r="J104" s="119"/>
+      <c r="K104" s="119"/>
+      <c r="L104" s="119"/>
+      <c r="M104" s="120"/>
       <c r="N104" s="5"/>
-      <c r="O104" s="142"/>
-      <c r="P104" s="142"/>
+      <c r="O104" s="116"/>
+      <c r="P104" s="116"/>
       <c r="Q104" s="44"/>
       <c r="R104" s="44"/>
     </row>
-    <row r="105" spans="2:18" ht="24.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B105" s="8"/>
       <c r="C105" s="8"/>
-      <c r="D105" s="105"/>
-      <c r="E105" s="108"/>
-      <c r="F105" s="108"/>
-      <c r="G105" s="108"/>
-      <c r="H105" s="108"/>
-      <c r="I105" s="106"/>
-      <c r="J105" s="106"/>
-      <c r="K105" s="106"/>
-      <c r="L105" s="106"/>
-      <c r="M105" s="106"/>
+      <c r="D105" s="125"/>
+      <c r="E105" s="121"/>
+      <c r="F105" s="122"/>
+      <c r="G105" s="122"/>
+      <c r="H105" s="122"/>
+      <c r="I105" s="122"/>
+      <c r="J105" s="122"/>
+      <c r="K105" s="122"/>
+      <c r="L105" s="122"/>
+      <c r="M105" s="123"/>
       <c r="N105" s="5"/>
-      <c r="O105" s="142"/>
-      <c r="P105" s="142"/>
+      <c r="O105" s="117"/>
+      <c r="P105" s="117"/>
       <c r="Q105" s="44"/>
       <c r="R105" s="44"/>
     </row>
-    <row r="106" spans="2:18" ht="39" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B106" s="8"/>
       <c r="C106" s="8"/>
-      <c r="D106" s="104"/>
-      <c r="E106" s="296" t="s">
-        <v>88</v>
-      </c>
-      <c r="F106" s="296"/>
-      <c r="G106" s="296"/>
-      <c r="H106" s="296"/>
-      <c r="I106" s="106"/>
-      <c r="J106" s="106"/>
-      <c r="K106" s="106"/>
-      <c r="L106" s="106"/>
-      <c r="M106" s="106"/>
+      <c r="D106" s="126">
+        <v>12</v>
+      </c>
+      <c r="E106" s="128"/>
+      <c r="F106" s="129"/>
+      <c r="G106" s="129"/>
+      <c r="H106" s="129"/>
+      <c r="I106" s="129"/>
+      <c r="J106" s="129"/>
+      <c r="K106" s="129"/>
+      <c r="L106" s="129"/>
+      <c r="M106" s="130"/>
       <c r="N106" s="5"/>
-      <c r="O106" s="194"/>
-      <c r="P106" s="194"/>
+      <c r="O106" s="135"/>
+      <c r="P106" s="135"/>
       <c r="Q106" s="44"/>
       <c r="R106" s="44"/>
     </row>
-    <row r="107" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B107" s="8"/>
       <c r="C107" s="8"/>
-      <c r="D107" s="105"/>
-      <c r="E107" s="102"/>
-      <c r="F107" s="106"/>
-      <c r="G107" s="106"/>
-      <c r="H107" s="106"/>
-      <c r="I107" s="106"/>
-      <c r="J107" s="106"/>
-      <c r="K107" s="106"/>
-      <c r="L107" s="106"/>
-      <c r="M107" s="106"/>
+      <c r="D107" s="127"/>
+      <c r="E107" s="131"/>
+      <c r="F107" s="132"/>
+      <c r="G107" s="132"/>
+      <c r="H107" s="132"/>
+      <c r="I107" s="132"/>
+      <c r="J107" s="132"/>
+      <c r="K107" s="132"/>
+      <c r="L107" s="132"/>
+      <c r="M107" s="133"/>
       <c r="N107" s="5"/>
-      <c r="O107" s="3"/>
-      <c r="P107" s="3"/>
+      <c r="O107" s="136"/>
+      <c r="P107" s="136"/>
       <c r="Q107" s="44"/>
       <c r="R107" s="44"/>
     </row>
-    <row r="108" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B108" s="8"/>
       <c r="C108" s="8"/>
-      <c r="D108" s="110" t="s">
-        <v>91</v>
-      </c>
-      <c r="E108" s="113" t="s">
-        <v>130</v>
-      </c>
-      <c r="F108" s="114"/>
-      <c r="G108" s="114"/>
-      <c r="H108" s="114"/>
-      <c r="I108" s="114"/>
-      <c r="J108" s="114"/>
-      <c r="K108" s="114"/>
-      <c r="L108" s="114"/>
-      <c r="M108" s="114"/>
-      <c r="N108" s="114"/>
-      <c r="O108" s="114"/>
-      <c r="P108" s="114"/>
+      <c r="D108" s="124">
+        <v>13</v>
+      </c>
+      <c r="E108" s="118"/>
+      <c r="F108" s="119"/>
+      <c r="G108" s="119"/>
+      <c r="H108" s="119"/>
+      <c r="I108" s="119"/>
+      <c r="J108" s="119"/>
+      <c r="K108" s="119"/>
+      <c r="L108" s="119"/>
+      <c r="M108" s="120"/>
+      <c r="N108" s="5"/>
+      <c r="O108" s="136"/>
+      <c r="P108" s="136"/>
       <c r="Q108" s="44"/>
       <c r="R108" s="44"/>
     </row>
-    <row r="109" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B109" s="8"/>
       <c r="C109" s="8"/>
-      <c r="D109" s="111">
-        <v>1</v>
-      </c>
-      <c r="E109" s="115" t="s">
-        <v>120</v>
-      </c>
-      <c r="F109" s="115"/>
-      <c r="G109" s="115"/>
-      <c r="H109" s="115"/>
-      <c r="I109" s="115"/>
-      <c r="J109" s="115"/>
-      <c r="K109" s="115"/>
-      <c r="L109" s="115"/>
-      <c r="M109" s="115"/>
-      <c r="N109" s="115"/>
-      <c r="O109" s="115"/>
-      <c r="P109" s="115"/>
-      <c r="Q109" s="55"/>
-      <c r="R109" s="55"/>
-    </row>
-    <row r="110" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D109" s="125"/>
+      <c r="E109" s="121"/>
+      <c r="F109" s="122"/>
+      <c r="G109" s="122"/>
+      <c r="H109" s="122"/>
+      <c r="I109" s="122"/>
+      <c r="J109" s="122"/>
+      <c r="K109" s="122"/>
+      <c r="L109" s="122"/>
+      <c r="M109" s="123"/>
+      <c r="N109" s="5"/>
+      <c r="O109" s="136"/>
+      <c r="P109" s="136"/>
+      <c r="Q109" s="44"/>
+      <c r="R109" s="44"/>
+    </row>
+    <row r="110" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B110" s="8"/>
       <c r="C110" s="8"/>
-      <c r="D110" s="295">
-        <v>2</v>
-      </c>
-      <c r="E110" s="122"/>
-      <c r="F110" s="122"/>
-      <c r="G110" s="122"/>
-      <c r="H110" s="122"/>
-      <c r="I110" s="122"/>
-      <c r="J110" s="122"/>
-      <c r="K110" s="122"/>
-      <c r="L110" s="122"/>
-      <c r="M110" s="122"/>
-      <c r="N110" s="122"/>
-      <c r="O110" s="122"/>
-      <c r="P110" s="122"/>
-      <c r="Q110" s="55"/>
-      <c r="R110" s="55"/>
-    </row>
-    <row r="111" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D110" s="126">
+        <v>14</v>
+      </c>
+      <c r="E110" s="128"/>
+      <c r="F110" s="129"/>
+      <c r="G110" s="129"/>
+      <c r="H110" s="129"/>
+      <c r="I110" s="129"/>
+      <c r="J110" s="129"/>
+      <c r="K110" s="129"/>
+      <c r="L110" s="129"/>
+      <c r="M110" s="130"/>
+      <c r="N110" s="5"/>
+      <c r="O110" s="136"/>
+      <c r="P110" s="136"/>
+      <c r="Q110" s="44"/>
+      <c r="R110" s="44"/>
+    </row>
+    <row r="111" spans="2:18" ht="27.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B111" s="8"/>
       <c r="C111" s="8"/>
-      <c r="D111" s="111">
-        <v>3</v>
-      </c>
-      <c r="E111" s="116"/>
-      <c r="F111" s="116"/>
-      <c r="G111" s="116"/>
-      <c r="H111" s="116"/>
-      <c r="I111" s="116"/>
-      <c r="J111" s="116"/>
-      <c r="K111" s="116"/>
-      <c r="L111" s="116"/>
-      <c r="M111" s="116"/>
-      <c r="N111" s="116"/>
-      <c r="O111" s="116"/>
-      <c r="P111" s="116"/>
-      <c r="Q111" s="55"/>
-      <c r="R111" s="55"/>
-    </row>
-    <row r="112" spans="2:18" ht="24" x14ac:dyDescent="0.3">
-      <c r="B112" s="3"/>
-      <c r="C112" s="3"/>
-      <c r="D112" s="295">
-        <v>4</v>
-      </c>
-      <c r="E112" s="122"/>
-      <c r="F112" s="122"/>
-      <c r="G112" s="122"/>
-      <c r="H112" s="122"/>
-      <c r="I112" s="122"/>
-      <c r="J112" s="122"/>
-      <c r="K112" s="122"/>
-      <c r="L112" s="122"/>
-      <c r="M112" s="122"/>
-      <c r="N112" s="122"/>
-      <c r="O112" s="122"/>
-      <c r="P112" s="122"/>
-    </row>
-    <row r="113" spans="2:18" ht="24" x14ac:dyDescent="0.3">
-      <c r="B113" s="3"/>
-      <c r="C113" s="3"/>
-      <c r="D113" s="111">
-        <v>5</v>
-      </c>
-      <c r="E113" s="117"/>
-      <c r="F113" s="117"/>
-      <c r="G113" s="117"/>
-      <c r="H113" s="117"/>
-      <c r="I113" s="117"/>
-      <c r="J113" s="117"/>
-      <c r="K113" s="117"/>
-      <c r="L113" s="117"/>
-      <c r="M113" s="117"/>
-      <c r="N113" s="117"/>
-      <c r="O113" s="117"/>
-      <c r="P113" s="117"/>
-    </row>
-    <row r="114" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D111" s="127"/>
+      <c r="E111" s="131"/>
+      <c r="F111" s="132"/>
+      <c r="G111" s="132"/>
+      <c r="H111" s="132"/>
+      <c r="I111" s="132"/>
+      <c r="J111" s="132"/>
+      <c r="K111" s="132"/>
+      <c r="L111" s="132"/>
+      <c r="M111" s="133"/>
+      <c r="N111" s="5"/>
+      <c r="O111" s="137"/>
+      <c r="P111" s="137"/>
+      <c r="Q111" s="46"/>
+      <c r="R111" s="46"/>
+    </row>
+    <row r="112" spans="2:18" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B112" s="8"/>
+      <c r="C112" s="8"/>
+      <c r="D112" s="295"/>
+      <c r="E112" s="296"/>
+      <c r="F112" s="296"/>
+      <c r="G112" s="296"/>
+      <c r="H112" s="296"/>
+      <c r="I112" s="296"/>
+      <c r="J112" s="296"/>
+      <c r="K112" s="296"/>
+      <c r="L112" s="296"/>
+      <c r="M112" s="296"/>
+      <c r="N112" s="5"/>
+      <c r="O112" s="134" t="s">
+        <v>88</v>
+      </c>
+      <c r="P112" s="134"/>
+      <c r="Q112" s="46"/>
+      <c r="R112" s="46"/>
+    </row>
+    <row r="113" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B113" s="8"/>
+      <c r="C113" s="8"/>
+      <c r="D113" s="104"/>
+      <c r="E113" s="102"/>
+      <c r="F113" s="105"/>
+      <c r="G113" s="105"/>
+      <c r="H113" s="105"/>
+      <c r="I113" s="105"/>
+      <c r="J113" s="105"/>
+      <c r="K113" s="105"/>
+      <c r="L113" s="105"/>
+      <c r="M113" s="105"/>
+      <c r="N113" s="5"/>
+      <c r="O113" s="3"/>
+      <c r="P113" s="3"/>
+      <c r="Q113" s="44"/>
+      <c r="R113" s="44"/>
+    </row>
+    <row r="114" spans="2:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B114" s="8"/>
       <c r="C114" s="8"/>
-      <c r="D114" s="295">
-        <v>6</v>
-      </c>
-      <c r="E114" s="122"/>
-      <c r="F114" s="122"/>
-      <c r="G114" s="122"/>
-      <c r="H114" s="122"/>
-      <c r="I114" s="122"/>
-      <c r="J114" s="122"/>
-      <c r="K114" s="122"/>
-      <c r="L114" s="122"/>
-      <c r="M114" s="122"/>
-      <c r="N114" s="122"/>
-      <c r="O114" s="122"/>
-      <c r="P114" s="122"/>
-      <c r="Q114" s="55"/>
-      <c r="R114" s="55"/>
+      <c r="D114" s="107" t="s">
+        <v>91</v>
+      </c>
+      <c r="E114" s="138" t="s">
+        <v>130</v>
+      </c>
+      <c r="F114" s="139"/>
+      <c r="G114" s="139"/>
+      <c r="H114" s="139"/>
+      <c r="I114" s="139"/>
+      <c r="J114" s="139"/>
+      <c r="K114" s="139"/>
+      <c r="L114" s="139"/>
+      <c r="M114" s="139"/>
+      <c r="N114" s="139"/>
+      <c r="O114" s="139"/>
+      <c r="P114" s="139"/>
+      <c r="Q114" s="44"/>
+      <c r="R114" s="44"/>
     </row>
     <row r="115" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B115" s="8"/>
       <c r="C115" s="8"/>
-      <c r="D115" s="111">
-        <v>7</v>
-      </c>
-      <c r="E115" s="116"/>
-      <c r="F115" s="116"/>
-      <c r="G115" s="116"/>
-      <c r="H115" s="116"/>
-      <c r="I115" s="116"/>
-      <c r="J115" s="116"/>
-      <c r="K115" s="116"/>
-      <c r="L115" s="116"/>
-      <c r="M115" s="116"/>
-      <c r="N115" s="116"/>
-      <c r="O115" s="116"/>
-      <c r="P115" s="116"/>
+      <c r="D115" s="108">
+        <v>1</v>
+      </c>
+      <c r="E115" s="140" t="s">
+        <v>120</v>
+      </c>
+      <c r="F115" s="140"/>
+      <c r="G115" s="140"/>
+      <c r="H115" s="140"/>
+      <c r="I115" s="140"/>
+      <c r="J115" s="140"/>
+      <c r="K115" s="140"/>
+      <c r="L115" s="140"/>
+      <c r="M115" s="140"/>
+      <c r="N115" s="140"/>
+      <c r="O115" s="140"/>
+      <c r="P115" s="140"/>
       <c r="Q115" s="55"/>
       <c r="R115" s="55"/>
     </row>
     <row r="116" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B116" s="8"/>
       <c r="C116" s="8"/>
-      <c r="D116" s="295">
-        <v>8</v>
-      </c>
-      <c r="E116" s="122"/>
-      <c r="F116" s="122"/>
-      <c r="G116" s="122"/>
-      <c r="H116" s="122"/>
-      <c r="I116" s="122"/>
-      <c r="J116" s="122"/>
-      <c r="K116" s="122"/>
-      <c r="L116" s="122"/>
-      <c r="M116" s="122"/>
-      <c r="N116" s="122"/>
-      <c r="O116" s="122"/>
-      <c r="P116" s="122"/>
+      <c r="D116" s="113">
+        <v>2</v>
+      </c>
+      <c r="E116" s="142"/>
+      <c r="F116" s="142"/>
+      <c r="G116" s="142"/>
+      <c r="H116" s="142"/>
+      <c r="I116" s="142"/>
+      <c r="J116" s="142"/>
+      <c r="K116" s="142"/>
+      <c r="L116" s="142"/>
+      <c r="M116" s="142"/>
+      <c r="N116" s="142"/>
+      <c r="O116" s="142"/>
+      <c r="P116" s="142"/>
       <c r="Q116" s="55"/>
       <c r="R116" s="55"/>
     </row>
-    <row r="117" spans="2:18" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B117" s="74"/>
-      <c r="C117" s="74"/>
-      <c r="D117" s="112"/>
-      <c r="E117" s="112"/>
-      <c r="F117" s="112"/>
-      <c r="G117" s="112"/>
-      <c r="H117" s="112"/>
-      <c r="I117" s="112"/>
-      <c r="J117" s="112"/>
-      <c r="K117" s="112"/>
-      <c r="L117" s="112"/>
-      <c r="M117" s="112"/>
-      <c r="N117" s="112"/>
-      <c r="O117" s="112"/>
-      <c r="P117" s="112"/>
+    <row r="117" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B117" s="8"/>
+      <c r="C117" s="8"/>
+      <c r="D117" s="108">
+        <v>3</v>
+      </c>
+      <c r="E117" s="141"/>
+      <c r="F117" s="141"/>
+      <c r="G117" s="141"/>
+      <c r="H117" s="141"/>
+      <c r="I117" s="141"/>
+      <c r="J117" s="141"/>
+      <c r="K117" s="141"/>
+      <c r="L117" s="141"/>
+      <c r="M117" s="141"/>
+      <c r="N117" s="141"/>
+      <c r="O117" s="141"/>
+      <c r="P117" s="141"/>
       <c r="Q117" s="55"/>
       <c r="R117" s="55"/>
     </row>
-    <row r="118" spans="2:18" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B118" s="74"/>
-      <c r="C118" s="74"/>
-      <c r="D118" s="153" t="s">
-        <v>121</v>
-      </c>
-      <c r="E118" s="153"/>
-      <c r="F118" s="153"/>
-      <c r="G118" s="153"/>
-      <c r="H118" s="153"/>
-      <c r="I118" s="153"/>
-      <c r="J118" s="153"/>
-      <c r="K118" s="153"/>
-      <c r="L118" s="153"/>
-      <c r="M118" s="153"/>
-      <c r="N118" s="153"/>
-      <c r="O118" s="153"/>
-      <c r="P118" s="153"/>
-      <c r="Q118" s="55"/>
-      <c r="R118" s="55"/>
-    </row>
-    <row r="119" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B119" s="74"/>
-      <c r="C119" s="74"/>
-      <c r="D119" s="56"/>
-      <c r="E119" s="55"/>
-      <c r="F119" s="55"/>
-      <c r="G119" s="55"/>
-      <c r="H119" s="55"/>
-      <c r="I119" s="55"/>
-      <c r="J119" s="55"/>
-      <c r="K119" s="55"/>
-      <c r="L119" s="55"/>
-      <c r="M119" s="55"/>
-      <c r="N119" s="55"/>
-      <c r="O119" s="55"/>
-      <c r="P119" s="55"/>
-      <c r="Q119" s="55"/>
-      <c r="R119" s="55"/>
-    </row>
-    <row r="120" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B120" s="74"/>
-      <c r="C120" s="74"/>
-      <c r="D120" s="130" t="s">
-        <v>122</v>
-      </c>
-      <c r="E120" s="130"/>
-      <c r="F120" s="130"/>
-      <c r="G120" s="55"/>
-      <c r="H120" s="130" t="s">
-        <v>122</v>
-      </c>
-      <c r="I120" s="130"/>
-      <c r="J120" s="130"/>
-      <c r="K120" s="55"/>
-      <c r="L120" s="130" t="s">
-        <v>122</v>
-      </c>
-      <c r="M120" s="130"/>
-      <c r="N120" s="55"/>
-      <c r="O120" s="130" t="s">
-        <v>123</v>
-      </c>
-      <c r="P120" s="130"/>
+    <row r="118" spans="2:18" ht="24" x14ac:dyDescent="0.3">
+      <c r="B118" s="3"/>
+      <c r="C118" s="3"/>
+      <c r="D118" s="113">
+        <v>4</v>
+      </c>
+      <c r="E118" s="142"/>
+      <c r="F118" s="142"/>
+      <c r="G118" s="142"/>
+      <c r="H118" s="142"/>
+      <c r="I118" s="142"/>
+      <c r="J118" s="142"/>
+      <c r="K118" s="142"/>
+      <c r="L118" s="142"/>
+      <c r="M118" s="142"/>
+      <c r="N118" s="142"/>
+      <c r="O118" s="142"/>
+      <c r="P118" s="142"/>
+    </row>
+    <row r="119" spans="2:18" ht="24" x14ac:dyDescent="0.3">
+      <c r="B119" s="3"/>
+      <c r="C119" s="3"/>
+      <c r="D119" s="108">
+        <v>5</v>
+      </c>
+      <c r="E119" s="143"/>
+      <c r="F119" s="143"/>
+      <c r="G119" s="143"/>
+      <c r="H119" s="143"/>
+      <c r="I119" s="143"/>
+      <c r="J119" s="143"/>
+      <c r="K119" s="143"/>
+      <c r="L119" s="143"/>
+      <c r="M119" s="143"/>
+      <c r="N119" s="143"/>
+      <c r="O119" s="143"/>
+      <c r="P119" s="143"/>
+    </row>
+    <row r="120" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B120" s="8"/>
+      <c r="C120" s="8"/>
+      <c r="D120" s="113">
+        <v>6</v>
+      </c>
+      <c r="E120" s="142"/>
+      <c r="F120" s="142"/>
+      <c r="G120" s="142"/>
+      <c r="H120" s="142"/>
+      <c r="I120" s="142"/>
+      <c r="J120" s="142"/>
+      <c r="K120" s="142"/>
+      <c r="L120" s="142"/>
+      <c r="M120" s="142"/>
+      <c r="N120" s="142"/>
+      <c r="O120" s="142"/>
+      <c r="P120" s="142"/>
       <c r="Q120" s="55"/>
       <c r="R120" s="55"/>
     </row>
-    <row r="121" spans="2:18" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B121" s="74"/>
-      <c r="C121" s="74"/>
-      <c r="D121" s="55"/>
-      <c r="E121" s="55"/>
-      <c r="F121" s="55"/>
-      <c r="G121" s="55"/>
-      <c r="H121" s="55"/>
-      <c r="I121" s="55"/>
-      <c r="J121" s="55"/>
-      <c r="K121" s="55"/>
-      <c r="L121" s="55"/>
-      <c r="M121" s="55"/>
-      <c r="N121" s="55"/>
-      <c r="O121" s="55"/>
-      <c r="P121" s="55"/>
+    <row r="121" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B121" s="8"/>
+      <c r="C121" s="8"/>
+      <c r="D121" s="108">
+        <v>7</v>
+      </c>
+      <c r="E121" s="141"/>
+      <c r="F121" s="141"/>
+      <c r="G121" s="141"/>
+      <c r="H121" s="141"/>
+      <c r="I121" s="141"/>
+      <c r="J121" s="141"/>
+      <c r="K121" s="141"/>
+      <c r="L121" s="141"/>
+      <c r="M121" s="141"/>
+      <c r="N121" s="141"/>
+      <c r="O121" s="141"/>
+      <c r="P121" s="141"/>
       <c r="Q121" s="55"/>
       <c r="R121" s="55"/>
     </row>
-    <row r="122" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B122" s="74"/>
-      <c r="C122" s="74"/>
-      <c r="D122" s="92"/>
-      <c r="E122" s="92"/>
-      <c r="F122" s="92"/>
-      <c r="G122" s="55"/>
-      <c r="H122" s="92"/>
-      <c r="I122" s="92"/>
-      <c r="J122" s="92"/>
-      <c r="K122" s="55"/>
-      <c r="L122" s="92"/>
-      <c r="M122" s="92"/>
-      <c r="N122" s="55"/>
-      <c r="O122" s="92"/>
-      <c r="P122" s="92"/>
+    <row r="122" spans="2:18" s="3" customFormat="1" ht="21" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B122" s="8"/>
+      <c r="C122" s="8"/>
+      <c r="D122" s="113">
+        <v>8</v>
+      </c>
+      <c r="E122" s="142"/>
+      <c r="F122" s="142"/>
+      <c r="G122" s="142"/>
+      <c r="H122" s="142"/>
+      <c r="I122" s="142"/>
+      <c r="J122" s="142"/>
+      <c r="K122" s="142"/>
+      <c r="L122" s="142"/>
+      <c r="M122" s="142"/>
+      <c r="N122" s="142"/>
+      <c r="O122" s="142"/>
+      <c r="P122" s="142"/>
       <c r="Q122" s="55"/>
       <c r="R122" s="55"/>
     </row>
-    <row r="123" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="2:18" s="3" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B123" s="74"/>
       <c r="C123" s="74"/>
-      <c r="D123" s="92"/>
-      <c r="E123" s="92"/>
-      <c r="F123" s="92"/>
-      <c r="G123" s="55"/>
-      <c r="H123" s="92"/>
-      <c r="I123" s="92"/>
-      <c r="J123" s="92"/>
-      <c r="K123" s="55"/>
-      <c r="L123" s="92"/>
-      <c r="M123" s="92"/>
-      <c r="N123" s="55"/>
-      <c r="O123" s="92"/>
-      <c r="P123" s="92"/>
+      <c r="D123" s="166"/>
+      <c r="E123" s="166"/>
+      <c r="F123" s="166"/>
+      <c r="G123" s="166"/>
+      <c r="H123" s="166"/>
+      <c r="I123" s="166"/>
+      <c r="J123" s="166"/>
+      <c r="K123" s="166"/>
+      <c r="L123" s="166"/>
+      <c r="M123" s="166"/>
+      <c r="N123" s="166"/>
+      <c r="O123" s="166"/>
+      <c r="P123" s="166"/>
       <c r="Q123" s="55"/>
       <c r="R123" s="55"/>
     </row>
-    <row r="124" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="2:18" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B124" s="74"/>
       <c r="C124" s="74"/>
-      <c r="D124" s="92"/>
-      <c r="E124" s="92"/>
-      <c r="F124" s="92"/>
-      <c r="G124" s="55"/>
-      <c r="H124" s="92"/>
-      <c r="I124" s="92"/>
-      <c r="J124" s="92"/>
-      <c r="K124" s="55"/>
-      <c r="L124" s="92"/>
-      <c r="M124" s="92"/>
-      <c r="N124" s="55"/>
-      <c r="O124" s="92"/>
-      <c r="P124" s="92"/>
+      <c r="D124" s="183" t="s">
+        <v>121</v>
+      </c>
+      <c r="E124" s="183"/>
+      <c r="F124" s="183"/>
+      <c r="G124" s="183"/>
+      <c r="H124" s="183"/>
+      <c r="I124" s="183"/>
+      <c r="J124" s="183"/>
+      <c r="K124" s="183"/>
+      <c r="L124" s="183"/>
+      <c r="M124" s="183"/>
+      <c r="N124" s="183"/>
+      <c r="O124" s="183"/>
+      <c r="P124" s="183"/>
       <c r="Q124" s="55"/>
       <c r="R124" s="55"/>
     </row>
-    <row r="125" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B125" s="74"/>
       <c r="C125" s="74"/>
-      <c r="D125" s="93"/>
-      <c r="E125" s="93"/>
-      <c r="F125" s="93"/>
+      <c r="D125" s="56"/>
+      <c r="E125" s="55"/>
+      <c r="F125" s="55"/>
       <c r="G125" s="55"/>
-      <c r="H125" s="93"/>
-      <c r="I125" s="93"/>
-      <c r="J125" s="93"/>
+      <c r="H125" s="55"/>
+      <c r="I125" s="55"/>
+      <c r="J125" s="55"/>
       <c r="K125" s="55"/>
-      <c r="L125" s="93"/>
-      <c r="M125" s="93"/>
+      <c r="L125" s="55"/>
+      <c r="M125" s="55"/>
       <c r="N125" s="55"/>
-      <c r="O125" s="93"/>
-      <c r="P125" s="93"/>
+      <c r="O125" s="55"/>
+      <c r="P125" s="55"/>
       <c r="Q125" s="55"/>
       <c r="R125" s="55"/>
     </row>
-    <row r="126" spans="2:18" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="126" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B126" s="74"/>
       <c r="C126" s="74"/>
-      <c r="D126" s="211" t="s">
-        <v>124</v>
-      </c>
-      <c r="E126" s="161"/>
-      <c r="F126" s="161"/>
-      <c r="G126" s="94"/>
-      <c r="H126" s="189" t="s">
-        <v>125</v>
-      </c>
-      <c r="I126" s="161"/>
-      <c r="J126" s="161"/>
-      <c r="K126" s="94"/>
-      <c r="L126" s="127" t="s">
-        <v>126</v>
-      </c>
-      <c r="M126" s="128"/>
-      <c r="N126" s="94"/>
-      <c r="O126" s="127" t="s">
-        <v>127</v>
-      </c>
-      <c r="P126" s="128"/>
+      <c r="D126" s="147" t="s">
+        <v>122</v>
+      </c>
+      <c r="E126" s="147"/>
+      <c r="F126" s="147"/>
+      <c r="G126" s="55"/>
+      <c r="H126" s="147" t="s">
+        <v>122</v>
+      </c>
+      <c r="I126" s="147"/>
+      <c r="J126" s="147"/>
+      <c r="K126" s="55"/>
+      <c r="L126" s="147" t="s">
+        <v>122</v>
+      </c>
+      <c r="M126" s="147"/>
+      <c r="N126" s="55"/>
+      <c r="O126" s="147" t="s">
+        <v>123</v>
+      </c>
+      <c r="P126" s="147"/>
       <c r="Q126" s="55"/>
       <c r="R126" s="55"/>
     </row>
-    <row r="127" spans="2:18" s="3" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="127" spans="2:18" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B127" s="74"/>
       <c r="C127" s="74"/>
-      <c r="D127" s="137" t="s">
-        <v>16</v>
-      </c>
-      <c r="E127" s="135"/>
-      <c r="F127" s="135"/>
-      <c r="G127" s="90"/>
-      <c r="H127" s="137" t="s">
-        <v>128</v>
-      </c>
-      <c r="I127" s="135"/>
-      <c r="J127" s="135"/>
-      <c r="K127" s="94"/>
-      <c r="L127" s="141" t="s">
-        <v>129</v>
-      </c>
-      <c r="M127" s="161"/>
-      <c r="N127" s="94"/>
-      <c r="O127" s="137" t="s">
-        <v>128</v>
-      </c>
-      <c r="P127" s="135"/>
+      <c r="D127" s="55"/>
+      <c r="E127" s="55"/>
+      <c r="F127" s="55"/>
+      <c r="G127" s="55"/>
+      <c r="H127" s="55"/>
+      <c r="I127" s="55"/>
+      <c r="J127" s="55"/>
+      <c r="K127" s="55"/>
+      <c r="L127" s="55"/>
+      <c r="M127" s="55"/>
+      <c r="N127" s="55"/>
+      <c r="O127" s="55"/>
+      <c r="P127" s="55"/>
       <c r="Q127" s="55"/>
       <c r="R127" s="55"/>
     </row>
-    <row r="128" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B128" s="74"/>
       <c r="C128" s="74"/>
-      <c r="D128" s="55"/>
-      <c r="E128" s="55"/>
-      <c r="F128" s="55"/>
+      <c r="D128" s="92"/>
+      <c r="E128" s="92"/>
+      <c r="F128" s="92"/>
       <c r="G128" s="55"/>
-      <c r="H128" s="55"/>
-      <c r="I128" s="55"/>
-      <c r="J128" s="55"/>
+      <c r="H128" s="92"/>
+      <c r="I128" s="92"/>
+      <c r="J128" s="92"/>
       <c r="K128" s="55"/>
-      <c r="L128" s="77"/>
-      <c r="M128" s="77"/>
+      <c r="L128" s="92"/>
+      <c r="M128" s="92"/>
       <c r="N128" s="55"/>
-      <c r="O128" s="77"/>
-      <c r="P128" s="78"/>
+      <c r="O128" s="92"/>
+      <c r="P128" s="92"/>
       <c r="Q128" s="55"/>
       <c r="R128" s="55"/>
     </row>
-    <row r="129" spans="2:18" s="3" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B129" s="74"/>
       <c r="C129" s="74"/>
-      <c r="D129" s="79"/>
-      <c r="E129" s="80"/>
-      <c r="F129" s="80"/>
-      <c r="G129" s="80"/>
-      <c r="H129" s="80"/>
-      <c r="I129" s="80"/>
-      <c r="J129" s="80"/>
-      <c r="K129" s="80"/>
-      <c r="L129" s="80"/>
-      <c r="M129" s="80"/>
-      <c r="N129" s="80"/>
-      <c r="O129" s="80"/>
-      <c r="P129" s="80"/>
+      <c r="D129" s="92"/>
+      <c r="E129" s="92"/>
+      <c r="F129" s="92"/>
+      <c r="G129" s="55"/>
+      <c r="H129" s="92"/>
+      <c r="I129" s="92"/>
+      <c r="J129" s="92"/>
+      <c r="K129" s="55"/>
+      <c r="L129" s="92"/>
+      <c r="M129" s="92"/>
+      <c r="N129" s="55"/>
+      <c r="O129" s="92"/>
+      <c r="P129" s="92"/>
       <c r="Q129" s="55"/>
       <c r="R129" s="55"/>
     </row>
-    <row r="130" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="130" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B130" s="74"/>
+      <c r="C130" s="74"/>
+      <c r="D130" s="92"/>
+      <c r="E130" s="92"/>
+      <c r="F130" s="92"/>
+      <c r="G130" s="55"/>
+      <c r="H130" s="92"/>
+      <c r="I130" s="92"/>
+      <c r="J130" s="92"/>
+      <c r="K130" s="55"/>
+      <c r="L130" s="92"/>
+      <c r="M130" s="92"/>
+      <c r="N130" s="55"/>
+      <c r="O130" s="92"/>
+      <c r="P130" s="92"/>
       <c r="Q130" s="55"/>
       <c r="R130" s="55"/>
     </row>
+    <row r="131" spans="2:18" ht="24" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B131" s="74"/>
+      <c r="C131" s="74"/>
+      <c r="D131" s="93"/>
+      <c r="E131" s="93"/>
+      <c r="F131" s="93"/>
+      <c r="G131" s="55"/>
+      <c r="H131" s="93"/>
+      <c r="I131" s="93"/>
+      <c r="J131" s="93"/>
+      <c r="K131" s="55"/>
+      <c r="L131" s="93"/>
+      <c r="M131" s="93"/>
+      <c r="N131" s="55"/>
+      <c r="O131" s="93"/>
+      <c r="P131" s="93"/>
+      <c r="Q131" s="55"/>
+      <c r="R131" s="55"/>
+    </row>
+    <row r="132" spans="2:18" s="3" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B132" s="74"/>
+      <c r="C132" s="74"/>
+      <c r="D132" s="229" t="s">
+        <v>124</v>
+      </c>
+      <c r="E132" s="154"/>
+      <c r="F132" s="154"/>
+      <c r="G132" s="94"/>
+      <c r="H132" s="153" t="s">
+        <v>125</v>
+      </c>
+      <c r="I132" s="154"/>
+      <c r="J132" s="154"/>
+      <c r="K132" s="94"/>
+      <c r="L132" s="145" t="s">
+        <v>126</v>
+      </c>
+      <c r="M132" s="146"/>
+      <c r="N132" s="94"/>
+      <c r="O132" s="145" t="s">
+        <v>127</v>
+      </c>
+      <c r="P132" s="146"/>
+      <c r="Q132" s="55"/>
+      <c r="R132" s="55"/>
+    </row>
+    <row r="133" spans="2:18" s="3" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B133" s="74"/>
+      <c r="C133" s="74"/>
+      <c r="D133" s="167" t="s">
+        <v>16</v>
+      </c>
+      <c r="E133" s="156"/>
+      <c r="F133" s="156"/>
+      <c r="G133" s="90"/>
+      <c r="H133" s="167" t="s">
+        <v>128</v>
+      </c>
+      <c r="I133" s="156"/>
+      <c r="J133" s="156"/>
+      <c r="K133" s="94"/>
+      <c r="L133" s="171" t="s">
+        <v>129</v>
+      </c>
+      <c r="M133" s="154"/>
+      <c r="N133" s="94"/>
+      <c r="O133" s="167" t="s">
+        <v>128</v>
+      </c>
+      <c r="P133" s="156"/>
+      <c r="Q133" s="55"/>
+      <c r="R133" s="55"/>
+    </row>
+    <row r="134" spans="2:18" s="3" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B134" s="74"/>
+      <c r="C134" s="74"/>
+      <c r="D134" s="55"/>
+      <c r="E134" s="55"/>
+      <c r="F134" s="55"/>
+      <c r="G134" s="55"/>
+      <c r="H134" s="55"/>
+      <c r="I134" s="55"/>
+      <c r="J134" s="55"/>
+      <c r="K134" s="55"/>
+      <c r="L134" s="77"/>
+      <c r="M134" s="77"/>
+      <c r="N134" s="55"/>
+      <c r="O134" s="77"/>
+      <c r="P134" s="78"/>
+      <c r="Q134" s="55"/>
+      <c r="R134" s="55"/>
+    </row>
+    <row r="135" spans="2:18" s="3" customFormat="1" ht="18" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B135" s="74"/>
+      <c r="C135" s="74"/>
+      <c r="D135" s="79"/>
+      <c r="E135" s="80"/>
+      <c r="F135" s="80"/>
+      <c r="G135" s="80"/>
+      <c r="H135" s="80"/>
+      <c r="I135" s="80"/>
+      <c r="J135" s="80"/>
+      <c r="K135" s="80"/>
+      <c r="L135" s="80"/>
+      <c r="M135" s="80"/>
+      <c r="N135" s="80"/>
+      <c r="O135" s="80"/>
+      <c r="P135" s="80"/>
+      <c r="Q135" s="55"/>
+      <c r="R135" s="55"/>
+    </row>
+    <row r="136" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="Q136" s="55"/>
+      <c r="R136" s="55"/>
+    </row>
   </sheetData>
-  <mergeCells count="184">
+  <mergeCells count="198">
+    <mergeCell ref="J64:L64"/>
+    <mergeCell ref="L4:N5"/>
     <mergeCell ref="D19:H19"/>
     <mergeCell ref="L21:O21"/>
     <mergeCell ref="D16:E16"/>
@@ -5759,6 +5886,15 @@
     <mergeCell ref="E77:P77"/>
     <mergeCell ref="E78:P78"/>
     <mergeCell ref="D14:E14"/>
+    <mergeCell ref="L14:O14"/>
+    <mergeCell ref="D41:I41"/>
+    <mergeCell ref="G61:I61"/>
+    <mergeCell ref="J61:L61"/>
+    <mergeCell ref="M61:P61"/>
+    <mergeCell ref="N58:O58"/>
+    <mergeCell ref="N49:O49"/>
+    <mergeCell ref="G64:I64"/>
+    <mergeCell ref="D40:I40"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="D15:E15"/>
     <mergeCell ref="H5:J5"/>
@@ -5782,19 +5918,18 @@
     <mergeCell ref="L15:O15"/>
     <mergeCell ref="F13:J13"/>
     <mergeCell ref="L12:O12"/>
-    <mergeCell ref="L4:N5"/>
-    <mergeCell ref="L14:O14"/>
+    <mergeCell ref="E52:J52"/>
+    <mergeCell ref="E71:P71"/>
     <mergeCell ref="F6:G6"/>
     <mergeCell ref="D13:E13"/>
     <mergeCell ref="L3:N3"/>
     <mergeCell ref="L32:O32"/>
-    <mergeCell ref="D126:F126"/>
+    <mergeCell ref="D132:F132"/>
     <mergeCell ref="I21:J21"/>
     <mergeCell ref="D38:I38"/>
     <mergeCell ref="E53:J53"/>
-    <mergeCell ref="E98:M98"/>
     <mergeCell ref="I23:J23"/>
-    <mergeCell ref="D120:F120"/>
+    <mergeCell ref="D126:F126"/>
     <mergeCell ref="E50:J50"/>
     <mergeCell ref="L33:O33"/>
     <mergeCell ref="L22:O22"/>
@@ -5807,37 +5942,6 @@
     <mergeCell ref="H6:J6"/>
     <mergeCell ref="D46:I46"/>
     <mergeCell ref="D24:H24"/>
-    <mergeCell ref="D40:I40"/>
-    <mergeCell ref="D41:I41"/>
-    <mergeCell ref="O100:P100"/>
-    <mergeCell ref="N53:O53"/>
-    <mergeCell ref="L26:O26"/>
-    <mergeCell ref="L24:P24"/>
-    <mergeCell ref="D32:I32"/>
-    <mergeCell ref="E70:P70"/>
-    <mergeCell ref="N52:O52"/>
-    <mergeCell ref="D62:F62"/>
-    <mergeCell ref="G62:I62"/>
-    <mergeCell ref="J62:L62"/>
-    <mergeCell ref="M62:P62"/>
-    <mergeCell ref="D63:F63"/>
-    <mergeCell ref="G63:I63"/>
-    <mergeCell ref="J63:L63"/>
-    <mergeCell ref="E86:M87"/>
-    <mergeCell ref="D86:D87"/>
-    <mergeCell ref="E88:M89"/>
-    <mergeCell ref="N56:O56"/>
-    <mergeCell ref="E55:J55"/>
-    <mergeCell ref="E52:J52"/>
-    <mergeCell ref="E71:P71"/>
-    <mergeCell ref="O92:P92"/>
-    <mergeCell ref="O87:P90"/>
-    <mergeCell ref="O86:P86"/>
-    <mergeCell ref="O93:P98"/>
-    <mergeCell ref="E90:M91"/>
-    <mergeCell ref="E92:M93"/>
-    <mergeCell ref="E94:M95"/>
-    <mergeCell ref="E96:M97"/>
     <mergeCell ref="H17:I17"/>
     <mergeCell ref="D33:I33"/>
     <mergeCell ref="D42:I42"/>
@@ -5857,12 +5961,12 @@
     <mergeCell ref="L35:P35"/>
     <mergeCell ref="L20:O20"/>
     <mergeCell ref="D61:F61"/>
-    <mergeCell ref="G61:I61"/>
-    <mergeCell ref="J61:L61"/>
-    <mergeCell ref="M61:P61"/>
-    <mergeCell ref="N58:O58"/>
-    <mergeCell ref="N49:O49"/>
-    <mergeCell ref="H127:J127"/>
+    <mergeCell ref="N53:O53"/>
+    <mergeCell ref="L26:O26"/>
+    <mergeCell ref="L24:P24"/>
+    <mergeCell ref="D32:I32"/>
+    <mergeCell ref="E70:P70"/>
+    <mergeCell ref="H133:J133"/>
     <mergeCell ref="D31:I31"/>
     <mergeCell ref="L46:P46"/>
     <mergeCell ref="D45:I45"/>
@@ -5873,31 +5977,27 @@
     <mergeCell ref="L40:O40"/>
     <mergeCell ref="N50:O50"/>
     <mergeCell ref="I25:J25"/>
-    <mergeCell ref="H120:J120"/>
+    <mergeCell ref="H126:J126"/>
     <mergeCell ref="N51:O51"/>
-    <mergeCell ref="D118:P118"/>
+    <mergeCell ref="D124:P124"/>
     <mergeCell ref="E79:P79"/>
     <mergeCell ref="L27:O27"/>
     <mergeCell ref="D43:I43"/>
     <mergeCell ref="L36:O36"/>
     <mergeCell ref="D26:J26"/>
-    <mergeCell ref="L127:M127"/>
-    <mergeCell ref="D127:F127"/>
-    <mergeCell ref="O127:P127"/>
+    <mergeCell ref="L133:M133"/>
+    <mergeCell ref="D133:F133"/>
+    <mergeCell ref="O133:P133"/>
     <mergeCell ref="M63:P63"/>
     <mergeCell ref="D64:F64"/>
-    <mergeCell ref="G64:I64"/>
-    <mergeCell ref="J64:L64"/>
-    <mergeCell ref="M64:P64"/>
-    <mergeCell ref="E49:J49"/>
+    <mergeCell ref="L132:M132"/>
+    <mergeCell ref="O126:P126"/>
+    <mergeCell ref="N55:O55"/>
     <mergeCell ref="L126:M126"/>
-    <mergeCell ref="O120:P120"/>
-    <mergeCell ref="N55:O55"/>
-    <mergeCell ref="L120:M120"/>
     <mergeCell ref="E80:P80"/>
     <mergeCell ref="N54:O54"/>
-    <mergeCell ref="H126:J126"/>
-    <mergeCell ref="O126:P126"/>
+    <mergeCell ref="H132:J132"/>
+    <mergeCell ref="O132:P132"/>
     <mergeCell ref="E81:P81"/>
     <mergeCell ref="E75:P75"/>
     <mergeCell ref="N57:O57"/>
@@ -5911,23 +6011,62 @@
     <mergeCell ref="G65:I65"/>
     <mergeCell ref="D65:F65"/>
     <mergeCell ref="E83:P83"/>
-    <mergeCell ref="D117:P117"/>
-    <mergeCell ref="E108:P108"/>
-    <mergeCell ref="E109:P109"/>
+    <mergeCell ref="D123:P123"/>
+    <mergeCell ref="E90:M91"/>
+    <mergeCell ref="E94:M95"/>
+    <mergeCell ref="E121:P121"/>
+    <mergeCell ref="E122:P122"/>
+    <mergeCell ref="E116:P116"/>
+    <mergeCell ref="E117:P117"/>
+    <mergeCell ref="E118:P118"/>
+    <mergeCell ref="E119:P119"/>
+    <mergeCell ref="E120:P120"/>
+    <mergeCell ref="M64:P64"/>
+    <mergeCell ref="E49:J49"/>
+    <mergeCell ref="E96:M97"/>
+    <mergeCell ref="O99:P99"/>
+    <mergeCell ref="N52:O52"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="G62:I62"/>
+    <mergeCell ref="J62:L62"/>
+    <mergeCell ref="M62:P62"/>
+    <mergeCell ref="D63:F63"/>
+    <mergeCell ref="G63:I63"/>
+    <mergeCell ref="J63:L63"/>
+    <mergeCell ref="E86:M87"/>
+    <mergeCell ref="D86:D87"/>
+    <mergeCell ref="E88:M89"/>
+    <mergeCell ref="N56:O56"/>
+    <mergeCell ref="E55:J55"/>
+    <mergeCell ref="O112:P112"/>
+    <mergeCell ref="D108:D109"/>
+    <mergeCell ref="E108:M109"/>
+    <mergeCell ref="D110:D111"/>
+    <mergeCell ref="E110:M111"/>
+    <mergeCell ref="E98:M99"/>
+    <mergeCell ref="O106:P111"/>
+    <mergeCell ref="E114:P114"/>
     <mergeCell ref="E115:P115"/>
-    <mergeCell ref="E116:P116"/>
-    <mergeCell ref="E110:P110"/>
-    <mergeCell ref="E111:P111"/>
-    <mergeCell ref="E112:P112"/>
-    <mergeCell ref="E113:P113"/>
-    <mergeCell ref="E114:P114"/>
-    <mergeCell ref="O101:P106"/>
+    <mergeCell ref="D104:D105"/>
+    <mergeCell ref="E104:M105"/>
+    <mergeCell ref="D106:D107"/>
+    <mergeCell ref="E106:M107"/>
+    <mergeCell ref="D98:D99"/>
+    <mergeCell ref="O100:P105"/>
     <mergeCell ref="D88:D89"/>
     <mergeCell ref="D90:D91"/>
     <mergeCell ref="D92:D93"/>
     <mergeCell ref="D94:D95"/>
     <mergeCell ref="D96:D97"/>
-    <mergeCell ref="E106:H106"/>
+    <mergeCell ref="O85:P85"/>
+    <mergeCell ref="O86:P89"/>
+    <mergeCell ref="O91:P91"/>
+    <mergeCell ref="O93:P97"/>
+    <mergeCell ref="E92:M93"/>
+    <mergeCell ref="D100:D101"/>
+    <mergeCell ref="E100:M101"/>
+    <mergeCell ref="D102:D103"/>
+    <mergeCell ref="E102:M103"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
